--- a/docs/reports/swift_space_weather_report_latest.xlsx
+++ b/docs/reports/swift_space_weather_report_latest.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="165">
   <si>
     <t>SWIFT Space Weather Excel Report</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Updated UTC</t>
   </si>
   <si>
-    <t>2026-09-16T11:13:17Z</t>
+    <t>2026-09-16T12:46:52Z</t>
   </si>
   <si>
     <t>Main URL root</t>
@@ -276,16 +276,16 @@
     <t>2026-09-13T19:48:00-CME-001</t>
   </si>
   <si>
+    <t>2026-09-13T01:24:00-CME-001</t>
+  </si>
+  <si>
+    <t>2026-09-14T11:08:00-CME-001</t>
+  </si>
+  <si>
+    <t>2026-09-13T21:12:00-CME-001</t>
+  </si>
+  <si>
     <t>LOW</t>
-  </si>
-  <si>
-    <t>2026-09-13T01:24:00-CME-001</t>
-  </si>
-  <si>
-    <t>2026-09-14T11:08:00-CME-001</t>
-  </si>
-  <si>
-    <t>2026-09-13T21:12:00-CME-001</t>
   </si>
   <si>
     <t>2026-09-13T10:23:00-CME-001</t>
@@ -680,10 +680,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>SolarWind_27d!$A$2:$A$26</c:f>
+              <c:f>SolarWind_27d!$A$2:$A$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>46280.45833333334</c:v>
                 </c:pt>
@@ -758,27 +758,30 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>46281.45833333334</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>46281.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>SolarWind_27d!$B$2:$B$26</c:f>
+              <c:f>SolarWind_27d!$B$2:$B$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>546.005</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>575.59</c:v>
+                  <c:v>569.6</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>535.5</c:v>
+                  <c:v>543.22</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>444.08</c:v>
+                  <c:v>451.575</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>444.55</c:v>
@@ -787,61 +790,64 @@
                   <c:v>457.77</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>431.84</c:v>
+                  <c:v>433.77</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>610.755</c:v>
+                  <c:v>683.64</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>622.275</c:v>
+                  <c:v>621.9349999999999</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>514.66</c:v>
+                  <c:v>515.8099999999999</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>463.25</c:v>
+                  <c:v>468.7</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>446.015</c:v>
+                  <c:v>448.01</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>462.475</c:v>
+                  <c:v>464.44</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>516.465</c:v>
+                  <c:v>517.8099999999999</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>524.36</c:v>
+                  <c:v>521.405</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>528.1950000000001</c:v>
+                  <c:v>528.495</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>531.165</c:v>
+                  <c:v>532.595</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>538.105</c:v>
+                  <c:v>538.515</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>536.405</c:v>
+                  <c:v>536.1849999999999</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>531.875</c:v>
+                  <c:v>531.8</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>521.885</c:v>
+                  <c:v>521.465</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>543.5</c:v>
+                  <c:v>543.22</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>541.64</c:v>
+                  <c:v>540.355</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>542.53</c:v>
+                  <c:v>542.835</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>536.175</c:v>
+                  <c:v>537.1</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>545.6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -965,10 +971,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>SolarWind_27d!$A$2:$A$26</c:f>
+              <c:f>SolarWind_27d!$A$2:$A$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>46280.45833333334</c:v>
                 </c:pt>
@@ -1043,90 +1049,96 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>46281.45833333334</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>46281.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>SolarWind_27d!$D$2:$D$26</c:f>
+              <c:f>SolarWind_27d!$D$2:$D$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>8.85</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>8.725</c:v>
+                  <c:v>8.785</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9.210000000000001</c:v>
+                  <c:v>9.365</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>9.640000000000001</c:v>
+                  <c:v>9.775</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>8.175000000000001</c:v>
+                  <c:v>7.995</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>10.29</c:v>
+                  <c:v>10.23</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>9.23</c:v>
+                  <c:v>9.119999999999999</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-4.87</c:v>
+                  <c:v>-5.845</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-9.385</c:v>
+                  <c:v>-9.345000000000001</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-9.23</c:v>
+                  <c:v>-9.16</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.14</c:v>
+                  <c:v>0.44</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-2.655</c:v>
+                  <c:v>-2.27</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-4.83</c:v>
+                  <c:v>-5.155</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.18</c:v>
+                  <c:v>1.795</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>5.7</c:v>
+                  <c:v>5.68</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>3.68</c:v>
+                  <c:v>3.7</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.435</c:v>
+                  <c:v>0.425</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-0.4</c:v>
+                  <c:v>-0.305</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.66</c:v>
+                  <c:v>1.51</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>4.505</c:v>
+                  <c:v>4.58</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3.465</c:v>
+                  <c:v>3.515</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>4.49</c:v>
+                  <c:v>4.32</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>2.805</c:v>
+                  <c:v>2.55</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>-2.31</c:v>
+                  <c:v>-2.345</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>-2.74</c:v>
+                  <c:v>-2.36</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.35</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1143,10 +1155,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>SolarWind_27d!$A$2:$A$26</c:f>
+              <c:f>SolarWind_27d!$A$2:$A$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>46280.45833333334</c:v>
                 </c:pt>
@@ -1221,90 +1233,96 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>46281.45833333334</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>46281.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>SolarWind_27d!$E$2:$E$26</c:f>
+              <c:f>SolarWind_27d!$E$2:$E$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>12.92</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>12.63</c:v>
+                  <c:v>12.62</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>13.355</c:v>
+                  <c:v>13.345</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>15.035</c:v>
+                  <c:v>15.04</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>14.705</c:v>
+                  <c:v>14.685</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>14.955</c:v>
+                  <c:v>14.97</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>16.12</c:v>
+                  <c:v>16.11</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>12.895</c:v>
+                  <c:v>12.62</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>12.23</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>13.56</c:v>
+                  <c:v>13.57</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>12.27</c:v>
+                  <c:v>12.37</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>10.485</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>11.055</c:v>
+                  <c:v>11.24</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>12.76</c:v>
+                  <c:v>12.775</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>10.93</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>10.25</c:v>
+                  <c:v>10.29</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>6.97</c:v>
+                  <c:v>6.76</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>7.035</c:v>
+                  <c:v>7.045</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>6.72</c:v>
+                  <c:v>6.68</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>6.34</c:v>
+                  <c:v>6.395</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>5.76</c:v>
+                  <c:v>5.77</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>4.9</c:v>
+                  <c:v>4.85</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>4.56</c:v>
+                  <c:v>4.57</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>4.625</c:v>
+                  <c:v>4.805</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>4.19</c:v>
+                  <c:v>4.31</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>4.22</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1433,232 +1451,232 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="76"/>
                 <c:pt idx="0">
-                  <c:v>46281.33333333334</c:v>
+                  <c:v>46281.375</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>46281.375</c:v>
+                  <c:v>46281.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46281.41666666666</c:v>
+                  <c:v>46281.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46281.45833333334</c:v>
+                  <c:v>46281.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46281.5</c:v>
+                  <c:v>46281.54166666666</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46281.54166666666</c:v>
+                  <c:v>46281.58333333334</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46281.58333333334</c:v>
+                  <c:v>46281.625</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>46281.625</c:v>
+                  <c:v>46281.66666666666</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>46281.66666666666</c:v>
+                  <c:v>46281.70833333334</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>46281.70833333334</c:v>
+                  <c:v>46281.75</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>46281.75</c:v>
+                  <c:v>46281.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>46281.79166666666</c:v>
+                  <c:v>46281.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>46281.83333333334</c:v>
+                  <c:v>46281.875</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>46281.875</c:v>
+                  <c:v>46281.91666666666</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>46281.91666666666</c:v>
+                  <c:v>46281.95833333334</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46281.95833333334</c:v>
+                  <c:v>46282</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>46282</c:v>
+                  <c:v>46282.04166666666</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>46282.04166666666</c:v>
+                  <c:v>46282.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>46282.08333333334</c:v>
+                  <c:v>46282.125</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>46282.125</c:v>
+                  <c:v>46282.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>46282.16666666666</c:v>
+                  <c:v>46282.20833333334</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>46282.20833333334</c:v>
+                  <c:v>46282.25</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>46282.25</c:v>
+                  <c:v>46282.29166666666</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>46282.29166666666</c:v>
+                  <c:v>46282.33333333334</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>46282.33333333334</c:v>
+                  <c:v>46282.375</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>46282.375</c:v>
+                  <c:v>46282.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>46282.41666666666</c:v>
+                  <c:v>46282.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>46282.45833333334</c:v>
+                  <c:v>46282.5</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>46282.5</c:v>
+                  <c:v>46282.54166666666</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>46282.54166666666</c:v>
+                  <c:v>46282.58333333334</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>46282.58333333334</c:v>
+                  <c:v>46282.625</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>46282.625</c:v>
+                  <c:v>46282.66666666666</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>46282.66666666666</c:v>
+                  <c:v>46282.70833333334</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>46282.70833333334</c:v>
+                  <c:v>46282.75</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>46282.75</c:v>
+                  <c:v>46282.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>46282.79166666666</c:v>
+                  <c:v>46282.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>46282.83333333334</c:v>
+                  <c:v>46282.875</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>46282.875</c:v>
+                  <c:v>46282.91666666666</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>46282.91666666666</c:v>
+                  <c:v>46282.95833333334</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>46282.95833333334</c:v>
+                  <c:v>46283</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>46283</c:v>
+                  <c:v>46283.04166666666</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>46283.04166666666</c:v>
+                  <c:v>46283.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>46283.08333333334</c:v>
+                  <c:v>46283.125</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>46283.125</c:v>
+                  <c:v>46283.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>46283.16666666666</c:v>
+                  <c:v>46283.20833333334</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>46283.20833333334</c:v>
+                  <c:v>46283.25</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>46283.25</c:v>
+                  <c:v>46283.29166666666</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>46283.29166666666</c:v>
+                  <c:v>46283.33333333334</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>46283.33333333334</c:v>
+                  <c:v>46283.375</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>46283.375</c:v>
+                  <c:v>46283.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>46283.41666666666</c:v>
+                  <c:v>46283.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>46283.45833333334</c:v>
+                  <c:v>46283.5</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>46283.5</c:v>
+                  <c:v>46283.54166666666</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>46283.54166666666</c:v>
+                  <c:v>46283.58333333334</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>46283.58333333334</c:v>
+                  <c:v>46283.625</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>46283.625</c:v>
+                  <c:v>46283.66666666666</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>46283.66666666666</c:v>
+                  <c:v>46283.70833333334</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>46283.70833333334</c:v>
+                  <c:v>46283.75</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>46283.75</c:v>
+                  <c:v>46283.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>46283.79166666666</c:v>
+                  <c:v>46283.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>46283.83333333334</c:v>
+                  <c:v>46283.875</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>46283.875</c:v>
+                  <c:v>46283.91666666666</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>46283.91666666666</c:v>
+                  <c:v>46283.95833333334</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>46283.95833333334</c:v>
+                  <c:v>46284</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>46284</c:v>
+                  <c:v>46284.04166666666</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>46284.04166666666</c:v>
+                  <c:v>46284.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>46284.08333333334</c:v>
+                  <c:v>46284.125</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>46284.125</c:v>
+                  <c:v>46284.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>46284.16666666666</c:v>
+                  <c:v>46284.20833333334</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>46284.20833333334</c:v>
+                  <c:v>46284.25</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>46284.25</c:v>
+                  <c:v>46284.29166666666</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>46284.29166666666</c:v>
+                  <c:v>46284.33333333334</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>46284.33333333334</c:v>
+                  <c:v>46284.375</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>46284.375</c:v>
+                  <c:v>46284.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>46284.41666666666</c:v>
+                  <c:v>46284.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>46284.45833333334</c:v>
+                  <c:v>46284.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1670,232 +1688,232 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="76"/>
                 <c:pt idx="0">
-                  <c:v>613.53</c:v>
+                  <c:v>591.4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>611.4</c:v>
+                  <c:v>589.14</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>608.28</c:v>
+                  <c:v>582.91</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>601.53</c:v>
+                  <c:v>579.8</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>599.8</c:v>
+                  <c:v>578</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>598.49</c:v>
+                  <c:v>578.09</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>599.61</c:v>
+                  <c:v>579.97</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>602.78</c:v>
+                  <c:v>585.45</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>609.52</c:v>
+                  <c:v>594.9299999999999</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>619.13</c:v>
+                  <c:v>611.08</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>633.45</c:v>
+                  <c:v>628.35</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>651.73</c:v>
+                  <c:v>648.21</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>672.22</c:v>
+                  <c:v>668.34</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>692.64</c:v>
+                  <c:v>686.26</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>710.55</c:v>
+                  <c:v>697.7</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>721.74</c:v>
+                  <c:v>704.65</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>727.96</c:v>
+                  <c:v>708.49</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>730.53</c:v>
+                  <c:v>710.08</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>730.42</c:v>
+                  <c:v>711.66</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>729.8200000000001</c:v>
+                  <c:v>708.41</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>724.08</c:v>
+                  <c:v>708.9</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>721.74</c:v>
+                  <c:v>711.5599999999999</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>721.47</c:v>
+                  <c:v>714.21</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>721.5599999999999</c:v>
+                  <c:v>712.0599999999999</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>716.9</c:v>
+                  <c:v>711</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>713.85</c:v>
+                  <c:v>708.3200000000001</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>709.95</c:v>
+                  <c:v>702.95</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>704.22</c:v>
+                  <c:v>694.9400000000001</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>696.59</c:v>
+                  <c:v>683.04</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>685.92</c:v>
+                  <c:v>669.16</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>673.76</c:v>
+                  <c:v>654.47</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>661.03</c:v>
+                  <c:v>639.6900000000001</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>648.27</c:v>
+                  <c:v>625.2</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>635.83</c:v>
+                  <c:v>611.24</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>623.86</c:v>
+                  <c:v>597.8099999999999</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>612.34</c:v>
+                  <c:v>583.59</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>600.47</c:v>
+                  <c:v>570.67</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>589.5700000000001</c:v>
+                  <c:v>558.8200000000001</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>579.5</c:v>
+                  <c:v>547.87</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>570.14</c:v>
+                  <c:v>537.72</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>561.4400000000001</c:v>
+                  <c:v>527.5599999999999</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>553.0700000000001</c:v>
+                  <c:v>519.38</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>546.34</c:v>
+                  <c:v>512.66</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>540.85</c:v>
+                  <c:v>507.17</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>536.41</c:v>
+                  <c:v>502.84</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>533</c:v>
+                  <c:v>499.79</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>530.77</c:v>
+                  <c:v>497.46</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>529.17</c:v>
+                  <c:v>496.66</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>529.01</c:v>
+                  <c:v>498.16</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>531.0599999999999</c:v>
+                  <c:v>502.68</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>536.02</c:v>
+                  <c:v>505.38</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>539.1799999999999</c:v>
+                  <c:v>514.08</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>548.16</c:v>
+                  <c:v>525.1900000000001</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>559.46</c:v>
+                  <c:v>540.0700000000001</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>574.41</c:v>
+                  <c:v>556.13</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>590.5</c:v>
+                  <c:v>570.71</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>605.11</c:v>
+                  <c:v>581.3200000000001</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>615.8099999999999</c:v>
+                  <c:v>583.8099999999999</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>618.5599999999999</c:v>
+                  <c:v>578.8</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>614.35</c:v>
+                  <c:v>571.59</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>607.8</c:v>
+                  <c:v>563.28</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>600.04</c:v>
+                  <c:v>552.27</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>589.96</c:v>
+                  <c:v>542.21</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>580.58</c:v>
+                  <c:v>532.96</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>571.84</c:v>
+                  <c:v>522.17</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>561.89</c:v>
+                  <c:v>513.05</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>553.33</c:v>
+                  <c:v>505.12</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>545.8</c:v>
+                  <c:v>498.07</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>539.04</c:v>
+                  <c:v>491.7</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>532.9</c:v>
+                  <c:v>485.89</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>527.26</c:v>
+                  <c:v>480.54</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>522.0599999999999</c:v>
+                  <c:v>475.58</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>517.23</c:v>
+                  <c:v>470.99</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>512.74</c:v>
+                  <c:v>466.71</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>508.56</c:v>
+                  <c:v>462.71</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>504.66</c:v>
+                  <c:v>458.99</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1917,232 +1935,232 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="76"/>
                 <c:pt idx="0">
-                  <c:v>46281.33333333334</c:v>
+                  <c:v>46281.375</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>46281.375</c:v>
+                  <c:v>46281.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46281.41666666666</c:v>
+                  <c:v>46281.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46281.45833333334</c:v>
+                  <c:v>46281.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46281.5</c:v>
+                  <c:v>46281.54166666666</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46281.54166666666</c:v>
+                  <c:v>46281.58333333334</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46281.58333333334</c:v>
+                  <c:v>46281.625</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>46281.625</c:v>
+                  <c:v>46281.66666666666</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>46281.66666666666</c:v>
+                  <c:v>46281.70833333334</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>46281.70833333334</c:v>
+                  <c:v>46281.75</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>46281.75</c:v>
+                  <c:v>46281.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>46281.79166666666</c:v>
+                  <c:v>46281.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>46281.83333333334</c:v>
+                  <c:v>46281.875</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>46281.875</c:v>
+                  <c:v>46281.91666666666</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>46281.91666666666</c:v>
+                  <c:v>46281.95833333334</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46281.95833333334</c:v>
+                  <c:v>46282</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>46282</c:v>
+                  <c:v>46282.04166666666</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>46282.04166666666</c:v>
+                  <c:v>46282.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>46282.08333333334</c:v>
+                  <c:v>46282.125</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>46282.125</c:v>
+                  <c:v>46282.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>46282.16666666666</c:v>
+                  <c:v>46282.20833333334</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>46282.20833333334</c:v>
+                  <c:v>46282.25</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>46282.25</c:v>
+                  <c:v>46282.29166666666</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>46282.29166666666</c:v>
+                  <c:v>46282.33333333334</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>46282.33333333334</c:v>
+                  <c:v>46282.375</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>46282.375</c:v>
+                  <c:v>46282.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>46282.41666666666</c:v>
+                  <c:v>46282.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>46282.45833333334</c:v>
+                  <c:v>46282.5</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>46282.5</c:v>
+                  <c:v>46282.54166666666</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>46282.54166666666</c:v>
+                  <c:v>46282.58333333334</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>46282.58333333334</c:v>
+                  <c:v>46282.625</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>46282.625</c:v>
+                  <c:v>46282.66666666666</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>46282.66666666666</c:v>
+                  <c:v>46282.70833333334</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>46282.70833333334</c:v>
+                  <c:v>46282.75</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>46282.75</c:v>
+                  <c:v>46282.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>46282.79166666666</c:v>
+                  <c:v>46282.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>46282.83333333334</c:v>
+                  <c:v>46282.875</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>46282.875</c:v>
+                  <c:v>46282.91666666666</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>46282.91666666666</c:v>
+                  <c:v>46282.95833333334</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>46282.95833333334</c:v>
+                  <c:v>46283</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>46283</c:v>
+                  <c:v>46283.04166666666</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>46283.04166666666</c:v>
+                  <c:v>46283.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>46283.08333333334</c:v>
+                  <c:v>46283.125</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>46283.125</c:v>
+                  <c:v>46283.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>46283.16666666666</c:v>
+                  <c:v>46283.20833333334</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>46283.20833333334</c:v>
+                  <c:v>46283.25</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>46283.25</c:v>
+                  <c:v>46283.29166666666</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>46283.29166666666</c:v>
+                  <c:v>46283.33333333334</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>46283.33333333334</c:v>
+                  <c:v>46283.375</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>46283.375</c:v>
+                  <c:v>46283.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>46283.41666666666</c:v>
+                  <c:v>46283.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>46283.45833333334</c:v>
+                  <c:v>46283.5</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>46283.5</c:v>
+                  <c:v>46283.54166666666</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>46283.54166666666</c:v>
+                  <c:v>46283.58333333334</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>46283.58333333334</c:v>
+                  <c:v>46283.625</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>46283.625</c:v>
+                  <c:v>46283.66666666666</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>46283.66666666666</c:v>
+                  <c:v>46283.70833333334</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>46283.70833333334</c:v>
+                  <c:v>46283.75</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>46283.75</c:v>
+                  <c:v>46283.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>46283.79166666666</c:v>
+                  <c:v>46283.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>46283.83333333334</c:v>
+                  <c:v>46283.875</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>46283.875</c:v>
+                  <c:v>46283.91666666666</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>46283.91666666666</c:v>
+                  <c:v>46283.95833333334</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>46283.95833333334</c:v>
+                  <c:v>46284</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>46284</c:v>
+                  <c:v>46284.04166666666</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>46284.04166666666</c:v>
+                  <c:v>46284.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>46284.08333333334</c:v>
+                  <c:v>46284.125</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>46284.125</c:v>
+                  <c:v>46284.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>46284.16666666666</c:v>
+                  <c:v>46284.20833333334</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>46284.20833333334</c:v>
+                  <c:v>46284.25</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>46284.25</c:v>
+                  <c:v>46284.29166666666</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>46284.29166666666</c:v>
+                  <c:v>46284.33333333334</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>46284.33333333334</c:v>
+                  <c:v>46284.375</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>46284.375</c:v>
+                  <c:v>46284.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>46284.41666666666</c:v>
+                  <c:v>46284.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>46284.45833333334</c:v>
+                  <c:v>46284.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2154,232 +2172,232 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="76"/>
                 <c:pt idx="0">
-                  <c:v>442.69</c:v>
+                  <c:v>400.06</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>444.41</c:v>
+                  <c:v>400.2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>444.65</c:v>
+                  <c:v>396.52</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>440.91</c:v>
+                  <c:v>396.07</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>440.13</c:v>
+                  <c:v>395.82</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>440.39</c:v>
+                  <c:v>396.74</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>441.88</c:v>
+                  <c:v>396.99</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>442.73</c:v>
+                  <c:v>397.12</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>443.4</c:v>
+                  <c:v>396.85</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>442.57</c:v>
+                  <c:v>398.8</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>442.13</c:v>
+                  <c:v>398.2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>442.16</c:v>
+                  <c:v>398.09</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>442.46</c:v>
+                  <c:v>398.28</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>442.92</c:v>
+                  <c:v>398.64</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>443.46</c:v>
+                  <c:v>399.1</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>444.04</c:v>
+                  <c:v>399.61</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>444.51</c:v>
+                  <c:v>399.81</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>444.56</c:v>
+                  <c:v>399.71</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>444.37</c:v>
+                  <c:v>399.44</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>444.02</c:v>
+                  <c:v>399.06</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>443.57</c:v>
+                  <c:v>398.61</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>443.08</c:v>
+                  <c:v>398.13</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>442.55</c:v>
+                  <c:v>397.95</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>442.33</c:v>
+                  <c:v>397.97</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>442.3</c:v>
+                  <c:v>398.11</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>442.39</c:v>
+                  <c:v>398.33</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>442.56</c:v>
+                  <c:v>398.6</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>442.78</c:v>
+                  <c:v>398.89</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>443.04</c:v>
+                  <c:v>399.06</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>443.16</c:v>
+                  <c:v>399.14</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>443.2</c:v>
+                  <c:v>399.17</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>443.2</c:v>
+                  <c:v>399.18</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>443.17</c:v>
+                  <c:v>399.16</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>443.13</c:v>
+                  <c:v>399.14</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>443.08</c:v>
+                  <c:v>398.99</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>442.91</c:v>
+                  <c:v>398.77</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>442.66</c:v>
+                  <c:v>398.5</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>442.38</c:v>
+                  <c:v>398.21</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>442.06</c:v>
+                  <c:v>397.9</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>441.74</c:v>
+                  <c:v>397.58</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>441.4</c:v>
+                  <c:v>398.17</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>441.96</c:v>
+                  <c:v>399.32</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>443.06</c:v>
+                  <c:v>400.83</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>444.51</c:v>
+                  <c:v>402.55</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>446.17</c:v>
+                  <c:v>404.41</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>447.96</c:v>
+                  <c:v>406.35</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>449.84</c:v>
+                  <c:v>407.46</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>450.91</c:v>
+                  <c:v>408.07</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>451.48</c:v>
+                  <c:v>408.35</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>451.74</c:v>
+                  <c:v>408.44</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>451.81</c:v>
+                  <c:v>408.4</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>451.77</c:v>
+                  <c:v>408.29</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>451.65</c:v>
+                  <c:v>408.14</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>451.49</c:v>
+                  <c:v>407.96</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>451.3</c:v>
+                  <c:v>407.77</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>451.1</c:v>
+                  <c:v>407.57</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>450.89</c:v>
+                  <c:v>407.36</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>450.68</c:v>
+                  <c:v>407.15</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>450.46</c:v>
+                  <c:v>406.94</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>450.24</c:v>
+                  <c:v>406.73</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>450.03</c:v>
+                  <c:v>406.51</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>449.81</c:v>
+                  <c:v>406.3</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>449.59</c:v>
+                  <c:v>406.09</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>449.38</c:v>
+                  <c:v>405.88</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>449.16</c:v>
+                  <c:v>405.74</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>449.02</c:v>
+                  <c:v>405.64</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>448.92</c:v>
+                  <c:v>405.58</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>448.84</c:v>
+                  <c:v>405.53</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>448.79</c:v>
+                  <c:v>405.49</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>448.75</c:v>
+                  <c:v>405.46</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>448.71</c:v>
+                  <c:v>405.44</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>448.68</c:v>
+                  <c:v>405.41</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>448.65</c:v>
+                  <c:v>405.4</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>448.63</c:v>
+                  <c:v>405.38</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>448.61</c:v>
+                  <c:v>405.36</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>448.59</c:v>
+                  <c:v>405.35</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2401,232 +2419,232 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="76"/>
                 <c:pt idx="0">
-                  <c:v>46281.33333333334</c:v>
+                  <c:v>46281.375</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>46281.375</c:v>
+                  <c:v>46281.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46281.41666666666</c:v>
+                  <c:v>46281.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46281.45833333334</c:v>
+                  <c:v>46281.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46281.5</c:v>
+                  <c:v>46281.54166666666</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46281.54166666666</c:v>
+                  <c:v>46281.58333333334</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46281.58333333334</c:v>
+                  <c:v>46281.625</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>46281.625</c:v>
+                  <c:v>46281.66666666666</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>46281.66666666666</c:v>
+                  <c:v>46281.70833333334</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>46281.70833333334</c:v>
+                  <c:v>46281.75</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>46281.75</c:v>
+                  <c:v>46281.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>46281.79166666666</c:v>
+                  <c:v>46281.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>46281.83333333334</c:v>
+                  <c:v>46281.875</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>46281.875</c:v>
+                  <c:v>46281.91666666666</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>46281.91666666666</c:v>
+                  <c:v>46281.95833333334</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46281.95833333334</c:v>
+                  <c:v>46282</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>46282</c:v>
+                  <c:v>46282.04166666666</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>46282.04166666666</c:v>
+                  <c:v>46282.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>46282.08333333334</c:v>
+                  <c:v>46282.125</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>46282.125</c:v>
+                  <c:v>46282.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>46282.16666666666</c:v>
+                  <c:v>46282.20833333334</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>46282.20833333334</c:v>
+                  <c:v>46282.25</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>46282.25</c:v>
+                  <c:v>46282.29166666666</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>46282.29166666666</c:v>
+                  <c:v>46282.33333333334</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>46282.33333333334</c:v>
+                  <c:v>46282.375</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>46282.375</c:v>
+                  <c:v>46282.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>46282.41666666666</c:v>
+                  <c:v>46282.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>46282.45833333334</c:v>
+                  <c:v>46282.5</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>46282.5</c:v>
+                  <c:v>46282.54166666666</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>46282.54166666666</c:v>
+                  <c:v>46282.58333333334</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>46282.58333333334</c:v>
+                  <c:v>46282.625</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>46282.625</c:v>
+                  <c:v>46282.66666666666</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>46282.66666666666</c:v>
+                  <c:v>46282.70833333334</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>46282.70833333334</c:v>
+                  <c:v>46282.75</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>46282.75</c:v>
+                  <c:v>46282.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>46282.79166666666</c:v>
+                  <c:v>46282.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>46282.83333333334</c:v>
+                  <c:v>46282.875</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>46282.875</c:v>
+                  <c:v>46282.91666666666</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>46282.91666666666</c:v>
+                  <c:v>46282.95833333334</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>46282.95833333334</c:v>
+                  <c:v>46283</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>46283</c:v>
+                  <c:v>46283.04166666666</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>46283.04166666666</c:v>
+                  <c:v>46283.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>46283.08333333334</c:v>
+                  <c:v>46283.125</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>46283.125</c:v>
+                  <c:v>46283.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>46283.16666666666</c:v>
+                  <c:v>46283.20833333334</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>46283.20833333334</c:v>
+                  <c:v>46283.25</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>46283.25</c:v>
+                  <c:v>46283.29166666666</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>46283.29166666666</c:v>
+                  <c:v>46283.33333333334</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>46283.33333333334</c:v>
+                  <c:v>46283.375</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>46283.375</c:v>
+                  <c:v>46283.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>46283.41666666666</c:v>
+                  <c:v>46283.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>46283.45833333334</c:v>
+                  <c:v>46283.5</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>46283.5</c:v>
+                  <c:v>46283.54166666666</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>46283.54166666666</c:v>
+                  <c:v>46283.58333333334</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>46283.58333333334</c:v>
+                  <c:v>46283.625</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>46283.625</c:v>
+                  <c:v>46283.66666666666</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>46283.66666666666</c:v>
+                  <c:v>46283.70833333334</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>46283.70833333334</c:v>
+                  <c:v>46283.75</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>46283.75</c:v>
+                  <c:v>46283.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>46283.79166666666</c:v>
+                  <c:v>46283.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>46283.83333333334</c:v>
+                  <c:v>46283.875</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>46283.875</c:v>
+                  <c:v>46283.91666666666</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>46283.91666666666</c:v>
+                  <c:v>46283.95833333334</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>46283.95833333334</c:v>
+                  <c:v>46284</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>46284</c:v>
+                  <c:v>46284.04166666666</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>46284.04166666666</c:v>
+                  <c:v>46284.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>46284.08333333334</c:v>
+                  <c:v>46284.125</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>46284.125</c:v>
+                  <c:v>46284.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>46284.16666666666</c:v>
+                  <c:v>46284.20833333334</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>46284.20833333334</c:v>
+                  <c:v>46284.25</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>46284.25</c:v>
+                  <c:v>46284.29166666666</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>46284.29166666666</c:v>
+                  <c:v>46284.33333333334</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>46284.33333333334</c:v>
+                  <c:v>46284.375</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>46284.375</c:v>
+                  <c:v>46284.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>46284.41666666666</c:v>
+                  <c:v>46284.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>46284.45833333334</c:v>
+                  <c:v>46284.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2638,232 +2656,232 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="76"/>
                 <c:pt idx="0">
-                  <c:v>234.68</c:v>
+                  <c:v>256.41</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>229.38</c:v>
+                  <c:v>253.21</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>224.77</c:v>
+                  <c:v>249.79</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>220.63</c:v>
+                  <c:v>246.21</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>217.22</c:v>
+                  <c:v>240.75</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>213.63</c:v>
+                  <c:v>241.23</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>215.86</c:v>
+                  <c:v>248.78</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>225.03</c:v>
+                  <c:v>264.06</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>241.81</c:v>
+                  <c:v>286.8</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>265.92</c:v>
+                  <c:v>315.54</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>295.86</c:v>
+                  <c:v>347.49</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>328.79</c:v>
+                  <c:v>378.86</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>360.83</c:v>
+                  <c:v>405.5</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>387.75</c:v>
+                  <c:v>423.83</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>405.82</c:v>
+                  <c:v>424.17</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>405.23</c:v>
+                  <c:v>422.88</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>402.23</c:v>
+                  <c:v>421.63</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>398.46</c:v>
+                  <c:v>419.62</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>393.12</c:v>
+                  <c:v>422.48</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>392.02</c:v>
+                  <c:v>408.31</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>373.44</c:v>
+                  <c:v>417.86</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>378.64</c:v>
+                  <c:v>426.91</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>383.72</c:v>
+                  <c:v>430</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>384.26</c:v>
+                  <c:v>416.18</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>366.84</c:v>
+                  <c:v>416.7</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>365.82</c:v>
+                  <c:v>409.07</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>358.2</c:v>
+                  <c:v>395.55</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>345.79</c:v>
+                  <c:v>378.59</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>330.6</c:v>
+                  <c:v>354.17</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>309.28</c:v>
+                  <c:v>331.33</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>289.34</c:v>
+                  <c:v>309.96</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>270.67</c:v>
+                  <c:v>289.97</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>253.22</c:v>
+                  <c:v>271.27</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>236.89</c:v>
+                  <c:v>253.77</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>221.61</c:v>
+                  <c:v>237.41</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>207.32</c:v>
+                  <c:v>217.06</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>190.7</c:v>
+                  <c:v>203.06</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>178.4</c:v>
+                  <c:v>189.97</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>166.9</c:v>
+                  <c:v>177.72</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>156.13</c:v>
+                  <c:v>166.32</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>146.13</c:v>
+                  <c:v>149.91</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>132.62</c:v>
+                  <c:v>140.47</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>124.3</c:v>
+                  <c:v>131.91</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>116.78</c:v>
+                  <c:v>124.42</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>110.28</c:v>
+                  <c:v>118.37</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>105.14</c:v>
+                  <c:v>114.32</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>101.96</c:v>
+                  <c:v>113.08</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>101.53</c:v>
+                  <c:v>115.64</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>104.85</c:v>
+                  <c:v>123.02</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>112.96</c:v>
+                  <c:v>136.01</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>126.65</c:v>
+                  <c:v>135.94</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>127.24</c:v>
+                  <c:v>161.02</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>152.96</c:v>
+                  <c:v>181.5</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>174.02</c:v>
+                  <c:v>209.94</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>203.03</c:v>
+                  <c:v>234.37</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>227.99</c:v>
+                  <c:v>250.96</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>245.06</c:v>
+                  <c:v>256.77</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>251.3</c:v>
+                  <c:v>242.65</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>237.54</c:v>
+                  <c:v>219.82</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>216.49</c:v>
+                  <c:v>205.64</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>202.52</c:v>
+                  <c:v>192.38</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>189.46</c:v>
+                  <c:v>172</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>170.71</c:v>
+                  <c:v>160.91</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>159.7</c:v>
+                  <c:v>150.53</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>149.4</c:v>
+                  <c:v>132.77</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>133.06</c:v>
+                  <c:v>124.21</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>124.48</c:v>
+                  <c:v>116.19</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>116.45</c:v>
+                  <c:v>108.7</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>108.94</c:v>
+                  <c:v>101.69</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>101.92</c:v>
+                  <c:v>95.13</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>95.34</c:v>
+                  <c:v>89</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>89.2</c:v>
+                  <c:v>83.26000000000001</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>83.44</c:v>
+                  <c:v>77.89</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>78.06</c:v>
+                  <c:v>72.86</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>73.03</c:v>
+                  <c:v>68.17</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>68.31999999999999</c:v>
+                  <c:v>63.77</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2987,144 +3005,147 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Kp_Forecast!$A$2:$A$40</c:f>
+              <c:f>Kp_Forecast!$A$2:$A$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="39"/>
+                <c:ptCount val="40"/>
                 <c:pt idx="0">
-                  <c:v>46281.375</c:v>
+                  <c:v>46281.625</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>46281.5</c:v>
+                  <c:v>46281.75</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46281.625</c:v>
+                  <c:v>46281.875</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46281.75</c:v>
+                  <c:v>46282</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46281.875</c:v>
+                  <c:v>46282.125</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46282</c:v>
+                  <c:v>46282.25</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46282.125</c:v>
+                  <c:v>46282.375</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>46282.25</c:v>
+                  <c:v>46282.5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>46282.375</c:v>
+                  <c:v>46282.625</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>46282.5</c:v>
+                  <c:v>46282.75</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>46282.625</c:v>
+                  <c:v>46282.875</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>46282.75</c:v>
+                  <c:v>46283</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>46282.875</c:v>
+                  <c:v>46283.125</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>46283</c:v>
+                  <c:v>46283.25</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>46283.125</c:v>
+                  <c:v>46283.375</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46283.25</c:v>
+                  <c:v>46283.5</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>46283.375</c:v>
+                  <c:v>46283.625</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>46283.5</c:v>
+                  <c:v>46283.75</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>46283.625</c:v>
+                  <c:v>46283.875</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>46283.75</c:v>
+                  <c:v>46284</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>46283.875</c:v>
+                  <c:v>46284.125</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>46284</c:v>
+                  <c:v>46284.25</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>46284.125</c:v>
+                  <c:v>46284.375</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>46284.25</c:v>
+                  <c:v>46284.5</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>46284.375</c:v>
+                  <c:v>46284.625</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>46284.5</c:v>
+                  <c:v>46284.75</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>46284.625</c:v>
+                  <c:v>46284.875</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>46284.75</c:v>
+                  <c:v>46285</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>46284.875</c:v>
+                  <c:v>46285.125</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>46285</c:v>
+                  <c:v>46285.25</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>46285.125</c:v>
+                  <c:v>46285.375</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>46285.25</c:v>
+                  <c:v>46285.5</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>46285.375</c:v>
+                  <c:v>46285.625</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>46285.5</c:v>
+                  <c:v>46285.75</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>46285.625</c:v>
+                  <c:v>46285.875</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>46285.75</c:v>
+                  <c:v>46286</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>46285.875</c:v>
+                  <c:v>46286.125</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>46286</c:v>
+                  <c:v>46286.25</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>46286.125</c:v>
+                  <c:v>46286.375</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>46286.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Kp_Forecast!$B$2:$B$40</c:f>
+              <c:f>Kp_Forecast!$B$2:$B$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="39"/>
+                <c:ptCount val="40"/>
                 <c:pt idx="0">
-                  <c:v>4</c:v>
+                  <c:v>4.33</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4</c:v>
+                  <c:v>4.67</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.67</c:v>
+                  <c:v>5.67</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>5.67</c:v>
@@ -3154,10 +3175,10 @@
                   <c:v>5.67</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>5.67</c:v>
+                  <c:v>4.67</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>5.67</c:v>
+                  <c:v>4.67</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>4.67</c:v>
@@ -3166,16 +3187,16 @@
                   <c:v>4.67</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>4.67</c:v>
+                  <c:v>5.67</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>4.67</c:v>
+                  <c:v>5.67</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>4.67</c:v>
+                  <c:v>5.67</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>4.67</c:v>
+                  <c:v>5.67</c:v>
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>4.67</c:v>
@@ -3205,34 +3226,37 @@
                   <c:v>4.67</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>4.67</c:v>
+                  <c:v>4.33</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>4.67</c:v>
+                  <c:v>4.33</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>4.67</c:v>
+                  <c:v>4.33</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>4.67</c:v>
+                  <c:v>4.33</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>4.67</c:v>
+                  <c:v>4.33</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>4.67</c:v>
+                  <c:v>4.33</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>4.67</c:v>
+                  <c:v>4.33</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>4.67</c:v>
+                  <c:v>4.33</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>4.67</c:v>
+                  <c:v>4.33</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>4.67</c:v>
+                  <c:v>4.33</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>4.33</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3361,79 +3385,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>46281.45833333334</c:v>
+                  <c:v>46281.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>46281.58333333334</c:v>
+                  <c:v>46281.625</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46281.70833333334</c:v>
+                  <c:v>46281.75</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46281.83333333334</c:v>
+                  <c:v>46281.875</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46281.95833333334</c:v>
+                  <c:v>46282</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46282.08333333334</c:v>
+                  <c:v>46282.125</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46282.20833333334</c:v>
+                  <c:v>46282.25</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>46282.33333333334</c:v>
+                  <c:v>46282.375</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>46282.45833333334</c:v>
+                  <c:v>46282.5</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>46282.58333333334</c:v>
+                  <c:v>46282.625</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>46282.70833333334</c:v>
+                  <c:v>46282.75</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>46282.83333333334</c:v>
+                  <c:v>46282.875</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>46282.95833333334</c:v>
+                  <c:v>46283</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>46283.08333333334</c:v>
+                  <c:v>46283.125</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>46283.20833333334</c:v>
+                  <c:v>46283.25</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46283.33333333334</c:v>
+                  <c:v>46283.375</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>46283.45833333334</c:v>
+                  <c:v>46283.5</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>46283.58333333334</c:v>
+                  <c:v>46283.625</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>46283.70833333334</c:v>
+                  <c:v>46283.75</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>46283.83333333334</c:v>
+                  <c:v>46283.875</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>46283.95833333334</c:v>
+                  <c:v>46284</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>46284.08333333334</c:v>
+                  <c:v>46284.125</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>46284.20833333334</c:v>
+                  <c:v>46284.25</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>46284.33333333334</c:v>
+                  <c:v>46284.375</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>46284.45833333334</c:v>
+                  <c:v>46284.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3445,79 +3469,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>2.28</c:v>
+                  <c:v>1.94</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.09</c:v>
+                  <c:v>1.79</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.93</c:v>
+                  <c:v>1.64</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.77</c:v>
+                  <c:v>1.51</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.63</c:v>
+                  <c:v>1.39</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.5</c:v>
+                  <c:v>1.28</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.38</c:v>
+                  <c:v>1.18</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.27</c:v>
+                  <c:v>1.08</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.17</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.08</c:v>
+                  <c:v>0.92</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.99</c:v>
+                  <c:v>0.84</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.91</c:v>
+                  <c:v>0.78</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.84</c:v>
+                  <c:v>0.71</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.77</c:v>
+                  <c:v>0.66</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.71</c:v>
+                  <c:v>0.6</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.65</c:v>
+                  <c:v>0.5600000000000001</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.6</c:v>
+                  <c:v>0.51</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.55</c:v>
+                  <c:v>0.47</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.51</c:v>
+                  <c:v>0.43</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.47</c:v>
+                  <c:v>0.4</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.46</c:v>
+                  <c:v>0.39</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.46</c:v>
+                  <c:v>0.39</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.46</c:v>
+                  <c:v>0.39</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.46</c:v>
+                  <c:v>0.39</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.46</c:v>
+                  <c:v>0.39</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3539,79 +3563,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>46281.45833333334</c:v>
+                  <c:v>46281.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>46281.58333333334</c:v>
+                  <c:v>46281.625</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46281.70833333334</c:v>
+                  <c:v>46281.75</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46281.83333333334</c:v>
+                  <c:v>46281.875</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46281.95833333334</c:v>
+                  <c:v>46282</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46282.08333333334</c:v>
+                  <c:v>46282.125</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46282.20833333334</c:v>
+                  <c:v>46282.25</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>46282.33333333334</c:v>
+                  <c:v>46282.375</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>46282.45833333334</c:v>
+                  <c:v>46282.5</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>46282.58333333334</c:v>
+                  <c:v>46282.625</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>46282.70833333334</c:v>
+                  <c:v>46282.75</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>46282.83333333334</c:v>
+                  <c:v>46282.875</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>46282.95833333334</c:v>
+                  <c:v>46283</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>46283.08333333334</c:v>
+                  <c:v>46283.125</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>46283.20833333334</c:v>
+                  <c:v>46283.25</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46283.33333333334</c:v>
+                  <c:v>46283.375</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>46283.45833333334</c:v>
+                  <c:v>46283.5</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>46283.58333333334</c:v>
+                  <c:v>46283.625</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>46283.70833333334</c:v>
+                  <c:v>46283.75</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>46283.83333333334</c:v>
+                  <c:v>46283.875</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>46283.95833333334</c:v>
+                  <c:v>46284</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>46284.08333333334</c:v>
+                  <c:v>46284.125</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>46284.20833333334</c:v>
+                  <c:v>46284.25</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>46284.33333333334</c:v>
+                  <c:v>46284.375</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>46284.45833333334</c:v>
+                  <c:v>46284.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3623,79 +3647,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>-12.52</c:v>
+                  <c:v>-13.07</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-12.41</c:v>
+                  <c:v>-12.36</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-10.76</c:v>
+                  <c:v>-11.33</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-12.17</c:v>
+                  <c:v>-12.86</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-12.71</c:v>
+                  <c:v>-12.82</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-11.92</c:v>
+                  <c:v>-12.87</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-13.42</c:v>
+                  <c:v>-13.83</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-13.4</c:v>
+                  <c:v>-13.9</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-13.63</c:v>
+                  <c:v>-14.01</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-13.43</c:v>
+                  <c:v>-13.23</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-11.7</c:v>
+                  <c:v>-11.14</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-9.26</c:v>
+                  <c:v>-8.68</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-7.04</c:v>
+                  <c:v>-6.67</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-5.54</c:v>
+                  <c:v>-5.63</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-6.35</c:v>
+                  <c:v>-7.14</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-8.35</c:v>
+                  <c:v>-9.33</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-10.79</c:v>
+                  <c:v>-11.78</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-12.94</c:v>
+                  <c:v>-13.61</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-13.89</c:v>
+                  <c:v>-14.01</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-13.19</c:v>
+                  <c:v>-12.81</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-11.2</c:v>
+                  <c:v>-10.58</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>-8.789999999999999</c:v>
+                  <c:v>-8.23</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>-6.78</c:v>
+                  <c:v>-6.45</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>-5.49</c:v>
+                  <c:v>-5.4</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>-5.04</c:v>
+                  <c:v>-4.97</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3717,79 +3741,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>46281.45833333334</c:v>
+                  <c:v>46281.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>46281.58333333334</c:v>
+                  <c:v>46281.625</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46281.70833333334</c:v>
+                  <c:v>46281.75</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46281.83333333334</c:v>
+                  <c:v>46281.875</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46281.95833333334</c:v>
+                  <c:v>46282</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46282.08333333334</c:v>
+                  <c:v>46282.125</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46282.20833333334</c:v>
+                  <c:v>46282.25</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>46282.33333333334</c:v>
+                  <c:v>46282.375</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>46282.45833333334</c:v>
+                  <c:v>46282.5</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>46282.58333333334</c:v>
+                  <c:v>46282.625</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>46282.70833333334</c:v>
+                  <c:v>46282.75</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>46282.83333333334</c:v>
+                  <c:v>46282.875</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>46282.95833333334</c:v>
+                  <c:v>46283</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>46283.08333333334</c:v>
+                  <c:v>46283.125</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>46283.20833333334</c:v>
+                  <c:v>46283.25</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46283.33333333334</c:v>
+                  <c:v>46283.375</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>46283.45833333334</c:v>
+                  <c:v>46283.5</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>46283.58333333334</c:v>
+                  <c:v>46283.625</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>46283.70833333334</c:v>
+                  <c:v>46283.75</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>46283.83333333334</c:v>
+                  <c:v>46283.875</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>46283.95833333334</c:v>
+                  <c:v>46284</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>46284.08333333334</c:v>
+                  <c:v>46284.125</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>46284.20833333334</c:v>
+                  <c:v>46284.25</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>46284.33333333334</c:v>
+                  <c:v>46284.375</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>46284.45833333334</c:v>
+                  <c:v>46284.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3801,79 +3825,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>15.48</c:v>
+                  <c:v>15.12</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>15.14</c:v>
+                  <c:v>14.25</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>13.28</c:v>
+                  <c:v>13.06</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>14.5</c:v>
+                  <c:v>14.45</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>14.85</c:v>
+                  <c:v>14.28</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>13.9</c:v>
+                  <c:v>14.22</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>15.25</c:v>
+                  <c:v>15.07</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>15.1</c:v>
+                  <c:v>15.04</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>15.2</c:v>
+                  <c:v>15.06</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>14.88</c:v>
+                  <c:v>14.19</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>13.04</c:v>
+                  <c:v>12.03</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>10.5</c:v>
+                  <c:v>9.5</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>8.19</c:v>
+                  <c:v>7.41</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>6.6</c:v>
+                  <c:v>6.32</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>7.34</c:v>
+                  <c:v>7.77</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>9.27</c:v>
+                  <c:v>9.91</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>11.65</c:v>
+                  <c:v>12.31</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>13.74</c:v>
+                  <c:v>14.09</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>14.63</c:v>
+                  <c:v>14.46</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>13.88</c:v>
+                  <c:v>13.22</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>11.87</c:v>
+                  <c:v>10.98</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>9.470000000000001</c:v>
+                  <c:v>8.630000000000001</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>7.46</c:v>
+                  <c:v>6.85</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>6.17</c:v>
+                  <c:v>5.8</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>5.51</c:v>
+                  <c:v>5.3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4002,79 +4026,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>46281.45833333334</c:v>
+                  <c:v>46281.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>46281.58333333334</c:v>
+                  <c:v>46281.625</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46281.70833333334</c:v>
+                  <c:v>46281.75</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46281.83333333334</c:v>
+                  <c:v>46281.875</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46281.95833333334</c:v>
+                  <c:v>46282</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46282.08333333334</c:v>
+                  <c:v>46282.125</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46282.20833333334</c:v>
+                  <c:v>46282.25</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>46282.33333333334</c:v>
+                  <c:v>46282.375</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>46282.45833333334</c:v>
+                  <c:v>46282.5</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>46282.58333333334</c:v>
+                  <c:v>46282.625</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>46282.70833333334</c:v>
+                  <c:v>46282.75</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>46282.83333333334</c:v>
+                  <c:v>46282.875</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>46282.95833333334</c:v>
+                  <c:v>46283</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>46283.08333333334</c:v>
+                  <c:v>46283.125</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>46283.20833333334</c:v>
+                  <c:v>46283.25</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46283.33333333334</c:v>
+                  <c:v>46283.375</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>46283.45833333334</c:v>
+                  <c:v>46283.5</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>46283.58333333334</c:v>
+                  <c:v>46283.625</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>46283.70833333334</c:v>
+                  <c:v>46283.75</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>46283.83333333334</c:v>
+                  <c:v>46283.875</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>46283.95833333334</c:v>
+                  <c:v>46284</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>46284.08333333334</c:v>
+                  <c:v>46284.125</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>46284.20833333334</c:v>
+                  <c:v>46284.25</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>46284.33333333334</c:v>
+                  <c:v>46284.375</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>46284.45833333334</c:v>
+                  <c:v>46284.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4086,79 +4110,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>58</c:v>
+                  <c:v>60.7</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>58.1</c:v>
+                  <c:v>58.6</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>52.4</c:v>
+                  <c:v>55.2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>58.3</c:v>
+                  <c:v>61.6</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>60.9</c:v>
+                  <c:v>61.9</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>62.6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>66.7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>67.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>68.3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>65.8</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>58.2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>49.2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>41.9</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>38.2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>44.3</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>52.9</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>62.4</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>69.59999999999999</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>71.3</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>58.5</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>64.7</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>65.09999999999999</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>66.5</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>66.09999999999999</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>60</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>51.1</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>43.1</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>37.7</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>41.1</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>49</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>58.6</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>67</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>70.90000000000001</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>68.5</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>61</c:v>
-                </c:pt>
                 <c:pt idx="21">
-                  <c:v>51.8</c:v>
+                  <c:v>49.6</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>44.2</c:v>
+                  <c:v>42.9</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>39.3</c:v>
+                  <c:v>38.9</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>36.8</c:v>
+                  <c:v>37</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4814,7 +4838,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>25</v>
@@ -4823,16 +4847,16 @@
         <v>24</v>
       </c>
       <c r="F9" s="5">
-        <v>119.917</v>
+        <v>88.89700000000001</v>
       </c>
       <c r="G9" s="5">
-        <v>118.443</v>
+        <v>82.65300000000001</v>
       </c>
       <c r="H9" s="5">
-        <v>8.300000000000001</v>
+        <v>41.7</v>
       </c>
       <c r="I9" s="5">
-        <v>62.5</v>
+        <v>66.7</v>
       </c>
       <c r="J9" s="5" t="s">
         <v>26</v>
@@ -4843,25 +4867,25 @@
         <v>10</v>
       </c>
       <c r="B10" s="5">
-        <v>2490</v>
+        <v>2581</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>27</v>
       </c>
       <c r="E10" s="5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F10" s="5">
-        <v>116.147</v>
+        <v>83.06</v>
       </c>
       <c r="G10" s="5">
-        <v>114.733</v>
+        <v>75.29300000000001</v>
       </c>
       <c r="H10" s="5">
-        <v>12</v>
+        <v>46.2</v>
       </c>
       <c r="I10" s="5">
-        <v>64</v>
+        <v>69.2</v>
       </c>
       <c r="J10" s="5" t="s">
         <v>26</v>
@@ -4872,25 +4896,25 @@
         <v>11</v>
       </c>
       <c r="B11" s="5">
-        <v>2478</v>
+        <v>2568</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>28</v>
       </c>
       <c r="E11" s="5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F11" s="5">
-        <v>116.147</v>
+        <v>83.06</v>
       </c>
       <c r="G11" s="5">
-        <v>114.733</v>
+        <v>75.29300000000001</v>
       </c>
       <c r="H11" s="5">
-        <v>12</v>
+        <v>46.2</v>
       </c>
       <c r="I11" s="5">
-        <v>64</v>
+        <v>69.2</v>
       </c>
       <c r="J11" s="5" t="s">
         <v>26</v>
@@ -4901,7 +4925,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="5">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>29</v>
@@ -4943,7 +4967,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="5">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>32</v>
@@ -4980,7 +5004,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -4993,7 +5017,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.7109375" customWidth="1"/>
@@ -5039,16 +5063,16 @@
         <v>46280.5</v>
       </c>
       <c r="B3" s="5">
-        <v>575.59</v>
+        <v>569.6</v>
       </c>
       <c r="C3" s="5">
         <v>2.53</v>
       </c>
       <c r="D3" s="5">
-        <v>8.725</v>
+        <v>8.785</v>
       </c>
       <c r="E3" s="5">
-        <v>12.63</v>
+        <v>12.62</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -5056,16 +5080,16 @@
         <v>46280.54166666666</v>
       </c>
       <c r="B4" s="5">
-        <v>535.5</v>
+        <v>543.22</v>
       </c>
       <c r="C4" s="5">
-        <v>3.17</v>
+        <v>3.02</v>
       </c>
       <c r="D4" s="5">
-        <v>9.210000000000001</v>
+        <v>9.365</v>
       </c>
       <c r="E4" s="5">
-        <v>13.355</v>
+        <v>13.345</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -5073,16 +5097,16 @@
         <v>46280.58333333334</v>
       </c>
       <c r="B5" s="5">
-        <v>444.08</v>
+        <v>451.575</v>
       </c>
       <c r="C5" s="5">
-        <v>2.405</v>
+        <v>2.52</v>
       </c>
       <c r="D5" s="5">
-        <v>9.640000000000001</v>
+        <v>9.775</v>
       </c>
       <c r="E5" s="5">
-        <v>15.035</v>
+        <v>15.04</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -5093,13 +5117,13 @@
         <v>444.55</v>
       </c>
       <c r="C6" s="5">
-        <v>2.75</v>
+        <v>2.68</v>
       </c>
       <c r="D6" s="5">
-        <v>8.175000000000001</v>
+        <v>7.995</v>
       </c>
       <c r="E6" s="5">
-        <v>14.705</v>
+        <v>14.685</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -5110,13 +5134,13 @@
         <v>457.77</v>
       </c>
       <c r="C7" s="5">
-        <v>0.805</v>
+        <v>0.79</v>
       </c>
       <c r="D7" s="5">
-        <v>10.29</v>
+        <v>10.23</v>
       </c>
       <c r="E7" s="5">
-        <v>14.955</v>
+        <v>14.97</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -5124,16 +5148,16 @@
         <v>46280.70833333334</v>
       </c>
       <c r="B8" s="5">
-        <v>431.84</v>
+        <v>433.77</v>
       </c>
       <c r="C8" s="5">
-        <v>0.825</v>
+        <v>0.78</v>
       </c>
       <c r="D8" s="5">
-        <v>9.23</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="E8" s="5">
-        <v>16.12</v>
+        <v>16.11</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -5141,16 +5165,16 @@
         <v>46280.75</v>
       </c>
       <c r="B9" s="5">
-        <v>610.755</v>
+        <v>683.64</v>
       </c>
       <c r="C9" s="5">
-        <v>0.255</v>
+        <v>0.265</v>
       </c>
       <c r="D9" s="5">
-        <v>-4.87</v>
+        <v>-5.845</v>
       </c>
       <c r="E9" s="5">
-        <v>12.895</v>
+        <v>12.62</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -5158,13 +5182,13 @@
         <v>46280.79166666666</v>
       </c>
       <c r="B10" s="5">
-        <v>622.275</v>
+        <v>621.9349999999999</v>
       </c>
       <c r="C10" s="5">
-        <v>0.22</v>
+        <v>0.37</v>
       </c>
       <c r="D10" s="5">
-        <v>-9.385</v>
+        <v>-9.345000000000001</v>
       </c>
       <c r="E10" s="5">
         <v>12.23</v>
@@ -5175,16 +5199,16 @@
         <v>46280.83333333334</v>
       </c>
       <c r="B11" s="5">
-        <v>514.66</v>
+        <v>515.8099999999999</v>
       </c>
       <c r="C11" s="5">
-        <v>0.35</v>
+        <v>0.72</v>
       </c>
       <c r="D11" s="5">
-        <v>-9.23</v>
+        <v>-9.16</v>
       </c>
       <c r="E11" s="5">
-        <v>13.56</v>
+        <v>13.57</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -5192,16 +5216,16 @@
         <v>46280.875</v>
       </c>
       <c r="B12" s="5">
-        <v>463.25</v>
+        <v>468.7</v>
       </c>
       <c r="C12" s="5">
-        <v>3.47</v>
+        <v>3.735</v>
       </c>
       <c r="D12" s="5">
-        <v>1.14</v>
+        <v>0.44</v>
       </c>
       <c r="E12" s="5">
-        <v>12.27</v>
+        <v>12.37</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -5209,13 +5233,13 @@
         <v>46280.91666666666</v>
       </c>
       <c r="B13" s="5">
-        <v>446.015</v>
+        <v>448.01</v>
       </c>
       <c r="C13" s="5">
-        <v>7.265</v>
+        <v>7.495</v>
       </c>
       <c r="D13" s="5">
-        <v>-2.655</v>
+        <v>-2.27</v>
       </c>
       <c r="E13" s="5">
         <v>10.485</v>
@@ -5226,16 +5250,16 @@
         <v>46280.95833333334</v>
       </c>
       <c r="B14" s="5">
-        <v>462.475</v>
+        <v>464.44</v>
       </c>
       <c r="C14" s="5">
-        <v>10.33</v>
+        <v>10.605</v>
       </c>
       <c r="D14" s="5">
-        <v>-4.83</v>
+        <v>-5.155</v>
       </c>
       <c r="E14" s="5">
-        <v>11.055</v>
+        <v>11.24</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -5243,16 +5267,16 @@
         <v>46281</v>
       </c>
       <c r="B15" s="5">
-        <v>516.465</v>
+        <v>517.8099999999999</v>
       </c>
       <c r="C15" s="5">
-        <v>18.25</v>
+        <v>22.045</v>
       </c>
       <c r="D15" s="5">
-        <v>2.18</v>
+        <v>1.795</v>
       </c>
       <c r="E15" s="5">
-        <v>12.76</v>
+        <v>12.775</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -5260,13 +5284,13 @@
         <v>46281.04166666666</v>
       </c>
       <c r="B16" s="5">
-        <v>524.36</v>
+        <v>521.405</v>
       </c>
       <c r="C16" s="5">
-        <v>13.585</v>
+        <v>13.36</v>
       </c>
       <c r="D16" s="5">
-        <v>5.7</v>
+        <v>5.68</v>
       </c>
       <c r="E16" s="5">
         <v>10.93</v>
@@ -5277,16 +5301,16 @@
         <v>46281.08333333334</v>
       </c>
       <c r="B17" s="5">
-        <v>528.1950000000001</v>
+        <v>528.495</v>
       </c>
       <c r="C17" s="5">
         <v>8.800000000000001</v>
       </c>
       <c r="D17" s="5">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="E17" s="5">
-        <v>10.25</v>
+        <v>10.29</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -5294,16 +5318,16 @@
         <v>46281.125</v>
       </c>
       <c r="B18" s="5">
-        <v>531.165</v>
+        <v>532.595</v>
       </c>
       <c r="C18" s="5">
-        <v>5.885</v>
+        <v>5.75</v>
       </c>
       <c r="D18" s="5">
-        <v>0.435</v>
+        <v>0.425</v>
       </c>
       <c r="E18" s="5">
-        <v>6.97</v>
+        <v>6.76</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -5311,16 +5335,16 @@
         <v>46281.16666666666</v>
       </c>
       <c r="B19" s="5">
-        <v>538.105</v>
+        <v>538.515</v>
       </c>
       <c r="C19" s="5">
         <v>5.305</v>
       </c>
       <c r="D19" s="5">
-        <v>-0.4</v>
+        <v>-0.305</v>
       </c>
       <c r="E19" s="5">
-        <v>7.035</v>
+        <v>7.045</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -5328,16 +5352,16 @@
         <v>46281.20833333334</v>
       </c>
       <c r="B20" s="5">
-        <v>536.405</v>
+        <v>536.1849999999999</v>
       </c>
       <c r="C20" s="5">
-        <v>5.47</v>
+        <v>5.605</v>
       </c>
       <c r="D20" s="5">
-        <v>1.66</v>
+        <v>1.51</v>
       </c>
       <c r="E20" s="5">
-        <v>6.72</v>
+        <v>6.68</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -5345,16 +5369,16 @@
         <v>46281.25</v>
       </c>
       <c r="B21" s="5">
-        <v>531.875</v>
+        <v>531.8</v>
       </c>
       <c r="C21" s="5">
-        <v>5.585</v>
+        <v>5.59</v>
       </c>
       <c r="D21" s="5">
-        <v>4.505</v>
+        <v>4.58</v>
       </c>
       <c r="E21" s="5">
-        <v>6.34</v>
+        <v>6.395</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -5362,16 +5386,16 @@
         <v>46281.29166666666</v>
       </c>
       <c r="B22" s="5">
-        <v>521.885</v>
+        <v>521.465</v>
       </c>
       <c r="C22" s="5">
-        <v>5.245</v>
+        <v>5.2</v>
       </c>
       <c r="D22" s="5">
-        <v>3.465</v>
+        <v>3.515</v>
       </c>
       <c r="E22" s="5">
-        <v>5.76</v>
+        <v>5.77</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -5379,16 +5403,16 @@
         <v>46281.33333333334</v>
       </c>
       <c r="B23" s="5">
-        <v>543.5</v>
+        <v>543.22</v>
       </c>
       <c r="C23" s="5">
-        <v>4.59</v>
+        <v>4.55</v>
       </c>
       <c r="D23" s="5">
-        <v>4.49</v>
+        <v>4.32</v>
       </c>
       <c r="E23" s="5">
-        <v>4.9</v>
+        <v>4.85</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -5396,16 +5420,16 @@
         <v>46281.375</v>
       </c>
       <c r="B24" s="5">
-        <v>541.64</v>
+        <v>540.355</v>
       </c>
       <c r="C24" s="5">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="D24" s="5">
-        <v>2.805</v>
+        <v>2.55</v>
       </c>
       <c r="E24" s="5">
-        <v>4.56</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -5413,16 +5437,16 @@
         <v>46281.41666666666</v>
       </c>
       <c r="B25" s="5">
-        <v>542.53</v>
+        <v>542.835</v>
       </c>
       <c r="C25" s="5">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="D25" s="5">
-        <v>-2.31</v>
+        <v>-2.345</v>
       </c>
       <c r="E25" s="5">
-        <v>4.625</v>
+        <v>4.805</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -5430,16 +5454,33 @@
         <v>46281.45833333334</v>
       </c>
       <c r="B26" s="5">
-        <v>536.175</v>
+        <v>537.1</v>
       </c>
       <c r="C26" s="5">
-        <v>0.305</v>
+        <v>0.315</v>
       </c>
       <c r="D26" s="5">
-        <v>-2.74</v>
+        <v>-2.36</v>
       </c>
       <c r="E26" s="5">
-        <v>4.19</v>
+        <v>4.31</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6">
+        <v>46281.5</v>
+      </c>
+      <c r="B27" s="5">
+        <v>545.6</v>
+      </c>
+      <c r="C27" s="5">
+        <v>0.11</v>
+      </c>
+      <c r="D27" s="5">
+        <v>0.35</v>
+      </c>
+      <c r="E27" s="5">
+        <v>4.22</v>
       </c>
     </row>
   </sheetData>
@@ -5483,19 +5524,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="6">
-        <v>46281.33333333334</v>
+        <v>46281.375</v>
       </c>
       <c r="B2" s="5">
-        <v>613.53</v>
+        <v>591.4</v>
       </c>
       <c r="C2" s="5">
-        <v>442.69</v>
+        <v>400.06</v>
       </c>
       <c r="D2" s="5">
-        <v>535.67</v>
+        <v>542.7</v>
       </c>
       <c r="E2" s="5">
-        <v>234.68</v>
+        <v>256.41</v>
       </c>
       <c r="F2" s="5"/>
       <c r="G2" s="5" t="s">
@@ -5504,19 +5545,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="6">
-        <v>46281.375</v>
+        <v>46281.41666666666</v>
       </c>
       <c r="B3" s="5">
-        <v>611.4</v>
+        <v>589.14</v>
       </c>
       <c r="C3" s="5">
-        <v>444.41</v>
+        <v>400.2</v>
       </c>
       <c r="D3" s="5">
-        <v>543.8</v>
+        <v>542.28</v>
       </c>
       <c r="E3" s="5">
-        <v>229.38</v>
+        <v>253.21</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5" t="s">
@@ -5525,19 +5566,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="6">
-        <v>46281.41666666666</v>
+        <v>46281.45833333334</v>
       </c>
       <c r="B4" s="5">
-        <v>608.28</v>
+        <v>582.91</v>
       </c>
       <c r="C4" s="5">
-        <v>444.65</v>
+        <v>396.52</v>
       </c>
       <c r="D4" s="5">
-        <v>541.4</v>
+        <v>538.6</v>
       </c>
       <c r="E4" s="5">
-        <v>224.77</v>
+        <v>249.79</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="5" t="s">
@@ -5546,19 +5587,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="6">
-        <v>46281.45833333334</v>
+        <v>46281.5</v>
       </c>
       <c r="B5" s="5">
-        <v>601.53</v>
+        <v>579.8</v>
       </c>
       <c r="C5" s="5">
-        <v>440.91</v>
+        <v>396.07</v>
       </c>
       <c r="D5" s="5">
-        <v>541.4</v>
+        <v>537.65</v>
       </c>
       <c r="E5" s="5">
-        <v>220.63</v>
+        <v>246.21</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5" t="s">
@@ -5567,17 +5608,17 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="6">
-        <v>46281.5</v>
+        <v>46281.54166666666</v>
       </c>
       <c r="B6" s="5">
-        <v>599.8</v>
+        <v>578</v>
       </c>
       <c r="C6" s="5">
-        <v>440.13</v>
+        <v>395.82</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5">
-        <v>217.22</v>
+        <v>240.75</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="5" t="s">
@@ -5586,17 +5627,17 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="6">
-        <v>46281.54166666666</v>
+        <v>46281.58333333334</v>
       </c>
       <c r="B7" s="5">
-        <v>598.49</v>
+        <v>578.09</v>
       </c>
       <c r="C7" s="5">
-        <v>440.39</v>
+        <v>396.74</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5">
-        <v>213.63</v>
+        <v>241.23</v>
       </c>
       <c r="F7" s="5"/>
       <c r="G7" s="5" t="s">
@@ -5605,17 +5646,17 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="6">
-        <v>46281.58333333334</v>
+        <v>46281.625</v>
       </c>
       <c r="B8" s="5">
-        <v>599.61</v>
+        <v>579.97</v>
       </c>
       <c r="C8" s="5">
-        <v>441.88</v>
+        <v>396.99</v>
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="5">
-        <v>215.86</v>
+        <v>248.78</v>
       </c>
       <c r="F8" s="5"/>
       <c r="G8" s="5" t="s">
@@ -5624,17 +5665,17 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="6">
-        <v>46281.625</v>
+        <v>46281.66666666666</v>
       </c>
       <c r="B9" s="5">
-        <v>602.78</v>
+        <v>585.45</v>
       </c>
       <c r="C9" s="5">
-        <v>442.73</v>
+        <v>397.12</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="5">
-        <v>225.03</v>
+        <v>264.06</v>
       </c>
       <c r="F9" s="5"/>
       <c r="G9" s="5" t="s">
@@ -5643,17 +5684,17 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="6">
-        <v>46281.66666666666</v>
+        <v>46281.70833333334</v>
       </c>
       <c r="B10" s="5">
-        <v>609.52</v>
+        <v>594.9299999999999</v>
       </c>
       <c r="C10" s="5">
-        <v>443.4</v>
+        <v>396.85</v>
       </c>
       <c r="D10" s="5"/>
       <c r="E10" s="5">
-        <v>241.81</v>
+        <v>286.8</v>
       </c>
       <c r="F10" s="5"/>
       <c r="G10" s="5" t="s">
@@ -5662,17 +5703,17 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="6">
-        <v>46281.70833333334</v>
+        <v>46281.75</v>
       </c>
       <c r="B11" s="5">
-        <v>619.13</v>
+        <v>611.08</v>
       </c>
       <c r="C11" s="5">
-        <v>442.57</v>
+        <v>398.8</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="5">
-        <v>265.92</v>
+        <v>315.54</v>
       </c>
       <c r="F11" s="5"/>
       <c r="G11" s="5" t="s">
@@ -5681,17 +5722,17 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="6">
-        <v>46281.75</v>
+        <v>46281.79166666666</v>
       </c>
       <c r="B12" s="5">
-        <v>633.45</v>
+        <v>628.35</v>
       </c>
       <c r="C12" s="5">
-        <v>442.13</v>
+        <v>398.2</v>
       </c>
       <c r="D12" s="5"/>
       <c r="E12" s="5">
-        <v>295.86</v>
+        <v>347.49</v>
       </c>
       <c r="F12" s="5"/>
       <c r="G12" s="5" t="s">
@@ -5700,17 +5741,17 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="6">
-        <v>46281.79166666666</v>
+        <v>46281.83333333334</v>
       </c>
       <c r="B13" s="5">
-        <v>651.73</v>
+        <v>648.21</v>
       </c>
       <c r="C13" s="5">
-        <v>442.16</v>
+        <v>398.09</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="5">
-        <v>328.79</v>
+        <v>378.86</v>
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="5" t="s">
@@ -5719,17 +5760,17 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="6">
-        <v>46281.83333333334</v>
+        <v>46281.875</v>
       </c>
       <c r="B14" s="5">
-        <v>672.22</v>
+        <v>668.34</v>
       </c>
       <c r="C14" s="5">
-        <v>442.46</v>
+        <v>398.28</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="5">
-        <v>360.83</v>
+        <v>405.5</v>
       </c>
       <c r="F14" s="5"/>
       <c r="G14" s="5" t="s">
@@ -5738,17 +5779,17 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="6">
-        <v>46281.875</v>
+        <v>46281.91666666666</v>
       </c>
       <c r="B15" s="5">
-        <v>692.64</v>
+        <v>686.26</v>
       </c>
       <c r="C15" s="5">
-        <v>442.92</v>
+        <v>398.64</v>
       </c>
       <c r="D15" s="5"/>
       <c r="E15" s="5">
-        <v>387.75</v>
+        <v>423.83</v>
       </c>
       <c r="F15" s="5"/>
       <c r="G15" s="5" t="s">
@@ -5757,17 +5798,17 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="6">
-        <v>46281.91666666666</v>
+        <v>46281.95833333334</v>
       </c>
       <c r="B16" s="5">
-        <v>710.55</v>
+        <v>697.7</v>
       </c>
       <c r="C16" s="5">
-        <v>443.46</v>
+        <v>399.1</v>
       </c>
       <c r="D16" s="5"/>
       <c r="E16" s="5">
-        <v>405.82</v>
+        <v>424.17</v>
       </c>
       <c r="F16" s="5"/>
       <c r="G16" s="5" t="s">
@@ -5776,17 +5817,17 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="6">
-        <v>46281.95833333334</v>
+        <v>46282</v>
       </c>
       <c r="B17" s="5">
-        <v>721.74</v>
+        <v>704.65</v>
       </c>
       <c r="C17" s="5">
-        <v>444.04</v>
+        <v>399.61</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="5">
-        <v>405.23</v>
+        <v>422.88</v>
       </c>
       <c r="F17" s="5"/>
       <c r="G17" s="5" t="s">
@@ -5795,17 +5836,17 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="6">
-        <v>46282</v>
+        <v>46282.04166666666</v>
       </c>
       <c r="B18" s="5">
-        <v>727.96</v>
+        <v>708.49</v>
       </c>
       <c r="C18" s="5">
-        <v>444.51</v>
+        <v>399.81</v>
       </c>
       <c r="D18" s="5"/>
       <c r="E18" s="5">
-        <v>402.23</v>
+        <v>421.63</v>
       </c>
       <c r="F18" s="5"/>
       <c r="G18" s="5" t="s">
@@ -5814,17 +5855,17 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="6">
-        <v>46282.04166666666</v>
+        <v>46282.08333333334</v>
       </c>
       <c r="B19" s="5">
-        <v>730.53</v>
+        <v>710.08</v>
       </c>
       <c r="C19" s="5">
-        <v>444.56</v>
+        <v>399.71</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="5">
-        <v>398.46</v>
+        <v>419.62</v>
       </c>
       <c r="F19" s="5"/>
       <c r="G19" s="5" t="s">
@@ -5833,17 +5874,17 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="6">
-        <v>46282.08333333334</v>
+        <v>46282.125</v>
       </c>
       <c r="B20" s="5">
-        <v>730.42</v>
+        <v>711.66</v>
       </c>
       <c r="C20" s="5">
-        <v>444.37</v>
+        <v>399.44</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="5">
-        <v>393.12</v>
+        <v>422.48</v>
       </c>
       <c r="F20" s="5"/>
       <c r="G20" s="5" t="s">
@@ -5852,17 +5893,17 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="6">
-        <v>46282.125</v>
+        <v>46282.16666666666</v>
       </c>
       <c r="B21" s="5">
-        <v>729.8200000000001</v>
+        <v>708.41</v>
       </c>
       <c r="C21" s="5">
-        <v>444.02</v>
+        <v>399.06</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5">
-        <v>392.02</v>
+        <v>408.31</v>
       </c>
       <c r="F21" s="5"/>
       <c r="G21" s="5" t="s">
@@ -5871,17 +5912,17 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="6">
-        <v>46282.16666666666</v>
+        <v>46282.20833333334</v>
       </c>
       <c r="B22" s="5">
-        <v>724.08</v>
+        <v>708.9</v>
       </c>
       <c r="C22" s="5">
-        <v>443.57</v>
+        <v>398.61</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="5">
-        <v>373.44</v>
+        <v>417.86</v>
       </c>
       <c r="F22" s="5"/>
       <c r="G22" s="5" t="s">
@@ -5890,17 +5931,17 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="6">
-        <v>46282.20833333334</v>
+        <v>46282.25</v>
       </c>
       <c r="B23" s="5">
-        <v>721.74</v>
+        <v>711.5599999999999</v>
       </c>
       <c r="C23" s="5">
-        <v>443.08</v>
+        <v>398.13</v>
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="5">
-        <v>378.64</v>
+        <v>426.91</v>
       </c>
       <c r="F23" s="5"/>
       <c r="G23" s="5" t="s">
@@ -5909,17 +5950,17 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="6">
-        <v>46282.25</v>
+        <v>46282.29166666666</v>
       </c>
       <c r="B24" s="5">
-        <v>721.47</v>
+        <v>714.21</v>
       </c>
       <c r="C24" s="5">
-        <v>442.55</v>
+        <v>397.95</v>
       </c>
       <c r="D24" s="5"/>
       <c r="E24" s="5">
-        <v>383.72</v>
+        <v>430</v>
       </c>
       <c r="F24" s="5"/>
       <c r="G24" s="5" t="s">
@@ -5928,17 +5969,17 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="6">
-        <v>46282.29166666666</v>
+        <v>46282.33333333334</v>
       </c>
       <c r="B25" s="5">
-        <v>721.5599999999999</v>
+        <v>712.0599999999999</v>
       </c>
       <c r="C25" s="5">
-        <v>442.33</v>
+        <v>397.97</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="5">
-        <v>384.26</v>
+        <v>416.18</v>
       </c>
       <c r="F25" s="5"/>
       <c r="G25" s="5" t="s">
@@ -5947,17 +5988,17 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="6">
-        <v>46282.33333333334</v>
+        <v>46282.375</v>
       </c>
       <c r="B26" s="5">
-        <v>716.9</v>
+        <v>711</v>
       </c>
       <c r="C26" s="5">
-        <v>442.3</v>
+        <v>398.11</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5">
-        <v>366.84</v>
+        <v>416.7</v>
       </c>
       <c r="F26" s="5"/>
       <c r="G26" s="5" t="s">
@@ -5966,17 +6007,17 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="6">
-        <v>46282.375</v>
+        <v>46282.41666666666</v>
       </c>
       <c r="B27" s="5">
-        <v>713.85</v>
+        <v>708.3200000000001</v>
       </c>
       <c r="C27" s="5">
-        <v>442.39</v>
+        <v>398.33</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="5">
-        <v>365.82</v>
+        <v>409.07</v>
       </c>
       <c r="F27" s="5"/>
       <c r="G27" s="5" t="s">
@@ -5985,17 +6026,17 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="6">
-        <v>46282.41666666666</v>
+        <v>46282.45833333334</v>
       </c>
       <c r="B28" s="5">
-        <v>709.95</v>
+        <v>702.95</v>
       </c>
       <c r="C28" s="5">
-        <v>442.56</v>
+        <v>398.6</v>
       </c>
       <c r="D28" s="5"/>
       <c r="E28" s="5">
-        <v>358.2</v>
+        <v>395.55</v>
       </c>
       <c r="F28" s="5"/>
       <c r="G28" s="5" t="s">
@@ -6004,17 +6045,17 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="6">
-        <v>46282.45833333334</v>
+        <v>46282.5</v>
       </c>
       <c r="B29" s="5">
-        <v>704.22</v>
+        <v>694.9400000000001</v>
       </c>
       <c r="C29" s="5">
-        <v>442.78</v>
+        <v>398.89</v>
       </c>
       <c r="D29" s="5"/>
       <c r="E29" s="5">
-        <v>345.79</v>
+        <v>378.59</v>
       </c>
       <c r="F29" s="5"/>
       <c r="G29" s="5" t="s">
@@ -6023,17 +6064,17 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="6">
-        <v>46282.5</v>
+        <v>46282.54166666666</v>
       </c>
       <c r="B30" s="5">
-        <v>696.59</v>
+        <v>683.04</v>
       </c>
       <c r="C30" s="5">
-        <v>443.04</v>
+        <v>399.06</v>
       </c>
       <c r="D30" s="5"/>
       <c r="E30" s="5">
-        <v>330.6</v>
+        <v>354.17</v>
       </c>
       <c r="F30" s="5"/>
       <c r="G30" s="5" t="s">
@@ -6042,17 +6083,17 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="6">
-        <v>46282.54166666666</v>
+        <v>46282.58333333334</v>
       </c>
       <c r="B31" s="5">
-        <v>685.92</v>
+        <v>669.16</v>
       </c>
       <c r="C31" s="5">
-        <v>443.16</v>
+        <v>399.14</v>
       </c>
       <c r="D31" s="5"/>
       <c r="E31" s="5">
-        <v>309.28</v>
+        <v>331.33</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="5" t="s">
@@ -6061,17 +6102,17 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="6">
-        <v>46282.58333333334</v>
+        <v>46282.625</v>
       </c>
       <c r="B32" s="5">
-        <v>673.76</v>
+        <v>654.47</v>
       </c>
       <c r="C32" s="5">
-        <v>443.2</v>
+        <v>399.17</v>
       </c>
       <c r="D32" s="5"/>
       <c r="E32" s="5">
-        <v>289.34</v>
+        <v>309.96</v>
       </c>
       <c r="F32" s="5"/>
       <c r="G32" s="5" t="s">
@@ -6080,17 +6121,17 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="6">
-        <v>46282.625</v>
+        <v>46282.66666666666</v>
       </c>
       <c r="B33" s="5">
-        <v>661.03</v>
+        <v>639.6900000000001</v>
       </c>
       <c r="C33" s="5">
-        <v>443.2</v>
+        <v>399.18</v>
       </c>
       <c r="D33" s="5"/>
       <c r="E33" s="5">
-        <v>270.67</v>
+        <v>289.97</v>
       </c>
       <c r="F33" s="5"/>
       <c r="G33" s="5" t="s">
@@ -6099,17 +6140,17 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="6">
-        <v>46282.66666666666</v>
+        <v>46282.70833333334</v>
       </c>
       <c r="B34" s="5">
-        <v>648.27</v>
+        <v>625.2</v>
       </c>
       <c r="C34" s="5">
-        <v>443.17</v>
+        <v>399.16</v>
       </c>
       <c r="D34" s="5"/>
       <c r="E34" s="5">
-        <v>253.22</v>
+        <v>271.27</v>
       </c>
       <c r="F34" s="5"/>
       <c r="G34" s="5" t="s">
@@ -6118,17 +6159,17 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="6">
-        <v>46282.70833333334</v>
+        <v>46282.75</v>
       </c>
       <c r="B35" s="5">
-        <v>635.83</v>
+        <v>611.24</v>
       </c>
       <c r="C35" s="5">
-        <v>443.13</v>
+        <v>399.14</v>
       </c>
       <c r="D35" s="5"/>
       <c r="E35" s="5">
-        <v>236.89</v>
+        <v>253.77</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="5" t="s">
@@ -6137,17 +6178,17 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="6">
-        <v>46282.75</v>
+        <v>46282.79166666666</v>
       </c>
       <c r="B36" s="5">
-        <v>623.86</v>
+        <v>597.8099999999999</v>
       </c>
       <c r="C36" s="5">
-        <v>443.08</v>
+        <v>398.99</v>
       </c>
       <c r="D36" s="5"/>
       <c r="E36" s="5">
-        <v>221.61</v>
+        <v>237.41</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="5" t="s">
@@ -6156,17 +6197,17 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="6">
-        <v>46282.79166666666</v>
+        <v>46282.83333333334</v>
       </c>
       <c r="B37" s="5">
-        <v>612.34</v>
+        <v>583.59</v>
       </c>
       <c r="C37" s="5">
-        <v>442.91</v>
+        <v>398.77</v>
       </c>
       <c r="D37" s="5"/>
       <c r="E37" s="5">
-        <v>207.32</v>
+        <v>217.06</v>
       </c>
       <c r="F37" s="5"/>
       <c r="G37" s="5" t="s">
@@ -6175,17 +6216,17 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="6">
-        <v>46282.83333333334</v>
+        <v>46282.875</v>
       </c>
       <c r="B38" s="5">
-        <v>600.47</v>
+        <v>570.67</v>
       </c>
       <c r="C38" s="5">
-        <v>442.66</v>
+        <v>398.5</v>
       </c>
       <c r="D38" s="5"/>
       <c r="E38" s="5">
-        <v>190.7</v>
+        <v>203.06</v>
       </c>
       <c r="F38" s="5"/>
       <c r="G38" s="5" t="s">
@@ -6194,17 +6235,17 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="6">
-        <v>46282.875</v>
+        <v>46282.91666666666</v>
       </c>
       <c r="B39" s="5">
-        <v>589.5700000000001</v>
+        <v>558.8200000000001</v>
       </c>
       <c r="C39" s="5">
-        <v>442.38</v>
+        <v>398.21</v>
       </c>
       <c r="D39" s="5"/>
       <c r="E39" s="5">
-        <v>178.4</v>
+        <v>189.97</v>
       </c>
       <c r="F39" s="5"/>
       <c r="G39" s="5" t="s">
@@ -6213,17 +6254,17 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="6">
-        <v>46282.91666666666</v>
+        <v>46282.95833333334</v>
       </c>
       <c r="B40" s="5">
-        <v>579.5</v>
+        <v>547.87</v>
       </c>
       <c r="C40" s="5">
-        <v>442.06</v>
+        <v>397.9</v>
       </c>
       <c r="D40" s="5"/>
       <c r="E40" s="5">
-        <v>166.9</v>
+        <v>177.72</v>
       </c>
       <c r="F40" s="5"/>
       <c r="G40" s="5" t="s">
@@ -6232,17 +6273,17 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="6">
-        <v>46282.95833333334</v>
+        <v>46283</v>
       </c>
       <c r="B41" s="5">
-        <v>570.14</v>
+        <v>537.72</v>
       </c>
       <c r="C41" s="5">
-        <v>441.74</v>
+        <v>397.58</v>
       </c>
       <c r="D41" s="5"/>
       <c r="E41" s="5">
-        <v>156.13</v>
+        <v>166.32</v>
       </c>
       <c r="F41" s="5"/>
       <c r="G41" s="5" t="s">
@@ -6251,17 +6292,17 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="6">
-        <v>46283</v>
+        <v>46283.04166666666</v>
       </c>
       <c r="B42" s="5">
-        <v>561.4400000000001</v>
+        <v>527.5599999999999</v>
       </c>
       <c r="C42" s="5">
-        <v>441.4</v>
+        <v>398.17</v>
       </c>
       <c r="D42" s="5"/>
       <c r="E42" s="5">
-        <v>146.13</v>
+        <v>149.91</v>
       </c>
       <c r="F42" s="5"/>
       <c r="G42" s="5" t="s">
@@ -6270,17 +6311,17 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="6">
-        <v>46283.04166666666</v>
+        <v>46283.08333333334</v>
       </c>
       <c r="B43" s="5">
-        <v>553.0700000000001</v>
+        <v>519.38</v>
       </c>
       <c r="C43" s="5">
-        <v>441.96</v>
+        <v>399.32</v>
       </c>
       <c r="D43" s="5"/>
       <c r="E43" s="5">
-        <v>132.62</v>
+        <v>140.47</v>
       </c>
       <c r="F43" s="5"/>
       <c r="G43" s="5" t="s">
@@ -6289,17 +6330,17 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="6">
-        <v>46283.08333333334</v>
+        <v>46283.125</v>
       </c>
       <c r="B44" s="5">
-        <v>546.34</v>
+        <v>512.66</v>
       </c>
       <c r="C44" s="5">
-        <v>443.06</v>
+        <v>400.83</v>
       </c>
       <c r="D44" s="5"/>
       <c r="E44" s="5">
-        <v>124.3</v>
+        <v>131.91</v>
       </c>
       <c r="F44" s="5"/>
       <c r="G44" s="5" t="s">
@@ -6308,17 +6349,17 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="6">
-        <v>46283.125</v>
+        <v>46283.16666666666</v>
       </c>
       <c r="B45" s="5">
-        <v>540.85</v>
+        <v>507.17</v>
       </c>
       <c r="C45" s="5">
-        <v>444.51</v>
+        <v>402.55</v>
       </c>
       <c r="D45" s="5"/>
       <c r="E45" s="5">
-        <v>116.78</v>
+        <v>124.42</v>
       </c>
       <c r="F45" s="5"/>
       <c r="G45" s="5" t="s">
@@ -6327,17 +6368,17 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="6">
-        <v>46283.16666666666</v>
+        <v>46283.20833333334</v>
       </c>
       <c r="B46" s="5">
-        <v>536.41</v>
+        <v>502.84</v>
       </c>
       <c r="C46" s="5">
-        <v>446.17</v>
+        <v>404.41</v>
       </c>
       <c r="D46" s="5"/>
       <c r="E46" s="5">
-        <v>110.28</v>
+        <v>118.37</v>
       </c>
       <c r="F46" s="5"/>
       <c r="G46" s="5" t="s">
@@ -6346,17 +6387,17 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="6">
-        <v>46283.20833333334</v>
+        <v>46283.25</v>
       </c>
       <c r="B47" s="5">
-        <v>533</v>
+        <v>499.79</v>
       </c>
       <c r="C47" s="5">
-        <v>447.96</v>
+        <v>406.35</v>
       </c>
       <c r="D47" s="5"/>
       <c r="E47" s="5">
-        <v>105.14</v>
+        <v>114.32</v>
       </c>
       <c r="F47" s="5"/>
       <c r="G47" s="5" t="s">
@@ -6365,17 +6406,17 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="6">
-        <v>46283.25</v>
+        <v>46283.29166666666</v>
       </c>
       <c r="B48" s="5">
-        <v>530.77</v>
+        <v>497.46</v>
       </c>
       <c r="C48" s="5">
-        <v>449.84</v>
+        <v>407.46</v>
       </c>
       <c r="D48" s="5"/>
       <c r="E48" s="5">
-        <v>101.96</v>
+        <v>113.08</v>
       </c>
       <c r="F48" s="5"/>
       <c r="G48" s="5" t="s">
@@ -6384,17 +6425,17 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="6">
-        <v>46283.29166666666</v>
+        <v>46283.33333333334</v>
       </c>
       <c r="B49" s="5">
-        <v>529.17</v>
+        <v>496.66</v>
       </c>
       <c r="C49" s="5">
-        <v>450.91</v>
+        <v>408.07</v>
       </c>
       <c r="D49" s="5"/>
       <c r="E49" s="5">
-        <v>101.53</v>
+        <v>115.64</v>
       </c>
       <c r="F49" s="5"/>
       <c r="G49" s="5" t="s">
@@ -6403,17 +6444,17 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="6">
-        <v>46283.33333333334</v>
+        <v>46283.375</v>
       </c>
       <c r="B50" s="5">
-        <v>529.01</v>
+        <v>498.16</v>
       </c>
       <c r="C50" s="5">
-        <v>451.48</v>
+        <v>408.35</v>
       </c>
       <c r="D50" s="5"/>
       <c r="E50" s="5">
-        <v>104.85</v>
+        <v>123.02</v>
       </c>
       <c r="F50" s="5"/>
       <c r="G50" s="5" t="s">
@@ -6422,17 +6463,17 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="6">
-        <v>46283.375</v>
+        <v>46283.41666666666</v>
       </c>
       <c r="B51" s="5">
-        <v>531.0599999999999</v>
+        <v>502.68</v>
       </c>
       <c r="C51" s="5">
-        <v>451.74</v>
+        <v>408.44</v>
       </c>
       <c r="D51" s="5"/>
       <c r="E51" s="5">
-        <v>112.96</v>
+        <v>136.01</v>
       </c>
       <c r="F51" s="5"/>
       <c r="G51" s="5" t="s">
@@ -6441,17 +6482,17 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="6">
-        <v>46283.41666666666</v>
+        <v>46283.45833333334</v>
       </c>
       <c r="B52" s="5">
-        <v>536.02</v>
+        <v>505.38</v>
       </c>
       <c r="C52" s="5">
-        <v>451.81</v>
+        <v>408.4</v>
       </c>
       <c r="D52" s="5"/>
       <c r="E52" s="5">
-        <v>126.65</v>
+        <v>135.94</v>
       </c>
       <c r="F52" s="5"/>
       <c r="G52" s="5" t="s">
@@ -6460,17 +6501,17 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="6">
-        <v>46283.45833333334</v>
+        <v>46283.5</v>
       </c>
       <c r="B53" s="5">
-        <v>539.1799999999999</v>
+        <v>514.08</v>
       </c>
       <c r="C53" s="5">
-        <v>451.77</v>
+        <v>408.29</v>
       </c>
       <c r="D53" s="5"/>
       <c r="E53" s="5">
-        <v>127.24</v>
+        <v>161.02</v>
       </c>
       <c r="F53" s="5"/>
       <c r="G53" s="5" t="s">
@@ -6479,17 +6520,17 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="6">
-        <v>46283.5</v>
+        <v>46283.54166666666</v>
       </c>
       <c r="B54" s="5">
-        <v>548.16</v>
+        <v>525.1900000000001</v>
       </c>
       <c r="C54" s="5">
-        <v>451.65</v>
+        <v>408.14</v>
       </c>
       <c r="D54" s="5"/>
       <c r="E54" s="5">
-        <v>152.96</v>
+        <v>181.5</v>
       </c>
       <c r="F54" s="5"/>
       <c r="G54" s="5" t="s">
@@ -6498,17 +6539,17 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="6">
-        <v>46283.54166666666</v>
+        <v>46283.58333333334</v>
       </c>
       <c r="B55" s="5">
-        <v>559.46</v>
+        <v>540.0700000000001</v>
       </c>
       <c r="C55" s="5">
-        <v>451.49</v>
+        <v>407.96</v>
       </c>
       <c r="D55" s="5"/>
       <c r="E55" s="5">
-        <v>174.02</v>
+        <v>209.94</v>
       </c>
       <c r="F55" s="5"/>
       <c r="G55" s="5" t="s">
@@ -6517,17 +6558,17 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="6">
-        <v>46283.58333333334</v>
+        <v>46283.625</v>
       </c>
       <c r="B56" s="5">
-        <v>574.41</v>
+        <v>556.13</v>
       </c>
       <c r="C56" s="5">
-        <v>451.3</v>
+        <v>407.77</v>
       </c>
       <c r="D56" s="5"/>
       <c r="E56" s="5">
-        <v>203.03</v>
+        <v>234.37</v>
       </c>
       <c r="F56" s="5"/>
       <c r="G56" s="5" t="s">
@@ -6536,17 +6577,17 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="6">
-        <v>46283.625</v>
+        <v>46283.66666666666</v>
       </c>
       <c r="B57" s="5">
-        <v>590.5</v>
+        <v>570.71</v>
       </c>
       <c r="C57" s="5">
-        <v>451.1</v>
+        <v>407.57</v>
       </c>
       <c r="D57" s="5"/>
       <c r="E57" s="5">
-        <v>227.99</v>
+        <v>250.96</v>
       </c>
       <c r="F57" s="5"/>
       <c r="G57" s="5" t="s">
@@ -6555,17 +6596,17 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="6">
-        <v>46283.66666666666</v>
+        <v>46283.70833333334</v>
       </c>
       <c r="B58" s="5">
-        <v>605.11</v>
+        <v>581.3200000000001</v>
       </c>
       <c r="C58" s="5">
-        <v>450.89</v>
+        <v>407.36</v>
       </c>
       <c r="D58" s="5"/>
       <c r="E58" s="5">
-        <v>245.06</v>
+        <v>256.77</v>
       </c>
       <c r="F58" s="5"/>
       <c r="G58" s="5" t="s">
@@ -6574,17 +6615,17 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="6">
-        <v>46283.70833333334</v>
+        <v>46283.75</v>
       </c>
       <c r="B59" s="5">
-        <v>615.8099999999999</v>
+        <v>583.8099999999999</v>
       </c>
       <c r="C59" s="5">
-        <v>450.68</v>
+        <v>407.15</v>
       </c>
       <c r="D59" s="5"/>
       <c r="E59" s="5">
-        <v>251.3</v>
+        <v>242.65</v>
       </c>
       <c r="F59" s="5"/>
       <c r="G59" s="5" t="s">
@@ -6593,17 +6634,17 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="6">
-        <v>46283.75</v>
+        <v>46283.79166666666</v>
       </c>
       <c r="B60" s="5">
-        <v>618.5599999999999</v>
+        <v>578.8</v>
       </c>
       <c r="C60" s="5">
-        <v>450.46</v>
+        <v>406.94</v>
       </c>
       <c r="D60" s="5"/>
       <c r="E60" s="5">
-        <v>237.54</v>
+        <v>219.82</v>
       </c>
       <c r="F60" s="5"/>
       <c r="G60" s="5" t="s">
@@ -6612,17 +6653,17 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="6">
-        <v>46283.79166666666</v>
+        <v>46283.83333333334</v>
       </c>
       <c r="B61" s="5">
-        <v>614.35</v>
+        <v>571.59</v>
       </c>
       <c r="C61" s="5">
-        <v>450.24</v>
+        <v>406.73</v>
       </c>
       <c r="D61" s="5"/>
       <c r="E61" s="5">
-        <v>216.49</v>
+        <v>205.64</v>
       </c>
       <c r="F61" s="5"/>
       <c r="G61" s="5" t="s">
@@ -6631,17 +6672,17 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="6">
-        <v>46283.83333333334</v>
+        <v>46283.875</v>
       </c>
       <c r="B62" s="5">
-        <v>607.8</v>
+        <v>563.28</v>
       </c>
       <c r="C62" s="5">
-        <v>450.03</v>
+        <v>406.51</v>
       </c>
       <c r="D62" s="5"/>
       <c r="E62" s="5">
-        <v>202.52</v>
+        <v>192.38</v>
       </c>
       <c r="F62" s="5"/>
       <c r="G62" s="5" t="s">
@@ -6650,17 +6691,17 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="6">
-        <v>46283.875</v>
+        <v>46283.91666666666</v>
       </c>
       <c r="B63" s="5">
-        <v>600.04</v>
+        <v>552.27</v>
       </c>
       <c r="C63" s="5">
-        <v>449.81</v>
+        <v>406.3</v>
       </c>
       <c r="D63" s="5"/>
       <c r="E63" s="5">
-        <v>189.46</v>
+        <v>172</v>
       </c>
       <c r="F63" s="5"/>
       <c r="G63" s="5" t="s">
@@ -6669,17 +6710,17 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="6">
-        <v>46283.91666666666</v>
+        <v>46283.95833333334</v>
       </c>
       <c r="B64" s="5">
-        <v>589.96</v>
+        <v>542.21</v>
       </c>
       <c r="C64" s="5">
-        <v>449.59</v>
+        <v>406.09</v>
       </c>
       <c r="D64" s="5"/>
       <c r="E64" s="5">
-        <v>170.71</v>
+        <v>160.91</v>
       </c>
       <c r="F64" s="5"/>
       <c r="G64" s="5" t="s">
@@ -6688,17 +6729,17 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="6">
-        <v>46283.95833333334</v>
+        <v>46284</v>
       </c>
       <c r="B65" s="5">
-        <v>580.58</v>
+        <v>532.96</v>
       </c>
       <c r="C65" s="5">
-        <v>449.38</v>
+        <v>405.88</v>
       </c>
       <c r="D65" s="5"/>
       <c r="E65" s="5">
-        <v>159.7</v>
+        <v>150.53</v>
       </c>
       <c r="F65" s="5"/>
       <c r="G65" s="5" t="s">
@@ -6707,17 +6748,17 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="6">
-        <v>46284</v>
+        <v>46284.04166666666</v>
       </c>
       <c r="B66" s="5">
-        <v>571.84</v>
+        <v>522.17</v>
       </c>
       <c r="C66" s="5">
-        <v>449.16</v>
+        <v>405.74</v>
       </c>
       <c r="D66" s="5"/>
       <c r="E66" s="5">
-        <v>149.4</v>
+        <v>132.77</v>
       </c>
       <c r="F66" s="5"/>
       <c r="G66" s="5" t="s">
@@ -6726,17 +6767,17 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="6">
-        <v>46284.04166666666</v>
+        <v>46284.08333333334</v>
       </c>
       <c r="B67" s="5">
-        <v>561.89</v>
+        <v>513.05</v>
       </c>
       <c r="C67" s="5">
-        <v>449.02</v>
+        <v>405.64</v>
       </c>
       <c r="D67" s="5"/>
       <c r="E67" s="5">
-        <v>133.06</v>
+        <v>124.21</v>
       </c>
       <c r="F67" s="5"/>
       <c r="G67" s="5" t="s">
@@ -6745,17 +6786,17 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="6">
-        <v>46284.08333333334</v>
+        <v>46284.125</v>
       </c>
       <c r="B68" s="5">
-        <v>553.33</v>
+        <v>505.12</v>
       </c>
       <c r="C68" s="5">
-        <v>448.92</v>
+        <v>405.58</v>
       </c>
       <c r="D68" s="5"/>
       <c r="E68" s="5">
-        <v>124.48</v>
+        <v>116.19</v>
       </c>
       <c r="F68" s="5"/>
       <c r="G68" s="5" t="s">
@@ -6764,17 +6805,17 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="6">
-        <v>46284.125</v>
+        <v>46284.16666666666</v>
       </c>
       <c r="B69" s="5">
-        <v>545.8</v>
+        <v>498.07</v>
       </c>
       <c r="C69" s="5">
-        <v>448.84</v>
+        <v>405.53</v>
       </c>
       <c r="D69" s="5"/>
       <c r="E69" s="5">
-        <v>116.45</v>
+        <v>108.7</v>
       </c>
       <c r="F69" s="5"/>
       <c r="G69" s="5" t="s">
@@ -6783,17 +6824,17 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="6">
-        <v>46284.16666666666</v>
+        <v>46284.20833333334</v>
       </c>
       <c r="B70" s="5">
-        <v>539.04</v>
+        <v>491.7</v>
       </c>
       <c r="C70" s="5">
-        <v>448.79</v>
+        <v>405.49</v>
       </c>
       <c r="D70" s="5"/>
       <c r="E70" s="5">
-        <v>108.94</v>
+        <v>101.69</v>
       </c>
       <c r="F70" s="5"/>
       <c r="G70" s="5" t="s">
@@ -6802,17 +6843,17 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="6">
-        <v>46284.20833333334</v>
+        <v>46284.25</v>
       </c>
       <c r="B71" s="5">
-        <v>532.9</v>
+        <v>485.89</v>
       </c>
       <c r="C71" s="5">
-        <v>448.75</v>
+        <v>405.46</v>
       </c>
       <c r="D71" s="5"/>
       <c r="E71" s="5">
-        <v>101.92</v>
+        <v>95.13</v>
       </c>
       <c r="F71" s="5"/>
       <c r="G71" s="5" t="s">
@@ -6821,17 +6862,17 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="6">
-        <v>46284.25</v>
+        <v>46284.29166666666</v>
       </c>
       <c r="B72" s="5">
-        <v>527.26</v>
+        <v>480.54</v>
       </c>
       <c r="C72" s="5">
-        <v>448.71</v>
+        <v>405.44</v>
       </c>
       <c r="D72" s="5"/>
       <c r="E72" s="5">
-        <v>95.34</v>
+        <v>89</v>
       </c>
       <c r="F72" s="5"/>
       <c r="G72" s="5" t="s">
@@ -6840,17 +6881,17 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="6">
-        <v>46284.29166666666</v>
+        <v>46284.33333333334</v>
       </c>
       <c r="B73" s="5">
-        <v>522.0599999999999</v>
+        <v>475.58</v>
       </c>
       <c r="C73" s="5">
-        <v>448.68</v>
+        <v>405.41</v>
       </c>
       <c r="D73" s="5"/>
       <c r="E73" s="5">
-        <v>89.2</v>
+        <v>83.26000000000001</v>
       </c>
       <c r="F73" s="5"/>
       <c r="G73" s="5" t="s">
@@ -6859,17 +6900,17 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="6">
-        <v>46284.33333333334</v>
+        <v>46284.375</v>
       </c>
       <c r="B74" s="5">
-        <v>517.23</v>
+        <v>470.99</v>
       </c>
       <c r="C74" s="5">
-        <v>448.65</v>
+        <v>405.4</v>
       </c>
       <c r="D74" s="5"/>
       <c r="E74" s="5">
-        <v>83.44</v>
+        <v>77.89</v>
       </c>
       <c r="F74" s="5"/>
       <c r="G74" s="5" t="s">
@@ -6878,17 +6919,17 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="6">
-        <v>46284.375</v>
+        <v>46284.41666666666</v>
       </c>
       <c r="B75" s="5">
-        <v>512.74</v>
+        <v>466.71</v>
       </c>
       <c r="C75" s="5">
-        <v>448.63</v>
+        <v>405.38</v>
       </c>
       <c r="D75" s="5"/>
       <c r="E75" s="5">
-        <v>78.06</v>
+        <v>72.86</v>
       </c>
       <c r="F75" s="5"/>
       <c r="G75" s="5" t="s">
@@ -6897,17 +6938,17 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="6">
-        <v>46284.41666666666</v>
+        <v>46284.45833333334</v>
       </c>
       <c r="B76" s="5">
-        <v>508.56</v>
+        <v>462.71</v>
       </c>
       <c r="C76" s="5">
-        <v>448.61</v>
+        <v>405.36</v>
       </c>
       <c r="D76" s="5"/>
       <c r="E76" s="5">
-        <v>73.03</v>
+        <v>68.17</v>
       </c>
       <c r="F76" s="5"/>
       <c r="G76" s="5" t="s">
@@ -6916,17 +6957,17 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="6">
-        <v>46284.45833333334</v>
+        <v>46284.5</v>
       </c>
       <c r="B77" s="5">
-        <v>504.66</v>
+        <v>458.99</v>
       </c>
       <c r="C77" s="5">
-        <v>448.59</v>
+        <v>405.35</v>
       </c>
       <c r="D77" s="5"/>
       <c r="E77" s="5">
-        <v>68.31999999999999</v>
+        <v>63.77</v>
       </c>
       <c r="F77" s="5"/>
       <c r="G77" s="5" t="s">
@@ -6941,7 +6982,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.7109375" customWidth="1"/>
@@ -6968,10 +7009,10 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="6">
-        <v>46281.375</v>
+        <v>46281.625</v>
       </c>
       <c r="B2" s="5">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>48</v>
@@ -6983,10 +7024,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="6">
-        <v>46281.5</v>
+        <v>46281.75</v>
       </c>
       <c r="B3" s="5">
-        <v>4</v>
+        <v>4.67</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>48</v>
@@ -6998,13 +7039,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="6">
-        <v>46281.625</v>
+        <v>46281.875</v>
       </c>
       <c r="B4" s="5">
-        <v>4.67</v>
+        <v>5.67</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D4" s="5"/>
       <c r="E4" s="5" t="s">
@@ -7013,7 +7054,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="6">
-        <v>46281.75</v>
+        <v>46282</v>
       </c>
       <c r="B5" s="5">
         <v>5.67</v>
@@ -7028,7 +7069,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="6">
-        <v>46281.875</v>
+        <v>46282.125</v>
       </c>
       <c r="B6" s="5">
         <v>5.67</v>
@@ -7043,7 +7084,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="6">
-        <v>46282</v>
+        <v>46282.25</v>
       </c>
       <c r="B7" s="5">
         <v>5.67</v>
@@ -7058,7 +7099,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="6">
-        <v>46282.125</v>
+        <v>46282.375</v>
       </c>
       <c r="B8" s="5">
         <v>5.67</v>
@@ -7073,7 +7114,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="6">
-        <v>46282.25</v>
+        <v>46282.5</v>
       </c>
       <c r="B9" s="5">
         <v>5.67</v>
@@ -7088,7 +7129,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="6">
-        <v>46282.375</v>
+        <v>46282.625</v>
       </c>
       <c r="B10" s="5">
         <v>5.67</v>
@@ -7103,7 +7144,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="6">
-        <v>46282.5</v>
+        <v>46282.75</v>
       </c>
       <c r="B11" s="5">
         <v>5.67</v>
@@ -7118,7 +7159,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="6">
-        <v>46282.625</v>
+        <v>46282.875</v>
       </c>
       <c r="B12" s="5">
         <v>5.67</v>
@@ -7133,7 +7174,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="6">
-        <v>46282.75</v>
+        <v>46283</v>
       </c>
       <c r="B13" s="5">
         <v>5.67</v>
@@ -7148,13 +7189,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="6">
-        <v>46282.875</v>
+        <v>46283.125</v>
       </c>
       <c r="B14" s="5">
-        <v>5.67</v>
+        <v>4.67</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="5" t="s">
@@ -7163,13 +7204,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="6">
-        <v>46283</v>
+        <v>46283.25</v>
       </c>
       <c r="B15" s="5">
-        <v>5.67</v>
+        <v>4.67</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D15" s="5"/>
       <c r="E15" s="5" t="s">
@@ -7178,7 +7219,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="6">
-        <v>46283.125</v>
+        <v>46283.375</v>
       </c>
       <c r="B16" s="5">
         <v>4.67</v>
@@ -7193,7 +7234,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="6">
-        <v>46283.25</v>
+        <v>46283.5</v>
       </c>
       <c r="B17" s="5">
         <v>4.67</v>
@@ -7208,13 +7249,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="6">
-        <v>46283.375</v>
+        <v>46283.625</v>
       </c>
       <c r="B18" s="5">
-        <v>4.67</v>
+        <v>5.67</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D18" s="5"/>
       <c r="E18" s="5" t="s">
@@ -7223,13 +7264,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="6">
-        <v>46283.5</v>
+        <v>46283.75</v>
       </c>
       <c r="B19" s="5">
-        <v>4.67</v>
+        <v>5.67</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="5" t="s">
@@ -7238,13 +7279,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="6">
-        <v>46283.625</v>
+        <v>46283.875</v>
       </c>
       <c r="B20" s="5">
-        <v>4.67</v>
+        <v>5.67</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="5" t="s">
@@ -7253,13 +7294,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="6">
-        <v>46283.75</v>
+        <v>46284</v>
       </c>
       <c r="B21" s="5">
-        <v>4.67</v>
+        <v>5.67</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5" t="s">
@@ -7268,7 +7309,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="6">
-        <v>46283.875</v>
+        <v>46284.125</v>
       </c>
       <c r="B22" s="5">
         <v>4.67</v>
@@ -7283,7 +7324,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="6">
-        <v>46284</v>
+        <v>46284.25</v>
       </c>
       <c r="B23" s="5">
         <v>4.67</v>
@@ -7298,7 +7339,7 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="6">
-        <v>46284.125</v>
+        <v>46284.375</v>
       </c>
       <c r="B24" s="5">
         <v>4.67</v>
@@ -7313,7 +7354,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="6">
-        <v>46284.25</v>
+        <v>46284.5</v>
       </c>
       <c r="B25" s="5">
         <v>4.67</v>
@@ -7328,7 +7369,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="6">
-        <v>46284.375</v>
+        <v>46284.625</v>
       </c>
       <c r="B26" s="5">
         <v>4.67</v>
@@ -7343,7 +7384,7 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="6">
-        <v>46284.5</v>
+        <v>46284.75</v>
       </c>
       <c r="B27" s="5">
         <v>4.67</v>
@@ -7358,7 +7399,7 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="6">
-        <v>46284.625</v>
+        <v>46284.875</v>
       </c>
       <c r="B28" s="5">
         <v>4.67</v>
@@ -7373,7 +7414,7 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="6">
-        <v>46284.75</v>
+        <v>46285</v>
       </c>
       <c r="B29" s="5">
         <v>4.67</v>
@@ -7388,7 +7429,7 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="6">
-        <v>46284.875</v>
+        <v>46285.125</v>
       </c>
       <c r="B30" s="5">
         <v>4.67</v>
@@ -7403,10 +7444,10 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="6">
-        <v>46285</v>
+        <v>46285.25</v>
       </c>
       <c r="B31" s="5">
-        <v>4.67</v>
+        <v>4.33</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>48</v>
@@ -7418,10 +7459,10 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="6">
-        <v>46285.125</v>
+        <v>46285.375</v>
       </c>
       <c r="B32" s="5">
-        <v>4.67</v>
+        <v>4.33</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>48</v>
@@ -7433,10 +7474,10 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="6">
-        <v>46285.25</v>
+        <v>46285.5</v>
       </c>
       <c r="B33" s="5">
-        <v>4.67</v>
+        <v>4.33</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>48</v>
@@ -7448,10 +7489,10 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="6">
-        <v>46285.375</v>
+        <v>46285.625</v>
       </c>
       <c r="B34" s="5">
-        <v>4.67</v>
+        <v>4.33</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>48</v>
@@ -7463,10 +7504,10 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="6">
-        <v>46285.5</v>
+        <v>46285.75</v>
       </c>
       <c r="B35" s="5">
-        <v>4.67</v>
+        <v>4.33</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>48</v>
@@ -7478,10 +7519,10 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="6">
-        <v>46285.625</v>
+        <v>46285.875</v>
       </c>
       <c r="B36" s="5">
-        <v>4.67</v>
+        <v>4.33</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>48</v>
@@ -7493,10 +7534,10 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="6">
-        <v>46285.75</v>
+        <v>46286</v>
       </c>
       <c r="B37" s="5">
-        <v>4.67</v>
+        <v>4.33</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>48</v>
@@ -7508,10 +7549,10 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="6">
-        <v>46285.875</v>
+        <v>46286.125</v>
       </c>
       <c r="B38" s="5">
-        <v>4.67</v>
+        <v>4.33</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>48</v>
@@ -7523,10 +7564,10 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="6">
-        <v>46286</v>
+        <v>46286.25</v>
       </c>
       <c r="B39" s="5">
-        <v>4.67</v>
+        <v>4.33</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>48</v>
@@ -7538,16 +7579,31 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="6">
-        <v>46286.125</v>
+        <v>46286.375</v>
       </c>
       <c r="B40" s="5">
-        <v>4.67</v>
+        <v>4.33</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>48</v>
       </c>
       <c r="D40" s="5"/>
       <c r="E40" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6">
+        <v>46286.5</v>
+      </c>
+      <c r="B41" s="5">
+        <v>4.33</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5" t="s">
         <v>49</v>
       </c>
     </row>
@@ -7559,7 +7615,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="9" width="16.7109375" customWidth="1"/>
@@ -7613,19 +7669,19 @@
         <v>24</v>
       </c>
       <c r="D4" s="5">
-        <v>119.917</v>
+        <v>88.89700000000001</v>
       </c>
       <c r="E4" s="5">
-        <v>138.412</v>
+        <v>104.957</v>
       </c>
       <c r="F4" s="5">
-        <v>118.443</v>
+        <v>82.65300000000001</v>
       </c>
       <c r="G4" s="5">
-        <v>8.300000000000001</v>
+        <v>41.7</v>
       </c>
       <c r="H4" s="5">
-        <v>62.5</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -7636,22 +7692,22 @@
         <v>62</v>
       </c>
       <c r="C5" s="5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5" s="5">
-        <v>116.147</v>
+        <v>83.06</v>
       </c>
       <c r="E5" s="5">
-        <v>135.713</v>
+        <v>100.912</v>
       </c>
       <c r="F5" s="5">
-        <v>114.733</v>
+        <v>75.29300000000001</v>
       </c>
       <c r="G5" s="5">
-        <v>12</v>
+        <v>46.2</v>
       </c>
       <c r="H5" s="5">
-        <v>64</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -7662,22 +7718,22 @@
         <v>63</v>
       </c>
       <c r="C6" s="5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6" s="5">
-        <v>116.147</v>
+        <v>83.06</v>
       </c>
       <c r="E6" s="5">
-        <v>135.713</v>
+        <v>100.912</v>
       </c>
       <c r="F6" s="5">
-        <v>114.733</v>
+        <v>75.29300000000001</v>
       </c>
       <c r="G6" s="5">
-        <v>12</v>
+        <v>46.2</v>
       </c>
       <c r="H6" s="5">
-        <v>64</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -7820,16 +7876,16 @@
         <v>46280.45833333334</v>
       </c>
       <c r="B19" s="5">
-        <v>524.8200000000001</v>
+        <v>526.49</v>
       </c>
       <c r="C19" s="5">
-        <v>550.5</v>
+        <v>509.02</v>
       </c>
       <c r="D19" s="5">
-        <v>439.47</v>
+        <v>396.15</v>
       </c>
       <c r="E19" s="5">
-        <v>25.67999999999995</v>
+        <v>-17.47000000000003</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -7837,16 +7893,16 @@
         <v>46280.5</v>
       </c>
       <c r="B20" s="5">
-        <v>566.89</v>
+        <v>566.35</v>
       </c>
       <c r="C20" s="5">
-        <v>599.62</v>
+        <v>557.79</v>
       </c>
       <c r="D20" s="5">
-        <v>459.61</v>
+        <v>417.12</v>
       </c>
       <c r="E20" s="5">
-        <v>32.73000000000002</v>
+        <v>-8.560000000000059</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -7854,16 +7910,16 @@
         <v>46280.54166666666</v>
       </c>
       <c r="B21" s="5">
-        <v>558.27</v>
+        <v>558.29</v>
       </c>
       <c r="C21" s="5">
-        <v>649.49</v>
+        <v>604.5700000000001</v>
       </c>
       <c r="D21" s="5">
-        <v>471.31</v>
+        <v>425.98</v>
       </c>
       <c r="E21" s="5">
-        <v>91.22000000000003</v>
+        <v>46.28000000000009</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -7871,16 +7927,16 @@
         <v>46280.58333333334</v>
       </c>
       <c r="B22" s="5">
-        <v>482.62</v>
+        <v>478.6</v>
       </c>
       <c r="C22" s="5">
-        <v>663.3</v>
+        <v>621.7</v>
       </c>
       <c r="D22" s="5">
-        <v>447.3</v>
+        <v>405.78</v>
       </c>
       <c r="E22" s="5">
-        <v>180.6799999999999</v>
+        <v>143.1</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -7888,16 +7944,16 @@
         <v>46280.625</v>
       </c>
       <c r="B23" s="5">
-        <v>444.01</v>
+        <v>445.28</v>
       </c>
       <c r="C23" s="5">
-        <v>672.86</v>
+        <v>627.91</v>
       </c>
       <c r="D23" s="5">
-        <v>423.27</v>
+        <v>379.13</v>
       </c>
       <c r="E23" s="5">
-        <v>228.85</v>
+        <v>182.63</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -7905,16 +7961,16 @@
         <v>46280.66666666666</v>
       </c>
       <c r="B24" s="5">
-        <v>453.8</v>
+        <v>452.23</v>
       </c>
       <c r="C24" s="5">
-        <v>691.66</v>
+        <v>645.78</v>
       </c>
       <c r="D24" s="5">
-        <v>416.84</v>
+        <v>372.67</v>
       </c>
       <c r="E24" s="5">
-        <v>237.86</v>
+        <v>193.55</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -7922,16 +7978,16 @@
         <v>46280.70833333334</v>
       </c>
       <c r="B25" s="5">
-        <v>433.23</v>
+        <v>437.41</v>
       </c>
       <c r="C25" s="5">
-        <v>696.77</v>
+        <v>649.2</v>
       </c>
       <c r="D25" s="5">
-        <v>413.89</v>
+        <v>369.14</v>
       </c>
       <c r="E25" s="5">
-        <v>263.54</v>
+        <v>211.79</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -7939,16 +7995,16 @@
         <v>46280.75</v>
       </c>
       <c r="B26" s="5">
-        <v>454.65</v>
+        <v>457.95</v>
       </c>
       <c r="C26" s="5">
-        <v>690.3099999999999</v>
+        <v>639.42</v>
       </c>
       <c r="D26" s="5">
-        <v>403.49</v>
+        <v>356.24</v>
       </c>
       <c r="E26" s="5">
-        <v>235.66</v>
+        <v>181.47</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -7956,16 +8012,16 @@
         <v>46280.79166666666</v>
       </c>
       <c r="B27" s="5">
-        <v>689.4</v>
+        <v>691.9</v>
       </c>
       <c r="C27" s="5">
-        <v>671.72</v>
+        <v>616.97</v>
       </c>
       <c r="D27" s="5">
-        <v>387.18</v>
+        <v>336.5</v>
       </c>
       <c r="E27" s="5">
-        <v>-17.67999999999995</v>
+        <v>-74.92999999999995</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -7973,16 +8029,16 @@
         <v>46280.83333333334</v>
       </c>
       <c r="B28" s="5">
-        <v>545.6799999999999</v>
+        <v>528.5</v>
       </c>
       <c r="C28" s="5">
-        <v>670.09</v>
+        <v>616.55</v>
       </c>
       <c r="D28" s="5">
-        <v>399.67</v>
+        <v>349.93</v>
       </c>
       <c r="E28" s="5">
-        <v>124.4100000000001</v>
+        <v>88.04999999999995</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -7990,16 +8046,16 @@
         <v>46280.875</v>
       </c>
       <c r="B29" s="5">
-        <v>503.06</v>
+        <v>508.07</v>
       </c>
       <c r="C29" s="5">
-        <v>665.13</v>
+        <v>616.47</v>
       </c>
       <c r="D29" s="5">
-        <v>411.54</v>
+        <v>366.09</v>
       </c>
       <c r="E29" s="5">
-        <v>162.07</v>
+        <v>108.4</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -8007,16 +8063,16 @@
         <v>46280.91666666666</v>
       </c>
       <c r="B30" s="5">
-        <v>447.12</v>
+        <v>450.43</v>
       </c>
       <c r="C30" s="5">
-        <v>649.42</v>
+        <v>603.0700000000001</v>
       </c>
       <c r="D30" s="5">
-        <v>411.16</v>
+        <v>367.22</v>
       </c>
       <c r="E30" s="5">
-        <v>202.3</v>
+        <v>152.64</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -8024,16 +8080,16 @@
         <v>46280.95833333334</v>
       </c>
       <c r="B31" s="5">
-        <v>451.19</v>
+        <v>453.25</v>
       </c>
       <c r="C31" s="5">
-        <v>613.26</v>
+        <v>566.05</v>
       </c>
       <c r="D31" s="5">
-        <v>388.72</v>
+        <v>342.82</v>
       </c>
       <c r="E31" s="5">
-        <v>162.07</v>
+        <v>112.8</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -8044,13 +8100,13 @@
         <v>507.31</v>
       </c>
       <c r="C32" s="5">
-        <v>598.72</v>
+        <v>554.72</v>
       </c>
       <c r="D32" s="5">
-        <v>386.19</v>
+        <v>342.02</v>
       </c>
       <c r="E32" s="5">
-        <v>91.41000000000003</v>
+        <v>47.41000000000003</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -8058,16 +8114,16 @@
         <v>46281.04166666666</v>
       </c>
       <c r="B33" s="5">
-        <v>520.5</v>
+        <v>521.49</v>
       </c>
       <c r="C33" s="5">
-        <v>604.6</v>
+        <v>566.49</v>
       </c>
       <c r="D33" s="5">
-        <v>402.25</v>
+        <v>362.01</v>
       </c>
       <c r="E33" s="5">
-        <v>84.10000000000002</v>
+        <v>45</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -8075,16 +8131,16 @@
         <v>46281.08333333334</v>
       </c>
       <c r="B34" s="5">
-        <v>525.24</v>
+        <v>525.3</v>
       </c>
       <c r="C34" s="5">
-        <v>611.49</v>
+        <v>575.37</v>
       </c>
       <c r="D34" s="5">
-        <v>417.45</v>
+        <v>376.71</v>
       </c>
       <c r="E34" s="5">
-        <v>86.25</v>
+        <v>50.07000000000005</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -8092,16 +8148,16 @@
         <v>46281.125</v>
       </c>
       <c r="B35" s="5">
-        <v>529.24</v>
+        <v>530.12</v>
       </c>
       <c r="C35" s="5">
-        <v>613.23</v>
+        <v>576.76</v>
       </c>
       <c r="D35" s="5">
-        <v>425.67</v>
+        <v>381.61</v>
       </c>
       <c r="E35" s="5">
-        <v>83.99000000000001</v>
+        <v>46.63999999999999</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -8109,16 +8165,16 @@
         <v>46281.16666666666</v>
       </c>
       <c r="B36" s="5">
-        <v>537.63</v>
+        <v>538.4</v>
       </c>
       <c r="C36" s="5">
-        <v>611.48</v>
+        <v>578.2</v>
       </c>
       <c r="D36" s="5">
-        <v>428.75</v>
+        <v>384.52</v>
       </c>
       <c r="E36" s="5">
-        <v>73.85000000000002</v>
+        <v>39.80000000000007</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -8129,13 +8185,13 @@
         <v>536.5</v>
       </c>
       <c r="C37" s="5">
-        <v>611.2</v>
+        <v>581.72</v>
       </c>
       <c r="D37" s="5">
-        <v>431.99</v>
+        <v>388</v>
       </c>
       <c r="E37" s="5">
-        <v>74.70000000000005</v>
+        <v>45.22000000000003</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -8146,13 +8202,13 @@
         <v>535.3</v>
       </c>
       <c r="C38" s="5">
-        <v>615.59</v>
+        <v>589.0700000000001</v>
       </c>
       <c r="D38" s="5">
-        <v>439.08</v>
+        <v>394.59</v>
       </c>
       <c r="E38" s="5">
-        <v>80.29000000000008</v>
+        <v>53.7700000000001</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -8160,16 +8216,16 @@
         <v>46281.29166666666</v>
       </c>
       <c r="B39" s="5">
-        <v>524.3</v>
+        <v>523.7</v>
       </c>
       <c r="C39" s="5">
-        <v>616.17</v>
+        <v>592.83</v>
       </c>
       <c r="D39" s="5">
-        <v>442.09</v>
+        <v>397.7</v>
       </c>
       <c r="E39" s="5">
-        <v>91.87</v>
+        <v>69.13</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -8177,16 +8233,16 @@
         <v>46281.33333333334</v>
       </c>
       <c r="B40" s="5">
-        <v>535.67</v>
+        <v>533.33</v>
       </c>
       <c r="C40" s="5">
-        <v>613.53</v>
+        <v>592.15</v>
       </c>
       <c r="D40" s="5">
-        <v>442.69</v>
+        <v>398.17</v>
       </c>
       <c r="E40" s="5">
-        <v>77.86000000000001</v>
+        <v>58.81999999999994</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -8194,16 +8250,16 @@
         <v>46281.375</v>
       </c>
       <c r="B41" s="5">
-        <v>543.8</v>
+        <v>542.7</v>
       </c>
       <c r="C41" s="5">
-        <v>611.4</v>
+        <v>591.4</v>
       </c>
       <c r="D41" s="5">
-        <v>444.41</v>
+        <v>400.06</v>
       </c>
       <c r="E41" s="5">
-        <v>67.60000000000002</v>
+        <v>48.69999999999993</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -8211,16 +8267,16 @@
         <v>46281.41666666666</v>
       </c>
       <c r="B42" s="5">
-        <v>541.4</v>
+        <v>542.28</v>
       </c>
       <c r="C42" s="5">
-        <v>608.28</v>
+        <v>589.14</v>
       </c>
       <c r="D42" s="5">
-        <v>444.65</v>
+        <v>400.2</v>
       </c>
       <c r="E42" s="5">
-        <v>66.88</v>
+        <v>46.86000000000001</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -8228,16 +8284,33 @@
         <v>46281.45833333334</v>
       </c>
       <c r="B43" s="5">
-        <v>541.4</v>
+        <v>538.6</v>
       </c>
       <c r="C43" s="5">
-        <v>601.53</v>
+        <v>582.91</v>
       </c>
       <c r="D43" s="5">
-        <v>440.91</v>
+        <v>396.52</v>
       </c>
       <c r="E43" s="5">
-        <v>60.13</v>
+        <v>44.30999999999995</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6">
+        <v>46281.5</v>
+      </c>
+      <c r="B44" s="5">
+        <v>537.65</v>
+      </c>
+      <c r="C44" s="5">
+        <v>579.8</v>
+      </c>
+      <c r="D44" s="5">
+        <v>396.07</v>
+      </c>
+      <c r="E44" s="5">
+        <v>42.14999999999998</v>
       </c>
     </row>
   </sheetData>
@@ -8284,19 +8357,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="6">
-        <v>46281.45833333334</v>
+        <v>46281.5</v>
       </c>
       <c r="B2" s="5">
-        <v>2.28</v>
+        <v>1.94</v>
       </c>
       <c r="C2" s="5">
-        <v>-12.52</v>
+        <v>-13.07</v>
       </c>
       <c r="D2" s="5">
-        <v>15.48</v>
+        <v>15.12</v>
       </c>
       <c r="E2" s="5">
-        <v>58</v>
+        <v>60.7</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>82</v>
@@ -8307,19 +8380,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="6">
-        <v>46281.58333333334</v>
+        <v>46281.625</v>
       </c>
       <c r="B3" s="5">
-        <v>2.09</v>
+        <v>1.79</v>
       </c>
       <c r="C3" s="5">
-        <v>-12.41</v>
+        <v>-12.36</v>
       </c>
       <c r="D3" s="5">
-        <v>15.14</v>
+        <v>14.25</v>
       </c>
       <c r="E3" s="5">
-        <v>58.1</v>
+        <v>58.6</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>82</v>
@@ -8330,298 +8403,298 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="6">
-        <v>46281.70833333334</v>
+        <v>46281.75</v>
       </c>
       <c r="B4" s="5">
-        <v>1.93</v>
+        <v>1.64</v>
       </c>
       <c r="C4" s="5">
-        <v>-10.76</v>
+        <v>-11.33</v>
       </c>
       <c r="D4" s="5">
-        <v>13.28</v>
+        <v>13.06</v>
       </c>
       <c r="E4" s="5">
-        <v>52.4</v>
+        <v>55.2</v>
       </c>
       <c r="F4" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G4" s="5" t="s">
         <v>84</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="6">
-        <v>46281.83333333334</v>
+        <v>46281.875</v>
       </c>
       <c r="B5" s="5">
-        <v>1.77</v>
+        <v>1.51</v>
       </c>
       <c r="C5" s="5">
-        <v>-12.17</v>
+        <v>-12.86</v>
       </c>
       <c r="D5" s="5">
-        <v>14.5</v>
+        <v>14.45</v>
       </c>
       <c r="E5" s="5">
-        <v>58.3</v>
+        <v>61.6</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>82</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="6">
-        <v>46281.95833333334</v>
+        <v>46282</v>
       </c>
       <c r="B6" s="5">
-        <v>1.63</v>
+        <v>1.39</v>
       </c>
       <c r="C6" s="5">
-        <v>-12.71</v>
+        <v>-12.82</v>
       </c>
       <c r="D6" s="5">
-        <v>14.85</v>
+        <v>14.28</v>
       </c>
       <c r="E6" s="5">
-        <v>60.9</v>
+        <v>61.9</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>82</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="6">
-        <v>46282.08333333334</v>
+        <v>46282.125</v>
       </c>
       <c r="B7" s="5">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="C7" s="5">
-        <v>-11.92</v>
+        <v>-12.87</v>
       </c>
       <c r="D7" s="5">
-        <v>13.9</v>
+        <v>14.22</v>
       </c>
       <c r="E7" s="5">
-        <v>58.5</v>
+        <v>62.6</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>82</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="6">
-        <v>46282.20833333334</v>
+        <v>46282.25</v>
       </c>
       <c r="B8" s="5">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="C8" s="5">
-        <v>-13.42</v>
+        <v>-13.83</v>
       </c>
       <c r="D8" s="5">
-        <v>15.25</v>
+        <v>15.07</v>
       </c>
       <c r="E8" s="5">
-        <v>64.7</v>
+        <v>66.7</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>82</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="6">
-        <v>46282.33333333334</v>
+        <v>46282.375</v>
       </c>
       <c r="B9" s="5">
-        <v>1.27</v>
+        <v>1.08</v>
       </c>
       <c r="C9" s="5">
-        <v>-13.4</v>
+        <v>-13.9</v>
       </c>
       <c r="D9" s="5">
-        <v>15.1</v>
+        <v>15.04</v>
       </c>
       <c r="E9" s="5">
-        <v>65.09999999999999</v>
+        <v>67.5</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>82</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="6">
-        <v>46282.45833333334</v>
+        <v>46282.5</v>
       </c>
       <c r="B10" s="5">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="C10" s="5">
-        <v>-13.63</v>
+        <v>-14.01</v>
       </c>
       <c r="D10" s="5">
-        <v>15.2</v>
+        <v>15.06</v>
       </c>
       <c r="E10" s="5">
-        <v>66.5</v>
+        <v>68.3</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>82</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="6">
-        <v>46282.58333333334</v>
+        <v>46282.625</v>
       </c>
       <c r="B11" s="5">
-        <v>1.08</v>
+        <v>0.92</v>
       </c>
       <c r="C11" s="5">
-        <v>-13.43</v>
+        <v>-13.23</v>
       </c>
       <c r="D11" s="5">
-        <v>14.88</v>
+        <v>14.19</v>
       </c>
       <c r="E11" s="5">
-        <v>66.09999999999999</v>
+        <v>65.8</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>82</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="6">
-        <v>46282.70833333334</v>
+        <v>46282.75</v>
       </c>
       <c r="B12" s="5">
-        <v>0.99</v>
+        <v>0.84</v>
       </c>
       <c r="C12" s="5">
-        <v>-11.7</v>
+        <v>-11.14</v>
       </c>
       <c r="D12" s="5">
-        <v>13.04</v>
+        <v>12.03</v>
       </c>
       <c r="E12" s="5">
-        <v>60</v>
+        <v>58.2</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>82</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="6">
-        <v>46282.83333333334</v>
+        <v>46282.875</v>
       </c>
       <c r="B13" s="5">
-        <v>0.91</v>
+        <v>0.78</v>
       </c>
       <c r="C13" s="5">
-        <v>-9.26</v>
+        <v>-8.68</v>
       </c>
       <c r="D13" s="5">
-        <v>10.5</v>
+        <v>9.5</v>
       </c>
       <c r="E13" s="5">
-        <v>51.1</v>
+        <v>49.2</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="6">
-        <v>46282.95833333334</v>
+        <v>46283</v>
       </c>
       <c r="B14" s="5">
-        <v>0.84</v>
+        <v>0.71</v>
       </c>
       <c r="C14" s="5">
-        <v>-7.04</v>
+        <v>-6.67</v>
       </c>
       <c r="D14" s="5">
-        <v>8.19</v>
+        <v>7.41</v>
       </c>
       <c r="E14" s="5">
-        <v>43.1</v>
+        <v>41.9</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="6">
-        <v>46283.08333333334</v>
+        <v>46283.125</v>
       </c>
       <c r="B15" s="5">
-        <v>0.77</v>
+        <v>0.66</v>
       </c>
       <c r="C15" s="5">
-        <v>-5.54</v>
+        <v>-5.63</v>
       </c>
       <c r="D15" s="5">
-        <v>6.6</v>
+        <v>6.32</v>
       </c>
       <c r="E15" s="5">
-        <v>37.7</v>
+        <v>38.2</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="6">
-        <v>46283.20833333334</v>
+        <v>46283.25</v>
       </c>
       <c r="B16" s="5">
-        <v>0.71</v>
+        <v>0.6</v>
       </c>
       <c r="C16" s="5">
-        <v>-6.35</v>
+        <v>-7.14</v>
       </c>
       <c r="D16" s="5">
-        <v>7.34</v>
+        <v>7.77</v>
       </c>
       <c r="E16" s="5">
-        <v>41.1</v>
+        <v>44.3</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>88</v>
@@ -8629,22 +8702,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="6">
-        <v>46283.33333333334</v>
+        <v>46283.375</v>
       </c>
       <c r="B17" s="5">
-        <v>0.65</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="C17" s="5">
-        <v>-8.35</v>
+        <v>-9.33</v>
       </c>
       <c r="D17" s="5">
-        <v>9.27</v>
+        <v>9.91</v>
       </c>
       <c r="E17" s="5">
-        <v>49</v>
+        <v>52.9</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G17" s="5" t="s">
         <v>88</v>
@@ -8652,19 +8725,19 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="6">
-        <v>46283.45833333334</v>
+        <v>46283.5</v>
       </c>
       <c r="B18" s="5">
-        <v>0.6</v>
+        <v>0.51</v>
       </c>
       <c r="C18" s="5">
-        <v>-10.79</v>
+        <v>-11.78</v>
       </c>
       <c r="D18" s="5">
-        <v>11.65</v>
+        <v>12.31</v>
       </c>
       <c r="E18" s="5">
-        <v>58.6</v>
+        <v>62.4</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>82</v>
@@ -8675,19 +8748,19 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="6">
-        <v>46283.58333333334</v>
+        <v>46283.625</v>
       </c>
       <c r="B19" s="5">
-        <v>0.55</v>
+        <v>0.47</v>
       </c>
       <c r="C19" s="5">
-        <v>-12.94</v>
+        <v>-13.61</v>
       </c>
       <c r="D19" s="5">
-        <v>13.74</v>
+        <v>14.09</v>
       </c>
       <c r="E19" s="5">
-        <v>67</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>82</v>
@@ -8698,19 +8771,19 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="6">
-        <v>46283.70833333334</v>
+        <v>46283.75</v>
       </c>
       <c r="B20" s="5">
-        <v>0.51</v>
+        <v>0.43</v>
       </c>
       <c r="C20" s="5">
-        <v>-13.89</v>
+        <v>-14.01</v>
       </c>
       <c r="D20" s="5">
-        <v>14.63</v>
+        <v>14.46</v>
       </c>
       <c r="E20" s="5">
-        <v>70.90000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>82</v>
@@ -8721,19 +8794,19 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="6">
-        <v>46283.83333333334</v>
+        <v>46283.875</v>
       </c>
       <c r="B21" s="5">
-        <v>0.47</v>
+        <v>0.4</v>
       </c>
       <c r="C21" s="5">
-        <v>-13.19</v>
+        <v>-12.81</v>
       </c>
       <c r="D21" s="5">
-        <v>13.88</v>
+        <v>13.22</v>
       </c>
       <c r="E21" s="5">
-        <v>68.5</v>
+        <v>67</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>82</v>
@@ -8744,19 +8817,19 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="6">
-        <v>46283.95833333334</v>
+        <v>46284</v>
       </c>
       <c r="B22" s="5">
-        <v>0.46</v>
+        <v>0.39</v>
       </c>
       <c r="C22" s="5">
-        <v>-11.2</v>
+        <v>-10.58</v>
       </c>
       <c r="D22" s="5">
-        <v>11.87</v>
+        <v>10.98</v>
       </c>
       <c r="E22" s="5">
-        <v>61</v>
+        <v>58.5</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>82</v>
@@ -8767,22 +8840,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="6">
-        <v>46284.08333333334</v>
+        <v>46284.125</v>
       </c>
       <c r="B23" s="5">
-        <v>0.46</v>
+        <v>0.39</v>
       </c>
       <c r="C23" s="5">
-        <v>-8.789999999999999</v>
+        <v>-8.23</v>
       </c>
       <c r="D23" s="5">
-        <v>9.470000000000001</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="E23" s="5">
-        <v>51.8</v>
+        <v>49.6</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G23" s="5" t="s">
         <v>88</v>
@@ -8790,22 +8863,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="6">
-        <v>46284.20833333334</v>
+        <v>46284.25</v>
       </c>
       <c r="B24" s="5">
-        <v>0.46</v>
+        <v>0.39</v>
       </c>
       <c r="C24" s="5">
-        <v>-6.78</v>
+        <v>-6.45</v>
       </c>
       <c r="D24" s="5">
-        <v>7.46</v>
+        <v>6.85</v>
       </c>
       <c r="E24" s="5">
-        <v>44.2</v>
+        <v>42.9</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G24" s="5" t="s">
         <v>88</v>
@@ -8813,22 +8886,22 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="6">
-        <v>46284.33333333334</v>
+        <v>46284.375</v>
       </c>
       <c r="B25" s="5">
-        <v>0.46</v>
+        <v>0.39</v>
       </c>
       <c r="C25" s="5">
-        <v>-5.49</v>
+        <v>-5.4</v>
       </c>
       <c r="D25" s="5">
-        <v>6.17</v>
+        <v>5.8</v>
       </c>
       <c r="E25" s="5">
-        <v>39.3</v>
+        <v>38.9</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G25" s="5" t="s">
         <v>88</v>
@@ -8836,22 +8909,22 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="6">
-        <v>46284.45833333334</v>
+        <v>46284.5</v>
       </c>
       <c r="B26" s="5">
-        <v>0.46</v>
+        <v>0.39</v>
       </c>
       <c r="C26" s="5">
-        <v>-5.04</v>
+        <v>-4.97</v>
       </c>
       <c r="D26" s="5">
-        <v>5.51</v>
+        <v>5.3</v>
       </c>
       <c r="E26" s="5">
-        <v>36.8</v>
+        <v>37</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G26" s="5" t="s">
         <v>88</v>
@@ -8947,7 +9020,7 @@
         <v>116.8</v>
       </c>
       <c r="J2" s="5">
-        <v>97.86</v>
+        <v>97.65000000000001</v>
       </c>
       <c r="K2" s="5">
         <v>-34</v>
@@ -8991,7 +9064,7 @@
         <v>68</v>
       </c>
       <c r="J3" s="5">
-        <v>102.25</v>
+        <v>101.6</v>
       </c>
       <c r="K3" s="5">
         <v>-60</v>
@@ -9035,7 +9108,7 @@
         <v>66.5</v>
       </c>
       <c r="J4" s="5">
-        <v>102.38</v>
+        <v>101.72</v>
       </c>
       <c r="K4" s="5">
         <v>-38</v>
@@ -9079,7 +9152,7 @@
         <v>352</v>
       </c>
       <c r="J5" s="5">
-        <v>92.13</v>
+        <v>106.74</v>
       </c>
       <c r="K5" s="5">
         <v>-18</v>
@@ -9123,7 +9196,7 @@
         <v>88</v>
       </c>
       <c r="J6" s="5">
-        <v>100.45</v>
+        <v>99.98</v>
       </c>
       <c r="K6" s="5">
         <v>-18</v>
@@ -9167,7 +9240,7 @@
         <v>71.2</v>
       </c>
       <c r="J7" s="5">
-        <v>101.96</v>
+        <v>101.33</v>
       </c>
       <c r="K7" s="5">
         <v>0</v>
@@ -9211,7 +9284,7 @@
         <v>72.8</v>
       </c>
       <c r="J8" s="5">
-        <v>101.82</v>
+        <v>101.21</v>
       </c>
       <c r="K8" s="5">
         <v>65</v>
@@ -9255,7 +9328,7 @@
         <v>91.2</v>
       </c>
       <c r="J9" s="5">
-        <v>100.16</v>
+        <v>99.70999999999999</v>
       </c>
       <c r="K9" s="5">
         <v>35</v>
@@ -9299,7 +9372,7 @@
         <v>193.8</v>
       </c>
       <c r="J10" s="5">
-        <v>90.93000000000001</v>
+        <v>91.42</v>
       </c>
       <c r="K10" s="5">
         <v>159</v>
@@ -9343,7 +9416,7 @@
         <v>510</v>
       </c>
       <c r="J11" s="5">
-        <v>214.69</v>
+        <v>215.17</v>
       </c>
       <c r="K11" s="5">
         <v>0</v>
@@ -9387,7 +9460,7 @@
         <v>138.5</v>
       </c>
       <c r="J12" s="5">
-        <v>95.90000000000001</v>
+        <v>95.89</v>
       </c>
       <c r="K12" s="5">
         <v>122</v>
@@ -9431,7 +9504,7 @@
         <v>282</v>
       </c>
       <c r="J13" s="5">
-        <v>95.28</v>
+        <v>109.57</v>
       </c>
       <c r="K13" s="5">
         <v>29</v>
@@ -9475,7 +9548,7 @@
         <v>137.2</v>
       </c>
       <c r="J14" s="5">
-        <v>96.02</v>
+        <v>95.98999999999999</v>
       </c>
       <c r="K14" s="5">
         <v>134</v>
@@ -9519,7 +9592,7 @@
         <v>116</v>
       </c>
       <c r="J15" s="5">
-        <v>97.93000000000001</v>
+        <v>97.70999999999999</v>
       </c>
       <c r="K15" s="5">
         <v>92</v>
@@ -9563,7 +9636,7 @@
         <v>77</v>
       </c>
       <c r="J16" s="5">
-        <v>101.44</v>
+        <v>100.87</v>
       </c>
       <c r="K16" s="5">
         <v>-100</v>
@@ -9607,7 +9680,7 @@
         <v>396.5</v>
       </c>
       <c r="J17" s="5">
-        <v>72.68000000000001</v>
+        <v>75</v>
       </c>
       <c r="K17" s="5">
         <v>39</v>
@@ -9651,7 +9724,7 @@
         <v>326.2</v>
       </c>
       <c r="J18" s="5">
-        <v>79.01000000000001</v>
+        <v>80.69</v>
       </c>
       <c r="K18" s="5">
         <v>39</v>
@@ -9695,7 +9768,7 @@
         <v>97.8</v>
       </c>
       <c r="J19" s="5">
-        <v>99.56999999999999</v>
+        <v>99.19</v>
       </c>
       <c r="K19" s="5">
         <v>129</v>
@@ -9739,7 +9812,7 @@
         <v>107</v>
       </c>
       <c r="J20" s="5">
-        <v>98.73999999999999</v>
+        <v>98.44</v>
       </c>
       <c r="K20" s="5">
         <v>0</v>
@@ -9783,7 +9856,7 @@
         <v>55.8</v>
       </c>
       <c r="J21" s="5">
-        <v>103.35</v>
+        <v>102.59</v>
       </c>
       <c r="K21" s="5">
         <v>88</v>
@@ -9827,7 +9900,7 @@
         <v>207</v>
       </c>
       <c r="J22" s="5">
-        <v>228.33</v>
+        <v>227.43</v>
       </c>
       <c r="K22" s="5">
         <v>5</v>
@@ -9871,7 +9944,7 @@
         <v>173.4</v>
       </c>
       <c r="J23" s="5">
-        <v>204.41</v>
+        <v>189.86</v>
       </c>
       <c r="K23" s="5">
         <v>29</v>
@@ -9915,7 +9988,7 @@
         <v>57</v>
       </c>
       <c r="J24" s="5">
-        <v>103.24</v>
+        <v>102.49</v>
       </c>
       <c r="K24" s="5">
         <v>-90</v>
@@ -9959,7 +10032,7 @@
         <v>76.2</v>
       </c>
       <c r="J25" s="5">
-        <v>101.51</v>
+        <v>100.93</v>
       </c>
       <c r="K25" s="5">
         <v>-86</v>
@@ -9976,7 +10049,7 @@
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>101</v>
@@ -10003,7 +10076,7 @@
         <v>224.2</v>
       </c>
       <c r="J26" s="5">
-        <v>88.19</v>
+        <v>88.95</v>
       </c>
       <c r="K26" s="5">
         <v>39</v>
@@ -10047,7 +10120,7 @@
         <v>85</v>
       </c>
       <c r="J27" s="5">
-        <v>100.72</v>
+        <v>100.22</v>
       </c>
       <c r="K27" s="5">
         <v>-80</v>
@@ -10064,7 +10137,7 @@
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>101</v>
@@ -10091,7 +10164,7 @@
         <v>161.2</v>
       </c>
       <c r="J28" s="5">
-        <v>93.86</v>
+        <v>94.05</v>
       </c>
       <c r="K28" s="5">
         <v>39</v>
@@ -10135,7 +10208,7 @@
         <v>1586</v>
       </c>
       <c r="J29" s="5">
-        <v>36.6</v>
+        <v>56.79</v>
       </c>
       <c r="K29" s="5">
         <v>39</v>
@@ -10179,7 +10252,7 @@
         <v>87.5</v>
       </c>
       <c r="J30" s="5">
-        <v>100.49</v>
+        <v>100.02</v>
       </c>
       <c r="K30" s="5">
         <v>0</v>
@@ -10223,7 +10296,7 @@
         <v>57.8</v>
       </c>
       <c r="J31" s="5">
-        <v>103.17</v>
+        <v>102.43</v>
       </c>
       <c r="K31" s="5">
         <v>49</v>
@@ -10267,7 +10340,7 @@
         <v>1305</v>
       </c>
       <c r="J32" s="5">
-        <v>49.24</v>
+        <v>68.16</v>
       </c>
       <c r="K32" s="5">
         <v>39</v>
@@ -10284,7 +10357,7 @@
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>101</v>
@@ -10311,7 +10384,7 @@
         <v>186</v>
       </c>
       <c r="J33" s="5">
-        <v>91.63</v>
+        <v>92.04000000000001</v>
       </c>
       <c r="K33" s="5">
         <v>40</v>
@@ -10355,7 +10428,7 @@
         <v>77.2</v>
       </c>
       <c r="J34" s="5">
-        <v>101.42</v>
+        <v>100.85</v>
       </c>
       <c r="K34" s="5">
         <v>75</v>
@@ -10372,7 +10445,7 @@
     </row>
     <row r="35" spans="1:14">
       <c r="A35" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>101</v>
@@ -10399,7 +10472,7 @@
         <v>403</v>
       </c>
       <c r="J35" s="5">
-        <v>219.51</v>
+        <v>219.5</v>
       </c>
       <c r="K35" s="5">
         <v>0</v>
@@ -10443,7 +10516,7 @@
         <v>84.2</v>
       </c>
       <c r="J36" s="5">
-        <v>100.79</v>
+        <v>100.28</v>
       </c>
       <c r="K36" s="5">
         <v>0</v>
@@ -10487,7 +10560,7 @@
         <v>148.1</v>
       </c>
       <c r="J37" s="5">
-        <v>84.95</v>
+        <v>84.66</v>
       </c>
       <c r="K37" s="5">
         <v>0</v>
@@ -10504,7 +10577,7 @@
     </row>
     <row r="38" spans="1:14">
       <c r="A38" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>101</v>
@@ -10531,7 +10604,7 @@
         <v>897</v>
       </c>
       <c r="J38" s="5">
-        <v>67.59999999999999</v>
+        <v>84.68000000000001</v>
       </c>
       <c r="K38" s="5">
         <v>39</v>
@@ -10548,7 +10621,7 @@
     </row>
     <row r="39" spans="1:14">
       <c r="A39" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>101</v>
@@ -10575,7 +10648,7 @@
         <v>744</v>
       </c>
       <c r="J39" s="5">
-        <v>74.48999999999999</v>
+        <v>90.87</v>
       </c>
       <c r="K39" s="5">
         <v>40</v>
@@ -10592,7 +10665,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>101</v>
@@ -10619,7 +10692,7 @@
         <v>645</v>
       </c>
       <c r="J40" s="5">
-        <v>78.94</v>
+        <v>94.88</v>
       </c>
       <c r="K40" s="5">
         <v>39</v>
@@ -10663,7 +10736,7 @@
         <v>67</v>
       </c>
       <c r="J41" s="5">
-        <v>102.34</v>
+        <v>101.68</v>
       </c>
       <c r="K41" s="5">
         <v>0</v>
@@ -10707,7 +10780,7 @@
         <v>115.2</v>
       </c>
       <c r="J42" s="5">
-        <v>98</v>
+        <v>97.77</v>
       </c>
       <c r="K42" s="5">
         <v>115</v>
@@ -10751,7 +10824,7 @@
         <v>79.8</v>
       </c>
       <c r="J43" s="5">
-        <v>101.19</v>
+        <v>100.65</v>
       </c>
       <c r="K43" s="5">
         <v>0</v>
@@ -10795,7 +10868,7 @@
         <v>295</v>
       </c>
       <c r="J44" s="5">
-        <v>224.37</v>
+        <v>223.87</v>
       </c>
       <c r="K44" s="5">
         <v>0</v>
@@ -10839,7 +10912,7 @@
         <v>98.8</v>
       </c>
       <c r="J45" s="5">
-        <v>99.48</v>
+        <v>99.11</v>
       </c>
       <c r="K45" s="5">
         <v>0</v>
@@ -10861,7 +10934,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -10893,10 +10966,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="5">
-        <v>48.82</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="D2" s="5">
-        <v>48.82</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="E2" s="5" t="b">
         <v>0</v>
@@ -10910,10 +10983,10 @@
         <v>1</v>
       </c>
       <c r="C3" s="5">
-        <v>284.59</v>
+        <v>285.62</v>
       </c>
       <c r="D3" s="5">
-        <v>284.59</v>
+        <v>285.62</v>
       </c>
       <c r="E3" s="5" t="b">
         <v>0</v>
@@ -10927,10 +11000,10 @@
         <v>1</v>
       </c>
       <c r="C4" s="5">
-        <v>254.11</v>
+        <v>229</v>
       </c>
       <c r="D4" s="5">
-        <v>254.11</v>
+        <v>229</v>
       </c>
       <c r="E4" s="5" t="b">
         <v>0</v>
@@ -11029,13 +11102,13 @@
         <v>207</v>
       </c>
       <c r="E12" s="5">
-        <v>561.66</v>
+        <v>560.63</v>
       </c>
       <c r="F12" s="5">
         <v>846.25</v>
       </c>
       <c r="G12" s="5">
-        <v>284.59</v>
+        <v>285.62</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -11052,13 +11125,13 @@
         <v>282</v>
       </c>
       <c r="E13" s="5">
-        <v>526.79</v>
+        <v>527.04</v>
       </c>
       <c r="F13" s="5">
-        <v>780.9</v>
+        <v>756.04</v>
       </c>
       <c r="G13" s="5">
-        <v>254.11</v>
+        <v>229</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -11075,13 +11148,13 @@
         <v>228</v>
       </c>
       <c r="E14" s="5">
-        <v>515.66</v>
+        <v>516.45</v>
       </c>
       <c r="F14" s="5">
-        <v>591.95</v>
+        <v>597.75</v>
       </c>
       <c r="G14" s="5">
-        <v>76.29000000000001</v>
+        <v>81.3</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -11098,18 +11171,18 @@
         <v>305</v>
       </c>
       <c r="E15" s="5">
-        <v>466.74</v>
+        <v>466.58</v>
       </c>
       <c r="F15" s="5">
-        <v>591.95</v>
+        <v>593.0599999999999</v>
       </c>
       <c r="G15" s="5">
-        <v>125.22</v>
+        <v>126.47</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>102</v>
@@ -11121,13 +11194,13 @@
         <v>897</v>
       </c>
       <c r="E16" s="5">
-        <v>500.05</v>
+        <v>502.84</v>
       </c>
       <c r="F16" s="5">
-        <v>571.09</v>
+        <v>593.0599999999999</v>
       </c>
       <c r="G16" s="5">
-        <v>71.04000000000001</v>
+        <v>90.22</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -11144,18 +11217,18 @@
         <v>340</v>
       </c>
       <c r="E17" s="5">
-        <v>514.01</v>
+        <v>514.3200000000001</v>
       </c>
       <c r="F17" s="5">
-        <v>570.09</v>
+        <v>593.0599999999999</v>
       </c>
       <c r="G17" s="5">
-        <v>56.08</v>
+        <v>78.73999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>102</v>
@@ -11167,13 +11240,13 @@
         <v>645</v>
       </c>
       <c r="E18" s="5">
-        <v>515.4</v>
+        <v>515.5700000000001</v>
       </c>
       <c r="F18" s="5">
-        <v>564.99</v>
+        <v>593.0599999999999</v>
       </c>
       <c r="G18" s="5">
-        <v>49.59</v>
+        <v>77.48999999999999</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -11190,13 +11263,36 @@
         <v>1586</v>
       </c>
       <c r="E19" s="5">
-        <v>516.17</v>
+        <v>516.21</v>
       </c>
       <c r="F19" s="5">
-        <v>564.99</v>
+        <v>593.0599999999999</v>
       </c>
       <c r="G19" s="5">
-        <v>48.82</v>
+        <v>76.84999999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C20" s="6">
+        <v>46281.41905092593</v>
+      </c>
+      <c r="D20" s="5">
+        <v>350</v>
+      </c>
+      <c r="E20" s="5">
+        <v>526.27</v>
+      </c>
+      <c r="F20" s="5">
+        <v>593.0599999999999</v>
+      </c>
+      <c r="G20" s="5">
+        <v>66.79000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/docs/reports/swift_space_weather_report_latest.xlsx
+++ b/docs/reports/swift_space_weather_report_latest.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="165">
   <si>
     <t>SWIFT Space Weather Excel Report</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Updated UTC</t>
   </si>
   <si>
-    <t>2026-09-16T12:46:52Z</t>
+    <t>2026-09-16T13:06:59Z</t>
   </si>
   <si>
     <t>Main URL root</t>
@@ -680,10 +680,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>SolarWind_27d!$A$2:$A$27</c:f>
+              <c:f>SolarWind_27d!$A$2:$A$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="27"/>
                 <c:pt idx="0">
                   <c:v>46280.45833333334</c:v>
                 </c:pt>
@@ -761,16 +761,19 @@
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>46281.5</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>46281.54166666666</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>SolarWind_27d!$B$2:$B$27</c:f>
+              <c:f>SolarWind_27d!$B$2:$B$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="27"/>
                 <c:pt idx="0">
                   <c:v>546.005</c:v>
                 </c:pt>
@@ -778,76 +781,79 @@
                   <c:v>569.6</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>543.22</c:v>
+                  <c:v>543.975</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>451.575</c:v>
+                  <c:v>450.34</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>444.55</c:v>
+                  <c:v>440.69</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>457.77</c:v>
+                  <c:v>449.915</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>433.77</c:v>
+                  <c:v>427.365</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>683.64</c:v>
+                  <c:v>659.035</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>621.9349999999999</c:v>
+                  <c:v>634.545</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>515.8099999999999</c:v>
+                  <c:v>515.015</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>468.7</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>448.01</c:v>
+                  <c:v>449.055</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>464.44</c:v>
+                  <c:v>464.65</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>517.8099999999999</c:v>
+                  <c:v>516.58</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>521.405</c:v>
+                  <c:v>522.625</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>528.495</c:v>
+                  <c:v>527.885</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>532.595</c:v>
+                  <c:v>531.665</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>538.515</c:v>
+                  <c:v>537</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>536.1849999999999</c:v>
+                  <c:v>535.985</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>531.8</c:v>
+                  <c:v>532.09</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>521.465</c:v>
+                  <c:v>522.285</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>543.22</c:v>
+                  <c:v>543.16</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>540.355</c:v>
+                  <c:v>541.03</c:v>
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>542.835</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>537.1</c:v>
+                  <c:v>537.6849999999999</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>545.6</c:v>
+                  <c:v>546.8</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>574.17</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -971,10 +977,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>SolarWind_27d!$A$2:$A$27</c:f>
+              <c:f>SolarWind_27d!$A$2:$A$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="27"/>
                 <c:pt idx="0">
                   <c:v>46280.45833333334</c:v>
                 </c:pt>
@@ -1052,16 +1058,19 @@
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>46281.5</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>46281.54166666666</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>SolarWind_27d!$D$2:$D$27</c:f>
+              <c:f>SolarWind_27d!$D$2:$D$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="27"/>
                 <c:pt idx="0">
                   <c:v>8.85</c:v>
                 </c:pt>
@@ -1069,76 +1078,79 @@
                   <c:v>8.785</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9.365</c:v>
+                  <c:v>9.164999999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>9.775</c:v>
+                  <c:v>9.720000000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>7.995</c:v>
+                  <c:v>8.130000000000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>10.23</c:v>
+                  <c:v>10.205</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>9.119999999999999</c:v>
+                  <c:v>9.23</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-5.845</c:v>
+                  <c:v>-5.585</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-9.345000000000001</c:v>
+                  <c:v>-8.895</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-9.16</c:v>
+                  <c:v>-9.119999999999999</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.44</c:v>
+                  <c:v>-0.54</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-2.27</c:v>
+                  <c:v>-3.525</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-5.155</c:v>
+                  <c:v>-4.68</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.795</c:v>
+                  <c:v>2.375</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>5.68</c:v>
+                  <c:v>5.715</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>3.7</c:v>
+                  <c:v>3.625</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.425</c:v>
+                  <c:v>0.475</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-0.305</c:v>
+                  <c:v>-0.545</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.51</c:v>
+                  <c:v>1.66</c:v>
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>4.58</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3.515</c:v>
+                  <c:v>3.425</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>4.32</c:v>
+                  <c:v>4.47</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>2.55</c:v>
+                  <c:v>2.57</c:v>
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>-2.345</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>-2.36</c:v>
+                  <c:v>-2.415</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.35</c:v>
+                  <c:v>0.925</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.92</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1155,10 +1167,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>SolarWind_27d!$A$2:$A$27</c:f>
+              <c:f>SolarWind_27d!$A$2:$A$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="27"/>
                 <c:pt idx="0">
                   <c:v>46280.45833333334</c:v>
                 </c:pt>
@@ -1236,16 +1248,19 @@
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>46281.5</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>46281.54166666666</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>SolarWind_27d!$E$2:$E$27</c:f>
+              <c:f>SolarWind_27d!$E$2:$E$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="27"/>
                 <c:pt idx="0">
                   <c:v>12.92</c:v>
                 </c:pt>
@@ -1253,37 +1268,37 @@
                   <c:v>12.62</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>13.345</c:v>
+                  <c:v>13.38</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>15.04</c:v>
+                  <c:v>15.035</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>14.685</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>14.97</c:v>
+                  <c:v>14.95</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>16.11</c:v>
+                  <c:v>16.08</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>12.62</c:v>
+                  <c:v>12.275</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>12.23</c:v>
+                  <c:v>11.91</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>13.57</c:v>
+                  <c:v>13.565</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>12.37</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>10.485</c:v>
+                  <c:v>11.045</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>11.24</c:v>
+                  <c:v>10.955</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>12.775</c:v>
@@ -1292,37 +1307,40 @@
                   <c:v>10.93</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>10.29</c:v>
+                  <c:v>10.295</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>6.76</c:v>
+                  <c:v>7.085</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>7.045</c:v>
+                  <c:v>6.86</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>6.68</c:v>
+                  <c:v>6.745</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>6.395</c:v>
+                  <c:v>6.41</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>5.77</c:v>
+                  <c:v>5.725</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>4.85</c:v>
+                  <c:v>4.9</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>4.57</c:v>
+                  <c:v>4.625</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>4.805</c:v>
+                  <c:v>4.775</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>4.31</c:v>
+                  <c:v>4.35</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>4.22</c:v>
+                  <c:v>4.465</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2.56</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1451,232 +1469,232 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="76"/>
                 <c:pt idx="0">
-                  <c:v>46281.375</c:v>
+                  <c:v>46281.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>46281.41666666666</c:v>
+                  <c:v>46281.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46281.45833333334</c:v>
+                  <c:v>46281.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46281.5</c:v>
+                  <c:v>46281.54166666666</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46281.54166666666</c:v>
+                  <c:v>46281.58333333334</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46281.58333333334</c:v>
+                  <c:v>46281.625</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46281.625</c:v>
+                  <c:v>46281.66666666666</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>46281.66666666666</c:v>
+                  <c:v>46281.70833333334</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>46281.70833333334</c:v>
+                  <c:v>46281.75</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>46281.75</c:v>
+                  <c:v>46281.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>46281.79166666666</c:v>
+                  <c:v>46281.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>46281.83333333334</c:v>
+                  <c:v>46281.875</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>46281.875</c:v>
+                  <c:v>46281.91666666666</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>46281.91666666666</c:v>
+                  <c:v>46281.95833333334</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>46281.95833333334</c:v>
+                  <c:v>46282</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46282</c:v>
+                  <c:v>46282.04166666666</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>46282.04166666666</c:v>
+                  <c:v>46282.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>46282.08333333334</c:v>
+                  <c:v>46282.125</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>46282.125</c:v>
+                  <c:v>46282.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>46282.16666666666</c:v>
+                  <c:v>46282.20833333334</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>46282.20833333334</c:v>
+                  <c:v>46282.25</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>46282.25</c:v>
+                  <c:v>46282.29166666666</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>46282.29166666666</c:v>
+                  <c:v>46282.33333333334</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>46282.33333333334</c:v>
+                  <c:v>46282.375</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>46282.375</c:v>
+                  <c:v>46282.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>46282.41666666666</c:v>
+                  <c:v>46282.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>46282.45833333334</c:v>
+                  <c:v>46282.5</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>46282.5</c:v>
+                  <c:v>46282.54166666666</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>46282.54166666666</c:v>
+                  <c:v>46282.58333333334</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>46282.58333333334</c:v>
+                  <c:v>46282.625</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>46282.625</c:v>
+                  <c:v>46282.66666666666</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>46282.66666666666</c:v>
+                  <c:v>46282.70833333334</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>46282.70833333334</c:v>
+                  <c:v>46282.75</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>46282.75</c:v>
+                  <c:v>46282.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>46282.79166666666</c:v>
+                  <c:v>46282.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>46282.83333333334</c:v>
+                  <c:v>46282.875</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>46282.875</c:v>
+                  <c:v>46282.91666666666</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>46282.91666666666</c:v>
+                  <c:v>46282.95833333334</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>46282.95833333334</c:v>
+                  <c:v>46283</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>46283</c:v>
+                  <c:v>46283.04166666666</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>46283.04166666666</c:v>
+                  <c:v>46283.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>46283.08333333334</c:v>
+                  <c:v>46283.125</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>46283.125</c:v>
+                  <c:v>46283.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>46283.16666666666</c:v>
+                  <c:v>46283.20833333334</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>46283.20833333334</c:v>
+                  <c:v>46283.25</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>46283.25</c:v>
+                  <c:v>46283.29166666666</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>46283.29166666666</c:v>
+                  <c:v>46283.33333333334</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>46283.33333333334</c:v>
+                  <c:v>46283.375</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>46283.375</c:v>
+                  <c:v>46283.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>46283.41666666666</c:v>
+                  <c:v>46283.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>46283.45833333334</c:v>
+                  <c:v>46283.5</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>46283.5</c:v>
+                  <c:v>46283.54166666666</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>46283.54166666666</c:v>
+                  <c:v>46283.58333333334</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>46283.58333333334</c:v>
+                  <c:v>46283.625</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>46283.625</c:v>
+                  <c:v>46283.66666666666</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>46283.66666666666</c:v>
+                  <c:v>46283.70833333334</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>46283.70833333334</c:v>
+                  <c:v>46283.75</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>46283.75</c:v>
+                  <c:v>46283.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>46283.79166666666</c:v>
+                  <c:v>46283.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>46283.83333333334</c:v>
+                  <c:v>46283.875</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>46283.875</c:v>
+                  <c:v>46283.91666666666</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>46283.91666666666</c:v>
+                  <c:v>46283.95833333334</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>46283.95833333334</c:v>
+                  <c:v>46284</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>46284</c:v>
+                  <c:v>46284.04166666666</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>46284.04166666666</c:v>
+                  <c:v>46284.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>46284.08333333334</c:v>
+                  <c:v>46284.125</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>46284.125</c:v>
+                  <c:v>46284.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>46284.16666666666</c:v>
+                  <c:v>46284.20833333334</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>46284.20833333334</c:v>
+                  <c:v>46284.25</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>46284.25</c:v>
+                  <c:v>46284.29166666666</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>46284.29166666666</c:v>
+                  <c:v>46284.33333333334</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>46284.33333333334</c:v>
+                  <c:v>46284.375</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>46284.375</c:v>
+                  <c:v>46284.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>46284.41666666666</c:v>
+                  <c:v>46284.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>46284.45833333334</c:v>
+                  <c:v>46284.5</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>46284.5</c:v>
+                  <c:v>46284.54166666666</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1688,232 +1706,232 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="76"/>
                 <c:pt idx="0">
-                  <c:v>591.4</c:v>
+                  <c:v>550.79</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>589.14</c:v>
+                  <c:v>544.22</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>582.91</c:v>
+                  <c:v>541.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>579.8</c:v>
+                  <c:v>539</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>578</c:v>
+                  <c:v>539.79</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>578.09</c:v>
+                  <c:v>542.5599999999999</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>579.97</c:v>
+                  <c:v>548.85</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>585.45</c:v>
+                  <c:v>559.0599999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>594.9299999999999</c:v>
+                  <c:v>575.3</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>611.08</c:v>
+                  <c:v>601.73</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>628.35</c:v>
+                  <c:v>618.25</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>648.21</c:v>
+                  <c:v>636.1799999999999</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>668.34</c:v>
+                  <c:v>652.5599999999999</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>686.26</c:v>
+                  <c:v>662.8099999999999</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>697.7</c:v>
+                  <c:v>668.72</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>704.65</c:v>
+                  <c:v>671.55</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>708.49</c:v>
+                  <c:v>672.11</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>710.08</c:v>
+                  <c:v>672.52</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>711.66</c:v>
+                  <c:v>667.97</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>708.41</c:v>
+                  <c:v>667.05</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>708.9</c:v>
+                  <c:v>668.3099999999999</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>711.5599999999999</c:v>
+                  <c:v>669.75</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>714.21</c:v>
+                  <c:v>666.27</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>712.0599999999999</c:v>
+                  <c:v>664.2</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>711</c:v>
+                  <c:v>660.9400000000001</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>708.3200000000001</c:v>
+                  <c:v>655.42</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>702.95</c:v>
+                  <c:v>647.63</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>694.9400000000001</c:v>
+                  <c:v>636.35</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>683.04</c:v>
+                  <c:v>623.3200000000001</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>669.16</c:v>
+                  <c:v>609.59</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>654.47</c:v>
+                  <c:v>595.8</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>639.6900000000001</c:v>
+                  <c:v>582.3099999999999</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>625.2</c:v>
+                  <c:v>569.3200000000001</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>611.24</c:v>
+                  <c:v>556.8200000000001</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>597.8099999999999</c:v>
+                  <c:v>543.75</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>583.59</c:v>
+                  <c:v>531.8099999999999</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>570.67</c:v>
+                  <c:v>520.83</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>558.8200000000001</c:v>
+                  <c:v>510.65</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>547.87</c:v>
+                  <c:v>501.2</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>537.72</c:v>
+                  <c:v>491.93</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>527.5599999999999</c:v>
+                  <c:v>484.49</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>519.38</c:v>
+                  <c:v>478.42</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>512.66</c:v>
+                  <c:v>473.5</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>507.17</c:v>
+                  <c:v>469.67</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>502.84</c:v>
+                  <c:v>467.1</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>499.79</c:v>
+                  <c:v>465.18</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>497.46</c:v>
+                  <c:v>464.74</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>496.66</c:v>
+                  <c:v>466.57</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>498.16</c:v>
+                  <c:v>471.39</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>502.68</c:v>
+                  <c:v>474.38</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>505.38</c:v>
+                  <c:v>483.32</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>514.08</c:v>
+                  <c:v>494.73</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>525.1900000000001</c:v>
+                  <c:v>509.83</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>540.0700000000001</c:v>
+                  <c:v>526.09</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>556.13</c:v>
+                  <c:v>540.84</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>570.71</c:v>
+                  <c:v>551.61</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>581.3200000000001</c:v>
+                  <c:v>554.27</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>583.8099999999999</c:v>
+                  <c:v>549.63</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>578.8</c:v>
+                  <c:v>542.7</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>571.59</c:v>
+                  <c:v>534.61</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>563.28</c:v>
+                  <c:v>523.98</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>552.27</c:v>
+                  <c:v>514.1799999999999</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>542.21</c:v>
+                  <c:v>505.11</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>532.96</c:v>
+                  <c:v>494.66</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>522.17</c:v>
+                  <c:v>485.75</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>513.05</c:v>
+                  <c:v>477.95</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>505.12</c:v>
+                  <c:v>470.99</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>498.07</c:v>
+                  <c:v>464.69</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>491.7</c:v>
+                  <c:v>458.92</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>485.89</c:v>
+                  <c:v>453.6</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>480.54</c:v>
+                  <c:v>448.67</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>475.58</c:v>
+                  <c:v>444.09</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>470.99</c:v>
+                  <c:v>439.82</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>466.71</c:v>
+                  <c:v>435.84</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>462.71</c:v>
+                  <c:v>432.13</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>458.99</c:v>
+                  <c:v>428.66</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1935,232 +1953,232 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="76"/>
                 <c:pt idx="0">
-                  <c:v>46281.375</c:v>
+                  <c:v>46281.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>46281.41666666666</c:v>
+                  <c:v>46281.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46281.45833333334</c:v>
+                  <c:v>46281.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46281.5</c:v>
+                  <c:v>46281.54166666666</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46281.54166666666</c:v>
+                  <c:v>46281.58333333334</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46281.58333333334</c:v>
+                  <c:v>46281.625</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46281.625</c:v>
+                  <c:v>46281.66666666666</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>46281.66666666666</c:v>
+                  <c:v>46281.70833333334</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>46281.70833333334</c:v>
+                  <c:v>46281.75</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>46281.75</c:v>
+                  <c:v>46281.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>46281.79166666666</c:v>
+                  <c:v>46281.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>46281.83333333334</c:v>
+                  <c:v>46281.875</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>46281.875</c:v>
+                  <c:v>46281.91666666666</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>46281.91666666666</c:v>
+                  <c:v>46281.95833333334</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>46281.95833333334</c:v>
+                  <c:v>46282</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46282</c:v>
+                  <c:v>46282.04166666666</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>46282.04166666666</c:v>
+                  <c:v>46282.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>46282.08333333334</c:v>
+                  <c:v>46282.125</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>46282.125</c:v>
+                  <c:v>46282.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>46282.16666666666</c:v>
+                  <c:v>46282.20833333334</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>46282.20833333334</c:v>
+                  <c:v>46282.25</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>46282.25</c:v>
+                  <c:v>46282.29166666666</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>46282.29166666666</c:v>
+                  <c:v>46282.33333333334</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>46282.33333333334</c:v>
+                  <c:v>46282.375</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>46282.375</c:v>
+                  <c:v>46282.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>46282.41666666666</c:v>
+                  <c:v>46282.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>46282.45833333334</c:v>
+                  <c:v>46282.5</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>46282.5</c:v>
+                  <c:v>46282.54166666666</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>46282.54166666666</c:v>
+                  <c:v>46282.58333333334</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>46282.58333333334</c:v>
+                  <c:v>46282.625</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>46282.625</c:v>
+                  <c:v>46282.66666666666</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>46282.66666666666</c:v>
+                  <c:v>46282.70833333334</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>46282.70833333334</c:v>
+                  <c:v>46282.75</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>46282.75</c:v>
+                  <c:v>46282.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>46282.79166666666</c:v>
+                  <c:v>46282.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>46282.83333333334</c:v>
+                  <c:v>46282.875</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>46282.875</c:v>
+                  <c:v>46282.91666666666</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>46282.91666666666</c:v>
+                  <c:v>46282.95833333334</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>46282.95833333334</c:v>
+                  <c:v>46283</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>46283</c:v>
+                  <c:v>46283.04166666666</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>46283.04166666666</c:v>
+                  <c:v>46283.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>46283.08333333334</c:v>
+                  <c:v>46283.125</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>46283.125</c:v>
+                  <c:v>46283.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>46283.16666666666</c:v>
+                  <c:v>46283.20833333334</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>46283.20833333334</c:v>
+                  <c:v>46283.25</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>46283.25</c:v>
+                  <c:v>46283.29166666666</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>46283.29166666666</c:v>
+                  <c:v>46283.33333333334</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>46283.33333333334</c:v>
+                  <c:v>46283.375</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>46283.375</c:v>
+                  <c:v>46283.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>46283.41666666666</c:v>
+                  <c:v>46283.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>46283.45833333334</c:v>
+                  <c:v>46283.5</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>46283.5</c:v>
+                  <c:v>46283.54166666666</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>46283.54166666666</c:v>
+                  <c:v>46283.58333333334</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>46283.58333333334</c:v>
+                  <c:v>46283.625</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>46283.625</c:v>
+                  <c:v>46283.66666666666</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>46283.66666666666</c:v>
+                  <c:v>46283.70833333334</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>46283.70833333334</c:v>
+                  <c:v>46283.75</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>46283.75</c:v>
+                  <c:v>46283.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>46283.79166666666</c:v>
+                  <c:v>46283.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>46283.83333333334</c:v>
+                  <c:v>46283.875</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>46283.875</c:v>
+                  <c:v>46283.91666666666</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>46283.91666666666</c:v>
+                  <c:v>46283.95833333334</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>46283.95833333334</c:v>
+                  <c:v>46284</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>46284</c:v>
+                  <c:v>46284.04166666666</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>46284.04166666666</c:v>
+                  <c:v>46284.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>46284.08333333334</c:v>
+                  <c:v>46284.125</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>46284.125</c:v>
+                  <c:v>46284.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>46284.16666666666</c:v>
+                  <c:v>46284.20833333334</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>46284.20833333334</c:v>
+                  <c:v>46284.25</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>46284.25</c:v>
+                  <c:v>46284.29166666666</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>46284.29166666666</c:v>
+                  <c:v>46284.33333333334</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>46284.33333333334</c:v>
+                  <c:v>46284.375</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>46284.375</c:v>
+                  <c:v>46284.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>46284.41666666666</c:v>
+                  <c:v>46284.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>46284.45833333334</c:v>
+                  <c:v>46284.5</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>46284.5</c:v>
+                  <c:v>46284.54166666666</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2172,232 +2190,232 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="76"/>
                 <c:pt idx="0">
-                  <c:v>400.06</c:v>
+                  <c:v>371.95</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>400.2</c:v>
+                  <c:v>368.3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>396.52</c:v>
+                  <c:v>368.27</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>396.07</c:v>
+                  <c:v>369.22</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>395.82</c:v>
+                  <c:v>369.66</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>396.74</c:v>
+                  <c:v>369.9</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>396.99</c:v>
+                  <c:v>370.16</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>397.12</c:v>
+                  <c:v>370.09</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>396.85</c:v>
+                  <c:v>371.76</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>398.8</c:v>
+                  <c:v>380.09</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>398.2</c:v>
+                  <c:v>376.57</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>398.09</c:v>
+                  <c:v>374.64</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>398.28</c:v>
+                  <c:v>373.69</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>398.64</c:v>
+                  <c:v>373.34</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>399.1</c:v>
+                  <c:v>373.36</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>399.61</c:v>
+                  <c:v>373.26</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>399.81</c:v>
+                  <c:v>373</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>399.71</c:v>
+                  <c:v>372.63</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>399.44</c:v>
+                  <c:v>372.18</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>399.06</c:v>
+                  <c:v>371.69</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>398.61</c:v>
+                  <c:v>371.18</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>398.13</c:v>
+                  <c:v>370.99</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>397.95</c:v>
+                  <c:v>371.01</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>397.97</c:v>
+                  <c:v>371.15</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>398.11</c:v>
+                  <c:v>371.38</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>398.33</c:v>
+                  <c:v>371.65</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>398.6</c:v>
+                  <c:v>371.96</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>398.89</c:v>
+                  <c:v>372.13</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>399.06</c:v>
+                  <c:v>372.22</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>399.14</c:v>
+                  <c:v>372.26</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>399.17</c:v>
+                  <c:v>372.26</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>399.18</c:v>
+                  <c:v>372.25</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>399.16</c:v>
+                  <c:v>372.24</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>399.14</c:v>
+                  <c:v>372.09</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>398.99</c:v>
+                  <c:v>371.87</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>398.77</c:v>
+                  <c:v>371.6</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>398.5</c:v>
+                  <c:v>371.3</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>398.21</c:v>
+                  <c:v>370.99</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>397.9</c:v>
+                  <c:v>370.67</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>397.58</c:v>
+                  <c:v>371.27</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>398.17</c:v>
+                  <c:v>372.45</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>399.32</c:v>
+                  <c:v>373.98</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>400.83</c:v>
+                  <c:v>375.73</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>402.55</c:v>
+                  <c:v>377.62</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>404.41</c:v>
+                  <c:v>379.6</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>406.35</c:v>
+                  <c:v>380.73</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>407.46</c:v>
+                  <c:v>381.35</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>408.07</c:v>
+                  <c:v>381.64</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>408.35</c:v>
+                  <c:v>381.73</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>408.44</c:v>
+                  <c:v>381.7</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>408.4</c:v>
+                  <c:v>381.59</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>408.29</c:v>
+                  <c:v>381.44</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>408.14</c:v>
+                  <c:v>381.26</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>407.96</c:v>
+                  <c:v>381.06</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>407.77</c:v>
+                  <c:v>380.86</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>407.57</c:v>
+                  <c:v>380.65</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>407.36</c:v>
+                  <c:v>380.44</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>407.15</c:v>
+                  <c:v>380.22</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>406.94</c:v>
+                  <c:v>380.01</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>406.73</c:v>
+                  <c:v>379.79</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>406.51</c:v>
+                  <c:v>379.58</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>406.3</c:v>
+                  <c:v>379.36</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>406.09</c:v>
+                  <c:v>379.15</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>405.88</c:v>
+                  <c:v>379.01</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>405.74</c:v>
+                  <c:v>378.92</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>405.64</c:v>
+                  <c:v>378.85</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>405.58</c:v>
+                  <c:v>378.8</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>405.53</c:v>
+                  <c:v>378.76</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>405.49</c:v>
+                  <c:v>378.74</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>405.46</c:v>
+                  <c:v>378.71</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>405.44</c:v>
+                  <c:v>378.69</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>405.41</c:v>
+                  <c:v>378.67</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>405.4</c:v>
+                  <c:v>378.65</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>405.38</c:v>
+                  <c:v>378.64</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>405.36</c:v>
+                  <c:v>378.62</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>405.35</c:v>
+                  <c:v>378.61</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2419,232 +2437,232 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="76"/>
                 <c:pt idx="0">
-                  <c:v>46281.375</c:v>
+                  <c:v>46281.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>46281.41666666666</c:v>
+                  <c:v>46281.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46281.45833333334</c:v>
+                  <c:v>46281.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46281.5</c:v>
+                  <c:v>46281.54166666666</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46281.54166666666</c:v>
+                  <c:v>46281.58333333334</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46281.58333333334</c:v>
+                  <c:v>46281.625</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46281.625</c:v>
+                  <c:v>46281.66666666666</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>46281.66666666666</c:v>
+                  <c:v>46281.70833333334</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>46281.70833333334</c:v>
+                  <c:v>46281.75</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>46281.75</c:v>
+                  <c:v>46281.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>46281.79166666666</c:v>
+                  <c:v>46281.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>46281.83333333334</c:v>
+                  <c:v>46281.875</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>46281.875</c:v>
+                  <c:v>46281.91666666666</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>46281.91666666666</c:v>
+                  <c:v>46281.95833333334</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>46281.95833333334</c:v>
+                  <c:v>46282</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46282</c:v>
+                  <c:v>46282.04166666666</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>46282.04166666666</c:v>
+                  <c:v>46282.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>46282.08333333334</c:v>
+                  <c:v>46282.125</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>46282.125</c:v>
+                  <c:v>46282.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>46282.16666666666</c:v>
+                  <c:v>46282.20833333334</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>46282.20833333334</c:v>
+                  <c:v>46282.25</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>46282.25</c:v>
+                  <c:v>46282.29166666666</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>46282.29166666666</c:v>
+                  <c:v>46282.33333333334</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>46282.33333333334</c:v>
+                  <c:v>46282.375</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>46282.375</c:v>
+                  <c:v>46282.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>46282.41666666666</c:v>
+                  <c:v>46282.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>46282.45833333334</c:v>
+                  <c:v>46282.5</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>46282.5</c:v>
+                  <c:v>46282.54166666666</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>46282.54166666666</c:v>
+                  <c:v>46282.58333333334</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>46282.58333333334</c:v>
+                  <c:v>46282.625</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>46282.625</c:v>
+                  <c:v>46282.66666666666</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>46282.66666666666</c:v>
+                  <c:v>46282.70833333334</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>46282.70833333334</c:v>
+                  <c:v>46282.75</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>46282.75</c:v>
+                  <c:v>46282.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>46282.79166666666</c:v>
+                  <c:v>46282.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>46282.83333333334</c:v>
+                  <c:v>46282.875</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>46282.875</c:v>
+                  <c:v>46282.91666666666</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>46282.91666666666</c:v>
+                  <c:v>46282.95833333334</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>46282.95833333334</c:v>
+                  <c:v>46283</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>46283</c:v>
+                  <c:v>46283.04166666666</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>46283.04166666666</c:v>
+                  <c:v>46283.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>46283.08333333334</c:v>
+                  <c:v>46283.125</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>46283.125</c:v>
+                  <c:v>46283.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>46283.16666666666</c:v>
+                  <c:v>46283.20833333334</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>46283.20833333334</c:v>
+                  <c:v>46283.25</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>46283.25</c:v>
+                  <c:v>46283.29166666666</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>46283.29166666666</c:v>
+                  <c:v>46283.33333333334</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>46283.33333333334</c:v>
+                  <c:v>46283.375</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>46283.375</c:v>
+                  <c:v>46283.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>46283.41666666666</c:v>
+                  <c:v>46283.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>46283.45833333334</c:v>
+                  <c:v>46283.5</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>46283.5</c:v>
+                  <c:v>46283.54166666666</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>46283.54166666666</c:v>
+                  <c:v>46283.58333333334</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>46283.58333333334</c:v>
+                  <c:v>46283.625</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>46283.625</c:v>
+                  <c:v>46283.66666666666</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>46283.66666666666</c:v>
+                  <c:v>46283.70833333334</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>46283.70833333334</c:v>
+                  <c:v>46283.75</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>46283.75</c:v>
+                  <c:v>46283.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>46283.79166666666</c:v>
+                  <c:v>46283.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>46283.83333333334</c:v>
+                  <c:v>46283.875</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>46283.875</c:v>
+                  <c:v>46283.91666666666</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>46283.91666666666</c:v>
+                  <c:v>46283.95833333334</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>46283.95833333334</c:v>
+                  <c:v>46284</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>46284</c:v>
+                  <c:v>46284.04166666666</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>46284.04166666666</c:v>
+                  <c:v>46284.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>46284.08333333334</c:v>
+                  <c:v>46284.125</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>46284.125</c:v>
+                  <c:v>46284.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>46284.16666666666</c:v>
+                  <c:v>46284.20833333334</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>46284.20833333334</c:v>
+                  <c:v>46284.25</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>46284.25</c:v>
+                  <c:v>46284.29166666666</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>46284.29166666666</c:v>
+                  <c:v>46284.33333333334</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>46284.33333333334</c:v>
+                  <c:v>46284.375</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>46284.375</c:v>
+                  <c:v>46284.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>46284.41666666666</c:v>
+                  <c:v>46284.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>46284.45833333334</c:v>
+                  <c:v>46284.5</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>46284.5</c:v>
+                  <c:v>46284.54166666666</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2656,232 +2674,232 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="76"/>
                 <c:pt idx="0">
-                  <c:v>256.41</c:v>
+                  <c:v>235.93</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>253.21</c:v>
+                  <c:v>232.08</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>249.79</c:v>
+                  <c:v>228.53</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>246.21</c:v>
+                  <c:v>223.98</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>240.75</c:v>
+                  <c:v>225.17</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>241.23</c:v>
+                  <c:v>233.21</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>248.78</c:v>
+                  <c:v>248.72</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>264.06</c:v>
+                  <c:v>271.44</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>286.8</c:v>
+                  <c:v>299.89</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>315.54</c:v>
+                  <c:v>331.31</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>347.49</c:v>
+                  <c:v>361.97</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>378.86</c:v>
+                  <c:v>387.77</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>405.5</c:v>
+                  <c:v>405.18</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>423.83</c:v>
+                  <c:v>404.69</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>424.17</c:v>
+                  <c:v>402.34</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>422.88</c:v>
+                  <c:v>399.81</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>421.63</c:v>
+                  <c:v>396.34</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>419.62</c:v>
+                  <c:v>397.32</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>422.48</c:v>
+                  <c:v>381.38</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>408.31</c:v>
+                  <c:v>388.72</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>417.86</c:v>
+                  <c:v>395.76</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>426.91</c:v>
+                  <c:v>397.65</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>430</c:v>
+                  <c:v>381.97</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>416.18</c:v>
+                  <c:v>381.85</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>416.7</c:v>
+                  <c:v>374.49</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>409.07</c:v>
+                  <c:v>361.89</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>395.55</c:v>
+                  <c:v>346.23</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>378.59</c:v>
+                  <c:v>323.9</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>354.17</c:v>
+                  <c:v>303.01</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>331.33</c:v>
+                  <c:v>283.47</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>309.96</c:v>
+                  <c:v>265.19</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>289.97</c:v>
+                  <c:v>248.08</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>271.27</c:v>
+                  <c:v>232.08</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>253.77</c:v>
+                  <c:v>217.12</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>237.41</c:v>
+                  <c:v>199.08</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>217.06</c:v>
+                  <c:v>186.24</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>203.06</c:v>
+                  <c:v>174.23</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>189.97</c:v>
+                  <c:v>163</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>177.72</c:v>
+                  <c:v>152.55</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>166.32</c:v>
+                  <c:v>137.94</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>149.91</c:v>
+                  <c:v>129.27</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>140.47</c:v>
+                  <c:v>121.42</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>131.91</c:v>
+                  <c:v>114.59</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>124.42</c:v>
+                  <c:v>109.14</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>118.37</c:v>
+                  <c:v>105.63</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>114.32</c:v>
+                  <c:v>104.83</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>113.08</c:v>
+                  <c:v>107.74</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>115.64</c:v>
+                  <c:v>115.36</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>123.02</c:v>
+                  <c:v>128.47</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>136.01</c:v>
+                  <c:v>128.76</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>135.94</c:v>
+                  <c:v>153.69</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>161.02</c:v>
+                  <c:v>174.34</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>181.5</c:v>
+                  <c:v>202.51</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>209.94</c:v>
+                  <c:v>226.74</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>234.37</c:v>
+                  <c:v>243.25</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>250.96</c:v>
+                  <c:v>249.16</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>256.77</c:v>
+                  <c:v>235.49</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>242.65</c:v>
+                  <c:v>213.97</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>219.82</c:v>
+                  <c:v>200.17</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>205.64</c:v>
+                  <c:v>187.26</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>192.38</c:v>
+                  <c:v>168.07</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>172</c:v>
+                  <c:v>157.23</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>160.91</c:v>
+                  <c:v>147.09</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>150.53</c:v>
+                  <c:v>130.37</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>132.77</c:v>
+                  <c:v>121.96</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>124.21</c:v>
+                  <c:v>114.1</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>116.19</c:v>
+                  <c:v>106.74</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>108.7</c:v>
+                  <c:v>99.86</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>101.69</c:v>
+                  <c:v>93.42</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>95.13</c:v>
+                  <c:v>87.39</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>89</c:v>
+                  <c:v>81.75</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>83.26000000000001</c:v>
+                  <c:v>76.48</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>77.89</c:v>
+                  <c:v>71.55</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>72.86</c:v>
+                  <c:v>66.94</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>68.17</c:v>
+                  <c:v>62.62</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>63.77</c:v>
+                  <c:v>58.58</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3385,79 +3403,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>46281.5</c:v>
+                  <c:v>46281.54166666666</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>46281.625</c:v>
+                  <c:v>46281.66666666666</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46281.75</c:v>
+                  <c:v>46281.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46281.875</c:v>
+                  <c:v>46281.91666666666</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46282</c:v>
+                  <c:v>46282.04166666666</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46282.125</c:v>
+                  <c:v>46282.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46282.25</c:v>
+                  <c:v>46282.29166666666</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>46282.375</c:v>
+                  <c:v>46282.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>46282.5</c:v>
+                  <c:v>46282.54166666666</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>46282.625</c:v>
+                  <c:v>46282.66666666666</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>46282.75</c:v>
+                  <c:v>46282.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>46282.875</c:v>
+                  <c:v>46282.91666666666</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>46283</c:v>
+                  <c:v>46283.04166666666</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>46283.125</c:v>
+                  <c:v>46283.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>46283.25</c:v>
+                  <c:v>46283.29166666666</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46283.375</c:v>
+                  <c:v>46283.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>46283.5</c:v>
+                  <c:v>46283.54166666666</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>46283.625</c:v>
+                  <c:v>46283.66666666666</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>46283.75</c:v>
+                  <c:v>46283.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>46283.875</c:v>
+                  <c:v>46283.91666666666</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>46284</c:v>
+                  <c:v>46284.04166666666</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>46284.125</c:v>
+                  <c:v>46284.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>46284.25</c:v>
+                  <c:v>46284.29166666666</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>46284.375</c:v>
+                  <c:v>46284.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>46284.5</c:v>
+                  <c:v>46284.54166666666</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3469,79 +3487,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>1.94</c:v>
+                  <c:v>1.4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.79</c:v>
+                  <c:v>1.29</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.64</c:v>
+                  <c:v>1.18</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.51</c:v>
+                  <c:v>1.09</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.39</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.28</c:v>
+                  <c:v>0.92</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.18</c:v>
+                  <c:v>0.85</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.08</c:v>
+                  <c:v>0.78</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1</c:v>
+                  <c:v>0.72</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.92</c:v>
+                  <c:v>0.66</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.84</c:v>
+                  <c:v>0.61</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.78</c:v>
+                  <c:v>0.5600000000000001</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.71</c:v>
+                  <c:v>0.51</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.66</c:v>
+                  <c:v>0.47</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.6</c:v>
+                  <c:v>0.44</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.5600000000000001</c:v>
+                  <c:v>0.4</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.51</c:v>
+                  <c:v>0.37</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.47</c:v>
+                  <c:v>0.34</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.43</c:v>
+                  <c:v>0.31</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.4</c:v>
+                  <c:v>0.29</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.39</c:v>
+                  <c:v>0.28</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.39</c:v>
+                  <c:v>0.28</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.39</c:v>
+                  <c:v>0.28</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.39</c:v>
+                  <c:v>0.28</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.39</c:v>
+                  <c:v>0.28</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3563,79 +3581,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>46281.5</c:v>
+                  <c:v>46281.54166666666</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>46281.625</c:v>
+                  <c:v>46281.66666666666</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46281.75</c:v>
+                  <c:v>46281.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46281.875</c:v>
+                  <c:v>46281.91666666666</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46282</c:v>
+                  <c:v>46282.04166666666</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46282.125</c:v>
+                  <c:v>46282.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46282.25</c:v>
+                  <c:v>46282.29166666666</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>46282.375</c:v>
+                  <c:v>46282.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>46282.5</c:v>
+                  <c:v>46282.54166666666</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>46282.625</c:v>
+                  <c:v>46282.66666666666</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>46282.75</c:v>
+                  <c:v>46282.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>46282.875</c:v>
+                  <c:v>46282.91666666666</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>46283</c:v>
+                  <c:v>46283.04166666666</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>46283.125</c:v>
+                  <c:v>46283.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>46283.25</c:v>
+                  <c:v>46283.29166666666</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46283.375</c:v>
+                  <c:v>46283.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>46283.5</c:v>
+                  <c:v>46283.54166666666</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>46283.625</c:v>
+                  <c:v>46283.66666666666</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>46283.75</c:v>
+                  <c:v>46283.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>46283.875</c:v>
+                  <c:v>46283.91666666666</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>46284</c:v>
+                  <c:v>46284.04166666666</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>46284.125</c:v>
+                  <c:v>46284.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>46284.25</c:v>
+                  <c:v>46284.29166666666</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>46284.375</c:v>
+                  <c:v>46284.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>46284.5</c:v>
+                  <c:v>46284.54166666666</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3647,79 +3665,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>-13.07</c:v>
+                  <c:v>-13.26</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-12.36</c:v>
+                  <c:v>-11.99</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-11.33</c:v>
+                  <c:v>-12.15</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-12.86</c:v>
+                  <c:v>-13.17</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-12.82</c:v>
+                  <c:v>-12.54</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-12.87</c:v>
+                  <c:v>-13.44</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-13.83</c:v>
+                  <c:v>-13.81</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-13.9</c:v>
+                  <c:v>-13.95</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-14.01</c:v>
+                  <c:v>-13.94</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-13.23</c:v>
+                  <c:v>-12.62</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-11.14</c:v>
+                  <c:v>-10.28</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-8.68</c:v>
+                  <c:v>-7.88</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-6.67</c:v>
+                  <c:v>-6.09</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-5.63</c:v>
+                  <c:v>-5.97</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-7.14</c:v>
+                  <c:v>-7.71</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-9.33</c:v>
+                  <c:v>-10.05</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-11.78</c:v>
+                  <c:v>-12.38</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-13.61</c:v>
+                  <c:v>-13.79</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-14.01</c:v>
+                  <c:v>-13.63</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-12.81</c:v>
+                  <c:v>-11.99</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-10.58</c:v>
+                  <c:v>-9.619999999999999</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>-8.23</c:v>
+                  <c:v>-7.41</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>-6.45</c:v>
+                  <c:v>-5.88</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>-5.4</c:v>
+                  <c:v>-5.12</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>-4.97</c:v>
+                  <c:v>-4.93</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3741,79 +3759,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>46281.5</c:v>
+                  <c:v>46281.54166666666</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>46281.625</c:v>
+                  <c:v>46281.66666666666</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46281.75</c:v>
+                  <c:v>46281.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46281.875</c:v>
+                  <c:v>46281.91666666666</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46282</c:v>
+                  <c:v>46282.04166666666</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46282.125</c:v>
+                  <c:v>46282.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46282.25</c:v>
+                  <c:v>46282.29166666666</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>46282.375</c:v>
+                  <c:v>46282.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>46282.5</c:v>
+                  <c:v>46282.54166666666</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>46282.625</c:v>
+                  <c:v>46282.66666666666</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>46282.75</c:v>
+                  <c:v>46282.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>46282.875</c:v>
+                  <c:v>46282.91666666666</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>46283</c:v>
+                  <c:v>46283.04166666666</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>46283.125</c:v>
+                  <c:v>46283.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>46283.25</c:v>
+                  <c:v>46283.29166666666</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46283.375</c:v>
+                  <c:v>46283.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>46283.5</c:v>
+                  <c:v>46283.54166666666</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>46283.625</c:v>
+                  <c:v>46283.66666666666</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>46283.75</c:v>
+                  <c:v>46283.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>46283.875</c:v>
+                  <c:v>46283.91666666666</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>46284</c:v>
+                  <c:v>46284.04166666666</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>46284.125</c:v>
+                  <c:v>46284.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>46284.25</c:v>
+                  <c:v>46284.29166666666</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>46284.375</c:v>
+                  <c:v>46284.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>46284.5</c:v>
+                  <c:v>46284.54166666666</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3825,79 +3843,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>15.12</c:v>
+                  <c:v>14.81</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>14.25</c:v>
+                  <c:v>13.44</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>13.06</c:v>
+                  <c:v>13.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>14.45</c:v>
+                  <c:v>14.43</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>14.28</c:v>
+                  <c:v>13.72</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>14.22</c:v>
+                  <c:v>14.55</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>15.07</c:v>
+                  <c:v>14.85</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>15.04</c:v>
+                  <c:v>14.93</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>15.06</c:v>
+                  <c:v>14.86</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>14.19</c:v>
+                  <c:v>13.48</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>12.03</c:v>
+                  <c:v>11.09</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>9.5</c:v>
+                  <c:v>8.640000000000001</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>7.41</c:v>
+                  <c:v>6.81</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>6.32</c:v>
+                  <c:v>6.65</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>7.77</c:v>
+                  <c:v>8.35</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>9.91</c:v>
+                  <c:v>10.66</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>12.31</c:v>
+                  <c:v>12.97</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>14.09</c:v>
+                  <c:v>14.35</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>14.46</c:v>
+                  <c:v>14.17</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>13.22</c:v>
+                  <c:v>12.5</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>10.98</c:v>
+                  <c:v>10.12</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>8.630000000000001</c:v>
+                  <c:v>7.92</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>6.85</c:v>
+                  <c:v>6.38</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>5.8</c:v>
+                  <c:v>5.54</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>5.3</c:v>
+                  <c:v>5.17</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4026,79 +4044,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>46281.5</c:v>
+                  <c:v>46281.54166666666</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>46281.625</c:v>
+                  <c:v>46281.66666666666</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46281.75</c:v>
+                  <c:v>46281.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46281.875</c:v>
+                  <c:v>46281.91666666666</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46282</c:v>
+                  <c:v>46282.04166666666</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46282.125</c:v>
+                  <c:v>46282.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46282.25</c:v>
+                  <c:v>46282.29166666666</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>46282.375</c:v>
+                  <c:v>46282.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>46282.5</c:v>
+                  <c:v>46282.54166666666</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>46282.625</c:v>
+                  <c:v>46282.66666666666</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>46282.75</c:v>
+                  <c:v>46282.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>46282.875</c:v>
+                  <c:v>46282.91666666666</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>46283</c:v>
+                  <c:v>46283.04166666666</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>46283.125</c:v>
+                  <c:v>46283.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>46283.25</c:v>
+                  <c:v>46283.29166666666</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46283.375</c:v>
+                  <c:v>46283.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>46283.5</c:v>
+                  <c:v>46283.54166666666</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>46283.625</c:v>
+                  <c:v>46283.66666666666</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>46283.75</c:v>
+                  <c:v>46283.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>46283.875</c:v>
+                  <c:v>46283.91666666666</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>46284</c:v>
+                  <c:v>46284.04166666666</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>46284.125</c:v>
+                  <c:v>46284.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>46284.25</c:v>
+                  <c:v>46284.29166666666</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>46284.375</c:v>
+                  <c:v>46284.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>46284.5</c:v>
+                  <c:v>46284.54166666666</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4110,79 +4128,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>60.7</c:v>
+                  <c:v>64.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>58.6</c:v>
+                  <c:v>60.2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>55.2</c:v>
+                  <c:v>61.3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>61.6</c:v>
+                  <c:v>65.59999999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>61.9</c:v>
+                  <c:v>63.7</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>62.6</c:v>
+                  <c:v>67.5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>66.7</c:v>
+                  <c:v>69.3</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>67.5</c:v>
+                  <c:v>70.2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>68.3</c:v>
+                  <c:v>70.5</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>65.8</c:v>
+                  <c:v>65.7</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>58.2</c:v>
+                  <c:v>57.1</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>49.2</c:v>
+                  <c:v>48.3</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>41.9</c:v>
+                  <c:v>41.7</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>38.2</c:v>
+                  <c:v>41.5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>44.3</c:v>
+                  <c:v>48.3</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>52.9</c:v>
+                  <c:v>57.4</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>62.4</c:v>
+                  <c:v>66.5</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>69.59999999999999</c:v>
+                  <c:v>72</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>71.3</c:v>
+                  <c:v>71.59999999999999</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>67</c:v>
+                  <c:v>65.5</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>58.5</c:v>
+                  <c:v>56.5</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>49.6</c:v>
+                  <c:v>48.1</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>42.9</c:v>
+                  <c:v>42.3</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>38.9</c:v>
+                  <c:v>39.1</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>37</c:v>
+                  <c:v>37.7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4838,7 +4856,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>25</v>
@@ -4847,16 +4865,16 @@
         <v>24</v>
       </c>
       <c r="F9" s="5">
-        <v>88.89700000000001</v>
+        <v>62.867</v>
       </c>
       <c r="G9" s="5">
-        <v>82.65300000000001</v>
+        <v>53.411</v>
       </c>
       <c r="H9" s="5">
-        <v>41.7</v>
+        <v>62.5</v>
       </c>
       <c r="I9" s="5">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="J9" s="5" t="s">
         <v>26</v>
@@ -4867,25 +4885,25 @@
         <v>10</v>
       </c>
       <c r="B10" s="5">
-        <v>2581</v>
+        <v>2601</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>27</v>
       </c>
       <c r="E10" s="5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F10" s="5">
-        <v>83.06</v>
+        <v>59.58</v>
       </c>
       <c r="G10" s="5">
-        <v>75.29300000000001</v>
+        <v>45.353</v>
       </c>
       <c r="H10" s="5">
-        <v>46.2</v>
+        <v>66.7</v>
       </c>
       <c r="I10" s="5">
-        <v>69.2</v>
+        <v>77.8</v>
       </c>
       <c r="J10" s="5" t="s">
         <v>26</v>
@@ -4896,25 +4914,25 @@
         <v>11</v>
       </c>
       <c r="B11" s="5">
-        <v>2568</v>
+        <v>2588</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>28</v>
       </c>
       <c r="E11" s="5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F11" s="5">
-        <v>83.06</v>
+        <v>59.58</v>
       </c>
       <c r="G11" s="5">
-        <v>75.29300000000001</v>
+        <v>45.353</v>
       </c>
       <c r="H11" s="5">
-        <v>46.2</v>
+        <v>66.7</v>
       </c>
       <c r="I11" s="5">
-        <v>69.2</v>
+        <v>77.8</v>
       </c>
       <c r="J11" s="5" t="s">
         <v>26</v>
@@ -5004,7 +5022,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -5017,7 +5035,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.7109375" customWidth="1"/>
@@ -5080,16 +5098,16 @@
         <v>46280.54166666666</v>
       </c>
       <c r="B4" s="5">
-        <v>543.22</v>
+        <v>543.975</v>
       </c>
       <c r="C4" s="5">
         <v>3.02</v>
       </c>
       <c r="D4" s="5">
-        <v>9.365</v>
+        <v>9.164999999999999</v>
       </c>
       <c r="E4" s="5">
-        <v>13.345</v>
+        <v>13.38</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -5097,16 +5115,16 @@
         <v>46280.58333333334</v>
       </c>
       <c r="B5" s="5">
-        <v>451.575</v>
+        <v>450.34</v>
       </c>
       <c r="C5" s="5">
-        <v>2.52</v>
+        <v>2.33</v>
       </c>
       <c r="D5" s="5">
-        <v>9.775</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="E5" s="5">
-        <v>15.04</v>
+        <v>15.035</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -5114,13 +5132,13 @@
         <v>46280.625</v>
       </c>
       <c r="B6" s="5">
-        <v>444.55</v>
+        <v>440.69</v>
       </c>
       <c r="C6" s="5">
-        <v>2.68</v>
+        <v>2.755</v>
       </c>
       <c r="D6" s="5">
-        <v>7.995</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="E6" s="5">
         <v>14.685</v>
@@ -5131,16 +5149,16 @@
         <v>46280.66666666666</v>
       </c>
       <c r="B7" s="5">
-        <v>457.77</v>
+        <v>449.915</v>
       </c>
       <c r="C7" s="5">
-        <v>0.79</v>
+        <v>0.805</v>
       </c>
       <c r="D7" s="5">
-        <v>10.23</v>
+        <v>10.205</v>
       </c>
       <c r="E7" s="5">
-        <v>14.97</v>
+        <v>14.95</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -5148,16 +5166,16 @@
         <v>46280.70833333334</v>
       </c>
       <c r="B8" s="5">
-        <v>433.77</v>
+        <v>427.365</v>
       </c>
       <c r="C8" s="5">
-        <v>0.78</v>
+        <v>0.845</v>
       </c>
       <c r="D8" s="5">
-        <v>9.119999999999999</v>
+        <v>9.23</v>
       </c>
       <c r="E8" s="5">
-        <v>16.11</v>
+        <v>16.08</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -5165,16 +5183,16 @@
         <v>46280.75</v>
       </c>
       <c r="B9" s="5">
-        <v>683.64</v>
+        <v>659.035</v>
       </c>
       <c r="C9" s="5">
         <v>0.265</v>
       </c>
       <c r="D9" s="5">
-        <v>-5.845</v>
+        <v>-5.585</v>
       </c>
       <c r="E9" s="5">
-        <v>12.62</v>
+        <v>12.275</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -5182,16 +5200,16 @@
         <v>46280.79166666666</v>
       </c>
       <c r="B10" s="5">
-        <v>621.9349999999999</v>
+        <v>634.545</v>
       </c>
       <c r="C10" s="5">
-        <v>0.37</v>
+        <v>0.165</v>
       </c>
       <c r="D10" s="5">
-        <v>-9.345000000000001</v>
+        <v>-8.895</v>
       </c>
       <c r="E10" s="5">
-        <v>12.23</v>
+        <v>11.91</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -5199,16 +5217,16 @@
         <v>46280.83333333334</v>
       </c>
       <c r="B11" s="5">
-        <v>515.8099999999999</v>
+        <v>515.015</v>
       </c>
       <c r="C11" s="5">
-        <v>0.72</v>
+        <v>0.585</v>
       </c>
       <c r="D11" s="5">
-        <v>-9.16</v>
+        <v>-9.119999999999999</v>
       </c>
       <c r="E11" s="5">
-        <v>13.57</v>
+        <v>13.565</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -5219,10 +5237,10 @@
         <v>468.7</v>
       </c>
       <c r="C12" s="5">
-        <v>3.735</v>
+        <v>2.025</v>
       </c>
       <c r="D12" s="5">
-        <v>0.44</v>
+        <v>-0.54</v>
       </c>
       <c r="E12" s="5">
         <v>12.37</v>
@@ -5233,16 +5251,16 @@
         <v>46280.91666666666</v>
       </c>
       <c r="B13" s="5">
-        <v>448.01</v>
+        <v>449.055</v>
       </c>
       <c r="C13" s="5">
-        <v>7.495</v>
+        <v>7.85</v>
       </c>
       <c r="D13" s="5">
-        <v>-2.27</v>
+        <v>-3.525</v>
       </c>
       <c r="E13" s="5">
-        <v>10.485</v>
+        <v>11.045</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -5250,16 +5268,16 @@
         <v>46280.95833333334</v>
       </c>
       <c r="B14" s="5">
-        <v>464.44</v>
+        <v>464.65</v>
       </c>
       <c r="C14" s="5">
-        <v>10.605</v>
+        <v>9.465</v>
       </c>
       <c r="D14" s="5">
-        <v>-5.155</v>
+        <v>-4.68</v>
       </c>
       <c r="E14" s="5">
-        <v>11.24</v>
+        <v>10.955</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -5267,13 +5285,13 @@
         <v>46281</v>
       </c>
       <c r="B15" s="5">
-        <v>517.8099999999999</v>
+        <v>516.58</v>
       </c>
       <c r="C15" s="5">
-        <v>22.045</v>
+        <v>18.725</v>
       </c>
       <c r="D15" s="5">
-        <v>1.795</v>
+        <v>2.375</v>
       </c>
       <c r="E15" s="5">
         <v>12.775</v>
@@ -5284,13 +5302,13 @@
         <v>46281.04166666666</v>
       </c>
       <c r="B16" s="5">
-        <v>521.405</v>
+        <v>522.625</v>
       </c>
       <c r="C16" s="5">
-        <v>13.36</v>
+        <v>13.585</v>
       </c>
       <c r="D16" s="5">
-        <v>5.68</v>
+        <v>5.715</v>
       </c>
       <c r="E16" s="5">
         <v>10.93</v>
@@ -5301,16 +5319,16 @@
         <v>46281.08333333334</v>
       </c>
       <c r="B17" s="5">
-        <v>528.495</v>
+        <v>527.885</v>
       </c>
       <c r="C17" s="5">
-        <v>8.800000000000001</v>
+        <v>8.715</v>
       </c>
       <c r="D17" s="5">
-        <v>3.7</v>
+        <v>3.625</v>
       </c>
       <c r="E17" s="5">
-        <v>10.29</v>
+        <v>10.295</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -5318,16 +5336,16 @@
         <v>46281.125</v>
       </c>
       <c r="B18" s="5">
-        <v>532.595</v>
+        <v>531.665</v>
       </c>
       <c r="C18" s="5">
-        <v>5.75</v>
+        <v>6.43</v>
       </c>
       <c r="D18" s="5">
-        <v>0.425</v>
+        <v>0.475</v>
       </c>
       <c r="E18" s="5">
-        <v>6.76</v>
+        <v>7.085</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -5335,16 +5353,16 @@
         <v>46281.16666666666</v>
       </c>
       <c r="B19" s="5">
-        <v>538.515</v>
+        <v>537</v>
       </c>
       <c r="C19" s="5">
-        <v>5.305</v>
+        <v>5.49</v>
       </c>
       <c r="D19" s="5">
-        <v>-0.305</v>
+        <v>-0.545</v>
       </c>
       <c r="E19" s="5">
-        <v>7.045</v>
+        <v>6.86</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -5352,16 +5370,16 @@
         <v>46281.20833333334</v>
       </c>
       <c r="B20" s="5">
-        <v>536.1849999999999</v>
+        <v>535.985</v>
       </c>
       <c r="C20" s="5">
-        <v>5.605</v>
+        <v>5.585</v>
       </c>
       <c r="D20" s="5">
-        <v>1.51</v>
+        <v>1.66</v>
       </c>
       <c r="E20" s="5">
-        <v>6.68</v>
+        <v>6.745</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -5369,16 +5387,16 @@
         <v>46281.25</v>
       </c>
       <c r="B21" s="5">
-        <v>531.8</v>
+        <v>532.09</v>
       </c>
       <c r="C21" s="5">
-        <v>5.59</v>
+        <v>5.57</v>
       </c>
       <c r="D21" s="5">
         <v>4.58</v>
       </c>
       <c r="E21" s="5">
-        <v>6.395</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -5386,16 +5404,16 @@
         <v>46281.29166666666</v>
       </c>
       <c r="B22" s="5">
-        <v>521.465</v>
+        <v>522.285</v>
       </c>
       <c r="C22" s="5">
-        <v>5.2</v>
+        <v>5.245</v>
       </c>
       <c r="D22" s="5">
-        <v>3.515</v>
+        <v>3.425</v>
       </c>
       <c r="E22" s="5">
-        <v>5.77</v>
+        <v>5.725</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -5403,16 +5421,16 @@
         <v>46281.33333333334</v>
       </c>
       <c r="B23" s="5">
-        <v>543.22</v>
+        <v>543.16</v>
       </c>
       <c r="C23" s="5">
-        <v>4.55</v>
+        <v>4.74</v>
       </c>
       <c r="D23" s="5">
-        <v>4.32</v>
+        <v>4.47</v>
       </c>
       <c r="E23" s="5">
-        <v>4.85</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -5420,16 +5438,16 @@
         <v>46281.375</v>
       </c>
       <c r="B24" s="5">
-        <v>540.355</v>
+        <v>541.03</v>
       </c>
       <c r="C24" s="5">
-        <v>0.64</v>
+        <v>0.625</v>
       </c>
       <c r="D24" s="5">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="E24" s="5">
-        <v>4.57</v>
+        <v>4.625</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -5440,13 +5458,13 @@
         <v>542.835</v>
       </c>
       <c r="C25" s="5">
-        <v>0.76</v>
+        <v>0.67</v>
       </c>
       <c r="D25" s="5">
         <v>-2.345</v>
       </c>
       <c r="E25" s="5">
-        <v>4.805</v>
+        <v>4.775</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -5454,16 +5472,16 @@
         <v>46281.45833333334</v>
       </c>
       <c r="B26" s="5">
-        <v>537.1</v>
+        <v>537.6849999999999</v>
       </c>
       <c r="C26" s="5">
-        <v>0.315</v>
+        <v>0.24</v>
       </c>
       <c r="D26" s="5">
-        <v>-2.36</v>
+        <v>-2.415</v>
       </c>
       <c r="E26" s="5">
-        <v>4.31</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -5471,16 +5489,33 @@
         <v>46281.5</v>
       </c>
       <c r="B27" s="5">
-        <v>545.6</v>
+        <v>546.8</v>
       </c>
       <c r="C27" s="5">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="D27" s="5">
-        <v>0.35</v>
+        <v>0.925</v>
       </c>
       <c r="E27" s="5">
-        <v>4.22</v>
+        <v>4.465</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6">
+        <v>46281.54166666666</v>
+      </c>
+      <c r="B28" s="5">
+        <v>574.17</v>
+      </c>
+      <c r="C28" s="5">
+        <v>0.04</v>
+      </c>
+      <c r="D28" s="5">
+        <v>0.92</v>
+      </c>
+      <c r="E28" s="5">
+        <v>2.56</v>
       </c>
     </row>
   </sheetData>
@@ -5524,19 +5559,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="6">
-        <v>46281.375</v>
+        <v>46281.41666666666</v>
       </c>
       <c r="B2" s="5">
-        <v>591.4</v>
+        <v>550.79</v>
       </c>
       <c r="C2" s="5">
-        <v>400.06</v>
+        <v>371.95</v>
       </c>
       <c r="D2" s="5">
-        <v>542.7</v>
+        <v>542.2</v>
       </c>
       <c r="E2" s="5">
-        <v>256.41</v>
+        <v>235.93</v>
       </c>
       <c r="F2" s="5"/>
       <c r="G2" s="5" t="s">
@@ -5545,19 +5580,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="6">
-        <v>46281.41666666666</v>
+        <v>46281.45833333334</v>
       </c>
       <c r="B3" s="5">
-        <v>589.14</v>
+        <v>544.22</v>
       </c>
       <c r="C3" s="5">
-        <v>400.2</v>
+        <v>368.3</v>
       </c>
       <c r="D3" s="5">
-        <v>542.28</v>
+        <v>540.48</v>
       </c>
       <c r="E3" s="5">
-        <v>253.21</v>
+        <v>232.08</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5" t="s">
@@ -5566,19 +5601,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="6">
-        <v>46281.45833333334</v>
+        <v>46281.5</v>
       </c>
       <c r="B4" s="5">
-        <v>582.91</v>
+        <v>541.5</v>
       </c>
       <c r="C4" s="5">
-        <v>396.52</v>
+        <v>368.27</v>
       </c>
       <c r="D4" s="5">
-        <v>538.6</v>
+        <v>537.9</v>
       </c>
       <c r="E4" s="5">
-        <v>249.79</v>
+        <v>228.53</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="5" t="s">
@@ -5587,19 +5622,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="6">
-        <v>46281.5</v>
+        <v>46281.54166666666</v>
       </c>
       <c r="B5" s="5">
-        <v>579.8</v>
+        <v>539</v>
       </c>
       <c r="C5" s="5">
-        <v>396.07</v>
+        <v>369.22</v>
       </c>
       <c r="D5" s="5">
-        <v>537.65</v>
+        <v>555.78</v>
       </c>
       <c r="E5" s="5">
-        <v>246.21</v>
+        <v>223.98</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5" t="s">
@@ -5608,17 +5643,17 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="6">
-        <v>46281.54166666666</v>
+        <v>46281.58333333334</v>
       </c>
       <c r="B6" s="5">
-        <v>578</v>
+        <v>539.79</v>
       </c>
       <c r="C6" s="5">
-        <v>395.82</v>
+        <v>369.66</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5">
-        <v>240.75</v>
+        <v>225.17</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="5" t="s">
@@ -5627,17 +5662,17 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="6">
-        <v>46281.58333333334</v>
+        <v>46281.625</v>
       </c>
       <c r="B7" s="5">
-        <v>578.09</v>
+        <v>542.5599999999999</v>
       </c>
       <c r="C7" s="5">
-        <v>396.74</v>
+        <v>369.9</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5">
-        <v>241.23</v>
+        <v>233.21</v>
       </c>
       <c r="F7" s="5"/>
       <c r="G7" s="5" t="s">
@@ -5646,17 +5681,17 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="6">
-        <v>46281.625</v>
+        <v>46281.66666666666</v>
       </c>
       <c r="B8" s="5">
-        <v>579.97</v>
+        <v>548.85</v>
       </c>
       <c r="C8" s="5">
-        <v>396.99</v>
+        <v>370.16</v>
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="5">
-        <v>248.78</v>
+        <v>248.72</v>
       </c>
       <c r="F8" s="5"/>
       <c r="G8" s="5" t="s">
@@ -5665,17 +5700,17 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="6">
-        <v>46281.66666666666</v>
+        <v>46281.70833333334</v>
       </c>
       <c r="B9" s="5">
-        <v>585.45</v>
+        <v>559.0599999999999</v>
       </c>
       <c r="C9" s="5">
-        <v>397.12</v>
+        <v>370.09</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="5">
-        <v>264.06</v>
+        <v>271.44</v>
       </c>
       <c r="F9" s="5"/>
       <c r="G9" s="5" t="s">
@@ -5684,17 +5719,17 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="6">
-        <v>46281.70833333334</v>
+        <v>46281.75</v>
       </c>
       <c r="B10" s="5">
-        <v>594.9299999999999</v>
+        <v>575.3</v>
       </c>
       <c r="C10" s="5">
-        <v>396.85</v>
+        <v>371.76</v>
       </c>
       <c r="D10" s="5"/>
       <c r="E10" s="5">
-        <v>286.8</v>
+        <v>299.89</v>
       </c>
       <c r="F10" s="5"/>
       <c r="G10" s="5" t="s">
@@ -5703,17 +5738,17 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="6">
-        <v>46281.75</v>
+        <v>46281.79166666666</v>
       </c>
       <c r="B11" s="5">
-        <v>611.08</v>
+        <v>601.73</v>
       </c>
       <c r="C11" s="5">
-        <v>398.8</v>
+        <v>380.09</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="5">
-        <v>315.54</v>
+        <v>331.31</v>
       </c>
       <c r="F11" s="5"/>
       <c r="G11" s="5" t="s">
@@ -5722,17 +5757,17 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="6">
-        <v>46281.79166666666</v>
+        <v>46281.83333333334</v>
       </c>
       <c r="B12" s="5">
-        <v>628.35</v>
+        <v>618.25</v>
       </c>
       <c r="C12" s="5">
-        <v>398.2</v>
+        <v>376.57</v>
       </c>
       <c r="D12" s="5"/>
       <c r="E12" s="5">
-        <v>347.49</v>
+        <v>361.97</v>
       </c>
       <c r="F12" s="5"/>
       <c r="G12" s="5" t="s">
@@ -5741,17 +5776,17 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="6">
-        <v>46281.83333333334</v>
+        <v>46281.875</v>
       </c>
       <c r="B13" s="5">
-        <v>648.21</v>
+        <v>636.1799999999999</v>
       </c>
       <c r="C13" s="5">
-        <v>398.09</v>
+        <v>374.64</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="5">
-        <v>378.86</v>
+        <v>387.77</v>
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="5" t="s">
@@ -5760,17 +5795,17 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="6">
-        <v>46281.875</v>
+        <v>46281.91666666666</v>
       </c>
       <c r="B14" s="5">
-        <v>668.34</v>
+        <v>652.5599999999999</v>
       </c>
       <c r="C14" s="5">
-        <v>398.28</v>
+        <v>373.69</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="5">
-        <v>405.5</v>
+        <v>405.18</v>
       </c>
       <c r="F14" s="5"/>
       <c r="G14" s="5" t="s">
@@ -5779,17 +5814,17 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="6">
-        <v>46281.91666666666</v>
+        <v>46281.95833333334</v>
       </c>
       <c r="B15" s="5">
-        <v>686.26</v>
+        <v>662.8099999999999</v>
       </c>
       <c r="C15" s="5">
-        <v>398.64</v>
+        <v>373.34</v>
       </c>
       <c r="D15" s="5"/>
       <c r="E15" s="5">
-        <v>423.83</v>
+        <v>404.69</v>
       </c>
       <c r="F15" s="5"/>
       <c r="G15" s="5" t="s">
@@ -5798,17 +5833,17 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="6">
-        <v>46281.95833333334</v>
+        <v>46282</v>
       </c>
       <c r="B16" s="5">
-        <v>697.7</v>
+        <v>668.72</v>
       </c>
       <c r="C16" s="5">
-        <v>399.1</v>
+        <v>373.36</v>
       </c>
       <c r="D16" s="5"/>
       <c r="E16" s="5">
-        <v>424.17</v>
+        <v>402.34</v>
       </c>
       <c r="F16" s="5"/>
       <c r="G16" s="5" t="s">
@@ -5817,17 +5852,17 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="6">
-        <v>46282</v>
+        <v>46282.04166666666</v>
       </c>
       <c r="B17" s="5">
-        <v>704.65</v>
+        <v>671.55</v>
       </c>
       <c r="C17" s="5">
-        <v>399.61</v>
+        <v>373.26</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="5">
-        <v>422.88</v>
+        <v>399.81</v>
       </c>
       <c r="F17" s="5"/>
       <c r="G17" s="5" t="s">
@@ -5836,17 +5871,17 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="6">
-        <v>46282.04166666666</v>
+        <v>46282.08333333334</v>
       </c>
       <c r="B18" s="5">
-        <v>708.49</v>
+        <v>672.11</v>
       </c>
       <c r="C18" s="5">
-        <v>399.81</v>
+        <v>373</v>
       </c>
       <c r="D18" s="5"/>
       <c r="E18" s="5">
-        <v>421.63</v>
+        <v>396.34</v>
       </c>
       <c r="F18" s="5"/>
       <c r="G18" s="5" t="s">
@@ -5855,17 +5890,17 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="6">
-        <v>46282.08333333334</v>
+        <v>46282.125</v>
       </c>
       <c r="B19" s="5">
-        <v>710.08</v>
+        <v>672.52</v>
       </c>
       <c r="C19" s="5">
-        <v>399.71</v>
+        <v>372.63</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="5">
-        <v>419.62</v>
+        <v>397.32</v>
       </c>
       <c r="F19" s="5"/>
       <c r="G19" s="5" t="s">
@@ -5874,17 +5909,17 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="6">
-        <v>46282.125</v>
+        <v>46282.16666666666</v>
       </c>
       <c r="B20" s="5">
-        <v>711.66</v>
+        <v>667.97</v>
       </c>
       <c r="C20" s="5">
-        <v>399.44</v>
+        <v>372.18</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="5">
-        <v>422.48</v>
+        <v>381.38</v>
       </c>
       <c r="F20" s="5"/>
       <c r="G20" s="5" t="s">
@@ -5893,17 +5928,17 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="6">
-        <v>46282.16666666666</v>
+        <v>46282.20833333334</v>
       </c>
       <c r="B21" s="5">
-        <v>708.41</v>
+        <v>667.05</v>
       </c>
       <c r="C21" s="5">
-        <v>399.06</v>
+        <v>371.69</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5">
-        <v>408.31</v>
+        <v>388.72</v>
       </c>
       <c r="F21" s="5"/>
       <c r="G21" s="5" t="s">
@@ -5912,17 +5947,17 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="6">
-        <v>46282.20833333334</v>
+        <v>46282.25</v>
       </c>
       <c r="B22" s="5">
-        <v>708.9</v>
+        <v>668.3099999999999</v>
       </c>
       <c r="C22" s="5">
-        <v>398.61</v>
+        <v>371.18</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="5">
-        <v>417.86</v>
+        <v>395.76</v>
       </c>
       <c r="F22" s="5"/>
       <c r="G22" s="5" t="s">
@@ -5931,17 +5966,17 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="6">
-        <v>46282.25</v>
+        <v>46282.29166666666</v>
       </c>
       <c r="B23" s="5">
-        <v>711.5599999999999</v>
+        <v>669.75</v>
       </c>
       <c r="C23" s="5">
-        <v>398.13</v>
+        <v>370.99</v>
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="5">
-        <v>426.91</v>
+        <v>397.65</v>
       </c>
       <c r="F23" s="5"/>
       <c r="G23" s="5" t="s">
@@ -5950,17 +5985,17 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="6">
-        <v>46282.29166666666</v>
+        <v>46282.33333333334</v>
       </c>
       <c r="B24" s="5">
-        <v>714.21</v>
+        <v>666.27</v>
       </c>
       <c r="C24" s="5">
-        <v>397.95</v>
+        <v>371.01</v>
       </c>
       <c r="D24" s="5"/>
       <c r="E24" s="5">
-        <v>430</v>
+        <v>381.97</v>
       </c>
       <c r="F24" s="5"/>
       <c r="G24" s="5" t="s">
@@ -5969,17 +6004,17 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="6">
-        <v>46282.33333333334</v>
+        <v>46282.375</v>
       </c>
       <c r="B25" s="5">
-        <v>712.0599999999999</v>
+        <v>664.2</v>
       </c>
       <c r="C25" s="5">
-        <v>397.97</v>
+        <v>371.15</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="5">
-        <v>416.18</v>
+        <v>381.85</v>
       </c>
       <c r="F25" s="5"/>
       <c r="G25" s="5" t="s">
@@ -5988,17 +6023,17 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="6">
-        <v>46282.375</v>
+        <v>46282.41666666666</v>
       </c>
       <c r="B26" s="5">
-        <v>711</v>
+        <v>660.9400000000001</v>
       </c>
       <c r="C26" s="5">
-        <v>398.11</v>
+        <v>371.38</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5">
-        <v>416.7</v>
+        <v>374.49</v>
       </c>
       <c r="F26" s="5"/>
       <c r="G26" s="5" t="s">
@@ -6007,17 +6042,17 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="6">
-        <v>46282.41666666666</v>
+        <v>46282.45833333334</v>
       </c>
       <c r="B27" s="5">
-        <v>708.3200000000001</v>
+        <v>655.42</v>
       </c>
       <c r="C27" s="5">
-        <v>398.33</v>
+        <v>371.65</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="5">
-        <v>409.07</v>
+        <v>361.89</v>
       </c>
       <c r="F27" s="5"/>
       <c r="G27" s="5" t="s">
@@ -6026,17 +6061,17 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="6">
-        <v>46282.45833333334</v>
+        <v>46282.5</v>
       </c>
       <c r="B28" s="5">
-        <v>702.95</v>
+        <v>647.63</v>
       </c>
       <c r="C28" s="5">
-        <v>398.6</v>
+        <v>371.96</v>
       </c>
       <c r="D28" s="5"/>
       <c r="E28" s="5">
-        <v>395.55</v>
+        <v>346.23</v>
       </c>
       <c r="F28" s="5"/>
       <c r="G28" s="5" t="s">
@@ -6045,17 +6080,17 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="6">
-        <v>46282.5</v>
+        <v>46282.54166666666</v>
       </c>
       <c r="B29" s="5">
-        <v>694.9400000000001</v>
+        <v>636.35</v>
       </c>
       <c r="C29" s="5">
-        <v>398.89</v>
+        <v>372.13</v>
       </c>
       <c r="D29" s="5"/>
       <c r="E29" s="5">
-        <v>378.59</v>
+        <v>323.9</v>
       </c>
       <c r="F29" s="5"/>
       <c r="G29" s="5" t="s">
@@ -6064,17 +6099,17 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="6">
-        <v>46282.54166666666</v>
+        <v>46282.58333333334</v>
       </c>
       <c r="B30" s="5">
-        <v>683.04</v>
+        <v>623.3200000000001</v>
       </c>
       <c r="C30" s="5">
-        <v>399.06</v>
+        <v>372.22</v>
       </c>
       <c r="D30" s="5"/>
       <c r="E30" s="5">
-        <v>354.17</v>
+        <v>303.01</v>
       </c>
       <c r="F30" s="5"/>
       <c r="G30" s="5" t="s">
@@ -6083,17 +6118,17 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="6">
-        <v>46282.58333333334</v>
+        <v>46282.625</v>
       </c>
       <c r="B31" s="5">
-        <v>669.16</v>
+        <v>609.59</v>
       </c>
       <c r="C31" s="5">
-        <v>399.14</v>
+        <v>372.26</v>
       </c>
       <c r="D31" s="5"/>
       <c r="E31" s="5">
-        <v>331.33</v>
+        <v>283.47</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="5" t="s">
@@ -6102,17 +6137,17 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="6">
-        <v>46282.625</v>
+        <v>46282.66666666666</v>
       </c>
       <c r="B32" s="5">
-        <v>654.47</v>
+        <v>595.8</v>
       </c>
       <c r="C32" s="5">
-        <v>399.17</v>
+        <v>372.26</v>
       </c>
       <c r="D32" s="5"/>
       <c r="E32" s="5">
-        <v>309.96</v>
+        <v>265.19</v>
       </c>
       <c r="F32" s="5"/>
       <c r="G32" s="5" t="s">
@@ -6121,17 +6156,17 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="6">
-        <v>46282.66666666666</v>
+        <v>46282.70833333334</v>
       </c>
       <c r="B33" s="5">
-        <v>639.6900000000001</v>
+        <v>582.3099999999999</v>
       </c>
       <c r="C33" s="5">
-        <v>399.18</v>
+        <v>372.25</v>
       </c>
       <c r="D33" s="5"/>
       <c r="E33" s="5">
-        <v>289.97</v>
+        <v>248.08</v>
       </c>
       <c r="F33" s="5"/>
       <c r="G33" s="5" t="s">
@@ -6140,17 +6175,17 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="6">
-        <v>46282.70833333334</v>
+        <v>46282.75</v>
       </c>
       <c r="B34" s="5">
-        <v>625.2</v>
+        <v>569.3200000000001</v>
       </c>
       <c r="C34" s="5">
-        <v>399.16</v>
+        <v>372.24</v>
       </c>
       <c r="D34" s="5"/>
       <c r="E34" s="5">
-        <v>271.27</v>
+        <v>232.08</v>
       </c>
       <c r="F34" s="5"/>
       <c r="G34" s="5" t="s">
@@ -6159,17 +6194,17 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="6">
-        <v>46282.75</v>
+        <v>46282.79166666666</v>
       </c>
       <c r="B35" s="5">
-        <v>611.24</v>
+        <v>556.8200000000001</v>
       </c>
       <c r="C35" s="5">
-        <v>399.14</v>
+        <v>372.09</v>
       </c>
       <c r="D35" s="5"/>
       <c r="E35" s="5">
-        <v>253.77</v>
+        <v>217.12</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="5" t="s">
@@ -6178,17 +6213,17 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="6">
-        <v>46282.79166666666</v>
+        <v>46282.83333333334</v>
       </c>
       <c r="B36" s="5">
-        <v>597.8099999999999</v>
+        <v>543.75</v>
       </c>
       <c r="C36" s="5">
-        <v>398.99</v>
+        <v>371.87</v>
       </c>
       <c r="D36" s="5"/>
       <c r="E36" s="5">
-        <v>237.41</v>
+        <v>199.08</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="5" t="s">
@@ -6197,17 +6232,17 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="6">
-        <v>46282.83333333334</v>
+        <v>46282.875</v>
       </c>
       <c r="B37" s="5">
-        <v>583.59</v>
+        <v>531.8099999999999</v>
       </c>
       <c r="C37" s="5">
-        <v>398.77</v>
+        <v>371.6</v>
       </c>
       <c r="D37" s="5"/>
       <c r="E37" s="5">
-        <v>217.06</v>
+        <v>186.24</v>
       </c>
       <c r="F37" s="5"/>
       <c r="G37" s="5" t="s">
@@ -6216,17 +6251,17 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="6">
-        <v>46282.875</v>
+        <v>46282.91666666666</v>
       </c>
       <c r="B38" s="5">
-        <v>570.67</v>
+        <v>520.83</v>
       </c>
       <c r="C38" s="5">
-        <v>398.5</v>
+        <v>371.3</v>
       </c>
       <c r="D38" s="5"/>
       <c r="E38" s="5">
-        <v>203.06</v>
+        <v>174.23</v>
       </c>
       <c r="F38" s="5"/>
       <c r="G38" s="5" t="s">
@@ -6235,17 +6270,17 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="6">
-        <v>46282.91666666666</v>
+        <v>46282.95833333334</v>
       </c>
       <c r="B39" s="5">
-        <v>558.8200000000001</v>
+        <v>510.65</v>
       </c>
       <c r="C39" s="5">
-        <v>398.21</v>
+        <v>370.99</v>
       </c>
       <c r="D39" s="5"/>
       <c r="E39" s="5">
-        <v>189.97</v>
+        <v>163</v>
       </c>
       <c r="F39" s="5"/>
       <c r="G39" s="5" t="s">
@@ -6254,17 +6289,17 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="6">
-        <v>46282.95833333334</v>
+        <v>46283</v>
       </c>
       <c r="B40" s="5">
-        <v>547.87</v>
+        <v>501.2</v>
       </c>
       <c r="C40" s="5">
-        <v>397.9</v>
+        <v>370.67</v>
       </c>
       <c r="D40" s="5"/>
       <c r="E40" s="5">
-        <v>177.72</v>
+        <v>152.55</v>
       </c>
       <c r="F40" s="5"/>
       <c r="G40" s="5" t="s">
@@ -6273,17 +6308,17 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="6">
-        <v>46283</v>
+        <v>46283.04166666666</v>
       </c>
       <c r="B41" s="5">
-        <v>537.72</v>
+        <v>491.93</v>
       </c>
       <c r="C41" s="5">
-        <v>397.58</v>
+        <v>371.27</v>
       </c>
       <c r="D41" s="5"/>
       <c r="E41" s="5">
-        <v>166.32</v>
+        <v>137.94</v>
       </c>
       <c r="F41" s="5"/>
       <c r="G41" s="5" t="s">
@@ -6292,17 +6327,17 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="6">
-        <v>46283.04166666666</v>
+        <v>46283.08333333334</v>
       </c>
       <c r="B42" s="5">
-        <v>527.5599999999999</v>
+        <v>484.49</v>
       </c>
       <c r="C42" s="5">
-        <v>398.17</v>
+        <v>372.45</v>
       </c>
       <c r="D42" s="5"/>
       <c r="E42" s="5">
-        <v>149.91</v>
+        <v>129.27</v>
       </c>
       <c r="F42" s="5"/>
       <c r="G42" s="5" t="s">
@@ -6311,17 +6346,17 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="6">
-        <v>46283.08333333334</v>
+        <v>46283.125</v>
       </c>
       <c r="B43" s="5">
-        <v>519.38</v>
+        <v>478.42</v>
       </c>
       <c r="C43" s="5">
-        <v>399.32</v>
+        <v>373.98</v>
       </c>
       <c r="D43" s="5"/>
       <c r="E43" s="5">
-        <v>140.47</v>
+        <v>121.42</v>
       </c>
       <c r="F43" s="5"/>
       <c r="G43" s="5" t="s">
@@ -6330,17 +6365,17 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="6">
-        <v>46283.125</v>
+        <v>46283.16666666666</v>
       </c>
       <c r="B44" s="5">
-        <v>512.66</v>
+        <v>473.5</v>
       </c>
       <c r="C44" s="5">
-        <v>400.83</v>
+        <v>375.73</v>
       </c>
       <c r="D44" s="5"/>
       <c r="E44" s="5">
-        <v>131.91</v>
+        <v>114.59</v>
       </c>
       <c r="F44" s="5"/>
       <c r="G44" s="5" t="s">
@@ -6349,17 +6384,17 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="6">
-        <v>46283.16666666666</v>
+        <v>46283.20833333334</v>
       </c>
       <c r="B45" s="5">
-        <v>507.17</v>
+        <v>469.67</v>
       </c>
       <c r="C45" s="5">
-        <v>402.55</v>
+        <v>377.62</v>
       </c>
       <c r="D45" s="5"/>
       <c r="E45" s="5">
-        <v>124.42</v>
+        <v>109.14</v>
       </c>
       <c r="F45" s="5"/>
       <c r="G45" s="5" t="s">
@@ -6368,17 +6403,17 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="6">
-        <v>46283.20833333334</v>
+        <v>46283.25</v>
       </c>
       <c r="B46" s="5">
-        <v>502.84</v>
+        <v>467.1</v>
       </c>
       <c r="C46" s="5">
-        <v>404.41</v>
+        <v>379.6</v>
       </c>
       <c r="D46" s="5"/>
       <c r="E46" s="5">
-        <v>118.37</v>
+        <v>105.63</v>
       </c>
       <c r="F46" s="5"/>
       <c r="G46" s="5" t="s">
@@ -6387,17 +6422,17 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="6">
-        <v>46283.25</v>
+        <v>46283.29166666666</v>
       </c>
       <c r="B47" s="5">
-        <v>499.79</v>
+        <v>465.18</v>
       </c>
       <c r="C47" s="5">
-        <v>406.35</v>
+        <v>380.73</v>
       </c>
       <c r="D47" s="5"/>
       <c r="E47" s="5">
-        <v>114.32</v>
+        <v>104.83</v>
       </c>
       <c r="F47" s="5"/>
       <c r="G47" s="5" t="s">
@@ -6406,17 +6441,17 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="6">
-        <v>46283.29166666666</v>
+        <v>46283.33333333334</v>
       </c>
       <c r="B48" s="5">
-        <v>497.46</v>
+        <v>464.74</v>
       </c>
       <c r="C48" s="5">
-        <v>407.46</v>
+        <v>381.35</v>
       </c>
       <c r="D48" s="5"/>
       <c r="E48" s="5">
-        <v>113.08</v>
+        <v>107.74</v>
       </c>
       <c r="F48" s="5"/>
       <c r="G48" s="5" t="s">
@@ -6425,17 +6460,17 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="6">
-        <v>46283.33333333334</v>
+        <v>46283.375</v>
       </c>
       <c r="B49" s="5">
-        <v>496.66</v>
+        <v>466.57</v>
       </c>
       <c r="C49" s="5">
-        <v>408.07</v>
+        <v>381.64</v>
       </c>
       <c r="D49" s="5"/>
       <c r="E49" s="5">
-        <v>115.64</v>
+        <v>115.36</v>
       </c>
       <c r="F49" s="5"/>
       <c r="G49" s="5" t="s">
@@ -6444,17 +6479,17 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="6">
-        <v>46283.375</v>
+        <v>46283.41666666666</v>
       </c>
       <c r="B50" s="5">
-        <v>498.16</v>
+        <v>471.39</v>
       </c>
       <c r="C50" s="5">
-        <v>408.35</v>
+        <v>381.73</v>
       </c>
       <c r="D50" s="5"/>
       <c r="E50" s="5">
-        <v>123.02</v>
+        <v>128.47</v>
       </c>
       <c r="F50" s="5"/>
       <c r="G50" s="5" t="s">
@@ -6463,17 +6498,17 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="6">
-        <v>46283.41666666666</v>
+        <v>46283.45833333334</v>
       </c>
       <c r="B51" s="5">
-        <v>502.68</v>
+        <v>474.38</v>
       </c>
       <c r="C51" s="5">
-        <v>408.44</v>
+        <v>381.7</v>
       </c>
       <c r="D51" s="5"/>
       <c r="E51" s="5">
-        <v>136.01</v>
+        <v>128.76</v>
       </c>
       <c r="F51" s="5"/>
       <c r="G51" s="5" t="s">
@@ -6482,17 +6517,17 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="6">
-        <v>46283.45833333334</v>
+        <v>46283.5</v>
       </c>
       <c r="B52" s="5">
-        <v>505.38</v>
+        <v>483.32</v>
       </c>
       <c r="C52" s="5">
-        <v>408.4</v>
+        <v>381.59</v>
       </c>
       <c r="D52" s="5"/>
       <c r="E52" s="5">
-        <v>135.94</v>
+        <v>153.69</v>
       </c>
       <c r="F52" s="5"/>
       <c r="G52" s="5" t="s">
@@ -6501,17 +6536,17 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="6">
-        <v>46283.5</v>
+        <v>46283.54166666666</v>
       </c>
       <c r="B53" s="5">
-        <v>514.08</v>
+        <v>494.73</v>
       </c>
       <c r="C53" s="5">
-        <v>408.29</v>
+        <v>381.44</v>
       </c>
       <c r="D53" s="5"/>
       <c r="E53" s="5">
-        <v>161.02</v>
+        <v>174.34</v>
       </c>
       <c r="F53" s="5"/>
       <c r="G53" s="5" t="s">
@@ -6520,17 +6555,17 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="6">
-        <v>46283.54166666666</v>
+        <v>46283.58333333334</v>
       </c>
       <c r="B54" s="5">
-        <v>525.1900000000001</v>
+        <v>509.83</v>
       </c>
       <c r="C54" s="5">
-        <v>408.14</v>
+        <v>381.26</v>
       </c>
       <c r="D54" s="5"/>
       <c r="E54" s="5">
-        <v>181.5</v>
+        <v>202.51</v>
       </c>
       <c r="F54" s="5"/>
       <c r="G54" s="5" t="s">
@@ -6539,17 +6574,17 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="6">
-        <v>46283.58333333334</v>
+        <v>46283.625</v>
       </c>
       <c r="B55" s="5">
-        <v>540.0700000000001</v>
+        <v>526.09</v>
       </c>
       <c r="C55" s="5">
-        <v>407.96</v>
+        <v>381.06</v>
       </c>
       <c r="D55" s="5"/>
       <c r="E55" s="5">
-        <v>209.94</v>
+        <v>226.74</v>
       </c>
       <c r="F55" s="5"/>
       <c r="G55" s="5" t="s">
@@ -6558,17 +6593,17 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="6">
-        <v>46283.625</v>
+        <v>46283.66666666666</v>
       </c>
       <c r="B56" s="5">
-        <v>556.13</v>
+        <v>540.84</v>
       </c>
       <c r="C56" s="5">
-        <v>407.77</v>
+        <v>380.86</v>
       </c>
       <c r="D56" s="5"/>
       <c r="E56" s="5">
-        <v>234.37</v>
+        <v>243.25</v>
       </c>
       <c r="F56" s="5"/>
       <c r="G56" s="5" t="s">
@@ -6577,17 +6612,17 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="6">
-        <v>46283.66666666666</v>
+        <v>46283.70833333334</v>
       </c>
       <c r="B57" s="5">
-        <v>570.71</v>
+        <v>551.61</v>
       </c>
       <c r="C57" s="5">
-        <v>407.57</v>
+        <v>380.65</v>
       </c>
       <c r="D57" s="5"/>
       <c r="E57" s="5">
-        <v>250.96</v>
+        <v>249.16</v>
       </c>
       <c r="F57" s="5"/>
       <c r="G57" s="5" t="s">
@@ -6596,17 +6631,17 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="6">
-        <v>46283.70833333334</v>
+        <v>46283.75</v>
       </c>
       <c r="B58" s="5">
-        <v>581.3200000000001</v>
+        <v>554.27</v>
       </c>
       <c r="C58" s="5">
-        <v>407.36</v>
+        <v>380.44</v>
       </c>
       <c r="D58" s="5"/>
       <c r="E58" s="5">
-        <v>256.77</v>
+        <v>235.49</v>
       </c>
       <c r="F58" s="5"/>
       <c r="G58" s="5" t="s">
@@ -6615,17 +6650,17 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="6">
-        <v>46283.75</v>
+        <v>46283.79166666666</v>
       </c>
       <c r="B59" s="5">
-        <v>583.8099999999999</v>
+        <v>549.63</v>
       </c>
       <c r="C59" s="5">
-        <v>407.15</v>
+        <v>380.22</v>
       </c>
       <c r="D59" s="5"/>
       <c r="E59" s="5">
-        <v>242.65</v>
+        <v>213.97</v>
       </c>
       <c r="F59" s="5"/>
       <c r="G59" s="5" t="s">
@@ -6634,17 +6669,17 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="6">
-        <v>46283.79166666666</v>
+        <v>46283.83333333334</v>
       </c>
       <c r="B60" s="5">
-        <v>578.8</v>
+        <v>542.7</v>
       </c>
       <c r="C60" s="5">
-        <v>406.94</v>
+        <v>380.01</v>
       </c>
       <c r="D60" s="5"/>
       <c r="E60" s="5">
-        <v>219.82</v>
+        <v>200.17</v>
       </c>
       <c r="F60" s="5"/>
       <c r="G60" s="5" t="s">
@@ -6653,17 +6688,17 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="6">
-        <v>46283.83333333334</v>
+        <v>46283.875</v>
       </c>
       <c r="B61" s="5">
-        <v>571.59</v>
+        <v>534.61</v>
       </c>
       <c r="C61" s="5">
-        <v>406.73</v>
+        <v>379.79</v>
       </c>
       <c r="D61" s="5"/>
       <c r="E61" s="5">
-        <v>205.64</v>
+        <v>187.26</v>
       </c>
       <c r="F61" s="5"/>
       <c r="G61" s="5" t="s">
@@ -6672,17 +6707,17 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="6">
-        <v>46283.875</v>
+        <v>46283.91666666666</v>
       </c>
       <c r="B62" s="5">
-        <v>563.28</v>
+        <v>523.98</v>
       </c>
       <c r="C62" s="5">
-        <v>406.51</v>
+        <v>379.58</v>
       </c>
       <c r="D62" s="5"/>
       <c r="E62" s="5">
-        <v>192.38</v>
+        <v>168.07</v>
       </c>
       <c r="F62" s="5"/>
       <c r="G62" s="5" t="s">
@@ -6691,17 +6726,17 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="6">
-        <v>46283.91666666666</v>
+        <v>46283.95833333334</v>
       </c>
       <c r="B63" s="5">
-        <v>552.27</v>
+        <v>514.1799999999999</v>
       </c>
       <c r="C63" s="5">
-        <v>406.3</v>
+        <v>379.36</v>
       </c>
       <c r="D63" s="5"/>
       <c r="E63" s="5">
-        <v>172</v>
+        <v>157.23</v>
       </c>
       <c r="F63" s="5"/>
       <c r="G63" s="5" t="s">
@@ -6710,17 +6745,17 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="6">
-        <v>46283.95833333334</v>
+        <v>46284</v>
       </c>
       <c r="B64" s="5">
-        <v>542.21</v>
+        <v>505.11</v>
       </c>
       <c r="C64" s="5">
-        <v>406.09</v>
+        <v>379.15</v>
       </c>
       <c r="D64" s="5"/>
       <c r="E64" s="5">
-        <v>160.91</v>
+        <v>147.09</v>
       </c>
       <c r="F64" s="5"/>
       <c r="G64" s="5" t="s">
@@ -6729,17 +6764,17 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="6">
-        <v>46284</v>
+        <v>46284.04166666666</v>
       </c>
       <c r="B65" s="5">
-        <v>532.96</v>
+        <v>494.66</v>
       </c>
       <c r="C65" s="5">
-        <v>405.88</v>
+        <v>379.01</v>
       </c>
       <c r="D65" s="5"/>
       <c r="E65" s="5">
-        <v>150.53</v>
+        <v>130.37</v>
       </c>
       <c r="F65" s="5"/>
       <c r="G65" s="5" t="s">
@@ -6748,17 +6783,17 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="6">
-        <v>46284.04166666666</v>
+        <v>46284.08333333334</v>
       </c>
       <c r="B66" s="5">
-        <v>522.17</v>
+        <v>485.75</v>
       </c>
       <c r="C66" s="5">
-        <v>405.74</v>
+        <v>378.92</v>
       </c>
       <c r="D66" s="5"/>
       <c r="E66" s="5">
-        <v>132.77</v>
+        <v>121.96</v>
       </c>
       <c r="F66" s="5"/>
       <c r="G66" s="5" t="s">
@@ -6767,17 +6802,17 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="6">
-        <v>46284.08333333334</v>
+        <v>46284.125</v>
       </c>
       <c r="B67" s="5">
-        <v>513.05</v>
+        <v>477.95</v>
       </c>
       <c r="C67" s="5">
-        <v>405.64</v>
+        <v>378.85</v>
       </c>
       <c r="D67" s="5"/>
       <c r="E67" s="5">
-        <v>124.21</v>
+        <v>114.1</v>
       </c>
       <c r="F67" s="5"/>
       <c r="G67" s="5" t="s">
@@ -6786,17 +6821,17 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="6">
-        <v>46284.125</v>
+        <v>46284.16666666666</v>
       </c>
       <c r="B68" s="5">
-        <v>505.12</v>
+        <v>470.99</v>
       </c>
       <c r="C68" s="5">
-        <v>405.58</v>
+        <v>378.8</v>
       </c>
       <c r="D68" s="5"/>
       <c r="E68" s="5">
-        <v>116.19</v>
+        <v>106.74</v>
       </c>
       <c r="F68" s="5"/>
       <c r="G68" s="5" t="s">
@@ -6805,17 +6840,17 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="6">
-        <v>46284.16666666666</v>
+        <v>46284.20833333334</v>
       </c>
       <c r="B69" s="5">
-        <v>498.07</v>
+        <v>464.69</v>
       </c>
       <c r="C69" s="5">
-        <v>405.53</v>
+        <v>378.76</v>
       </c>
       <c r="D69" s="5"/>
       <c r="E69" s="5">
-        <v>108.7</v>
+        <v>99.86</v>
       </c>
       <c r="F69" s="5"/>
       <c r="G69" s="5" t="s">
@@ -6824,17 +6859,17 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="6">
-        <v>46284.20833333334</v>
+        <v>46284.25</v>
       </c>
       <c r="B70" s="5">
-        <v>491.7</v>
+        <v>458.92</v>
       </c>
       <c r="C70" s="5">
-        <v>405.49</v>
+        <v>378.74</v>
       </c>
       <c r="D70" s="5"/>
       <c r="E70" s="5">
-        <v>101.69</v>
+        <v>93.42</v>
       </c>
       <c r="F70" s="5"/>
       <c r="G70" s="5" t="s">
@@ -6843,17 +6878,17 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="6">
-        <v>46284.25</v>
+        <v>46284.29166666666</v>
       </c>
       <c r="B71" s="5">
-        <v>485.89</v>
+        <v>453.6</v>
       </c>
       <c r="C71" s="5">
-        <v>405.46</v>
+        <v>378.71</v>
       </c>
       <c r="D71" s="5"/>
       <c r="E71" s="5">
-        <v>95.13</v>
+        <v>87.39</v>
       </c>
       <c r="F71" s="5"/>
       <c r="G71" s="5" t="s">
@@ -6862,17 +6897,17 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="6">
-        <v>46284.29166666666</v>
+        <v>46284.33333333334</v>
       </c>
       <c r="B72" s="5">
-        <v>480.54</v>
+        <v>448.67</v>
       </c>
       <c r="C72" s="5">
-        <v>405.44</v>
+        <v>378.69</v>
       </c>
       <c r="D72" s="5"/>
       <c r="E72" s="5">
-        <v>89</v>
+        <v>81.75</v>
       </c>
       <c r="F72" s="5"/>
       <c r="G72" s="5" t="s">
@@ -6881,17 +6916,17 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="6">
-        <v>46284.33333333334</v>
+        <v>46284.375</v>
       </c>
       <c r="B73" s="5">
-        <v>475.58</v>
+        <v>444.09</v>
       </c>
       <c r="C73" s="5">
-        <v>405.41</v>
+        <v>378.67</v>
       </c>
       <c r="D73" s="5"/>
       <c r="E73" s="5">
-        <v>83.26000000000001</v>
+        <v>76.48</v>
       </c>
       <c r="F73" s="5"/>
       <c r="G73" s="5" t="s">
@@ -6900,17 +6935,17 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="6">
-        <v>46284.375</v>
+        <v>46284.41666666666</v>
       </c>
       <c r="B74" s="5">
-        <v>470.99</v>
+        <v>439.82</v>
       </c>
       <c r="C74" s="5">
-        <v>405.4</v>
+        <v>378.65</v>
       </c>
       <c r="D74" s="5"/>
       <c r="E74" s="5">
-        <v>77.89</v>
+        <v>71.55</v>
       </c>
       <c r="F74" s="5"/>
       <c r="G74" s="5" t="s">
@@ -6919,17 +6954,17 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="6">
-        <v>46284.41666666666</v>
+        <v>46284.45833333334</v>
       </c>
       <c r="B75" s="5">
-        <v>466.71</v>
+        <v>435.84</v>
       </c>
       <c r="C75" s="5">
-        <v>405.38</v>
+        <v>378.64</v>
       </c>
       <c r="D75" s="5"/>
       <c r="E75" s="5">
-        <v>72.86</v>
+        <v>66.94</v>
       </c>
       <c r="F75" s="5"/>
       <c r="G75" s="5" t="s">
@@ -6938,17 +6973,17 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="6">
-        <v>46284.45833333334</v>
+        <v>46284.5</v>
       </c>
       <c r="B76" s="5">
-        <v>462.71</v>
+        <v>432.13</v>
       </c>
       <c r="C76" s="5">
-        <v>405.36</v>
+        <v>378.62</v>
       </c>
       <c r="D76" s="5"/>
       <c r="E76" s="5">
-        <v>68.17</v>
+        <v>62.62</v>
       </c>
       <c r="F76" s="5"/>
       <c r="G76" s="5" t="s">
@@ -6957,17 +6992,17 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="6">
-        <v>46284.5</v>
+        <v>46284.54166666666</v>
       </c>
       <c r="B77" s="5">
-        <v>458.99</v>
+        <v>428.66</v>
       </c>
       <c r="C77" s="5">
-        <v>405.35</v>
+        <v>378.61</v>
       </c>
       <c r="D77" s="5"/>
       <c r="E77" s="5">
-        <v>63.77</v>
+        <v>58.58</v>
       </c>
       <c r="F77" s="5"/>
       <c r="G77" s="5" t="s">
@@ -7615,7 +7650,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="9" width="16.7109375" customWidth="1"/>
@@ -7669,19 +7704,19 @@
         <v>24</v>
       </c>
       <c r="D4" s="5">
-        <v>88.89700000000001</v>
+        <v>62.867</v>
       </c>
       <c r="E4" s="5">
-        <v>104.957</v>
+        <v>89.024</v>
       </c>
       <c r="F4" s="5">
-        <v>82.65300000000001</v>
+        <v>53.411</v>
       </c>
       <c r="G4" s="5">
-        <v>41.7</v>
+        <v>62.5</v>
       </c>
       <c r="H4" s="5">
-        <v>66.7</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -7692,22 +7727,22 @@
         <v>62</v>
       </c>
       <c r="C5" s="5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D5" s="5">
-        <v>83.06</v>
+        <v>59.58</v>
       </c>
       <c r="E5" s="5">
-        <v>100.912</v>
+        <v>84.718</v>
       </c>
       <c r="F5" s="5">
-        <v>75.29300000000001</v>
+        <v>45.353</v>
       </c>
       <c r="G5" s="5">
-        <v>46.2</v>
+        <v>66.7</v>
       </c>
       <c r="H5" s="5">
-        <v>69.2</v>
+        <v>77.8</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -7718,22 +7753,22 @@
         <v>63</v>
       </c>
       <c r="C6" s="5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D6" s="5">
-        <v>83.06</v>
+        <v>59.58</v>
       </c>
       <c r="E6" s="5">
-        <v>100.912</v>
+        <v>84.718</v>
       </c>
       <c r="F6" s="5">
-        <v>75.29300000000001</v>
+        <v>45.353</v>
       </c>
       <c r="G6" s="5">
-        <v>46.2</v>
+        <v>66.7</v>
       </c>
       <c r="H6" s="5">
-        <v>69.2</v>
+        <v>77.8</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -7879,13 +7914,13 @@
         <v>526.49</v>
       </c>
       <c r="C19" s="5">
-        <v>509.02</v>
+        <v>482.83</v>
       </c>
       <c r="D19" s="5">
-        <v>396.15</v>
+        <v>369.3</v>
       </c>
       <c r="E19" s="5">
-        <v>-17.47000000000003</v>
+        <v>-43.66000000000003</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -7893,16 +7928,16 @@
         <v>46280.5</v>
       </c>
       <c r="B20" s="5">
-        <v>566.35</v>
+        <v>566.6799999999999</v>
       </c>
       <c r="C20" s="5">
-        <v>557.79</v>
+        <v>531.75</v>
       </c>
       <c r="D20" s="5">
-        <v>417.12</v>
+        <v>389.26</v>
       </c>
       <c r="E20" s="5">
-        <v>-8.560000000000059</v>
+        <v>-34.92999999999995</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -7910,16 +7945,16 @@
         <v>46280.54166666666</v>
       </c>
       <c r="B21" s="5">
-        <v>558.29</v>
+        <v>559.84</v>
       </c>
       <c r="C21" s="5">
-        <v>604.5700000000001</v>
+        <v>581.11</v>
       </c>
       <c r="D21" s="5">
-        <v>425.98</v>
+        <v>399.82</v>
       </c>
       <c r="E21" s="5">
-        <v>46.28000000000009</v>
+        <v>21.26999999999998</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -7927,16 +7962,16 @@
         <v>46280.58333333334</v>
       </c>
       <c r="B22" s="5">
-        <v>478.6</v>
+        <v>483.67</v>
       </c>
       <c r="C22" s="5">
-        <v>621.7</v>
+        <v>598.0599999999999</v>
       </c>
       <c r="D22" s="5">
-        <v>405.78</v>
+        <v>378.34</v>
       </c>
       <c r="E22" s="5">
-        <v>143.1</v>
+        <v>114.3899999999999</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -7944,16 +7979,16 @@
         <v>46280.625</v>
       </c>
       <c r="B23" s="5">
-        <v>445.28</v>
+        <v>443.5</v>
       </c>
       <c r="C23" s="5">
-        <v>627.91</v>
+        <v>605.61</v>
       </c>
       <c r="D23" s="5">
-        <v>379.13</v>
+        <v>351.82</v>
       </c>
       <c r="E23" s="5">
-        <v>182.63</v>
+        <v>162.11</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -7961,16 +7996,16 @@
         <v>46280.66666666666</v>
       </c>
       <c r="B24" s="5">
-        <v>452.23</v>
+        <v>444.63</v>
       </c>
       <c r="C24" s="5">
-        <v>645.78</v>
+        <v>623.9</v>
       </c>
       <c r="D24" s="5">
-        <v>372.67</v>
+        <v>344.53</v>
       </c>
       <c r="E24" s="5">
-        <v>193.55</v>
+        <v>179.27</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -7978,16 +8013,16 @@
         <v>46280.70833333334</v>
       </c>
       <c r="B25" s="5">
-        <v>437.41</v>
+        <v>427.25</v>
       </c>
       <c r="C25" s="5">
-        <v>649.2</v>
+        <v>629.17</v>
       </c>
       <c r="D25" s="5">
-        <v>369.14</v>
+        <v>341.71</v>
       </c>
       <c r="E25" s="5">
-        <v>211.79</v>
+        <v>201.92</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -7995,16 +8030,16 @@
         <v>46280.75</v>
       </c>
       <c r="B26" s="5">
-        <v>457.95</v>
+        <v>455.12</v>
       </c>
       <c r="C26" s="5">
-        <v>639.42</v>
+        <v>621.54</v>
       </c>
       <c r="D26" s="5">
-        <v>356.24</v>
+        <v>330.14</v>
       </c>
       <c r="E26" s="5">
-        <v>181.47</v>
+        <v>166.42</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -8012,16 +8047,16 @@
         <v>46280.79166666666</v>
       </c>
       <c r="B27" s="5">
-        <v>691.9</v>
+        <v>695.88</v>
       </c>
       <c r="C27" s="5">
-        <v>616.97</v>
+        <v>599.1900000000001</v>
       </c>
       <c r="D27" s="5">
-        <v>336.5</v>
+        <v>310.12</v>
       </c>
       <c r="E27" s="5">
-        <v>-74.92999999999995</v>
+        <v>-96.68999999999994</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -8029,16 +8064,16 @@
         <v>46280.83333333334</v>
       </c>
       <c r="B28" s="5">
-        <v>528.5</v>
+        <v>553.27</v>
       </c>
       <c r="C28" s="5">
-        <v>616.55</v>
+        <v>602.3099999999999</v>
       </c>
       <c r="D28" s="5">
-        <v>349.93</v>
+        <v>327.52</v>
       </c>
       <c r="E28" s="5">
-        <v>88.04999999999995</v>
+        <v>49.03999999999996</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -8046,16 +8081,16 @@
         <v>46280.875</v>
       </c>
       <c r="B29" s="5">
-        <v>508.07</v>
+        <v>505.91</v>
       </c>
       <c r="C29" s="5">
-        <v>616.47</v>
+        <v>598.23</v>
       </c>
       <c r="D29" s="5">
-        <v>366.09</v>
+        <v>340.37</v>
       </c>
       <c r="E29" s="5">
-        <v>108.4</v>
+        <v>92.31999999999999</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -8063,16 +8098,16 @@
         <v>46280.91666666666</v>
       </c>
       <c r="B30" s="5">
-        <v>450.43</v>
+        <v>450.34</v>
       </c>
       <c r="C30" s="5">
-        <v>603.0700000000001</v>
+        <v>582.37</v>
       </c>
       <c r="D30" s="5">
-        <v>367.22</v>
+        <v>339.82</v>
       </c>
       <c r="E30" s="5">
-        <v>152.64</v>
+        <v>132.03</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -8080,16 +8115,16 @@
         <v>46280.95833333334</v>
       </c>
       <c r="B31" s="5">
-        <v>453.25</v>
+        <v>455.13</v>
       </c>
       <c r="C31" s="5">
-        <v>566.05</v>
+        <v>544.97</v>
       </c>
       <c r="D31" s="5">
-        <v>342.82</v>
+        <v>315.95</v>
       </c>
       <c r="E31" s="5">
-        <v>112.8</v>
+        <v>89.84000000000003</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -8100,13 +8135,13 @@
         <v>507.31</v>
       </c>
       <c r="C32" s="5">
-        <v>554.72</v>
+        <v>531.85</v>
       </c>
       <c r="D32" s="5">
-        <v>342.02</v>
+        <v>314.43</v>
       </c>
       <c r="E32" s="5">
-        <v>47.41000000000003</v>
+        <v>24.54000000000002</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -8114,16 +8149,16 @@
         <v>46281.04166666666</v>
       </c>
       <c r="B33" s="5">
-        <v>521.49</v>
+        <v>521.25</v>
       </c>
       <c r="C33" s="5">
-        <v>566.49</v>
+        <v>539.78</v>
       </c>
       <c r="D33" s="5">
-        <v>362.01</v>
+        <v>331.87</v>
       </c>
       <c r="E33" s="5">
-        <v>45</v>
+        <v>18.52999999999997</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -8134,13 +8169,13 @@
         <v>525.3</v>
       </c>
       <c r="C34" s="5">
-        <v>575.37</v>
+        <v>548.39</v>
       </c>
       <c r="D34" s="5">
-        <v>376.71</v>
+        <v>347.84</v>
       </c>
       <c r="E34" s="5">
-        <v>50.07000000000005</v>
+        <v>23.09000000000003</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -8148,16 +8183,16 @@
         <v>46281.125</v>
       </c>
       <c r="B35" s="5">
-        <v>530.12</v>
+        <v>529.76</v>
       </c>
       <c r="C35" s="5">
-        <v>576.76</v>
+        <v>548.83</v>
       </c>
       <c r="D35" s="5">
-        <v>381.61</v>
+        <v>353.55</v>
       </c>
       <c r="E35" s="5">
-        <v>46.63999999999999</v>
+        <v>19.07000000000005</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -8165,16 +8200,16 @@
         <v>46281.16666666666</v>
       </c>
       <c r="B36" s="5">
-        <v>538.4</v>
+        <v>537</v>
       </c>
       <c r="C36" s="5">
-        <v>578.2</v>
+        <v>547.6</v>
       </c>
       <c r="D36" s="5">
-        <v>384.52</v>
+        <v>355.73</v>
       </c>
       <c r="E36" s="5">
-        <v>39.80000000000007</v>
+        <v>10.60000000000002</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -8182,16 +8217,16 @@
         <v>46281.20833333334</v>
       </c>
       <c r="B37" s="5">
-        <v>536.5</v>
+        <v>536.16</v>
       </c>
       <c r="C37" s="5">
-        <v>581.72</v>
+        <v>549.04</v>
       </c>
       <c r="D37" s="5">
-        <v>388</v>
+        <v>359.13</v>
       </c>
       <c r="E37" s="5">
-        <v>45.22000000000003</v>
+        <v>12.88</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -8199,16 +8234,16 @@
         <v>46281.25</v>
       </c>
       <c r="B38" s="5">
-        <v>535.3</v>
+        <v>535.1</v>
       </c>
       <c r="C38" s="5">
-        <v>589.0700000000001</v>
+        <v>554.77</v>
       </c>
       <c r="D38" s="5">
-        <v>394.59</v>
+        <v>366.05</v>
       </c>
       <c r="E38" s="5">
-        <v>53.7700000000001</v>
+        <v>19.66999999999996</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -8216,16 +8251,16 @@
         <v>46281.29166666666</v>
       </c>
       <c r="B39" s="5">
-        <v>523.7</v>
+        <v>525.3</v>
       </c>
       <c r="C39" s="5">
-        <v>592.83</v>
+        <v>557.0700000000001</v>
       </c>
       <c r="D39" s="5">
-        <v>397.7</v>
+        <v>369.44</v>
       </c>
       <c r="E39" s="5">
-        <v>69.13</v>
+        <v>31.7700000000001</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -8233,16 +8268,16 @@
         <v>46281.33333333334</v>
       </c>
       <c r="B40" s="5">
-        <v>533.33</v>
+        <v>534.39</v>
       </c>
       <c r="C40" s="5">
-        <v>592.15</v>
+        <v>555.21</v>
       </c>
       <c r="D40" s="5">
-        <v>398.17</v>
+        <v>369.94</v>
       </c>
       <c r="E40" s="5">
-        <v>58.81999999999994</v>
+        <v>20.82000000000005</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -8250,16 +8285,16 @@
         <v>46281.375</v>
       </c>
       <c r="B41" s="5">
-        <v>542.7</v>
+        <v>542.6</v>
       </c>
       <c r="C41" s="5">
-        <v>591.4</v>
+        <v>553.6900000000001</v>
       </c>
       <c r="D41" s="5">
-        <v>400.06</v>
+        <v>371.83</v>
       </c>
       <c r="E41" s="5">
-        <v>48.69999999999993</v>
+        <v>11.09000000000003</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -8267,16 +8302,16 @@
         <v>46281.41666666666</v>
       </c>
       <c r="B42" s="5">
-        <v>542.28</v>
+        <v>542.2</v>
       </c>
       <c r="C42" s="5">
-        <v>589.14</v>
+        <v>550.79</v>
       </c>
       <c r="D42" s="5">
-        <v>400.2</v>
+        <v>371.95</v>
       </c>
       <c r="E42" s="5">
-        <v>46.86000000000001</v>
+        <v>8.589999999999918</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -8284,16 +8319,16 @@
         <v>46281.45833333334</v>
       </c>
       <c r="B43" s="5">
-        <v>538.6</v>
+        <v>540.48</v>
       </c>
       <c r="C43" s="5">
-        <v>582.91</v>
+        <v>544.22</v>
       </c>
       <c r="D43" s="5">
-        <v>396.52</v>
+        <v>368.3</v>
       </c>
       <c r="E43" s="5">
-        <v>44.30999999999995</v>
+        <v>3.740000000000009</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -8301,16 +8336,33 @@
         <v>46281.5</v>
       </c>
       <c r="B44" s="5">
-        <v>537.65</v>
+        <v>537.9</v>
       </c>
       <c r="C44" s="5">
-        <v>579.8</v>
+        <v>541.5</v>
       </c>
       <c r="D44" s="5">
-        <v>396.07</v>
+        <v>368.27</v>
       </c>
       <c r="E44" s="5">
-        <v>42.14999999999998</v>
+        <v>3.600000000000023</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6">
+        <v>46281.54166666666</v>
+      </c>
+      <c r="B45" s="5">
+        <v>555.78</v>
+      </c>
+      <c r="C45" s="5">
+        <v>539</v>
+      </c>
+      <c r="D45" s="5">
+        <v>369.22</v>
+      </c>
+      <c r="E45" s="5">
+        <v>-16.77999999999997</v>
       </c>
     </row>
   </sheetData>
@@ -8357,19 +8409,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="6">
-        <v>46281.5</v>
+        <v>46281.54166666666</v>
       </c>
       <c r="B2" s="5">
-        <v>1.94</v>
+        <v>1.4</v>
       </c>
       <c r="C2" s="5">
-        <v>-13.07</v>
+        <v>-13.26</v>
       </c>
       <c r="D2" s="5">
-        <v>15.12</v>
+        <v>14.81</v>
       </c>
       <c r="E2" s="5">
-        <v>60.7</v>
+        <v>64.5</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>82</v>
@@ -8380,19 +8432,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="6">
-        <v>46281.625</v>
+        <v>46281.66666666666</v>
       </c>
       <c r="B3" s="5">
-        <v>1.79</v>
+        <v>1.29</v>
       </c>
       <c r="C3" s="5">
-        <v>-12.36</v>
+        <v>-11.99</v>
       </c>
       <c r="D3" s="5">
-        <v>14.25</v>
+        <v>13.44</v>
       </c>
       <c r="E3" s="5">
-        <v>58.6</v>
+        <v>60.2</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>82</v>
@@ -8403,19 +8455,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="6">
-        <v>46281.75</v>
+        <v>46281.79166666666</v>
       </c>
       <c r="B4" s="5">
-        <v>1.64</v>
+        <v>1.18</v>
       </c>
       <c r="C4" s="5">
-        <v>-11.33</v>
+        <v>-12.15</v>
       </c>
       <c r="D4" s="5">
-        <v>13.06</v>
+        <v>13.5</v>
       </c>
       <c r="E4" s="5">
-        <v>55.2</v>
+        <v>61.3</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>82</v>
@@ -8426,19 +8478,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="6">
-        <v>46281.875</v>
+        <v>46281.91666666666</v>
       </c>
       <c r="B5" s="5">
-        <v>1.51</v>
+        <v>1.09</v>
       </c>
       <c r="C5" s="5">
-        <v>-12.86</v>
+        <v>-13.17</v>
       </c>
       <c r="D5" s="5">
-        <v>14.45</v>
+        <v>14.43</v>
       </c>
       <c r="E5" s="5">
-        <v>61.6</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>82</v>
@@ -8449,19 +8501,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="6">
-        <v>46282</v>
+        <v>46282.04166666666</v>
       </c>
       <c r="B6" s="5">
-        <v>1.39</v>
+        <v>1</v>
       </c>
       <c r="C6" s="5">
-        <v>-12.82</v>
+        <v>-12.54</v>
       </c>
       <c r="D6" s="5">
-        <v>14.28</v>
+        <v>13.72</v>
       </c>
       <c r="E6" s="5">
-        <v>61.9</v>
+        <v>63.7</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>82</v>
@@ -8472,19 +8524,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="6">
-        <v>46282.125</v>
+        <v>46282.16666666666</v>
       </c>
       <c r="B7" s="5">
-        <v>1.28</v>
+        <v>0.92</v>
       </c>
       <c r="C7" s="5">
-        <v>-12.87</v>
+        <v>-13.44</v>
       </c>
       <c r="D7" s="5">
-        <v>14.22</v>
+        <v>14.55</v>
       </c>
       <c r="E7" s="5">
-        <v>62.6</v>
+        <v>67.5</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>82</v>
@@ -8495,19 +8547,19 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="6">
-        <v>46282.25</v>
+        <v>46282.29166666666</v>
       </c>
       <c r="B8" s="5">
-        <v>1.18</v>
+        <v>0.85</v>
       </c>
       <c r="C8" s="5">
-        <v>-13.83</v>
+        <v>-13.81</v>
       </c>
       <c r="D8" s="5">
-        <v>15.07</v>
+        <v>14.85</v>
       </c>
       <c r="E8" s="5">
-        <v>66.7</v>
+        <v>69.3</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>82</v>
@@ -8518,19 +8570,19 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="6">
-        <v>46282.375</v>
+        <v>46282.41666666666</v>
       </c>
       <c r="B9" s="5">
-        <v>1.08</v>
+        <v>0.78</v>
       </c>
       <c r="C9" s="5">
-        <v>-13.9</v>
+        <v>-13.95</v>
       </c>
       <c r="D9" s="5">
-        <v>15.04</v>
+        <v>14.93</v>
       </c>
       <c r="E9" s="5">
-        <v>67.5</v>
+        <v>70.2</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>82</v>
@@ -8541,19 +8593,19 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="6">
-        <v>46282.5</v>
+        <v>46282.54166666666</v>
       </c>
       <c r="B10" s="5">
-        <v>1</v>
+        <v>0.72</v>
       </c>
       <c r="C10" s="5">
-        <v>-14.01</v>
+        <v>-13.94</v>
       </c>
       <c r="D10" s="5">
-        <v>15.06</v>
+        <v>14.86</v>
       </c>
       <c r="E10" s="5">
-        <v>68.3</v>
+        <v>70.5</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>82</v>
@@ -8564,19 +8616,19 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="6">
-        <v>46282.625</v>
+        <v>46282.66666666666</v>
       </c>
       <c r="B11" s="5">
-        <v>0.92</v>
+        <v>0.66</v>
       </c>
       <c r="C11" s="5">
-        <v>-13.23</v>
+        <v>-12.62</v>
       </c>
       <c r="D11" s="5">
-        <v>14.19</v>
+        <v>13.48</v>
       </c>
       <c r="E11" s="5">
-        <v>65.8</v>
+        <v>65.7</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>82</v>
@@ -8587,19 +8639,19 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="6">
-        <v>46282.75</v>
+        <v>46282.79166666666</v>
       </c>
       <c r="B12" s="5">
-        <v>0.84</v>
+        <v>0.61</v>
       </c>
       <c r="C12" s="5">
-        <v>-11.14</v>
+        <v>-10.28</v>
       </c>
       <c r="D12" s="5">
-        <v>12.03</v>
+        <v>11.09</v>
       </c>
       <c r="E12" s="5">
-        <v>58.2</v>
+        <v>57.1</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>82</v>
@@ -8610,19 +8662,19 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="6">
-        <v>46282.875</v>
+        <v>46282.91666666666</v>
       </c>
       <c r="B13" s="5">
-        <v>0.78</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="C13" s="5">
-        <v>-8.68</v>
+        <v>-7.88</v>
       </c>
       <c r="D13" s="5">
-        <v>9.5</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="E13" s="5">
-        <v>49.2</v>
+        <v>48.3</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>87</v>
@@ -8633,19 +8685,19 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="6">
-        <v>46283</v>
+        <v>46283.04166666666</v>
       </c>
       <c r="B14" s="5">
-        <v>0.71</v>
+        <v>0.51</v>
       </c>
       <c r="C14" s="5">
-        <v>-6.67</v>
+        <v>-6.09</v>
       </c>
       <c r="D14" s="5">
-        <v>7.41</v>
+        <v>6.81</v>
       </c>
       <c r="E14" s="5">
-        <v>41.9</v>
+        <v>41.7</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>87</v>
@@ -8656,19 +8708,19 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="6">
-        <v>46283.125</v>
+        <v>46283.16666666666</v>
       </c>
       <c r="B15" s="5">
-        <v>0.66</v>
+        <v>0.47</v>
       </c>
       <c r="C15" s="5">
-        <v>-5.63</v>
+        <v>-5.97</v>
       </c>
       <c r="D15" s="5">
-        <v>6.32</v>
+        <v>6.65</v>
       </c>
       <c r="E15" s="5">
-        <v>38.2</v>
+        <v>41.5</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>87</v>
@@ -8679,19 +8731,19 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="6">
-        <v>46283.25</v>
+        <v>46283.29166666666</v>
       </c>
       <c r="B16" s="5">
-        <v>0.6</v>
+        <v>0.44</v>
       </c>
       <c r="C16" s="5">
-        <v>-7.14</v>
+        <v>-7.71</v>
       </c>
       <c r="D16" s="5">
-        <v>7.77</v>
+        <v>8.35</v>
       </c>
       <c r="E16" s="5">
-        <v>44.3</v>
+        <v>48.3</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>87</v>
@@ -8702,22 +8754,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="6">
-        <v>46283.375</v>
+        <v>46283.41666666666</v>
       </c>
       <c r="B17" s="5">
-        <v>0.5600000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="C17" s="5">
-        <v>-9.33</v>
+        <v>-10.05</v>
       </c>
       <c r="D17" s="5">
-        <v>9.91</v>
+        <v>10.66</v>
       </c>
       <c r="E17" s="5">
-        <v>52.9</v>
+        <v>57.4</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="G17" s="5" t="s">
         <v>88</v>
@@ -8725,19 +8777,19 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="6">
-        <v>46283.5</v>
+        <v>46283.54166666666</v>
       </c>
       <c r="B18" s="5">
-        <v>0.51</v>
+        <v>0.37</v>
       </c>
       <c r="C18" s="5">
-        <v>-11.78</v>
+        <v>-12.38</v>
       </c>
       <c r="D18" s="5">
-        <v>12.31</v>
+        <v>12.97</v>
       </c>
       <c r="E18" s="5">
-        <v>62.4</v>
+        <v>66.5</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>82</v>
@@ -8748,19 +8800,19 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="6">
-        <v>46283.625</v>
+        <v>46283.66666666666</v>
       </c>
       <c r="B19" s="5">
-        <v>0.47</v>
+        <v>0.34</v>
       </c>
       <c r="C19" s="5">
-        <v>-13.61</v>
+        <v>-13.79</v>
       </c>
       <c r="D19" s="5">
-        <v>14.09</v>
+        <v>14.35</v>
       </c>
       <c r="E19" s="5">
-        <v>69.59999999999999</v>
+        <v>72</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>82</v>
@@ -8771,19 +8823,19 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="6">
-        <v>46283.75</v>
+        <v>46283.79166666666</v>
       </c>
       <c r="B20" s="5">
-        <v>0.43</v>
+        <v>0.31</v>
       </c>
       <c r="C20" s="5">
-        <v>-14.01</v>
+        <v>-13.63</v>
       </c>
       <c r="D20" s="5">
-        <v>14.46</v>
+        <v>14.17</v>
       </c>
       <c r="E20" s="5">
-        <v>71.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>82</v>
@@ -8794,19 +8846,19 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="6">
-        <v>46283.875</v>
+        <v>46283.91666666666</v>
       </c>
       <c r="B21" s="5">
-        <v>0.4</v>
+        <v>0.29</v>
       </c>
       <c r="C21" s="5">
-        <v>-12.81</v>
+        <v>-11.99</v>
       </c>
       <c r="D21" s="5">
-        <v>13.22</v>
+        <v>12.5</v>
       </c>
       <c r="E21" s="5">
-        <v>67</v>
+        <v>65.5</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>82</v>
@@ -8817,19 +8869,19 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="6">
-        <v>46284</v>
+        <v>46284.04166666666</v>
       </c>
       <c r="B22" s="5">
-        <v>0.39</v>
+        <v>0.28</v>
       </c>
       <c r="C22" s="5">
-        <v>-10.58</v>
+        <v>-9.619999999999999</v>
       </c>
       <c r="D22" s="5">
-        <v>10.98</v>
+        <v>10.12</v>
       </c>
       <c r="E22" s="5">
-        <v>58.5</v>
+        <v>56.5</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>82</v>
@@ -8840,19 +8892,19 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="6">
-        <v>46284.125</v>
+        <v>46284.16666666666</v>
       </c>
       <c r="B23" s="5">
-        <v>0.39</v>
+        <v>0.28</v>
       </c>
       <c r="C23" s="5">
-        <v>-8.23</v>
+        <v>-7.41</v>
       </c>
       <c r="D23" s="5">
-        <v>8.630000000000001</v>
+        <v>7.92</v>
       </c>
       <c r="E23" s="5">
-        <v>49.6</v>
+        <v>48.1</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>87</v>
@@ -8863,19 +8915,19 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="6">
-        <v>46284.25</v>
+        <v>46284.29166666666</v>
       </c>
       <c r="B24" s="5">
-        <v>0.39</v>
+        <v>0.28</v>
       </c>
       <c r="C24" s="5">
-        <v>-6.45</v>
+        <v>-5.88</v>
       </c>
       <c r="D24" s="5">
-        <v>6.85</v>
+        <v>6.38</v>
       </c>
       <c r="E24" s="5">
-        <v>42.9</v>
+        <v>42.3</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>87</v>
@@ -8886,19 +8938,19 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="6">
-        <v>46284.375</v>
+        <v>46284.41666666666</v>
       </c>
       <c r="B25" s="5">
-        <v>0.39</v>
+        <v>0.28</v>
       </c>
       <c r="C25" s="5">
-        <v>-5.4</v>
+        <v>-5.12</v>
       </c>
       <c r="D25" s="5">
-        <v>5.8</v>
+        <v>5.54</v>
       </c>
       <c r="E25" s="5">
-        <v>38.9</v>
+        <v>39.1</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>87</v>
@@ -8909,19 +8961,19 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="6">
-        <v>46284.5</v>
+        <v>46284.54166666666</v>
       </c>
       <c r="B26" s="5">
-        <v>0.39</v>
+        <v>0.28</v>
       </c>
       <c r="C26" s="5">
-        <v>-4.97</v>
+        <v>-4.93</v>
       </c>
       <c r="D26" s="5">
-        <v>5.3</v>
+        <v>5.17</v>
       </c>
       <c r="E26" s="5">
-        <v>37</v>
+        <v>37.7</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>87</v>
@@ -9020,7 +9072,7 @@
         <v>116.8</v>
       </c>
       <c r="J2" s="5">
-        <v>97.65000000000001</v>
+        <v>93.27</v>
       </c>
       <c r="K2" s="5">
         <v>-34</v>
@@ -9064,7 +9116,7 @@
         <v>68</v>
       </c>
       <c r="J3" s="5">
-        <v>101.6</v>
+        <v>97.39</v>
       </c>
       <c r="K3" s="5">
         <v>-60</v>
@@ -9108,7 +9160,7 @@
         <v>66.5</v>
       </c>
       <c r="J4" s="5">
-        <v>101.72</v>
+        <v>97.52</v>
       </c>
       <c r="K4" s="5">
         <v>-38</v>
@@ -9152,7 +9204,7 @@
         <v>352</v>
       </c>
       <c r="J5" s="5">
-        <v>106.74</v>
+        <v>97.63</v>
       </c>
       <c r="K5" s="5">
         <v>-18</v>
@@ -9196,7 +9248,7 @@
         <v>88</v>
       </c>
       <c r="J6" s="5">
-        <v>99.98</v>
+        <v>95.7</v>
       </c>
       <c r="K6" s="5">
         <v>-18</v>
@@ -9240,7 +9292,7 @@
         <v>71.2</v>
       </c>
       <c r="J7" s="5">
-        <v>101.33</v>
+        <v>97.11</v>
       </c>
       <c r="K7" s="5">
         <v>0</v>
@@ -9284,7 +9336,7 @@
         <v>72.8</v>
       </c>
       <c r="J8" s="5">
-        <v>101.21</v>
+        <v>96.98999999999999</v>
       </c>
       <c r="K8" s="5">
         <v>65</v>
@@ -9328,7 +9380,7 @@
         <v>91.2</v>
       </c>
       <c r="J9" s="5">
-        <v>99.70999999999999</v>
+        <v>95.42</v>
       </c>
       <c r="K9" s="5">
         <v>35</v>
@@ -9372,7 +9424,7 @@
         <v>193.8</v>
       </c>
       <c r="J10" s="5">
-        <v>91.42</v>
+        <v>86.76000000000001</v>
       </c>
       <c r="K10" s="5">
         <v>159</v>
@@ -9416,7 +9468,7 @@
         <v>510</v>
       </c>
       <c r="J11" s="5">
-        <v>215.17</v>
+        <v>210.74</v>
       </c>
       <c r="K11" s="5">
         <v>0</v>
@@ -9460,7 +9512,7 @@
         <v>138.5</v>
       </c>
       <c r="J12" s="5">
-        <v>95.89</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="K12" s="5">
         <v>122</v>
@@ -9504,7 +9556,7 @@
         <v>282</v>
       </c>
       <c r="J13" s="5">
-        <v>109.57</v>
+        <v>100.59</v>
       </c>
       <c r="K13" s="5">
         <v>29</v>
@@ -9548,7 +9600,7 @@
         <v>137.2</v>
       </c>
       <c r="J14" s="5">
-        <v>95.98999999999999</v>
+        <v>91.53</v>
       </c>
       <c r="K14" s="5">
         <v>134</v>
@@ -9592,7 +9644,7 @@
         <v>116</v>
       </c>
       <c r="J15" s="5">
-        <v>97.70999999999999</v>
+        <v>93.33</v>
       </c>
       <c r="K15" s="5">
         <v>92</v>
@@ -9636,7 +9688,7 @@
         <v>77</v>
       </c>
       <c r="J16" s="5">
-        <v>100.87</v>
+        <v>96.63</v>
       </c>
       <c r="K16" s="5">
         <v>-100</v>
@@ -9680,7 +9732,7 @@
         <v>396.5</v>
       </c>
       <c r="J17" s="5">
-        <v>75</v>
+        <v>69.62</v>
       </c>
       <c r="K17" s="5">
         <v>39</v>
@@ -9724,7 +9776,7 @@
         <v>326.2</v>
       </c>
       <c r="J18" s="5">
-        <v>80.69</v>
+        <v>75.56</v>
       </c>
       <c r="K18" s="5">
         <v>39</v>
@@ -9768,7 +9820,7 @@
         <v>97.8</v>
       </c>
       <c r="J19" s="5">
-        <v>99.19</v>
+        <v>94.87</v>
       </c>
       <c r="K19" s="5">
         <v>129</v>
@@ -9812,7 +9864,7 @@
         <v>107</v>
       </c>
       <c r="J20" s="5">
-        <v>98.44</v>
+        <v>94.09</v>
       </c>
       <c r="K20" s="5">
         <v>0</v>
@@ -9856,7 +9908,7 @@
         <v>55.8</v>
       </c>
       <c r="J21" s="5">
-        <v>102.59</v>
+        <v>98.42</v>
       </c>
       <c r="K21" s="5">
         <v>88</v>
@@ -9900,7 +9952,7 @@
         <v>207</v>
       </c>
       <c r="J22" s="5">
-        <v>227.43</v>
+        <v>223.55</v>
       </c>
       <c r="K22" s="5">
         <v>5</v>
@@ -9944,7 +9996,7 @@
         <v>173.4</v>
       </c>
       <c r="J23" s="5">
-        <v>189.86</v>
+        <v>198.68</v>
       </c>
       <c r="K23" s="5">
         <v>29</v>
@@ -9988,7 +10040,7 @@
         <v>57</v>
       </c>
       <c r="J24" s="5">
-        <v>102.49</v>
+        <v>98.31999999999999</v>
       </c>
       <c r="K24" s="5">
         <v>-90</v>
@@ -10032,7 +10084,7 @@
         <v>76.2</v>
       </c>
       <c r="J25" s="5">
-        <v>100.93</v>
+        <v>96.69</v>
       </c>
       <c r="K25" s="5">
         <v>-86</v>
@@ -10076,7 +10128,7 @@
         <v>224.2</v>
       </c>
       <c r="J26" s="5">
-        <v>88.95</v>
+        <v>84.18000000000001</v>
       </c>
       <c r="K26" s="5">
         <v>39</v>
@@ -10120,7 +10172,7 @@
         <v>85</v>
       </c>
       <c r="J27" s="5">
-        <v>100.22</v>
+        <v>95.95</v>
       </c>
       <c r="K27" s="5">
         <v>-80</v>
@@ -10164,7 +10216,7 @@
         <v>161.2</v>
       </c>
       <c r="J28" s="5">
-        <v>94.05</v>
+        <v>89.51000000000001</v>
       </c>
       <c r="K28" s="5">
         <v>39</v>
@@ -10208,7 +10260,7 @@
         <v>1586</v>
       </c>
       <c r="J29" s="5">
-        <v>56.79</v>
+        <v>45.47</v>
       </c>
       <c r="K29" s="5">
         <v>39</v>
@@ -10252,7 +10304,7 @@
         <v>87.5</v>
       </c>
       <c r="J30" s="5">
-        <v>100.02</v>
+        <v>95.73999999999999</v>
       </c>
       <c r="K30" s="5">
         <v>0</v>
@@ -10296,7 +10348,7 @@
         <v>57.8</v>
       </c>
       <c r="J31" s="5">
-        <v>102.43</v>
+        <v>98.26000000000001</v>
       </c>
       <c r="K31" s="5">
         <v>49</v>
@@ -10340,7 +10392,7 @@
         <v>1305</v>
       </c>
       <c r="J32" s="5">
-        <v>68.16</v>
+        <v>57.34</v>
       </c>
       <c r="K32" s="5">
         <v>39</v>
@@ -10384,7 +10436,7 @@
         <v>186</v>
       </c>
       <c r="J33" s="5">
-        <v>92.04000000000001</v>
+        <v>87.41</v>
       </c>
       <c r="K33" s="5">
         <v>40</v>
@@ -10428,7 +10480,7 @@
         <v>77.2</v>
       </c>
       <c r="J34" s="5">
-        <v>100.85</v>
+        <v>96.61</v>
       </c>
       <c r="K34" s="5">
         <v>75</v>
@@ -10472,7 +10524,7 @@
         <v>403</v>
       </c>
       <c r="J35" s="5">
-        <v>219.5</v>
+        <v>215.26</v>
       </c>
       <c r="K35" s="5">
         <v>0</v>
@@ -10516,7 +10568,7 @@
         <v>84.2</v>
       </c>
       <c r="J36" s="5">
-        <v>100.28</v>
+        <v>96.01000000000001</v>
       </c>
       <c r="K36" s="5">
         <v>0</v>
@@ -10560,7 +10612,7 @@
         <v>148.1</v>
       </c>
       <c r="J37" s="5">
-        <v>84.66</v>
+        <v>80.31</v>
       </c>
       <c r="K37" s="5">
         <v>0</v>
@@ -10604,7 +10656,7 @@
         <v>897</v>
       </c>
       <c r="J38" s="5">
-        <v>84.68000000000001</v>
+        <v>74.59</v>
       </c>
       <c r="K38" s="5">
         <v>39</v>
@@ -10648,7 +10700,7 @@
         <v>744</v>
       </c>
       <c r="J39" s="5">
-        <v>90.87</v>
+        <v>81.06</v>
       </c>
       <c r="K39" s="5">
         <v>40</v>
@@ -10692,7 +10744,7 @@
         <v>645</v>
       </c>
       <c r="J40" s="5">
-        <v>94.88</v>
+        <v>85.23999999999999</v>
       </c>
       <c r="K40" s="5">
         <v>39</v>
@@ -10736,7 +10788,7 @@
         <v>67</v>
       </c>
       <c r="J41" s="5">
-        <v>101.68</v>
+        <v>97.47</v>
       </c>
       <c r="K41" s="5">
         <v>0</v>
@@ -10780,7 +10832,7 @@
         <v>115.2</v>
       </c>
       <c r="J42" s="5">
-        <v>97.77</v>
+        <v>93.39</v>
       </c>
       <c r="K42" s="5">
         <v>115</v>
@@ -10824,7 +10876,7 @@
         <v>79.8</v>
       </c>
       <c r="J43" s="5">
-        <v>100.65</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="K43" s="5">
         <v>0</v>
@@ -10868,7 +10920,7 @@
         <v>295</v>
       </c>
       <c r="J44" s="5">
-        <v>223.87</v>
+        <v>219.83</v>
       </c>
       <c r="K44" s="5">
         <v>0</v>
@@ -10912,7 +10964,7 @@
         <v>98.8</v>
       </c>
       <c r="J45" s="5">
-        <v>99.11</v>
+        <v>94.79000000000001</v>
       </c>
       <c r="K45" s="5">
         <v>0</v>
@@ -10934,7 +10986,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -10966,10 +11018,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="5">
-        <v>76.84999999999999</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="D2" s="5">
-        <v>76.84999999999999</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="E2" s="5" t="b">
         <v>0</v>
@@ -11000,10 +11052,10 @@
         <v>1</v>
       </c>
       <c r="C4" s="5">
-        <v>229</v>
+        <v>252.63</v>
       </c>
       <c r="D4" s="5">
-        <v>229</v>
+        <v>252.63</v>
       </c>
       <c r="E4" s="5" t="b">
         <v>0</v>
@@ -11125,13 +11177,13 @@
         <v>282</v>
       </c>
       <c r="E13" s="5">
-        <v>527.04</v>
+        <v>528.27</v>
       </c>
       <c r="F13" s="5">
-        <v>756.04</v>
+        <v>780.9</v>
       </c>
       <c r="G13" s="5">
-        <v>229</v>
+        <v>252.63</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -11148,13 +11200,13 @@
         <v>228</v>
       </c>
       <c r="E14" s="5">
-        <v>516.45</v>
+        <v>516.79</v>
       </c>
       <c r="F14" s="5">
         <v>597.75</v>
       </c>
       <c r="G14" s="5">
-        <v>81.3</v>
+        <v>80.95999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -11171,13 +11223,13 @@
         <v>305</v>
       </c>
       <c r="E15" s="5">
-        <v>466.58</v>
+        <v>468.45</v>
       </c>
       <c r="F15" s="5">
-        <v>593.0599999999999</v>
+        <v>592.53</v>
       </c>
       <c r="G15" s="5">
-        <v>126.47</v>
+        <v>124.08</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -11194,13 +11246,13 @@
         <v>897</v>
       </c>
       <c r="E16" s="5">
-        <v>502.84</v>
+        <v>502.97</v>
       </c>
       <c r="F16" s="5">
-        <v>593.0599999999999</v>
+        <v>584.16</v>
       </c>
       <c r="G16" s="5">
-        <v>90.22</v>
+        <v>81.19</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -11217,13 +11269,13 @@
         <v>340</v>
       </c>
       <c r="E17" s="5">
-        <v>514.3200000000001</v>
+        <v>514.34</v>
       </c>
       <c r="F17" s="5">
-        <v>593.0599999999999</v>
+        <v>584.16</v>
       </c>
       <c r="G17" s="5">
-        <v>78.73999999999999</v>
+        <v>69.81999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -11240,13 +11292,13 @@
         <v>645</v>
       </c>
       <c r="E18" s="5">
-        <v>515.5700000000001</v>
+        <v>515.8099999999999</v>
       </c>
       <c r="F18" s="5">
-        <v>593.0599999999999</v>
+        <v>584.16</v>
       </c>
       <c r="G18" s="5">
-        <v>77.48999999999999</v>
+        <v>68.34999999999999</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -11263,13 +11315,13 @@
         <v>1586</v>
       </c>
       <c r="E19" s="5">
-        <v>516.21</v>
+        <v>516.34</v>
       </c>
       <c r="F19" s="5">
-        <v>593.0599999999999</v>
+        <v>584.16</v>
       </c>
       <c r="G19" s="5">
-        <v>76.84999999999999</v>
+        <v>67.81999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -11286,13 +11338,36 @@
         <v>350</v>
       </c>
       <c r="E20" s="5">
-        <v>526.27</v>
+        <v>526.23</v>
       </c>
       <c r="F20" s="5">
-        <v>593.0599999999999</v>
+        <v>584.16</v>
       </c>
       <c r="G20" s="5">
-        <v>66.79000000000001</v>
+        <v>57.93</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C21" s="6">
+        <v>46281.45834490741</v>
+      </c>
+      <c r="D21" s="5">
+        <v>231</v>
+      </c>
+      <c r="E21" s="5">
+        <v>528.17</v>
+      </c>
+      <c r="F21" s="5">
+        <v>584.16</v>
+      </c>
+      <c r="G21" s="5">
+        <v>55.99</v>
       </c>
     </row>
   </sheetData>

--- a/docs/reports/swift_space_weather_report_latest.xlsx
+++ b/docs/reports/swift_space_weather_report_latest.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="163">
   <si>
     <t>SWIFT Space Weather Excel Report</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Updated UTC</t>
   </si>
   <si>
-    <t>2026-09-16T17:08:31Z</t>
+    <t>2026-09-16T21:26:17Z</t>
   </si>
   <si>
     <t>Main URL root</t>
@@ -267,108 +267,111 @@
     <t>Risk</t>
   </si>
   <si>
+    <t>MODERATE</t>
+  </si>
+  <si>
+    <t>2026-09-13T01:24:00-CME-001</t>
+  </si>
+  <si>
+    <t>2026-09-14T11:08:00-CME-001</t>
+  </si>
+  <si>
+    <t>2026-09-13T21:12:00-CME-001</t>
+  </si>
+  <si>
     <t>LOW</t>
   </si>
   <si>
+    <t>2026-09-13T10:23:00-CME-001</t>
+  </si>
+  <si>
+    <t>2026-09-15T08:36:00-CME-001</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Impact_Class</t>
+  </si>
+  <si>
+    <t>Earth_Candidate</t>
+  </si>
+  <si>
+    <t>Start_UTC</t>
+  </si>
+  <si>
+    <t>Arrival_UTC</t>
+  </si>
+  <si>
+    <t>Transit_h</t>
+  </si>
+  <si>
+    <t>Effective_Speed_km_s</t>
+  </si>
+  <si>
+    <t>Expected_Wind_Increase_km_s</t>
+  </si>
+  <si>
+    <t>Longitude</t>
+  </si>
+  <si>
+    <t>Latitude</t>
+  </si>
+  <si>
+    <t>Angular_Separation_deg</t>
+  </si>
+  <si>
+    <t>2026-09-04T15:24:00-CME-001</t>
+  </si>
+  <si>
+    <t>DONKI</t>
+  </si>
+  <si>
+    <t>MISS</t>
+  </si>
+  <si>
+    <t>2026-09-05T06:38:00-CME-001</t>
+  </si>
+  <si>
+    <t>2026-09-07T09:23:00-CME-001</t>
+  </si>
+  <si>
+    <t>ENLIL-HIT</t>
+  </si>
+  <si>
+    <t>2026-09-06T21:53:00-CME-001</t>
+  </si>
+  <si>
+    <t>2026-09-07T02:48:00-CME-001</t>
+  </si>
+  <si>
+    <t>2026-09-08T13:59:00-CME-001</t>
+  </si>
+  <si>
+    <t>2026-09-10T20:12:00-CME-001</t>
+  </si>
+  <si>
+    <t>2026-09-09T21:45:00-CME-001</t>
+  </si>
+  <si>
+    <t>CORE-HIT</t>
+  </si>
+  <si>
+    <t>2026-09-09T16:00:00-CME-001</t>
+  </si>
+  <si>
+    <t>2026-09-11T05:36:00-CME-001</t>
+  </si>
+  <si>
+    <t>2026-09-10T23:36:00-CME-001</t>
+  </si>
+  <si>
+    <t>2026-09-09T10:36:00-CME-001</t>
+  </si>
+  <si>
     <t>2026-09-13T19:48:00-CME-001</t>
   </si>
   <si>
-    <t>2026-09-13T01:24:00-CME-001</t>
-  </si>
-  <si>
-    <t>MODERATE</t>
-  </si>
-  <si>
-    <t>2026-09-14T11:08:00-CME-001</t>
-  </si>
-  <si>
-    <t>2026-09-13T21:12:00-CME-001</t>
-  </si>
-  <si>
-    <t>2026-09-13T10:23:00-CME-001</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Impact_Class</t>
-  </si>
-  <si>
-    <t>Earth_Candidate</t>
-  </si>
-  <si>
-    <t>Start_UTC</t>
-  </si>
-  <si>
-    <t>Arrival_UTC</t>
-  </si>
-  <si>
-    <t>Transit_h</t>
-  </si>
-  <si>
-    <t>Effective_Speed_km_s</t>
-  </si>
-  <si>
-    <t>Expected_Wind_Increase_km_s</t>
-  </si>
-  <si>
-    <t>Longitude</t>
-  </si>
-  <si>
-    <t>Latitude</t>
-  </si>
-  <si>
-    <t>Angular_Separation_deg</t>
-  </si>
-  <si>
-    <t>2026-09-04T15:24:00-CME-001</t>
-  </si>
-  <si>
-    <t>DONKI</t>
-  </si>
-  <si>
-    <t>MISS</t>
-  </si>
-  <si>
-    <t>2026-09-05T06:38:00-CME-001</t>
-  </si>
-  <si>
-    <t>2026-09-07T09:23:00-CME-001</t>
-  </si>
-  <si>
-    <t>ENLIL-HIT</t>
-  </si>
-  <si>
-    <t>2026-09-06T21:53:00-CME-001</t>
-  </si>
-  <si>
-    <t>2026-09-07T02:48:00-CME-001</t>
-  </si>
-  <si>
-    <t>2026-09-08T13:59:00-CME-001</t>
-  </si>
-  <si>
-    <t>2026-09-10T20:12:00-CME-001</t>
-  </si>
-  <si>
-    <t>2026-09-09T21:45:00-CME-001</t>
-  </si>
-  <si>
-    <t>CORE-HIT</t>
-  </si>
-  <si>
-    <t>2026-09-09T16:00:00-CME-001</t>
-  </si>
-  <si>
-    <t>2026-09-11T05:36:00-CME-001</t>
-  </si>
-  <si>
-    <t>2026-09-10T23:36:00-CME-001</t>
-  </si>
-  <si>
-    <t>2026-09-09T10:36:00-CME-001</t>
-  </si>
-  <si>
     <t>2026-09-11T06:24:00-CME-001</t>
   </si>
   <si>
@@ -418,9 +421,6 @@
   </si>
   <si>
     <t>2026-09-13T07:48:00-CME-001</t>
-  </si>
-  <si>
-    <t>2026-09-15T08:36:00-CME-001</t>
   </si>
   <si>
     <t>Median_Delta_V</t>
@@ -674,10 +674,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>SolarWind_27d!$A$2:$A$32</c:f>
+              <c:f>SolarWind_27d!$A$2:$A$36</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="31"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
                   <c:v>46280.45833333334</c:v>
                 </c:pt>
@@ -770,16 +770,28 @@
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>46281.70833333334</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>46281.75</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>46281.79166666666</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>46281.83333333334</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>46281.875</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>SolarWind_27d!$B$2:$B$32</c:f>
+              <c:f>SolarWind_27d!$B$2:$B$36</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="31"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
                   <c:v>546.005</c:v>
                 </c:pt>
@@ -799,79 +811,91 @@
                   <c:v>453.015</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>425</c:v>
+                  <c:v>425.95</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>683.64</c:v>
+                  <c:v>612.25</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>621.9349999999999</c:v>
+                  <c:v>626.875</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>515.475</c:v>
+                  <c:v>515.75</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>468.7</c:v>
+                  <c:v>464.39</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>446.015</c:v>
+                  <c:v>446.05</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>465.25</c:v>
+                  <c:v>462.23</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>516.8049999999999</c:v>
+                  <c:v>517.345</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>521.405</c:v>
+                  <c:v>522.005</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>526.9</c:v>
+                  <c:v>527.735</c:v>
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>531.665</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>538.105</c:v>
+                  <c:v>537.3200000000001</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>536.1900000000001</c:v>
+                  <c:v>536.5</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>532.135</c:v>
+                  <c:v>532.015</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>522.005</c:v>
+                  <c:v>521.465</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>543.4</c:v>
+                  <c:v>542.7</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>540.355</c:v>
+                  <c:v>539.8</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>543.275</c:v>
+                  <c:v>542.86</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>537.65</c:v>
+                  <c:v>537.5</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>550.7</c:v>
+                  <c:v>549.295</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>564.675</c:v>
+                  <c:v>562.86</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>545.58</c:v>
+                  <c:v>545.145</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>533.715</c:v>
+                  <c:v>534.22</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>524.7</c:v>
+                  <c:v>524.6</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>527.55</c:v>
+                  <c:v>535.595</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>524</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>501.43</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>509.7</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>504.155</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -995,10 +1019,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>SolarWind_27d!$A$2:$A$32</c:f>
+              <c:f>SolarWind_27d!$A$2:$A$36</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="31"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
                   <c:v>46280.45833333334</c:v>
                 </c:pt>
@@ -1091,16 +1115,28 @@
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>46281.70833333334</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>46281.75</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>46281.79166666666</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>46281.83333333334</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>46281.875</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>SolarWind_27d!$D$2:$D$32</c:f>
+              <c:f>SolarWind_27d!$D$2:$D$36</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="31"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
                   <c:v>8.85</c:v>
                 </c:pt>
@@ -1126,73 +1162,85 @@
                   <c:v>-7.3</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-8.824999999999999</c:v>
+                  <c:v>-8.91</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-9.07</c:v>
+                  <c:v>-9.185</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.85</c:v>
+                  <c:v>0.44</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-2.27</c:v>
+                  <c:v>-2.73</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-4.725</c:v>
+                  <c:v>-4.73</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>1.87</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>5.805</c:v>
+                  <c:v>5.7</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>3.745</c:v>
+                  <c:v>3.645</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.475</c:v>
+                  <c:v>0.195</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-0.54</c:v>
+                  <c:v>-0.465</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.89</c:v>
+                  <c:v>2.175</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>4.58</c:v>
+                  <c:v>4.84</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3.16</c:v>
+                  <c:v>3.395</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>4.49</c:v>
+                  <c:v>4.47</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>2.415</c:v>
+                  <c:v>2.71</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>-2.185</c:v>
+                  <c:v>-2.115</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>-2.36</c:v>
+                  <c:v>-2.31</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1.03</c:v>
+                  <c:v>0.825</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>2.95</c:v>
+                  <c:v>2.8</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>4.84</c:v>
+                  <c:v>4.75</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>4.465</c:v>
+                  <c:v>3.97</c:v>
                 </c:pt>
                 <c:pt idx="29">
+                  <c:v>4.115</c:v>
+                </c:pt>
+                <c:pt idx="30">
                   <c:v>4.095</c:v>
                 </c:pt>
-                <c:pt idx="30">
-                  <c:v>4.29</c:v>
+                <c:pt idx="31">
+                  <c:v>3.035</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2.18</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.58</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>2.395</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1209,10 +1257,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>SolarWind_27d!$A$2:$A$32</c:f>
+              <c:f>SolarWind_27d!$A$2:$A$36</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="31"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
                   <c:v>46280.45833333334</c:v>
                 </c:pt>
@@ -1305,16 +1353,28 @@
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>46281.70833333334</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>46281.75</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>46281.79166666666</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>46281.83333333334</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>46281.875</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>SolarWind_27d!$E$2:$E$32</c:f>
+              <c:f>SolarWind_27d!$E$2:$E$36</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="31"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
                   <c:v>12.92</c:v>
                 </c:pt>
@@ -1337,76 +1397,88 @@
                   <c:v>16.09</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>12.51</c:v>
+                  <c:v>12.535</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>11.945</c:v>
+                  <c:v>11.86</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>13.505</c:v>
+                  <c:v>13.555</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>12.37</c:v>
+                  <c:v>12.31</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>10.64</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>11.045</c:v>
+                  <c:v>10.94</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>12.76</c:v>
+                  <c:v>12.745</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>10.84</c:v>
+                  <c:v>10.875</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>10.305</c:v>
+                  <c:v>10.335</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>7.155</c:v>
+                  <c:v>6.895</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>7.025</c:v>
+                  <c:v>7.055</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>6.79</c:v>
+                  <c:v>6.81</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>6.435</c:v>
+                  <c:v>6.46</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>5.75</c:v>
+                  <c:v>5.66</c:v>
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>4.89</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>4.65</c:v>
+                  <c:v>4.67</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>4.76</c:v>
+                  <c:v>4.775</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>4.31</c:v>
+                  <c:v>4.285</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>4.475</c:v>
+                  <c:v>4.505</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>5.025</c:v>
+                  <c:v>4.875</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>5.485</c:v>
+                  <c:v>5.5</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>5.845</c:v>
+                  <c:v>5.77</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>5.61</c:v>
+                  <c:v>5.645</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>5.585</c:v>
+                  <c:v>5.645</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>5.44</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>4.7</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>5.05</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>4.9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1535,232 +1607,232 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="76"/>
                 <c:pt idx="0">
-                  <c:v>46281.58333333334</c:v>
+                  <c:v>46281.75</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>46281.625</c:v>
+                  <c:v>46281.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46281.66666666666</c:v>
+                  <c:v>46281.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46281.70833333334</c:v>
+                  <c:v>46281.875</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46281.75</c:v>
+                  <c:v>46281.91666666666</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46281.79166666666</c:v>
+                  <c:v>46281.95833333334</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46281.83333333334</c:v>
+                  <c:v>46282</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>46281.875</c:v>
+                  <c:v>46282.04166666666</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>46281.91666666666</c:v>
+                  <c:v>46282.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>46281.95833333334</c:v>
+                  <c:v>46282.125</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>46282</c:v>
+                  <c:v>46282.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>46282.04166666666</c:v>
+                  <c:v>46282.20833333334</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>46282.08333333334</c:v>
+                  <c:v>46282.25</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>46282.125</c:v>
+                  <c:v>46282.29166666666</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>46282.16666666666</c:v>
+                  <c:v>46282.33333333334</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46282.20833333334</c:v>
+                  <c:v>46282.375</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>46282.25</c:v>
+                  <c:v>46282.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>46282.29166666666</c:v>
+                  <c:v>46282.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>46282.33333333334</c:v>
+                  <c:v>46282.5</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>46282.375</c:v>
+                  <c:v>46282.54166666666</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>46282.41666666666</c:v>
+                  <c:v>46282.58333333334</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>46282.45833333334</c:v>
+                  <c:v>46282.625</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>46282.5</c:v>
+                  <c:v>46282.66666666666</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>46282.54166666666</c:v>
+                  <c:v>46282.70833333334</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>46282.58333333334</c:v>
+                  <c:v>46282.75</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>46282.625</c:v>
+                  <c:v>46282.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>46282.66666666666</c:v>
+                  <c:v>46282.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>46282.70833333334</c:v>
+                  <c:v>46282.875</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>46282.75</c:v>
+                  <c:v>46282.91666666666</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>46282.79166666666</c:v>
+                  <c:v>46282.95833333334</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>46282.83333333334</c:v>
+                  <c:v>46283</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>46282.875</c:v>
+                  <c:v>46283.04166666666</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>46282.91666666666</c:v>
+                  <c:v>46283.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>46282.95833333334</c:v>
+                  <c:v>46283.125</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>46283</c:v>
+                  <c:v>46283.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>46283.04166666666</c:v>
+                  <c:v>46283.20833333334</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>46283.08333333334</c:v>
+                  <c:v>46283.25</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>46283.125</c:v>
+                  <c:v>46283.29166666666</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>46283.16666666666</c:v>
+                  <c:v>46283.33333333334</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>46283.20833333334</c:v>
+                  <c:v>46283.375</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>46283.25</c:v>
+                  <c:v>46283.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>46283.29166666666</c:v>
+                  <c:v>46283.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>46283.33333333334</c:v>
+                  <c:v>46283.5</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>46283.375</c:v>
+                  <c:v>46283.54166666666</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>46283.41666666666</c:v>
+                  <c:v>46283.58333333334</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>46283.45833333334</c:v>
+                  <c:v>46283.625</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>46283.5</c:v>
+                  <c:v>46283.66666666666</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>46283.54166666666</c:v>
+                  <c:v>46283.70833333334</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>46283.58333333334</c:v>
+                  <c:v>46283.75</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>46283.625</c:v>
+                  <c:v>46283.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>46283.66666666666</c:v>
+                  <c:v>46283.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>46283.70833333334</c:v>
+                  <c:v>46283.875</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>46283.75</c:v>
+                  <c:v>46283.91666666666</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>46283.79166666666</c:v>
+                  <c:v>46283.95833333334</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>46283.83333333334</c:v>
+                  <c:v>46284</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>46283.875</c:v>
+                  <c:v>46284.04166666666</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>46283.91666666666</c:v>
+                  <c:v>46284.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>46283.95833333334</c:v>
+                  <c:v>46284.125</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>46284</c:v>
+                  <c:v>46284.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>46284.04166666666</c:v>
+                  <c:v>46284.20833333334</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>46284.08333333334</c:v>
+                  <c:v>46284.25</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>46284.125</c:v>
+                  <c:v>46284.29166666666</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>46284.16666666666</c:v>
+                  <c:v>46284.33333333334</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>46284.20833333334</c:v>
+                  <c:v>46284.375</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>46284.25</c:v>
+                  <c:v>46284.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>46284.29166666666</c:v>
+                  <c:v>46284.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>46284.33333333334</c:v>
+                  <c:v>46284.5</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>46284.375</c:v>
+                  <c:v>46284.54166666666</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>46284.41666666666</c:v>
+                  <c:v>46284.58333333334</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>46284.45833333334</c:v>
+                  <c:v>46284.625</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>46284.5</c:v>
+                  <c:v>46284.66666666666</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>46284.54166666666</c:v>
+                  <c:v>46284.70833333334</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>46284.58333333334</c:v>
+                  <c:v>46284.75</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>46284.625</c:v>
+                  <c:v>46284.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>46284.66666666666</c:v>
+                  <c:v>46284.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>46284.70833333334</c:v>
+                  <c:v>46284.875</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1772,232 +1844,232 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="76"/>
                 <c:pt idx="0">
-                  <c:v>506.49</c:v>
+                  <c:v>604.42</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>512.8</c:v>
+                  <c:v>623.3200000000001</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>523</c:v>
+                  <c:v>636.67</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>536.65</c:v>
+                  <c:v>649.9400000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>545.01</c:v>
+                  <c:v>654.25</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>558.05</c:v>
+                  <c:v>655.86</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>573.1799999999999</c:v>
+                  <c:v>655.39</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>589.47</c:v>
+                  <c:v>653.39</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>603.46</c:v>
+                  <c:v>651.72</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>612.8200000000001</c:v>
+                  <c:v>649.52</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>621.51</c:v>
+                  <c:v>645.62</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>625.97</c:v>
+                  <c:v>644.9299999999999</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>627.51</c:v>
+                  <c:v>646.13</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>628.49</c:v>
+                  <c:v>647.36</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>624.35</c:v>
+                  <c:v>643.6900000000001</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>623.59</c:v>
+                  <c:v>641.37</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>624.8200000000001</c:v>
+                  <c:v>637.99</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>626.1900000000001</c:v>
+                  <c:v>632.58</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>622.55</c:v>
+                  <c:v>625.0599999999999</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>620.36</c:v>
+                  <c:v>614.1799999999999</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>617.05</c:v>
+                  <c:v>601.63</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>611.59</c:v>
+                  <c:v>588.42</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>603.96</c:v>
+                  <c:v>575.15</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>592.95</c:v>
+                  <c:v>562.1799999999999</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>580.27</c:v>
+                  <c:v>549.7</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>566.92</c:v>
+                  <c:v>537.6900000000001</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>553.51</c:v>
+                  <c:v>524.95</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>540.4</c:v>
+                  <c:v>513.38</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>527.78</c:v>
+                  <c:v>502.79</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>515.64</c:v>
+                  <c:v>493</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>502.88</c:v>
+                  <c:v>483.95</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>491.25</c:v>
+                  <c:v>474.98</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>480.56</c:v>
+                  <c:v>467.85</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>470.65</c:v>
+                  <c:v>462.11</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>461.47</c:v>
+                  <c:v>457.5</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>452.48</c:v>
+                  <c:v>453.98</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>445.31</c:v>
+                  <c:v>451.68</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>439.51</c:v>
+                  <c:v>450</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>434.83</c:v>
+                  <c:v>449.75</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>431.24</c:v>
+                  <c:v>451.7</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>428.87</c:v>
+                  <c:v>456.56</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>427.1</c:v>
+                  <c:v>459.6</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>426.76</c:v>
+                  <c:v>468.45</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>428.62</c:v>
+                  <c:v>479.76</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>433.4</c:v>
+                  <c:v>494.65</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>436.36</c:v>
+                  <c:v>510.65</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>445.16</c:v>
+                  <c:v>525.17</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>456.34</c:v>
+                  <c:v>535.79</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>471.15</c:v>
+                  <c:v>538.49</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>487.09</c:v>
+                  <c:v>534.03</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>501.56</c:v>
+                  <c:v>527.33</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>512.13</c:v>
+                  <c:v>519.51</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>514.76</c:v>
+                  <c:v>509.2</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>510.26</c:v>
+                  <c:v>499.72</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>503.5</c:v>
+                  <c:v>490.94</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>495.6</c:v>
+                  <c:v>480.83</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>485.24</c:v>
+                  <c:v>472.21</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>475.69</c:v>
+                  <c:v>464.69</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>466.83</c:v>
+                  <c:v>457.97</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>456.65</c:v>
+                  <c:v>451.9</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>447.97</c:v>
+                  <c:v>446.34</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>440.36</c:v>
+                  <c:v>441.23</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>433.57</c:v>
+                  <c:v>436.49</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>427.42</c:v>
+                  <c:v>432.09</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>421.79</c:v>
+                  <c:v>427.99</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>416.6</c:v>
+                  <c:v>424.17</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>411.79</c:v>
+                  <c:v>420.61</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>407.32</c:v>
+                  <c:v>417.28</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>403.16</c:v>
+                  <c:v>414.17</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>399.28</c:v>
+                  <c:v>411.26</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>395.65</c:v>
+                  <c:v>408.54</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>392.26</c:v>
+                  <c:v>406</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>389.1</c:v>
+                  <c:v>403.62</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>386.14</c:v>
+                  <c:v>401.4</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>383.37</c:v>
+                  <c:v>399.32</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>380.78</c:v>
+                  <c:v>397.38</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2019,232 +2091,232 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="76"/>
                 <c:pt idx="0">
-                  <c:v>46281.58333333334</c:v>
+                  <c:v>46281.75</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>46281.625</c:v>
+                  <c:v>46281.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46281.66666666666</c:v>
+                  <c:v>46281.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46281.70833333334</c:v>
+                  <c:v>46281.875</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46281.75</c:v>
+                  <c:v>46281.91666666666</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46281.79166666666</c:v>
+                  <c:v>46281.95833333334</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46281.83333333334</c:v>
+                  <c:v>46282</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>46281.875</c:v>
+                  <c:v>46282.04166666666</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>46281.91666666666</c:v>
+                  <c:v>46282.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>46281.95833333334</c:v>
+                  <c:v>46282.125</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>46282</c:v>
+                  <c:v>46282.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>46282.04166666666</c:v>
+                  <c:v>46282.20833333334</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>46282.08333333334</c:v>
+                  <c:v>46282.25</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>46282.125</c:v>
+                  <c:v>46282.29166666666</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>46282.16666666666</c:v>
+                  <c:v>46282.33333333334</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46282.20833333334</c:v>
+                  <c:v>46282.375</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>46282.25</c:v>
+                  <c:v>46282.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>46282.29166666666</c:v>
+                  <c:v>46282.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>46282.33333333334</c:v>
+                  <c:v>46282.5</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>46282.375</c:v>
+                  <c:v>46282.54166666666</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>46282.41666666666</c:v>
+                  <c:v>46282.58333333334</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>46282.45833333334</c:v>
+                  <c:v>46282.625</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>46282.5</c:v>
+                  <c:v>46282.66666666666</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>46282.54166666666</c:v>
+                  <c:v>46282.70833333334</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>46282.58333333334</c:v>
+                  <c:v>46282.75</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>46282.625</c:v>
+                  <c:v>46282.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>46282.66666666666</c:v>
+                  <c:v>46282.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>46282.70833333334</c:v>
+                  <c:v>46282.875</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>46282.75</c:v>
+                  <c:v>46282.91666666666</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>46282.79166666666</c:v>
+                  <c:v>46282.95833333334</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>46282.83333333334</c:v>
+                  <c:v>46283</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>46282.875</c:v>
+                  <c:v>46283.04166666666</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>46282.91666666666</c:v>
+                  <c:v>46283.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>46282.95833333334</c:v>
+                  <c:v>46283.125</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>46283</c:v>
+                  <c:v>46283.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>46283.04166666666</c:v>
+                  <c:v>46283.20833333334</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>46283.08333333334</c:v>
+                  <c:v>46283.25</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>46283.125</c:v>
+                  <c:v>46283.29166666666</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>46283.16666666666</c:v>
+                  <c:v>46283.33333333334</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>46283.20833333334</c:v>
+                  <c:v>46283.375</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>46283.25</c:v>
+                  <c:v>46283.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>46283.29166666666</c:v>
+                  <c:v>46283.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>46283.33333333334</c:v>
+                  <c:v>46283.5</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>46283.375</c:v>
+                  <c:v>46283.54166666666</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>46283.41666666666</c:v>
+                  <c:v>46283.58333333334</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>46283.45833333334</c:v>
+                  <c:v>46283.625</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>46283.5</c:v>
+                  <c:v>46283.66666666666</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>46283.54166666666</c:v>
+                  <c:v>46283.70833333334</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>46283.58333333334</c:v>
+                  <c:v>46283.75</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>46283.625</c:v>
+                  <c:v>46283.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>46283.66666666666</c:v>
+                  <c:v>46283.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>46283.70833333334</c:v>
+                  <c:v>46283.875</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>46283.75</c:v>
+                  <c:v>46283.91666666666</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>46283.79166666666</c:v>
+                  <c:v>46283.95833333334</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>46283.83333333334</c:v>
+                  <c:v>46284</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>46283.875</c:v>
+                  <c:v>46284.04166666666</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>46283.91666666666</c:v>
+                  <c:v>46284.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>46283.95833333334</c:v>
+                  <c:v>46284.125</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>46284</c:v>
+                  <c:v>46284.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>46284.04166666666</c:v>
+                  <c:v>46284.20833333334</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>46284.08333333334</c:v>
+                  <c:v>46284.25</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>46284.125</c:v>
+                  <c:v>46284.29166666666</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>46284.16666666666</c:v>
+                  <c:v>46284.33333333334</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>46284.20833333334</c:v>
+                  <c:v>46284.375</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>46284.25</c:v>
+                  <c:v>46284.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>46284.29166666666</c:v>
+                  <c:v>46284.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>46284.33333333334</c:v>
+                  <c:v>46284.5</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>46284.375</c:v>
+                  <c:v>46284.54166666666</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>46284.41666666666</c:v>
+                  <c:v>46284.58333333334</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>46284.45833333334</c:v>
+                  <c:v>46284.625</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>46284.5</c:v>
+                  <c:v>46284.66666666666</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>46284.54166666666</c:v>
+                  <c:v>46284.70833333334</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>46284.58333333334</c:v>
+                  <c:v>46284.75</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>46284.625</c:v>
+                  <c:v>46284.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>46284.66666666666</c:v>
+                  <c:v>46284.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>46284.70833333334</c:v>
+                  <c:v>46284.875</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2256,232 +2328,232 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="76"/>
                 <c:pt idx="0">
-                  <c:v>336.73</c:v>
+                  <c:v>377.68</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>337.2</c:v>
+                  <c:v>373.72</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>335.99</c:v>
+                  <c:v>364.8</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>332.85</c:v>
+                  <c:v>359.37</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>333.21</c:v>
+                  <c:v>358.92</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>332.42</c:v>
+                  <c:v>357.83</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>330.34</c:v>
+                  <c:v>356.4</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>328.68</c:v>
+                  <c:v>354.54</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>326.65</c:v>
+                  <c:v>353.87</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>326.24</c:v>
+                  <c:v>351.96</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>329.57</c:v>
+                  <c:v>352.66</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>331.49</c:v>
+                  <c:v>352.7</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>332.53</c:v>
+                  <c:v>352.36</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>333.02</c:v>
+                  <c:v>352.14</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>333.16</c:v>
+                  <c:v>352.02</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>333.1</c:v>
+                  <c:v>351.97</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>332.89</c:v>
+                  <c:v>352.13</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>332.93</c:v>
+                  <c:v>352.53</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>333.13</c:v>
+                  <c:v>353.07</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>333.43</c:v>
+                  <c:v>353.54</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>333.78</c:v>
+                  <c:v>353.96</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>334.18</c:v>
+                  <c:v>354.33</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>334.59</c:v>
+                  <c:v>354.69</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>334.86</c:v>
+                  <c:v>355.02</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>335.04</c:v>
+                  <c:v>355.33</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>335.16</c:v>
+                  <c:v>355.51</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>335.25</c:v>
+                  <c:v>355.6</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>335.31</c:v>
+                  <c:v>355.64</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>335.36</c:v>
+                  <c:v>355.63</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>335.28</c:v>
+                  <c:v>355.6</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>335.12</c:v>
+                  <c:v>355.54</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>334.91</c:v>
+                  <c:v>356.4</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>334.67</c:v>
+                  <c:v>357.83</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>334.4</c:v>
+                  <c:v>359.59</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>334.13</c:v>
+                  <c:v>361.57</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>334.8</c:v>
+                  <c:v>363.68</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>336.05</c:v>
+                  <c:v>365.87</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>337.67</c:v>
+                  <c:v>367.21</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>339.51</c:v>
+                  <c:v>368.01</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>341.49</c:v>
+                  <c:v>368.49</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>343.56</c:v>
+                  <c:v>368.75</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>344.76</c:v>
+                  <c:v>368.89</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>345.43</c:v>
+                  <c:v>368.95</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>345.76</c:v>
+                  <c:v>368.95</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>345.89</c:v>
+                  <c:v>368.92</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>345.89</c:v>
+                  <c:v>368.87</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>345.81</c:v>
+                  <c:v>368.81</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>345.69</c:v>
+                  <c:v>368.73</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>345.54</c:v>
+                  <c:v>368.65</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>345.37</c:v>
+                  <c:v>368.55</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>345.19</c:v>
+                  <c:v>368.46</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>345</c:v>
+                  <c:v>368.35</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>344.81</c:v>
+                  <c:v>368.24</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>344.62</c:v>
+                  <c:v>368.13</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>344.42</c:v>
+                  <c:v>368.02</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>344.22</c:v>
+                  <c:v>367.97</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>344.03</c:v>
+                  <c:v>367.97</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>343.83</c:v>
+                  <c:v>367.99</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>343.63</c:v>
+                  <c:v>368.03</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>343.5</c:v>
+                  <c:v>368.07</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>343.42</c:v>
+                  <c:v>368.12</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>343.38</c:v>
+                  <c:v>368.17</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>343.34</c:v>
+                  <c:v>368.22</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>343.32</c:v>
+                  <c:v>368.27</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>343.31</c:v>
+                  <c:v>368.31</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>343.3</c:v>
+                  <c:v>368.36</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>343.29</c:v>
+                  <c:v>368.41</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>343.29</c:v>
+                  <c:v>368.45</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>343.28</c:v>
+                  <c:v>368.49</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>343.28</c:v>
+                  <c:v>368.53</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>343.28</c:v>
+                  <c:v>368.57</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>343.27</c:v>
+                  <c:v>368.61</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>343.27</c:v>
+                  <c:v>368.64</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>343.27</c:v>
+                  <c:v>368.68</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>343.27</c:v>
+                  <c:v>368.71</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>343.26</c:v>
+                  <c:v>368.74</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2503,232 +2575,232 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="76"/>
                 <c:pt idx="0">
-                  <c:v>46281.58333333334</c:v>
+                  <c:v>46281.75</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>46281.625</c:v>
+                  <c:v>46281.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46281.66666666666</c:v>
+                  <c:v>46281.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46281.70833333334</c:v>
+                  <c:v>46281.875</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46281.75</c:v>
+                  <c:v>46281.91666666666</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46281.79166666666</c:v>
+                  <c:v>46281.95833333334</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46281.83333333334</c:v>
+                  <c:v>46282</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>46281.875</c:v>
+                  <c:v>46282.04166666666</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>46281.91666666666</c:v>
+                  <c:v>46282.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>46281.95833333334</c:v>
+                  <c:v>46282.125</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>46282</c:v>
+                  <c:v>46282.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>46282.04166666666</c:v>
+                  <c:v>46282.20833333334</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>46282.08333333334</c:v>
+                  <c:v>46282.25</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>46282.125</c:v>
+                  <c:v>46282.29166666666</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>46282.16666666666</c:v>
+                  <c:v>46282.33333333334</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46282.20833333334</c:v>
+                  <c:v>46282.375</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>46282.25</c:v>
+                  <c:v>46282.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>46282.29166666666</c:v>
+                  <c:v>46282.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>46282.33333333334</c:v>
+                  <c:v>46282.5</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>46282.375</c:v>
+                  <c:v>46282.54166666666</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>46282.41666666666</c:v>
+                  <c:v>46282.58333333334</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>46282.45833333334</c:v>
+                  <c:v>46282.625</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>46282.5</c:v>
+                  <c:v>46282.66666666666</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>46282.54166666666</c:v>
+                  <c:v>46282.70833333334</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>46282.58333333334</c:v>
+                  <c:v>46282.75</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>46282.625</c:v>
+                  <c:v>46282.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>46282.66666666666</c:v>
+                  <c:v>46282.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>46282.70833333334</c:v>
+                  <c:v>46282.875</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>46282.75</c:v>
+                  <c:v>46282.91666666666</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>46282.79166666666</c:v>
+                  <c:v>46282.95833333334</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>46282.83333333334</c:v>
+                  <c:v>46283</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>46282.875</c:v>
+                  <c:v>46283.04166666666</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>46282.91666666666</c:v>
+                  <c:v>46283.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>46282.95833333334</c:v>
+                  <c:v>46283.125</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>46283</c:v>
+                  <c:v>46283.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>46283.04166666666</c:v>
+                  <c:v>46283.20833333334</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>46283.08333333334</c:v>
+                  <c:v>46283.25</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>46283.125</c:v>
+                  <c:v>46283.29166666666</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>46283.16666666666</c:v>
+                  <c:v>46283.33333333334</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>46283.20833333334</c:v>
+                  <c:v>46283.375</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>46283.25</c:v>
+                  <c:v>46283.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>46283.29166666666</c:v>
+                  <c:v>46283.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>46283.33333333334</c:v>
+                  <c:v>46283.5</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>46283.375</c:v>
+                  <c:v>46283.54166666666</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>46283.41666666666</c:v>
+                  <c:v>46283.58333333334</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>46283.45833333334</c:v>
+                  <c:v>46283.625</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>46283.5</c:v>
+                  <c:v>46283.66666666666</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>46283.54166666666</c:v>
+                  <c:v>46283.70833333334</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>46283.58333333334</c:v>
+                  <c:v>46283.75</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>46283.625</c:v>
+                  <c:v>46283.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>46283.66666666666</c:v>
+                  <c:v>46283.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>46283.70833333334</c:v>
+                  <c:v>46283.875</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>46283.75</c:v>
+                  <c:v>46283.91666666666</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>46283.79166666666</c:v>
+                  <c:v>46283.95833333334</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>46283.83333333334</c:v>
+                  <c:v>46284</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>46283.875</c:v>
+                  <c:v>46284.04166666666</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>46283.91666666666</c:v>
+                  <c:v>46284.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>46283.95833333334</c:v>
+                  <c:v>46284.125</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>46284</c:v>
+                  <c:v>46284.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>46284.04166666666</c:v>
+                  <c:v>46284.20833333334</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>46284.08333333334</c:v>
+                  <c:v>46284.25</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>46284.125</c:v>
+                  <c:v>46284.29166666666</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>46284.16666666666</c:v>
+                  <c:v>46284.33333333334</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>46284.20833333334</c:v>
+                  <c:v>46284.375</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>46284.25</c:v>
+                  <c:v>46284.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>46284.29166666666</c:v>
+                  <c:v>46284.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>46284.33333333334</c:v>
+                  <c:v>46284.5</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>46284.375</c:v>
+                  <c:v>46284.54166666666</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>46284.41666666666</c:v>
+                  <c:v>46284.58333333334</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>46284.45833333334</c:v>
+                  <c:v>46284.625</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>46284.5</c:v>
+                  <c:v>46284.66666666666</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>46284.54166666666</c:v>
+                  <c:v>46284.70833333334</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>46284.58333333334</c:v>
+                  <c:v>46284.75</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>46284.625</c:v>
+                  <c:v>46284.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>46284.66666666666</c:v>
+                  <c:v>46284.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>46284.70833333334</c:v>
+                  <c:v>46284.875</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2740,232 +2812,232 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="76"/>
                 <c:pt idx="0">
-                  <c:v>218.74</c:v>
+                  <c:v>299.12</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>226.26</c:v>
+                  <c:v>329.26</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>240.97</c:v>
+                  <c:v>358.66</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>262.6</c:v>
+                  <c:v>383.33</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>289.76</c:v>
+                  <c:v>399.87</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>319.78</c:v>
+                  <c:v>399</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>349.09</c:v>
+                  <c:v>396.46</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>373.76</c:v>
+                  <c:v>393.96</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>390.37</c:v>
+                  <c:v>390.75</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>389.81</c:v>
+                  <c:v>391.92</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>387.42</c:v>
+                  <c:v>376.61</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>384.78</c:v>
+                  <c:v>383.92</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>381.15</c:v>
+                  <c:v>390.85</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>381.76</c:v>
+                  <c:v>392.57</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>366.18</c:v>
+                  <c:v>377.15</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>372.84</c:v>
+                  <c:v>376.88</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>379.19</c:v>
+                  <c:v>369.49</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>380.65</c:v>
+                  <c:v>356.95</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>364.85</c:v>
+                  <c:v>341.44</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>364.49</c:v>
+                  <c:v>319.42</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>357.3</c:v>
+                  <c:v>298.82</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>345.16</c:v>
+                  <c:v>279.55</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>330.15</c:v>
+                  <c:v>261.52</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>308.86</c:v>
+                  <c:v>244.65</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>288.94</c:v>
+                  <c:v>228.88</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>270.3</c:v>
+                  <c:v>214.11</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>252.87</c:v>
+                  <c:v>195.77</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>236.56</c:v>
+                  <c:v>183.14</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>221.3</c:v>
+                  <c:v>171.33</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>207.03</c:v>
+                  <c:v>160.28</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>189.68</c:v>
+                  <c:v>150</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>177.45</c:v>
+                  <c:v>135.26</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>166</c:v>
+                  <c:v>126.76</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>155.3</c:v>
+                  <c:v>119.06</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>145.34</c:v>
+                  <c:v>112.36</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>131.34</c:v>
+                  <c:v>107.01</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>123.08</c:v>
+                  <c:v>103.54</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>115.61</c:v>
+                  <c:v>102.74</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>109.12</c:v>
+                  <c:v>105.55</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>103.93</c:v>
+                  <c:v>112.95</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>100.6</c:v>
+                  <c:v>125.72</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>99.87</c:v>
+                  <c:v>125.91</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>102.67</c:v>
+                  <c:v>150.21</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>109.98</c:v>
+                  <c:v>170.52</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>122.54</c:v>
+                  <c:v>197.98</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>122.8</c:v>
+                  <c:v>221.58</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>146.66</c:v>
+                  <c:v>237.67</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>166.34</c:v>
+                  <c:v>243.41</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>193.3</c:v>
+                  <c:v>230.06</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>216.48</c:v>
+                  <c:v>208.88</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>232.29</c:v>
+                  <c:v>195.4</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>237.96</c:v>
+                  <c:v>182.8</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>224.91</c:v>
+                  <c:v>163.99</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>204.38</c:v>
+                  <c:v>153.42</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>191.2</c:v>
+                  <c:v>143.52</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>178.86</c:v>
+                  <c:v>127.19</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>160.6</c:v>
+                  <c:v>118.99</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>150.24</c:v>
+                  <c:v>111.32</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>140.55</c:v>
+                  <c:v>104.14</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>124.65</c:v>
+                  <c:v>97.42</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>116.62</c:v>
+                  <c:v>91.14</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>109.09</c:v>
+                  <c:v>85.26000000000001</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>102.06</c:v>
+                  <c:v>79.76000000000001</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>95.48</c:v>
+                  <c:v>74.62</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>89.31999999999999</c:v>
+                  <c:v>69.81</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>83.56</c:v>
+                  <c:v>65.3</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>78.17</c:v>
+                  <c:v>61.09</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>73.13</c:v>
+                  <c:v>57.15</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>68.41</c:v>
+                  <c:v>53.47</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>64</c:v>
+                  <c:v>50.02</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>59.87</c:v>
+                  <c:v>46.79</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>56.01</c:v>
+                  <c:v>43.77</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>52.4</c:v>
+                  <c:v>40.95</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>49.02</c:v>
+                  <c:v>38.31</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>45.86</c:v>
+                  <c:v>35.84</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>42.9</c:v>
+                  <c:v>33.53</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3094,76 +3166,76 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="24"/>
                 <c:pt idx="0">
-                  <c:v>46281.625</c:v>
+                  <c:v>46281.875</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>46281.75</c:v>
+                  <c:v>46282</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46281.875</c:v>
+                  <c:v>46282.125</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46282</c:v>
+                  <c:v>46282.25</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46282.125</c:v>
+                  <c:v>46282.375</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46282.25</c:v>
+                  <c:v>46282.5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46282.375</c:v>
+                  <c:v>46282.625</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>46282.5</c:v>
+                  <c:v>46282.75</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>46282.625</c:v>
+                  <c:v>46282.875</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>46282.75</c:v>
+                  <c:v>46283</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>46282.875</c:v>
+                  <c:v>46283.125</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>46283</c:v>
+                  <c:v>46283.25</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>46283.125</c:v>
+                  <c:v>46283.375</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>46283.25</c:v>
+                  <c:v>46283.5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>46283.375</c:v>
+                  <c:v>46283.625</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46283.5</c:v>
+                  <c:v>46283.75</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>46283.625</c:v>
+                  <c:v>46283.875</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>46283.75</c:v>
+                  <c:v>46284</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>46283.875</c:v>
+                  <c:v>46284.125</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>46284</c:v>
+                  <c:v>46284.25</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>46284.125</c:v>
+                  <c:v>46284.375</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>46284.25</c:v>
+                  <c:v>46284.5</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>46284.375</c:v>
+                  <c:v>46284.625</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>46284.5</c:v>
+                  <c:v>46284.75</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3175,7 +3247,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="24"/>
                 <c:pt idx="0">
-                  <c:v>1.33</c:v>
+                  <c:v>1.67</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>1.67</c:v>
@@ -3193,58 +3265,58 @@
                   <c:v>3.33</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3.67</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.33</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.33</c:v>
+                  <c:v>1.33</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.67</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1</c:v>
+                  <c:v>0.67</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>0.67</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.33</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.67</c:v>
+                  <c:v>1.67</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.67</c:v>
+                  <c:v>2.33</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.33</c:v>
+                  <c:v>2.67</c:v>
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2</c:v>
+                  <c:v>1.33</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.33</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1</c:v>
+                  <c:v>0.67</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.33</c:v>
+                  <c:v>0.67</c:v>
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>0.33</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0</c:v>
+                  <c:v>0.33</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0</c:v>
+                  <c:v>0.33</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3373,79 +3445,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>46281.70833333334</c:v>
+                  <c:v>46281.875</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>46281.83333333334</c:v>
+                  <c:v>46282</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46281.95833333334</c:v>
+                  <c:v>46282.125</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46282.08333333334</c:v>
+                  <c:v>46282.25</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46282.20833333334</c:v>
+                  <c:v>46282.375</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46282.33333333334</c:v>
+                  <c:v>46282.5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46282.45833333334</c:v>
+                  <c:v>46282.625</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>46282.58333333334</c:v>
+                  <c:v>46282.75</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>46282.70833333334</c:v>
+                  <c:v>46282.875</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>46282.83333333334</c:v>
+                  <c:v>46283</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>46282.95833333334</c:v>
+                  <c:v>46283.125</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>46283.08333333334</c:v>
+                  <c:v>46283.25</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>46283.20833333334</c:v>
+                  <c:v>46283.375</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>46283.33333333334</c:v>
+                  <c:v>46283.5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>46283.45833333334</c:v>
+                  <c:v>46283.625</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46283.58333333334</c:v>
+                  <c:v>46283.75</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>46283.70833333334</c:v>
+                  <c:v>46283.875</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>46283.83333333334</c:v>
+                  <c:v>46284</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>46283.95833333334</c:v>
+                  <c:v>46284.125</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>46284.08333333334</c:v>
+                  <c:v>46284.25</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>46284.20833333334</c:v>
+                  <c:v>46284.375</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>46284.33333333334</c:v>
+                  <c:v>46284.5</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>46284.45833333334</c:v>
+                  <c:v>46284.625</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>46284.58333333334</c:v>
+                  <c:v>46284.75</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>46284.70833333334</c:v>
+                  <c:v>46284.875</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3457,79 +3529,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>2.62</c:v>
+                  <c:v>2.07</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.41</c:v>
+                  <c:v>1.9</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.22</c:v>
+                  <c:v>1.75</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.04</c:v>
+                  <c:v>1.61</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.88</c:v>
+                  <c:v>1.48</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.73</c:v>
+                  <c:v>1.36</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.59</c:v>
+                  <c:v>1.26</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.46</c:v>
+                  <c:v>1.16</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.34</c:v>
+                  <c:v>1.06</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.24</c:v>
+                  <c:v>0.98</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.14</c:v>
+                  <c:v>0.9</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.05</c:v>
+                  <c:v>0.83</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.96</c:v>
+                  <c:v>0.76</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.89</c:v>
+                  <c:v>0.7</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.82</c:v>
+                  <c:v>0.64</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.75</c:v>
+                  <c:v>0.59</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.6899999999999999</c:v>
+                  <c:v>0.55</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.63</c:v>
+                  <c:v>0.5</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.58</c:v>
+                  <c:v>0.46</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.54</c:v>
+                  <c:v>0.42</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.52</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.52</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.52</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.52</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.52</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3551,79 +3623,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>46281.70833333334</c:v>
+                  <c:v>46281.875</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>46281.83333333334</c:v>
+                  <c:v>46282</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46281.95833333334</c:v>
+                  <c:v>46282.125</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46282.08333333334</c:v>
+                  <c:v>46282.25</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46282.20833333334</c:v>
+                  <c:v>46282.375</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46282.33333333334</c:v>
+                  <c:v>46282.5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46282.45833333334</c:v>
+                  <c:v>46282.625</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>46282.58333333334</c:v>
+                  <c:v>46282.75</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>46282.70833333334</c:v>
+                  <c:v>46282.875</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>46282.83333333334</c:v>
+                  <c:v>46283</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>46282.95833333334</c:v>
+                  <c:v>46283.125</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>46283.08333333334</c:v>
+                  <c:v>46283.25</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>46283.20833333334</c:v>
+                  <c:v>46283.375</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>46283.33333333334</c:v>
+                  <c:v>46283.5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>46283.45833333334</c:v>
+                  <c:v>46283.625</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46283.58333333334</c:v>
+                  <c:v>46283.75</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>46283.70833333334</c:v>
+                  <c:v>46283.875</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>46283.83333333334</c:v>
+                  <c:v>46284</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>46283.95833333334</c:v>
+                  <c:v>46284.125</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>46284.08333333334</c:v>
+                  <c:v>46284.25</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>46284.20833333334</c:v>
+                  <c:v>46284.375</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>46284.33333333334</c:v>
+                  <c:v>46284.5</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>46284.45833333334</c:v>
+                  <c:v>46284.625</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>46284.58333333334</c:v>
+                  <c:v>46284.75</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>46284.70833333334</c:v>
+                  <c:v>46284.875</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3635,79 +3707,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>-9.56</c:v>
+                  <c:v>-9.77</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-11.03</c:v>
+                  <c:v>-9.77</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-11.61</c:v>
+                  <c:v>-9.859999999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-10.87</c:v>
+                  <c:v>-10.86</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-12.41</c:v>
+                  <c:v>-10.97</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-12.44</c:v>
+                  <c:v>-11.11</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-12.7</c:v>
+                  <c:v>-10.36</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-12.53</c:v>
+                  <c:v>-8.300000000000001</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-10.83</c:v>
+                  <c:v>-5.98</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-8.42</c:v>
+                  <c:v>-4.94</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-6.23</c:v>
+                  <c:v>-4.4</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-5.06</c:v>
+                  <c:v>-5.13</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-5.59</c:v>
+                  <c:v>-6.59</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-7.6</c:v>
+                  <c:v>-9.050000000000001</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-10.07</c:v>
+                  <c:v>-10.9</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-12.23</c:v>
+                  <c:v>-11.32</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-13.19</c:v>
+                  <c:v>-10.13</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-12.52</c:v>
+                  <c:v>-7.93</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-10.56</c:v>
+                  <c:v>-5.62</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-8.199999999999999</c:v>
+                  <c:v>-4.67</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-6.2</c:v>
+                  <c:v>-4.15</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>-4.91</c:v>
+                  <c:v>-3.9</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>-4.56</c:v>
+                  <c:v>-3.8</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>-4.42</c:v>
+                  <c:v>-3.76</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>-4.38</c:v>
+                  <c:v>-3.76</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3729,79 +3801,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>46281.70833333334</c:v>
+                  <c:v>46281.875</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>46281.83333333334</c:v>
+                  <c:v>46282</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46281.95833333334</c:v>
+                  <c:v>46282.125</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46282.08333333334</c:v>
+                  <c:v>46282.25</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46282.20833333334</c:v>
+                  <c:v>46282.375</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46282.33333333334</c:v>
+                  <c:v>46282.5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46282.45833333334</c:v>
+                  <c:v>46282.625</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>46282.58333333334</c:v>
+                  <c:v>46282.75</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>46282.70833333334</c:v>
+                  <c:v>46282.875</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>46282.83333333334</c:v>
+                  <c:v>46283</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>46282.95833333334</c:v>
+                  <c:v>46283.125</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>46283.08333333334</c:v>
+                  <c:v>46283.25</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>46283.20833333334</c:v>
+                  <c:v>46283.375</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>46283.33333333334</c:v>
+                  <c:v>46283.5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>46283.45833333334</c:v>
+                  <c:v>46283.625</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46283.58333333334</c:v>
+                  <c:v>46283.75</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>46283.70833333334</c:v>
+                  <c:v>46283.875</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>46283.83333333334</c:v>
+                  <c:v>46284</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>46283.95833333334</c:v>
+                  <c:v>46284.125</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>46284.08333333334</c:v>
+                  <c:v>46284.25</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>46284.20833333334</c:v>
+                  <c:v>46284.375</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>46284.33333333334</c:v>
+                  <c:v>46284.5</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>46284.45833333334</c:v>
+                  <c:v>46284.625</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>46284.58333333334</c:v>
+                  <c:v>46284.75</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>46284.70833333334</c:v>
+                  <c:v>46284.875</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3813,79 +3885,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>13.03</c:v>
+                  <c:v>14.6</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>14.27</c:v>
+                  <c:v>14.41</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>14.64</c:v>
+                  <c:v>14.34</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>13.71</c:v>
+                  <c:v>15.18</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>15.07</c:v>
+                  <c:v>15.14</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>14.94</c:v>
+                  <c:v>15.15</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>15.05</c:v>
+                  <c:v>14.28</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>14.74</c:v>
+                  <c:v>12.11</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>12.91</c:v>
+                  <c:v>9.57</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>10.39</c:v>
+                  <c:v>7.48</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>8.09</c:v>
+                  <c:v>6.38</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>6.5</c:v>
+                  <c:v>7.83</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>7.25</c:v>
+                  <c:v>9.960000000000001</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>9.18</c:v>
+                  <c:v>12.36</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>11.57</c:v>
+                  <c:v>14.14</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>13.66</c:v>
+                  <c:v>14.5</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>14.56</c:v>
+                  <c:v>13.26</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>13.82</c:v>
+                  <c:v>11.01</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>11.81</c:v>
+                  <c:v>8.66</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>9.4</c:v>
+                  <c:v>6.88</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>7.39</c:v>
+                  <c:v>5.82</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>6.1</c:v>
+                  <c:v>5.32</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>5.44</c:v>
+                  <c:v>5.13</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>5.17</c:v>
+                  <c:v>5.05</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>5.08</c:v>
+                  <c:v>5.05</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4014,79 +4086,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>46281.70833333334</c:v>
+                  <c:v>46281.875</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>46281.83333333334</c:v>
+                  <c:v>46282</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46281.95833333334</c:v>
+                  <c:v>46282.125</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46282.08333333334</c:v>
+                  <c:v>46282.25</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46282.20833333334</c:v>
+                  <c:v>46282.375</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46282.33333333334</c:v>
+                  <c:v>46282.5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46282.45833333334</c:v>
+                  <c:v>46282.625</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>46282.58333333334</c:v>
+                  <c:v>46282.75</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>46282.70833333334</c:v>
+                  <c:v>46282.875</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>46282.83333333334</c:v>
+                  <c:v>46283</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>46282.95833333334</c:v>
+                  <c:v>46283.125</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>46283.08333333334</c:v>
+                  <c:v>46283.25</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>46283.20833333334</c:v>
+                  <c:v>46283.375</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>46283.33333333334</c:v>
+                  <c:v>46283.5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>46283.45833333334</c:v>
+                  <c:v>46283.625</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46283.58333333334</c:v>
+                  <c:v>46283.75</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>46283.70833333334</c:v>
+                  <c:v>46283.875</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>46283.83333333334</c:v>
+                  <c:v>46284</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>46283.95833333334</c:v>
+                  <c:v>46284.125</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>46284.08333333334</c:v>
+                  <c:v>46284.25</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>46284.20833333334</c:v>
+                  <c:v>46284.375</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>46284.33333333334</c:v>
+                  <c:v>46284.5</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>46284.45833333334</c:v>
+                  <c:v>46284.625</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>46284.58333333334</c:v>
+                  <c:v>46284.75</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>46284.70833333334</c:v>
+                  <c:v>46284.875</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4098,79 +4170,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>47.7</c:v>
+                  <c:v>57.3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>53.9</c:v>
+                  <c:v>57.9</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>56.6</c:v>
+                  <c:v>58.8</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>54.4</c:v>
+                  <c:v>63.2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>60.8</c:v>
+                  <c:v>64.09999999999999</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>61.5</c:v>
+                  <c:v>65.2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>63</c:v>
+                  <c:v>62.8</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>62.9</c:v>
+                  <c:v>55.5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>57</c:v>
+                  <c:v>46.6</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>48.3</c:v>
+                  <c:v>39.5</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>40.4</c:v>
+                  <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>35.2</c:v>
+                  <c:v>42.2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>38.8</c:v>
+                  <c:v>51</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>46.9</c:v>
+                  <c:v>60.6</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>56.6</c:v>
+                  <c:v>68</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>65.2</c:v>
+                  <c:v>69.8</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>69.2</c:v>
+                  <c:v>65.59999999999999</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>66.90000000000001</c:v>
+                  <c:v>57.5</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>59.8</c:v>
+                  <c:v>48.9</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>51</c:v>
+                  <c:v>42.5</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>43.5</c:v>
+                  <c:v>38.6</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>38.6</c:v>
+                  <c:v>36.7</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>36.1</c:v>
+                  <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>35.1</c:v>
+                  <c:v>35.7</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>34.8</c:v>
+                  <c:v>35.7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4826,7 +4898,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="5">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>25</v>
@@ -4835,16 +4907,16 @@
         <v>24</v>
       </c>
       <c r="F9" s="5">
-        <v>37.788</v>
+        <v>48.483</v>
       </c>
       <c r="G9" s="5">
-        <v>-8.276</v>
+        <v>47.4</v>
       </c>
       <c r="H9" s="5">
         <v>70.8</v>
       </c>
       <c r="I9" s="5">
-        <v>91.7</v>
+        <v>83.3</v>
       </c>
       <c r="J9" s="5" t="s">
         <v>26</v>
@@ -4855,25 +4927,25 @@
         <v>10</v>
       </c>
       <c r="B10" s="5">
-        <v>2844</v>
+        <v>3271</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>27</v>
       </c>
       <c r="E10" s="5">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F10" s="5">
-        <v>50.431</v>
+        <v>66.477</v>
       </c>
       <c r="G10" s="5">
-        <v>3.9</v>
+        <v>57.005</v>
       </c>
       <c r="H10" s="5">
-        <v>58.1</v>
+        <v>54.3</v>
       </c>
       <c r="I10" s="5">
-        <v>83.90000000000001</v>
+        <v>74.3</v>
       </c>
       <c r="J10" s="5" t="s">
         <v>26</v>
@@ -4884,25 +4956,25 @@
         <v>11</v>
       </c>
       <c r="B11" s="5">
-        <v>2831</v>
+        <v>3259</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>28</v>
       </c>
       <c r="E11" s="5">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F11" s="5">
-        <v>50.431</v>
+        <v>66.477</v>
       </c>
       <c r="G11" s="5">
-        <v>3.9</v>
+        <v>57.005</v>
       </c>
       <c r="H11" s="5">
-        <v>58.1</v>
+        <v>54.3</v>
       </c>
       <c r="I11" s="5">
-        <v>83.90000000000001</v>
+        <v>74.3</v>
       </c>
       <c r="J11" s="5" t="s">
         <v>26</v>
@@ -4984,7 +5056,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="5">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -4992,7 +5064,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="5">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -5005,7 +5077,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.7109375" customWidth="1"/>
@@ -5136,10 +5208,10 @@
         <v>46280.70833333334</v>
       </c>
       <c r="B8" s="5">
-        <v>425</v>
+        <v>425.95</v>
       </c>
       <c r="C8" s="5">
-        <v>0.805</v>
+        <v>0.79</v>
       </c>
       <c r="D8" s="5">
         <v>9.25</v>
@@ -5153,16 +5225,16 @@
         <v>46280.75</v>
       </c>
       <c r="B9" s="5">
-        <v>683.64</v>
+        <v>612.25</v>
       </c>
       <c r="C9" s="5">
-        <v>0.27</v>
+        <v>0.22</v>
       </c>
       <c r="D9" s="5">
         <v>-7.3</v>
       </c>
       <c r="E9" s="5">
-        <v>12.51</v>
+        <v>12.535</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -5170,16 +5242,16 @@
         <v>46280.79166666666</v>
       </c>
       <c r="B10" s="5">
-        <v>621.9349999999999</v>
+        <v>626.875</v>
       </c>
       <c r="C10" s="5">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="D10" s="5">
-        <v>-8.824999999999999</v>
+        <v>-8.91</v>
       </c>
       <c r="E10" s="5">
-        <v>11.945</v>
+        <v>11.86</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -5187,16 +5259,16 @@
         <v>46280.83333333334</v>
       </c>
       <c r="B11" s="5">
-        <v>515.475</v>
+        <v>515.75</v>
       </c>
       <c r="C11" s="5">
-        <v>0.35</v>
+        <v>0.25</v>
       </c>
       <c r="D11" s="5">
-        <v>-9.07</v>
+        <v>-9.185</v>
       </c>
       <c r="E11" s="5">
-        <v>13.505</v>
+        <v>13.555</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -5204,16 +5276,16 @@
         <v>46280.875</v>
       </c>
       <c r="B12" s="5">
-        <v>468.7</v>
+        <v>464.39</v>
       </c>
       <c r="C12" s="5">
-        <v>3.88</v>
+        <v>3.91</v>
       </c>
       <c r="D12" s="5">
-        <v>0.85</v>
+        <v>0.44</v>
       </c>
       <c r="E12" s="5">
-        <v>12.37</v>
+        <v>12.31</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -5221,13 +5293,13 @@
         <v>46280.91666666666</v>
       </c>
       <c r="B13" s="5">
-        <v>446.015</v>
+        <v>446.05</v>
       </c>
       <c r="C13" s="5">
-        <v>8.135</v>
+        <v>7.54</v>
       </c>
       <c r="D13" s="5">
-        <v>-2.27</v>
+        <v>-2.73</v>
       </c>
       <c r="E13" s="5">
         <v>10.64</v>
@@ -5238,16 +5310,16 @@
         <v>46280.95833333334</v>
       </c>
       <c r="B14" s="5">
-        <v>465.25</v>
+        <v>462.23</v>
       </c>
       <c r="C14" s="5">
-        <v>9.465</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="D14" s="5">
-        <v>-4.725</v>
+        <v>-4.73</v>
       </c>
       <c r="E14" s="5">
-        <v>11.045</v>
+        <v>10.94</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -5255,16 +5327,16 @@
         <v>46281</v>
       </c>
       <c r="B15" s="5">
-        <v>516.8049999999999</v>
+        <v>517.345</v>
       </c>
       <c r="C15" s="5">
-        <v>18.99</v>
+        <v>20.685</v>
       </c>
       <c r="D15" s="5">
         <v>1.87</v>
       </c>
       <c r="E15" s="5">
-        <v>12.76</v>
+        <v>12.745</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -5272,16 +5344,16 @@
         <v>46281.04166666666</v>
       </c>
       <c r="B16" s="5">
-        <v>521.405</v>
+        <v>522.005</v>
       </c>
       <c r="C16" s="5">
-        <v>13.26</v>
+        <v>13.335</v>
       </c>
       <c r="D16" s="5">
-        <v>5.805</v>
+        <v>5.7</v>
       </c>
       <c r="E16" s="5">
-        <v>10.84</v>
+        <v>10.875</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -5289,16 +5361,16 @@
         <v>46281.08333333334</v>
       </c>
       <c r="B17" s="5">
-        <v>526.9</v>
+        <v>527.735</v>
       </c>
       <c r="C17" s="5">
-        <v>8.585000000000001</v>
+        <v>8.984999999999999</v>
       </c>
       <c r="D17" s="5">
-        <v>3.745</v>
+        <v>3.645</v>
       </c>
       <c r="E17" s="5">
-        <v>10.305</v>
+        <v>10.335</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -5309,13 +5381,13 @@
         <v>531.665</v>
       </c>
       <c r="C18" s="5">
-        <v>6.305</v>
+        <v>6.48</v>
       </c>
       <c r="D18" s="5">
-        <v>0.475</v>
+        <v>0.195</v>
       </c>
       <c r="E18" s="5">
-        <v>7.155</v>
+        <v>6.895</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -5323,16 +5395,16 @@
         <v>46281.16666666666</v>
       </c>
       <c r="B19" s="5">
-        <v>538.105</v>
+        <v>537.3200000000001</v>
       </c>
       <c r="C19" s="5">
-        <v>5.405</v>
+        <v>5.49</v>
       </c>
       <c r="D19" s="5">
-        <v>-0.54</v>
+        <v>-0.465</v>
       </c>
       <c r="E19" s="5">
-        <v>7.025</v>
+        <v>7.055</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -5340,16 +5412,16 @@
         <v>46281.20833333334</v>
       </c>
       <c r="B20" s="5">
-        <v>536.1900000000001</v>
+        <v>536.5</v>
       </c>
       <c r="C20" s="5">
-        <v>5.515</v>
+        <v>5.47</v>
       </c>
       <c r="D20" s="5">
-        <v>1.89</v>
+        <v>2.175</v>
       </c>
       <c r="E20" s="5">
-        <v>6.79</v>
+        <v>6.81</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -5357,16 +5429,16 @@
         <v>46281.25</v>
       </c>
       <c r="B21" s="5">
-        <v>532.135</v>
+        <v>532.015</v>
       </c>
       <c r="C21" s="5">
-        <v>5.54</v>
+        <v>5.57</v>
       </c>
       <c r="D21" s="5">
-        <v>4.58</v>
+        <v>4.84</v>
       </c>
       <c r="E21" s="5">
-        <v>6.435</v>
+        <v>6.46</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -5374,16 +5446,16 @@
         <v>46281.29166666666</v>
       </c>
       <c r="B22" s="5">
-        <v>522.005</v>
+        <v>521.465</v>
       </c>
       <c r="C22" s="5">
-        <v>5.155</v>
+        <v>5.2</v>
       </c>
       <c r="D22" s="5">
-        <v>3.16</v>
+        <v>3.395</v>
       </c>
       <c r="E22" s="5">
-        <v>5.75</v>
+        <v>5.66</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -5391,13 +5463,13 @@
         <v>46281.33333333334</v>
       </c>
       <c r="B23" s="5">
-        <v>543.4</v>
+        <v>542.7</v>
       </c>
       <c r="C23" s="5">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="D23" s="5">
-        <v>4.49</v>
+        <v>4.47</v>
       </c>
       <c r="E23" s="5">
         <v>4.89</v>
@@ -5408,16 +5480,16 @@
         <v>46281.375</v>
       </c>
       <c r="B24" s="5">
-        <v>540.355</v>
+        <v>539.8</v>
       </c>
       <c r="C24" s="5">
-        <v>0.585</v>
+        <v>0.61</v>
       </c>
       <c r="D24" s="5">
-        <v>2.415</v>
+        <v>2.71</v>
       </c>
       <c r="E24" s="5">
-        <v>4.65</v>
+        <v>4.67</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -5425,16 +5497,16 @@
         <v>46281.41666666666</v>
       </c>
       <c r="B25" s="5">
-        <v>543.275</v>
+        <v>542.86</v>
       </c>
       <c r="C25" s="5">
-        <v>0.77</v>
+        <v>0.985</v>
       </c>
       <c r="D25" s="5">
-        <v>-2.185</v>
+        <v>-2.115</v>
       </c>
       <c r="E25" s="5">
-        <v>4.76</v>
+        <v>4.775</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -5442,16 +5514,16 @@
         <v>46281.45833333334</v>
       </c>
       <c r="B26" s="5">
-        <v>537.65</v>
+        <v>537.5</v>
       </c>
       <c r="C26" s="5">
-        <v>0.285</v>
+        <v>0.33</v>
       </c>
       <c r="D26" s="5">
-        <v>-2.36</v>
+        <v>-2.31</v>
       </c>
       <c r="E26" s="5">
-        <v>4.31</v>
+        <v>4.285</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -5459,16 +5531,16 @@
         <v>46281.5</v>
       </c>
       <c r="B27" s="5">
-        <v>550.7</v>
+        <v>549.295</v>
       </c>
       <c r="C27" s="5">
-        <v>0.105</v>
+        <v>0.1</v>
       </c>
       <c r="D27" s="5">
-        <v>1.03</v>
+        <v>0.825</v>
       </c>
       <c r="E27" s="5">
-        <v>4.475</v>
+        <v>4.505</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -5476,16 +5548,16 @@
         <v>46281.54166666666</v>
       </c>
       <c r="B28" s="5">
-        <v>564.675</v>
+        <v>562.86</v>
       </c>
       <c r="C28" s="5">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="D28" s="5">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="E28" s="5">
-        <v>5.025</v>
+        <v>4.875</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -5493,16 +5565,16 @@
         <v>46281.58333333334</v>
       </c>
       <c r="B29" s="5">
-        <v>545.58</v>
+        <v>545.145</v>
       </c>
       <c r="C29" s="5">
-        <v>0.075</v>
+        <v>0.08</v>
       </c>
       <c r="D29" s="5">
-        <v>4.84</v>
+        <v>4.75</v>
       </c>
       <c r="E29" s="5">
-        <v>5.485</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -5510,16 +5582,16 @@
         <v>46281.625</v>
       </c>
       <c r="B30" s="5">
-        <v>533.715</v>
+        <v>534.22</v>
       </c>
       <c r="C30" s="5">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="D30" s="5">
-        <v>4.465</v>
+        <v>3.97</v>
       </c>
       <c r="E30" s="5">
-        <v>5.845</v>
+        <v>5.77</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -5527,16 +5599,16 @@
         <v>46281.66666666666</v>
       </c>
       <c r="B31" s="5">
-        <v>524.7</v>
+        <v>524.6</v>
       </c>
       <c r="C31" s="5">
-        <v>0.345</v>
+        <v>0.17</v>
       </c>
       <c r="D31" s="5">
-        <v>4.095</v>
+        <v>4.115</v>
       </c>
       <c r="E31" s="5">
-        <v>5.61</v>
+        <v>5.645</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -5544,16 +5616,84 @@
         <v>46281.70833333334</v>
       </c>
       <c r="B32" s="5">
-        <v>527.55</v>
+        <v>535.595</v>
       </c>
       <c r="C32" s="5">
-        <v>4.82</v>
+        <v>0.2</v>
       </c>
       <c r="D32" s="5">
-        <v>4.29</v>
+        <v>4.095</v>
       </c>
       <c r="E32" s="5">
-        <v>5.585</v>
+        <v>5.645</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6">
+        <v>46281.75</v>
+      </c>
+      <c r="B33" s="5">
+        <v>524</v>
+      </c>
+      <c r="C33" s="5">
+        <v>2.55</v>
+      </c>
+      <c r="D33" s="5">
+        <v>3.035</v>
+      </c>
+      <c r="E33" s="5">
+        <v>5.44</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6">
+        <v>46281.79166666666</v>
+      </c>
+      <c r="B34" s="5">
+        <v>501.43</v>
+      </c>
+      <c r="C34" s="5">
+        <v>3.785</v>
+      </c>
+      <c r="D34" s="5">
+        <v>2.18</v>
+      </c>
+      <c r="E34" s="5">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6">
+        <v>46281.83333333334</v>
+      </c>
+      <c r="B35" s="5">
+        <v>509.7</v>
+      </c>
+      <c r="C35" s="5">
+        <v>3.12</v>
+      </c>
+      <c r="D35" s="5">
+        <v>0.58</v>
+      </c>
+      <c r="E35" s="5">
+        <v>5.05</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6">
+        <v>46281.875</v>
+      </c>
+      <c r="B36" s="5">
+        <v>504.155</v>
+      </c>
+      <c r="C36" s="5">
+        <v>3.02</v>
+      </c>
+      <c r="D36" s="5">
+        <v>2.395</v>
+      </c>
+      <c r="E36" s="5">
+        <v>4.9</v>
       </c>
     </row>
   </sheetData>
@@ -5597,19 +5737,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="6">
-        <v>46281.58333333334</v>
+        <v>46281.75</v>
       </c>
       <c r="B2" s="5">
-        <v>506.49</v>
+        <v>604.42</v>
       </c>
       <c r="C2" s="5">
-        <v>336.73</v>
+        <v>377.68</v>
       </c>
       <c r="D2" s="5">
-        <v>559.8</v>
+        <v>531.42</v>
       </c>
       <c r="E2" s="5">
-        <v>218.74</v>
+        <v>299.12</v>
       </c>
       <c r="F2" s="5"/>
       <c r="G2" s="5" t="s">
@@ -5618,19 +5758,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="6">
-        <v>46281.625</v>
+        <v>46281.79166666666</v>
       </c>
       <c r="B3" s="5">
-        <v>512.8</v>
+        <v>623.3200000000001</v>
       </c>
       <c r="C3" s="5">
-        <v>337.2</v>
+        <v>373.72</v>
       </c>
       <c r="D3" s="5">
-        <v>535.9</v>
+        <v>505.04</v>
       </c>
       <c r="E3" s="5">
-        <v>226.26</v>
+        <v>329.26</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5" t="s">
@@ -5639,19 +5779,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="6">
-        <v>46281.66666666666</v>
+        <v>46281.83333333334</v>
       </c>
       <c r="B4" s="5">
-        <v>523</v>
+        <v>636.67</v>
       </c>
       <c r="C4" s="5">
-        <v>335.99</v>
+        <v>364.8</v>
       </c>
       <c r="D4" s="5">
-        <v>527.89</v>
+        <v>505.5</v>
       </c>
       <c r="E4" s="5">
-        <v>240.97</v>
+        <v>358.66</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="5" t="s">
@@ -5660,19 +5800,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="6">
-        <v>46281.70833333334</v>
+        <v>46281.875</v>
       </c>
       <c r="B5" s="5">
-        <v>536.65</v>
+        <v>649.9400000000001</v>
       </c>
       <c r="C5" s="5">
-        <v>332.85</v>
+        <v>359.37</v>
       </c>
       <c r="D5" s="5">
-        <v>525.35</v>
+        <v>508.88</v>
       </c>
       <c r="E5" s="5">
-        <v>262.6</v>
+        <v>383.33</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5" t="s">
@@ -5681,17 +5821,17 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="6">
-        <v>46281.75</v>
+        <v>46281.91666666666</v>
       </c>
       <c r="B6" s="5">
-        <v>545.01</v>
+        <v>654.25</v>
       </c>
       <c r="C6" s="5">
-        <v>333.21</v>
+        <v>358.92</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5">
-        <v>289.76</v>
+        <v>399.87</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="5" t="s">
@@ -5700,17 +5840,17 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="6">
-        <v>46281.79166666666</v>
+        <v>46281.95833333334</v>
       </c>
       <c r="B7" s="5">
-        <v>558.05</v>
+        <v>655.86</v>
       </c>
       <c r="C7" s="5">
-        <v>332.42</v>
+        <v>357.83</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5">
-        <v>319.78</v>
+        <v>399</v>
       </c>
       <c r="F7" s="5"/>
       <c r="G7" s="5" t="s">
@@ -5719,17 +5859,17 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="6">
-        <v>46281.83333333334</v>
+        <v>46282</v>
       </c>
       <c r="B8" s="5">
-        <v>573.1799999999999</v>
+        <v>655.39</v>
       </c>
       <c r="C8" s="5">
-        <v>330.34</v>
+        <v>356.4</v>
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="5">
-        <v>349.09</v>
+        <v>396.46</v>
       </c>
       <c r="F8" s="5"/>
       <c r="G8" s="5" t="s">
@@ -5738,17 +5878,17 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="6">
-        <v>46281.875</v>
+        <v>46282.04166666666</v>
       </c>
       <c r="B9" s="5">
-        <v>589.47</v>
+        <v>653.39</v>
       </c>
       <c r="C9" s="5">
-        <v>328.68</v>
+        <v>354.54</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="5">
-        <v>373.76</v>
+        <v>393.96</v>
       </c>
       <c r="F9" s="5"/>
       <c r="G9" s="5" t="s">
@@ -5757,17 +5897,17 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="6">
-        <v>46281.91666666666</v>
+        <v>46282.08333333334</v>
       </c>
       <c r="B10" s="5">
-        <v>603.46</v>
+        <v>651.72</v>
       </c>
       <c r="C10" s="5">
-        <v>326.65</v>
+        <v>353.87</v>
       </c>
       <c r="D10" s="5"/>
       <c r="E10" s="5">
-        <v>390.37</v>
+        <v>390.75</v>
       </c>
       <c r="F10" s="5"/>
       <c r="G10" s="5" t="s">
@@ -5776,17 +5916,17 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="6">
-        <v>46281.95833333334</v>
+        <v>46282.125</v>
       </c>
       <c r="B11" s="5">
-        <v>612.8200000000001</v>
+        <v>649.52</v>
       </c>
       <c r="C11" s="5">
-        <v>326.24</v>
+        <v>351.96</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="5">
-        <v>389.81</v>
+        <v>391.92</v>
       </c>
       <c r="F11" s="5"/>
       <c r="G11" s="5" t="s">
@@ -5795,17 +5935,17 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="6">
-        <v>46282</v>
+        <v>46282.16666666666</v>
       </c>
       <c r="B12" s="5">
-        <v>621.51</v>
+        <v>645.62</v>
       </c>
       <c r="C12" s="5">
-        <v>329.57</v>
+        <v>352.66</v>
       </c>
       <c r="D12" s="5"/>
       <c r="E12" s="5">
-        <v>387.42</v>
+        <v>376.61</v>
       </c>
       <c r="F12" s="5"/>
       <c r="G12" s="5" t="s">
@@ -5814,17 +5954,17 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="6">
-        <v>46282.04166666666</v>
+        <v>46282.20833333334</v>
       </c>
       <c r="B13" s="5">
-        <v>625.97</v>
+        <v>644.9299999999999</v>
       </c>
       <c r="C13" s="5">
-        <v>331.49</v>
+        <v>352.7</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="5">
-        <v>384.78</v>
+        <v>383.92</v>
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="5" t="s">
@@ -5833,17 +5973,17 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="6">
-        <v>46282.08333333334</v>
+        <v>46282.25</v>
       </c>
       <c r="B14" s="5">
-        <v>627.51</v>
+        <v>646.13</v>
       </c>
       <c r="C14" s="5">
-        <v>332.53</v>
+        <v>352.36</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="5">
-        <v>381.15</v>
+        <v>390.85</v>
       </c>
       <c r="F14" s="5"/>
       <c r="G14" s="5" t="s">
@@ -5852,17 +5992,17 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="6">
-        <v>46282.125</v>
+        <v>46282.29166666666</v>
       </c>
       <c r="B15" s="5">
-        <v>628.49</v>
+        <v>647.36</v>
       </c>
       <c r="C15" s="5">
-        <v>333.02</v>
+        <v>352.14</v>
       </c>
       <c r="D15" s="5"/>
       <c r="E15" s="5">
-        <v>381.76</v>
+        <v>392.57</v>
       </c>
       <c r="F15" s="5"/>
       <c r="G15" s="5" t="s">
@@ -5871,17 +6011,17 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="6">
-        <v>46282.16666666666</v>
+        <v>46282.33333333334</v>
       </c>
       <c r="B16" s="5">
-        <v>624.35</v>
+        <v>643.6900000000001</v>
       </c>
       <c r="C16" s="5">
-        <v>333.16</v>
+        <v>352.02</v>
       </c>
       <c r="D16" s="5"/>
       <c r="E16" s="5">
-        <v>366.18</v>
+        <v>377.15</v>
       </c>
       <c r="F16" s="5"/>
       <c r="G16" s="5" t="s">
@@ -5890,17 +6030,17 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="6">
-        <v>46282.20833333334</v>
+        <v>46282.375</v>
       </c>
       <c r="B17" s="5">
-        <v>623.59</v>
+        <v>641.37</v>
       </c>
       <c r="C17" s="5">
-        <v>333.1</v>
+        <v>351.97</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="5">
-        <v>372.84</v>
+        <v>376.88</v>
       </c>
       <c r="F17" s="5"/>
       <c r="G17" s="5" t="s">
@@ -5909,17 +6049,17 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="6">
-        <v>46282.25</v>
+        <v>46282.41666666666</v>
       </c>
       <c r="B18" s="5">
-        <v>624.8200000000001</v>
+        <v>637.99</v>
       </c>
       <c r="C18" s="5">
-        <v>332.89</v>
+        <v>352.13</v>
       </c>
       <c r="D18" s="5"/>
       <c r="E18" s="5">
-        <v>379.19</v>
+        <v>369.49</v>
       </c>
       <c r="F18" s="5"/>
       <c r="G18" s="5" t="s">
@@ -5928,17 +6068,17 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="6">
-        <v>46282.29166666666</v>
+        <v>46282.45833333334</v>
       </c>
       <c r="B19" s="5">
-        <v>626.1900000000001</v>
+        <v>632.58</v>
       </c>
       <c r="C19" s="5">
-        <v>332.93</v>
+        <v>352.53</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="5">
-        <v>380.65</v>
+        <v>356.95</v>
       </c>
       <c r="F19" s="5"/>
       <c r="G19" s="5" t="s">
@@ -5947,17 +6087,17 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="6">
-        <v>46282.33333333334</v>
+        <v>46282.5</v>
       </c>
       <c r="B20" s="5">
-        <v>622.55</v>
+        <v>625.0599999999999</v>
       </c>
       <c r="C20" s="5">
-        <v>333.13</v>
+        <v>353.07</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="5">
-        <v>364.85</v>
+        <v>341.44</v>
       </c>
       <c r="F20" s="5"/>
       <c r="G20" s="5" t="s">
@@ -5966,17 +6106,17 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="6">
-        <v>46282.375</v>
+        <v>46282.54166666666</v>
       </c>
       <c r="B21" s="5">
-        <v>620.36</v>
+        <v>614.1799999999999</v>
       </c>
       <c r="C21" s="5">
-        <v>333.43</v>
+        <v>353.54</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5">
-        <v>364.49</v>
+        <v>319.42</v>
       </c>
       <c r="F21" s="5"/>
       <c r="G21" s="5" t="s">
@@ -5985,17 +6125,17 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="6">
-        <v>46282.41666666666</v>
+        <v>46282.58333333334</v>
       </c>
       <c r="B22" s="5">
-        <v>617.05</v>
+        <v>601.63</v>
       </c>
       <c r="C22" s="5">
-        <v>333.78</v>
+        <v>353.96</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="5">
-        <v>357.3</v>
+        <v>298.82</v>
       </c>
       <c r="F22" s="5"/>
       <c r="G22" s="5" t="s">
@@ -6004,17 +6144,17 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="6">
-        <v>46282.45833333334</v>
+        <v>46282.625</v>
       </c>
       <c r="B23" s="5">
-        <v>611.59</v>
+        <v>588.42</v>
       </c>
       <c r="C23" s="5">
-        <v>334.18</v>
+        <v>354.33</v>
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="5">
-        <v>345.16</v>
+        <v>279.55</v>
       </c>
       <c r="F23" s="5"/>
       <c r="G23" s="5" t="s">
@@ -6023,17 +6163,17 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="6">
-        <v>46282.5</v>
+        <v>46282.66666666666</v>
       </c>
       <c r="B24" s="5">
-        <v>603.96</v>
+        <v>575.15</v>
       </c>
       <c r="C24" s="5">
-        <v>334.59</v>
+        <v>354.69</v>
       </c>
       <c r="D24" s="5"/>
       <c r="E24" s="5">
-        <v>330.15</v>
+        <v>261.52</v>
       </c>
       <c r="F24" s="5"/>
       <c r="G24" s="5" t="s">
@@ -6042,17 +6182,17 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="6">
-        <v>46282.54166666666</v>
+        <v>46282.70833333334</v>
       </c>
       <c r="B25" s="5">
-        <v>592.95</v>
+        <v>562.1799999999999</v>
       </c>
       <c r="C25" s="5">
-        <v>334.86</v>
+        <v>355.02</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="5">
-        <v>308.86</v>
+        <v>244.65</v>
       </c>
       <c r="F25" s="5"/>
       <c r="G25" s="5" t="s">
@@ -6061,17 +6201,17 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="6">
-        <v>46282.58333333334</v>
+        <v>46282.75</v>
       </c>
       <c r="B26" s="5">
-        <v>580.27</v>
+        <v>549.7</v>
       </c>
       <c r="C26" s="5">
-        <v>335.04</v>
+        <v>355.33</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5">
-        <v>288.94</v>
+        <v>228.88</v>
       </c>
       <c r="F26" s="5"/>
       <c r="G26" s="5" t="s">
@@ -6080,17 +6220,17 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="6">
-        <v>46282.625</v>
+        <v>46282.79166666666</v>
       </c>
       <c r="B27" s="5">
-        <v>566.92</v>
+        <v>537.6900000000001</v>
       </c>
       <c r="C27" s="5">
-        <v>335.16</v>
+        <v>355.51</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="5">
-        <v>270.3</v>
+        <v>214.11</v>
       </c>
       <c r="F27" s="5"/>
       <c r="G27" s="5" t="s">
@@ -6099,17 +6239,17 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="6">
-        <v>46282.66666666666</v>
+        <v>46282.83333333334</v>
       </c>
       <c r="B28" s="5">
-        <v>553.51</v>
+        <v>524.95</v>
       </c>
       <c r="C28" s="5">
-        <v>335.25</v>
+        <v>355.6</v>
       </c>
       <c r="D28" s="5"/>
       <c r="E28" s="5">
-        <v>252.87</v>
+        <v>195.77</v>
       </c>
       <c r="F28" s="5"/>
       <c r="G28" s="5" t="s">
@@ -6118,17 +6258,17 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="6">
-        <v>46282.70833333334</v>
+        <v>46282.875</v>
       </c>
       <c r="B29" s="5">
-        <v>540.4</v>
+        <v>513.38</v>
       </c>
       <c r="C29" s="5">
-        <v>335.31</v>
+        <v>355.64</v>
       </c>
       <c r="D29" s="5"/>
       <c r="E29" s="5">
-        <v>236.56</v>
+        <v>183.14</v>
       </c>
       <c r="F29" s="5"/>
       <c r="G29" s="5" t="s">
@@ -6137,17 +6277,17 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="6">
-        <v>46282.75</v>
+        <v>46282.91666666666</v>
       </c>
       <c r="B30" s="5">
-        <v>527.78</v>
+        <v>502.79</v>
       </c>
       <c r="C30" s="5">
-        <v>335.36</v>
+        <v>355.63</v>
       </c>
       <c r="D30" s="5"/>
       <c r="E30" s="5">
-        <v>221.3</v>
+        <v>171.33</v>
       </c>
       <c r="F30" s="5"/>
       <c r="G30" s="5" t="s">
@@ -6156,17 +6296,17 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="6">
-        <v>46282.79166666666</v>
+        <v>46282.95833333334</v>
       </c>
       <c r="B31" s="5">
-        <v>515.64</v>
+        <v>493</v>
       </c>
       <c r="C31" s="5">
-        <v>335.28</v>
+        <v>355.6</v>
       </c>
       <c r="D31" s="5"/>
       <c r="E31" s="5">
-        <v>207.03</v>
+        <v>160.28</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="5" t="s">
@@ -6175,17 +6315,17 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="6">
-        <v>46282.83333333334</v>
+        <v>46283</v>
       </c>
       <c r="B32" s="5">
-        <v>502.88</v>
+        <v>483.95</v>
       </c>
       <c r="C32" s="5">
-        <v>335.12</v>
+        <v>355.54</v>
       </c>
       <c r="D32" s="5"/>
       <c r="E32" s="5">
-        <v>189.68</v>
+        <v>150</v>
       </c>
       <c r="F32" s="5"/>
       <c r="G32" s="5" t="s">
@@ -6194,17 +6334,17 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="6">
-        <v>46282.875</v>
+        <v>46283.04166666666</v>
       </c>
       <c r="B33" s="5">
-        <v>491.25</v>
+        <v>474.98</v>
       </c>
       <c r="C33" s="5">
-        <v>334.91</v>
+        <v>356.4</v>
       </c>
       <c r="D33" s="5"/>
       <c r="E33" s="5">
-        <v>177.45</v>
+        <v>135.26</v>
       </c>
       <c r="F33" s="5"/>
       <c r="G33" s="5" t="s">
@@ -6213,17 +6353,17 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="6">
-        <v>46282.91666666666</v>
+        <v>46283.08333333334</v>
       </c>
       <c r="B34" s="5">
-        <v>480.56</v>
+        <v>467.85</v>
       </c>
       <c r="C34" s="5">
-        <v>334.67</v>
+        <v>357.83</v>
       </c>
       <c r="D34" s="5"/>
       <c r="E34" s="5">
-        <v>166</v>
+        <v>126.76</v>
       </c>
       <c r="F34" s="5"/>
       <c r="G34" s="5" t="s">
@@ -6232,17 +6372,17 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="6">
-        <v>46282.95833333334</v>
+        <v>46283.125</v>
       </c>
       <c r="B35" s="5">
-        <v>470.65</v>
+        <v>462.11</v>
       </c>
       <c r="C35" s="5">
-        <v>334.4</v>
+        <v>359.59</v>
       </c>
       <c r="D35" s="5"/>
       <c r="E35" s="5">
-        <v>155.3</v>
+        <v>119.06</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="5" t="s">
@@ -6251,17 +6391,17 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="6">
-        <v>46283</v>
+        <v>46283.16666666666</v>
       </c>
       <c r="B36" s="5">
-        <v>461.47</v>
+        <v>457.5</v>
       </c>
       <c r="C36" s="5">
-        <v>334.13</v>
+        <v>361.57</v>
       </c>
       <c r="D36" s="5"/>
       <c r="E36" s="5">
-        <v>145.34</v>
+        <v>112.36</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="5" t="s">
@@ -6270,17 +6410,17 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="6">
-        <v>46283.04166666666</v>
+        <v>46283.20833333334</v>
       </c>
       <c r="B37" s="5">
-        <v>452.48</v>
+        <v>453.98</v>
       </c>
       <c r="C37" s="5">
-        <v>334.8</v>
+        <v>363.68</v>
       </c>
       <c r="D37" s="5"/>
       <c r="E37" s="5">
-        <v>131.34</v>
+        <v>107.01</v>
       </c>
       <c r="F37" s="5"/>
       <c r="G37" s="5" t="s">
@@ -6289,17 +6429,17 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="6">
-        <v>46283.08333333334</v>
+        <v>46283.25</v>
       </c>
       <c r="B38" s="5">
-        <v>445.31</v>
+        <v>451.68</v>
       </c>
       <c r="C38" s="5">
-        <v>336.05</v>
+        <v>365.87</v>
       </c>
       <c r="D38" s="5"/>
       <c r="E38" s="5">
-        <v>123.08</v>
+        <v>103.54</v>
       </c>
       <c r="F38" s="5"/>
       <c r="G38" s="5" t="s">
@@ -6308,17 +6448,17 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="6">
-        <v>46283.125</v>
+        <v>46283.29166666666</v>
       </c>
       <c r="B39" s="5">
-        <v>439.51</v>
+        <v>450</v>
       </c>
       <c r="C39" s="5">
-        <v>337.67</v>
+        <v>367.21</v>
       </c>
       <c r="D39" s="5"/>
       <c r="E39" s="5">
-        <v>115.61</v>
+        <v>102.74</v>
       </c>
       <c r="F39" s="5"/>
       <c r="G39" s="5" t="s">
@@ -6327,17 +6467,17 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="6">
-        <v>46283.16666666666</v>
+        <v>46283.33333333334</v>
       </c>
       <c r="B40" s="5">
-        <v>434.83</v>
+        <v>449.75</v>
       </c>
       <c r="C40" s="5">
-        <v>339.51</v>
+        <v>368.01</v>
       </c>
       <c r="D40" s="5"/>
       <c r="E40" s="5">
-        <v>109.12</v>
+        <v>105.55</v>
       </c>
       <c r="F40" s="5"/>
       <c r="G40" s="5" t="s">
@@ -6346,17 +6486,17 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="6">
-        <v>46283.20833333334</v>
+        <v>46283.375</v>
       </c>
       <c r="B41" s="5">
-        <v>431.24</v>
+        <v>451.7</v>
       </c>
       <c r="C41" s="5">
-        <v>341.49</v>
+        <v>368.49</v>
       </c>
       <c r="D41" s="5"/>
       <c r="E41" s="5">
-        <v>103.93</v>
+        <v>112.95</v>
       </c>
       <c r="F41" s="5"/>
       <c r="G41" s="5" t="s">
@@ -6365,17 +6505,17 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="6">
-        <v>46283.25</v>
+        <v>46283.41666666666</v>
       </c>
       <c r="B42" s="5">
-        <v>428.87</v>
+        <v>456.56</v>
       </c>
       <c r="C42" s="5">
-        <v>343.56</v>
+        <v>368.75</v>
       </c>
       <c r="D42" s="5"/>
       <c r="E42" s="5">
-        <v>100.6</v>
+        <v>125.72</v>
       </c>
       <c r="F42" s="5"/>
       <c r="G42" s="5" t="s">
@@ -6384,17 +6524,17 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="6">
-        <v>46283.29166666666</v>
+        <v>46283.45833333334</v>
       </c>
       <c r="B43" s="5">
-        <v>427.1</v>
+        <v>459.6</v>
       </c>
       <c r="C43" s="5">
-        <v>344.76</v>
+        <v>368.89</v>
       </c>
       <c r="D43" s="5"/>
       <c r="E43" s="5">
-        <v>99.87</v>
+        <v>125.91</v>
       </c>
       <c r="F43" s="5"/>
       <c r="G43" s="5" t="s">
@@ -6403,17 +6543,17 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="6">
-        <v>46283.33333333334</v>
+        <v>46283.5</v>
       </c>
       <c r="B44" s="5">
-        <v>426.76</v>
+        <v>468.45</v>
       </c>
       <c r="C44" s="5">
-        <v>345.43</v>
+        <v>368.95</v>
       </c>
       <c r="D44" s="5"/>
       <c r="E44" s="5">
-        <v>102.67</v>
+        <v>150.21</v>
       </c>
       <c r="F44" s="5"/>
       <c r="G44" s="5" t="s">
@@ -6422,17 +6562,17 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="6">
-        <v>46283.375</v>
+        <v>46283.54166666666</v>
       </c>
       <c r="B45" s="5">
-        <v>428.62</v>
+        <v>479.76</v>
       </c>
       <c r="C45" s="5">
-        <v>345.76</v>
+        <v>368.95</v>
       </c>
       <c r="D45" s="5"/>
       <c r="E45" s="5">
-        <v>109.98</v>
+        <v>170.52</v>
       </c>
       <c r="F45" s="5"/>
       <c r="G45" s="5" t="s">
@@ -6441,17 +6581,17 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="6">
-        <v>46283.41666666666</v>
+        <v>46283.58333333334</v>
       </c>
       <c r="B46" s="5">
-        <v>433.4</v>
+        <v>494.65</v>
       </c>
       <c r="C46" s="5">
-        <v>345.89</v>
+        <v>368.92</v>
       </c>
       <c r="D46" s="5"/>
       <c r="E46" s="5">
-        <v>122.54</v>
+        <v>197.98</v>
       </c>
       <c r="F46" s="5"/>
       <c r="G46" s="5" t="s">
@@ -6460,17 +6600,17 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="6">
-        <v>46283.45833333334</v>
+        <v>46283.625</v>
       </c>
       <c r="B47" s="5">
-        <v>436.36</v>
+        <v>510.65</v>
       </c>
       <c r="C47" s="5">
-        <v>345.89</v>
+        <v>368.87</v>
       </c>
       <c r="D47" s="5"/>
       <c r="E47" s="5">
-        <v>122.8</v>
+        <v>221.58</v>
       </c>
       <c r="F47" s="5"/>
       <c r="G47" s="5" t="s">
@@ -6479,17 +6619,17 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="6">
-        <v>46283.5</v>
+        <v>46283.66666666666</v>
       </c>
       <c r="B48" s="5">
-        <v>445.16</v>
+        <v>525.17</v>
       </c>
       <c r="C48" s="5">
-        <v>345.81</v>
+        <v>368.81</v>
       </c>
       <c r="D48" s="5"/>
       <c r="E48" s="5">
-        <v>146.66</v>
+        <v>237.67</v>
       </c>
       <c r="F48" s="5"/>
       <c r="G48" s="5" t="s">
@@ -6498,17 +6638,17 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="6">
-        <v>46283.54166666666</v>
+        <v>46283.70833333334</v>
       </c>
       <c r="B49" s="5">
-        <v>456.34</v>
+        <v>535.79</v>
       </c>
       <c r="C49" s="5">
-        <v>345.69</v>
+        <v>368.73</v>
       </c>
       <c r="D49" s="5"/>
       <c r="E49" s="5">
-        <v>166.34</v>
+        <v>243.41</v>
       </c>
       <c r="F49" s="5"/>
       <c r="G49" s="5" t="s">
@@ -6517,17 +6657,17 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="6">
-        <v>46283.58333333334</v>
+        <v>46283.75</v>
       </c>
       <c r="B50" s="5">
-        <v>471.15</v>
+        <v>538.49</v>
       </c>
       <c r="C50" s="5">
-        <v>345.54</v>
+        <v>368.65</v>
       </c>
       <c r="D50" s="5"/>
       <c r="E50" s="5">
-        <v>193.3</v>
+        <v>230.06</v>
       </c>
       <c r="F50" s="5"/>
       <c r="G50" s="5" t="s">
@@ -6536,17 +6676,17 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="6">
-        <v>46283.625</v>
+        <v>46283.79166666666</v>
       </c>
       <c r="B51" s="5">
-        <v>487.09</v>
+        <v>534.03</v>
       </c>
       <c r="C51" s="5">
-        <v>345.37</v>
+        <v>368.55</v>
       </c>
       <c r="D51" s="5"/>
       <c r="E51" s="5">
-        <v>216.48</v>
+        <v>208.88</v>
       </c>
       <c r="F51" s="5"/>
       <c r="G51" s="5" t="s">
@@ -6555,17 +6695,17 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="6">
-        <v>46283.66666666666</v>
+        <v>46283.83333333334</v>
       </c>
       <c r="B52" s="5">
-        <v>501.56</v>
+        <v>527.33</v>
       </c>
       <c r="C52" s="5">
-        <v>345.19</v>
+        <v>368.46</v>
       </c>
       <c r="D52" s="5"/>
       <c r="E52" s="5">
-        <v>232.29</v>
+        <v>195.4</v>
       </c>
       <c r="F52" s="5"/>
       <c r="G52" s="5" t="s">
@@ -6574,17 +6714,17 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="6">
-        <v>46283.70833333334</v>
+        <v>46283.875</v>
       </c>
       <c r="B53" s="5">
-        <v>512.13</v>
+        <v>519.51</v>
       </c>
       <c r="C53" s="5">
-        <v>345</v>
+        <v>368.35</v>
       </c>
       <c r="D53" s="5"/>
       <c r="E53" s="5">
-        <v>237.96</v>
+        <v>182.8</v>
       </c>
       <c r="F53" s="5"/>
       <c r="G53" s="5" t="s">
@@ -6593,17 +6733,17 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="6">
-        <v>46283.75</v>
+        <v>46283.91666666666</v>
       </c>
       <c r="B54" s="5">
-        <v>514.76</v>
+        <v>509.2</v>
       </c>
       <c r="C54" s="5">
-        <v>344.81</v>
+        <v>368.24</v>
       </c>
       <c r="D54" s="5"/>
       <c r="E54" s="5">
-        <v>224.91</v>
+        <v>163.99</v>
       </c>
       <c r="F54" s="5"/>
       <c r="G54" s="5" t="s">
@@ -6612,17 +6752,17 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="6">
-        <v>46283.79166666666</v>
+        <v>46283.95833333334</v>
       </c>
       <c r="B55" s="5">
-        <v>510.26</v>
+        <v>499.72</v>
       </c>
       <c r="C55" s="5">
-        <v>344.62</v>
+        <v>368.13</v>
       </c>
       <c r="D55" s="5"/>
       <c r="E55" s="5">
-        <v>204.38</v>
+        <v>153.42</v>
       </c>
       <c r="F55" s="5"/>
       <c r="G55" s="5" t="s">
@@ -6631,17 +6771,17 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="6">
-        <v>46283.83333333334</v>
+        <v>46284</v>
       </c>
       <c r="B56" s="5">
-        <v>503.5</v>
+        <v>490.94</v>
       </c>
       <c r="C56" s="5">
-        <v>344.42</v>
+        <v>368.02</v>
       </c>
       <c r="D56" s="5"/>
       <c r="E56" s="5">
-        <v>191.2</v>
+        <v>143.52</v>
       </c>
       <c r="F56" s="5"/>
       <c r="G56" s="5" t="s">
@@ -6650,17 +6790,17 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="6">
-        <v>46283.875</v>
+        <v>46284.04166666666</v>
       </c>
       <c r="B57" s="5">
-        <v>495.6</v>
+        <v>480.83</v>
       </c>
       <c r="C57" s="5">
-        <v>344.22</v>
+        <v>367.97</v>
       </c>
       <c r="D57" s="5"/>
       <c r="E57" s="5">
-        <v>178.86</v>
+        <v>127.19</v>
       </c>
       <c r="F57" s="5"/>
       <c r="G57" s="5" t="s">
@@ -6669,17 +6809,17 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="6">
-        <v>46283.91666666666</v>
+        <v>46284.08333333334</v>
       </c>
       <c r="B58" s="5">
-        <v>485.24</v>
+        <v>472.21</v>
       </c>
       <c r="C58" s="5">
-        <v>344.03</v>
+        <v>367.97</v>
       </c>
       <c r="D58" s="5"/>
       <c r="E58" s="5">
-        <v>160.6</v>
+        <v>118.99</v>
       </c>
       <c r="F58" s="5"/>
       <c r="G58" s="5" t="s">
@@ -6688,17 +6828,17 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="6">
-        <v>46283.95833333334</v>
+        <v>46284.125</v>
       </c>
       <c r="B59" s="5">
-        <v>475.69</v>
+        <v>464.69</v>
       </c>
       <c r="C59" s="5">
-        <v>343.83</v>
+        <v>367.99</v>
       </c>
       <c r="D59" s="5"/>
       <c r="E59" s="5">
-        <v>150.24</v>
+        <v>111.32</v>
       </c>
       <c r="F59" s="5"/>
       <c r="G59" s="5" t="s">
@@ -6707,17 +6847,17 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="6">
-        <v>46284</v>
+        <v>46284.16666666666</v>
       </c>
       <c r="B60" s="5">
-        <v>466.83</v>
+        <v>457.97</v>
       </c>
       <c r="C60" s="5">
-        <v>343.63</v>
+        <v>368.03</v>
       </c>
       <c r="D60" s="5"/>
       <c r="E60" s="5">
-        <v>140.55</v>
+        <v>104.14</v>
       </c>
       <c r="F60" s="5"/>
       <c r="G60" s="5" t="s">
@@ -6726,17 +6866,17 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="6">
-        <v>46284.04166666666</v>
+        <v>46284.20833333334</v>
       </c>
       <c r="B61" s="5">
-        <v>456.65</v>
+        <v>451.9</v>
       </c>
       <c r="C61" s="5">
-        <v>343.5</v>
+        <v>368.07</v>
       </c>
       <c r="D61" s="5"/>
       <c r="E61" s="5">
-        <v>124.65</v>
+        <v>97.42</v>
       </c>
       <c r="F61" s="5"/>
       <c r="G61" s="5" t="s">
@@ -6745,17 +6885,17 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="6">
-        <v>46284.08333333334</v>
+        <v>46284.25</v>
       </c>
       <c r="B62" s="5">
-        <v>447.97</v>
+        <v>446.34</v>
       </c>
       <c r="C62" s="5">
-        <v>343.42</v>
+        <v>368.12</v>
       </c>
       <c r="D62" s="5"/>
       <c r="E62" s="5">
-        <v>116.62</v>
+        <v>91.14</v>
       </c>
       <c r="F62" s="5"/>
       <c r="G62" s="5" t="s">
@@ -6764,17 +6904,17 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="6">
-        <v>46284.125</v>
+        <v>46284.29166666666</v>
       </c>
       <c r="B63" s="5">
-        <v>440.36</v>
+        <v>441.23</v>
       </c>
       <c r="C63" s="5">
-        <v>343.38</v>
+        <v>368.17</v>
       </c>
       <c r="D63" s="5"/>
       <c r="E63" s="5">
-        <v>109.09</v>
+        <v>85.26000000000001</v>
       </c>
       <c r="F63" s="5"/>
       <c r="G63" s="5" t="s">
@@ -6783,17 +6923,17 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="6">
-        <v>46284.16666666666</v>
+        <v>46284.33333333334</v>
       </c>
       <c r="B64" s="5">
-        <v>433.57</v>
+        <v>436.49</v>
       </c>
       <c r="C64" s="5">
-        <v>343.34</v>
+        <v>368.22</v>
       </c>
       <c r="D64" s="5"/>
       <c r="E64" s="5">
-        <v>102.06</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="F64" s="5"/>
       <c r="G64" s="5" t="s">
@@ -6802,17 +6942,17 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="6">
-        <v>46284.20833333334</v>
+        <v>46284.375</v>
       </c>
       <c r="B65" s="5">
-        <v>427.42</v>
+        <v>432.09</v>
       </c>
       <c r="C65" s="5">
-        <v>343.32</v>
+        <v>368.27</v>
       </c>
       <c r="D65" s="5"/>
       <c r="E65" s="5">
-        <v>95.48</v>
+        <v>74.62</v>
       </c>
       <c r="F65" s="5"/>
       <c r="G65" s="5" t="s">
@@ -6821,17 +6961,17 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="6">
-        <v>46284.25</v>
+        <v>46284.41666666666</v>
       </c>
       <c r="B66" s="5">
-        <v>421.79</v>
+        <v>427.99</v>
       </c>
       <c r="C66" s="5">
-        <v>343.31</v>
+        <v>368.31</v>
       </c>
       <c r="D66" s="5"/>
       <c r="E66" s="5">
-        <v>89.31999999999999</v>
+        <v>69.81</v>
       </c>
       <c r="F66" s="5"/>
       <c r="G66" s="5" t="s">
@@ -6840,17 +6980,17 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="6">
-        <v>46284.29166666666</v>
+        <v>46284.45833333334</v>
       </c>
       <c r="B67" s="5">
-        <v>416.6</v>
+        <v>424.17</v>
       </c>
       <c r="C67" s="5">
-        <v>343.3</v>
+        <v>368.36</v>
       </c>
       <c r="D67" s="5"/>
       <c r="E67" s="5">
-        <v>83.56</v>
+        <v>65.3</v>
       </c>
       <c r="F67" s="5"/>
       <c r="G67" s="5" t="s">
@@ -6859,17 +6999,17 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="6">
-        <v>46284.33333333334</v>
+        <v>46284.5</v>
       </c>
       <c r="B68" s="5">
-        <v>411.79</v>
+        <v>420.61</v>
       </c>
       <c r="C68" s="5">
-        <v>343.29</v>
+        <v>368.41</v>
       </c>
       <c r="D68" s="5"/>
       <c r="E68" s="5">
-        <v>78.17</v>
+        <v>61.09</v>
       </c>
       <c r="F68" s="5"/>
       <c r="G68" s="5" t="s">
@@ -6878,17 +7018,17 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="6">
-        <v>46284.375</v>
+        <v>46284.54166666666</v>
       </c>
       <c r="B69" s="5">
-        <v>407.32</v>
+        <v>417.28</v>
       </c>
       <c r="C69" s="5">
-        <v>343.29</v>
+        <v>368.45</v>
       </c>
       <c r="D69" s="5"/>
       <c r="E69" s="5">
-        <v>73.13</v>
+        <v>57.15</v>
       </c>
       <c r="F69" s="5"/>
       <c r="G69" s="5" t="s">
@@ -6897,17 +7037,17 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="6">
-        <v>46284.41666666666</v>
+        <v>46284.58333333334</v>
       </c>
       <c r="B70" s="5">
-        <v>403.16</v>
+        <v>414.17</v>
       </c>
       <c r="C70" s="5">
-        <v>343.28</v>
+        <v>368.49</v>
       </c>
       <c r="D70" s="5"/>
       <c r="E70" s="5">
-        <v>68.41</v>
+        <v>53.47</v>
       </c>
       <c r="F70" s="5"/>
       <c r="G70" s="5" t="s">
@@ -6916,17 +7056,17 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="6">
-        <v>46284.45833333334</v>
+        <v>46284.625</v>
       </c>
       <c r="B71" s="5">
-        <v>399.28</v>
+        <v>411.26</v>
       </c>
       <c r="C71" s="5">
-        <v>343.28</v>
+        <v>368.53</v>
       </c>
       <c r="D71" s="5"/>
       <c r="E71" s="5">
-        <v>64</v>
+        <v>50.02</v>
       </c>
       <c r="F71" s="5"/>
       <c r="G71" s="5" t="s">
@@ -6935,17 +7075,17 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="6">
-        <v>46284.5</v>
+        <v>46284.66666666666</v>
       </c>
       <c r="B72" s="5">
-        <v>395.65</v>
+        <v>408.54</v>
       </c>
       <c r="C72" s="5">
-        <v>343.28</v>
+        <v>368.57</v>
       </c>
       <c r="D72" s="5"/>
       <c r="E72" s="5">
-        <v>59.87</v>
+        <v>46.79</v>
       </c>
       <c r="F72" s="5"/>
       <c r="G72" s="5" t="s">
@@ -6954,17 +7094,17 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="6">
-        <v>46284.54166666666</v>
+        <v>46284.70833333334</v>
       </c>
       <c r="B73" s="5">
-        <v>392.26</v>
+        <v>406</v>
       </c>
       <c r="C73" s="5">
-        <v>343.27</v>
+        <v>368.61</v>
       </c>
       <c r="D73" s="5"/>
       <c r="E73" s="5">
-        <v>56.01</v>
+        <v>43.77</v>
       </c>
       <c r="F73" s="5"/>
       <c r="G73" s="5" t="s">
@@ -6973,17 +7113,17 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="6">
-        <v>46284.58333333334</v>
+        <v>46284.75</v>
       </c>
       <c r="B74" s="5">
-        <v>389.1</v>
+        <v>403.62</v>
       </c>
       <c r="C74" s="5">
-        <v>343.27</v>
+        <v>368.64</v>
       </c>
       <c r="D74" s="5"/>
       <c r="E74" s="5">
-        <v>52.4</v>
+        <v>40.95</v>
       </c>
       <c r="F74" s="5"/>
       <c r="G74" s="5" t="s">
@@ -6992,17 +7132,17 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="6">
-        <v>46284.625</v>
+        <v>46284.79166666666</v>
       </c>
       <c r="B75" s="5">
-        <v>386.14</v>
+        <v>401.4</v>
       </c>
       <c r="C75" s="5">
-        <v>343.27</v>
+        <v>368.68</v>
       </c>
       <c r="D75" s="5"/>
       <c r="E75" s="5">
-        <v>49.02</v>
+        <v>38.31</v>
       </c>
       <c r="F75" s="5"/>
       <c r="G75" s="5" t="s">
@@ -7011,17 +7151,17 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="6">
-        <v>46284.66666666666</v>
+        <v>46284.83333333334</v>
       </c>
       <c r="B76" s="5">
-        <v>383.37</v>
+        <v>399.32</v>
       </c>
       <c r="C76" s="5">
-        <v>343.27</v>
+        <v>368.71</v>
       </c>
       <c r="D76" s="5"/>
       <c r="E76" s="5">
-        <v>45.86</v>
+        <v>35.84</v>
       </c>
       <c r="F76" s="5"/>
       <c r="G76" s="5" t="s">
@@ -7030,17 +7170,17 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="6">
-        <v>46284.70833333334</v>
+        <v>46284.875</v>
       </c>
       <c r="B77" s="5">
-        <v>380.78</v>
+        <v>397.38</v>
       </c>
       <c r="C77" s="5">
-        <v>343.26</v>
+        <v>368.74</v>
       </c>
       <c r="D77" s="5"/>
       <c r="E77" s="5">
-        <v>42.9</v>
+        <v>33.53</v>
       </c>
       <c r="F77" s="5"/>
       <c r="G77" s="5" t="s">
@@ -7082,10 +7222,10 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="6">
-        <v>46281.625</v>
+        <v>46281.875</v>
       </c>
       <c r="B2" s="5">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>48</v>
@@ -7097,7 +7237,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="6">
-        <v>46281.75</v>
+        <v>46282</v>
       </c>
       <c r="B3" s="5">
         <v>1.67</v>
@@ -7112,7 +7252,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="6">
-        <v>46281.875</v>
+        <v>46282.125</v>
       </c>
       <c r="B4" s="5">
         <v>2</v>
@@ -7127,7 +7267,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="6">
-        <v>46282</v>
+        <v>46282.25</v>
       </c>
       <c r="B5" s="5">
         <v>2.67</v>
@@ -7142,7 +7282,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="6">
-        <v>46282.125</v>
+        <v>46282.375</v>
       </c>
       <c r="B6" s="5">
         <v>3</v>
@@ -7157,7 +7297,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="6">
-        <v>46282.25</v>
+        <v>46282.5</v>
       </c>
       <c r="B7" s="5">
         <v>3.33</v>
@@ -7172,10 +7312,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="6">
-        <v>46282.375</v>
+        <v>46282.625</v>
       </c>
       <c r="B8" s="5">
-        <v>3.67</v>
+        <v>3</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>48</v>
@@ -7187,10 +7327,10 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="6">
-        <v>46282.5</v>
+        <v>46282.75</v>
       </c>
       <c r="B9" s="5">
-        <v>3.33</v>
+        <v>2</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>48</v>
@@ -7202,10 +7342,10 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="6">
-        <v>46282.625</v>
+        <v>46282.875</v>
       </c>
       <c r="B10" s="5">
-        <v>2.33</v>
+        <v>1.33</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>48</v>
@@ -7217,10 +7357,10 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="6">
-        <v>46282.75</v>
+        <v>46283</v>
       </c>
       <c r="B11" s="5">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>48</v>
@@ -7232,10 +7372,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="6">
-        <v>46282.875</v>
+        <v>46283.125</v>
       </c>
       <c r="B12" s="5">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>48</v>
@@ -7247,7 +7387,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="6">
-        <v>46283</v>
+        <v>46283.25</v>
       </c>
       <c r="B13" s="5">
         <v>0.67</v>
@@ -7262,10 +7402,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="6">
-        <v>46283.125</v>
+        <v>46283.375</v>
       </c>
       <c r="B14" s="5">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>48</v>
@@ -7277,10 +7417,10 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="6">
-        <v>46283.25</v>
+        <v>46283.5</v>
       </c>
       <c r="B15" s="5">
-        <v>0.67</v>
+        <v>1.67</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>48</v>
@@ -7292,10 +7432,10 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="6">
-        <v>46283.375</v>
+        <v>46283.625</v>
       </c>
       <c r="B16" s="5">
-        <v>0.67</v>
+        <v>2.33</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>48</v>
@@ -7307,10 +7447,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="6">
-        <v>46283.5</v>
+        <v>46283.75</v>
       </c>
       <c r="B17" s="5">
-        <v>1.33</v>
+        <v>2.67</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>48</v>
@@ -7322,7 +7462,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="6">
-        <v>46283.625</v>
+        <v>46283.875</v>
       </c>
       <c r="B18" s="5">
         <v>2</v>
@@ -7337,10 +7477,10 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="6">
-        <v>46283.75</v>
+        <v>46284</v>
       </c>
       <c r="B19" s="5">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>48</v>
@@ -7352,10 +7492,10 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="6">
-        <v>46283.875</v>
+        <v>46284.125</v>
       </c>
       <c r="B20" s="5">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>48</v>
@@ -7367,10 +7507,10 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="6">
-        <v>46284</v>
+        <v>46284.25</v>
       </c>
       <c r="B21" s="5">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>48</v>
@@ -7382,10 +7522,10 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="6">
-        <v>46284.125</v>
+        <v>46284.375</v>
       </c>
       <c r="B22" s="5">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>48</v>
@@ -7397,7 +7537,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="6">
-        <v>46284.25</v>
+        <v>46284.5</v>
       </c>
       <c r="B23" s="5">
         <v>0.33</v>
@@ -7412,10 +7552,10 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="6">
-        <v>46284.375</v>
+        <v>46284.625</v>
       </c>
       <c r="B24" s="5">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>48</v>
@@ -7427,10 +7567,10 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="6">
-        <v>46284.5</v>
+        <v>46284.75</v>
       </c>
       <c r="B25" s="5">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>48</v>
@@ -7448,7 +7588,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:M53"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="9" width="16.7109375" customWidth="1"/>
@@ -7502,19 +7642,19 @@
         <v>24</v>
       </c>
       <c r="D4" s="5">
-        <v>37.788</v>
+        <v>48.483</v>
       </c>
       <c r="E4" s="5">
-        <v>51.073</v>
+        <v>64.10599999999999</v>
       </c>
       <c r="F4" s="5">
-        <v>-8.276</v>
+        <v>47.4</v>
       </c>
       <c r="G4" s="5">
         <v>70.8</v>
       </c>
       <c r="H4" s="5">
-        <v>91.7</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -7525,22 +7665,22 @@
         <v>61</v>
       </c>
       <c r="C5" s="5">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D5" s="5">
-        <v>50.431</v>
+        <v>66.477</v>
       </c>
       <c r="E5" s="5">
-        <v>66.51600000000001</v>
+        <v>86.486</v>
       </c>
       <c r="F5" s="5">
-        <v>3.9</v>
+        <v>57.005</v>
       </c>
       <c r="G5" s="5">
-        <v>58.1</v>
+        <v>54.3</v>
       </c>
       <c r="H5" s="5">
-        <v>83.90000000000001</v>
+        <v>74.3</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -7551,22 +7691,22 @@
         <v>62</v>
       </c>
       <c r="C6" s="5">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D6" s="5">
-        <v>50.431</v>
+        <v>66.477</v>
       </c>
       <c r="E6" s="5">
-        <v>66.51600000000001</v>
+        <v>86.486</v>
       </c>
       <c r="F6" s="5">
-        <v>3.9</v>
+        <v>57.005</v>
       </c>
       <c r="G6" s="5">
-        <v>58.1</v>
+        <v>54.3</v>
       </c>
       <c r="H6" s="5">
-        <v>83.90000000000001</v>
+        <v>74.3</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -7709,16 +7849,16 @@
         <v>46280.45833333334</v>
       </c>
       <c r="B19" s="5">
-        <v>526.49</v>
+        <v>524.8200000000001</v>
       </c>
       <c r="C19" s="5">
-        <v>445.53</v>
+        <v>470.85</v>
       </c>
       <c r="D19" s="5">
-        <v>334.01</v>
+        <v>360.49</v>
       </c>
       <c r="E19" s="5">
-        <v>-80.96000000000004</v>
+        <v>-53.97000000000003</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -7726,16 +7866,16 @@
         <v>46280.5</v>
       </c>
       <c r="B20" s="5">
-        <v>566.6799999999999</v>
+        <v>566.89</v>
       </c>
       <c r="C20" s="5">
-        <v>494.12</v>
+        <v>536.28</v>
       </c>
       <c r="D20" s="5">
-        <v>353.8</v>
+        <v>397.56</v>
       </c>
       <c r="E20" s="5">
-        <v>-72.55999999999995</v>
+        <v>-30.61000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -7743,16 +7883,16 @@
         <v>46280.54166666666</v>
       </c>
       <c r="B21" s="5">
-        <v>558.29</v>
+        <v>561.75</v>
       </c>
       <c r="C21" s="5">
-        <v>543.34</v>
+        <v>584.85</v>
       </c>
       <c r="D21" s="5">
-        <v>364.61</v>
+        <v>408.34</v>
       </c>
       <c r="E21" s="5">
-        <v>-14.94999999999993</v>
+        <v>23.10000000000002</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -7760,16 +7900,16 @@
         <v>46280.58333333334</v>
       </c>
       <c r="B22" s="5">
-        <v>479.3</v>
+        <v>482.62</v>
       </c>
       <c r="C22" s="5">
-        <v>558.87</v>
+        <v>605.11</v>
       </c>
       <c r="D22" s="5">
-        <v>342.01</v>
+        <v>391.17</v>
       </c>
       <c r="E22" s="5">
-        <v>79.56999999999999</v>
+        <v>122.49</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -7777,16 +7917,16 @@
         <v>46280.625</v>
       </c>
       <c r="B23" s="5">
-        <v>444.15</v>
+        <v>443.5</v>
       </c>
       <c r="C23" s="5">
-        <v>565.6</v>
+        <v>609.13</v>
       </c>
       <c r="D23" s="5">
-        <v>314.79</v>
+        <v>361.97</v>
       </c>
       <c r="E23" s="5">
-        <v>121.45</v>
+        <v>165.63</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -7797,13 +7937,13 @@
         <v>451.89</v>
       </c>
       <c r="C24" s="5">
-        <v>584.11</v>
+        <v>626.14</v>
       </c>
       <c r="D24" s="5">
-        <v>307.66</v>
+        <v>354.05</v>
       </c>
       <c r="E24" s="5">
-        <v>132.22</v>
+        <v>174.25</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -7811,16 +7951,16 @@
         <v>46280.70833333334</v>
       </c>
       <c r="B25" s="5">
-        <v>434.72</v>
+        <v>431.62</v>
       </c>
       <c r="C25" s="5">
-        <v>589.46</v>
+        <v>630.77</v>
       </c>
       <c r="D25" s="5">
-        <v>304.54</v>
+        <v>350.74</v>
       </c>
       <c r="E25" s="5">
-        <v>154.74</v>
+        <v>199.15</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -7828,16 +7968,16 @@
         <v>46280.75</v>
       </c>
       <c r="B26" s="5">
-        <v>454.87</v>
+        <v>453.4</v>
       </c>
       <c r="C26" s="5">
-        <v>581.89</v>
+        <v>624.02</v>
       </c>
       <c r="D26" s="5">
-        <v>292.68</v>
+        <v>340.1</v>
       </c>
       <c r="E26" s="5">
-        <v>127.02</v>
+        <v>170.62</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -7845,16 +7985,16 @@
         <v>46280.79166666666</v>
       </c>
       <c r="B27" s="5">
-        <v>691.9</v>
+        <v>666.5</v>
       </c>
       <c r="C27" s="5">
-        <v>557.54</v>
+        <v>598.3200000000001</v>
       </c>
       <c r="D27" s="5">
-        <v>270.4</v>
+        <v>316.62</v>
       </c>
       <c r="E27" s="5">
-        <v>-134.36</v>
+        <v>-68.17999999999995</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -7862,16 +8002,16 @@
         <v>46280.83333333334</v>
       </c>
       <c r="B28" s="5">
-        <v>540.12</v>
+        <v>536.49</v>
       </c>
       <c r="C28" s="5">
-        <v>558.22</v>
+        <v>597.6900000000001</v>
       </c>
       <c r="D28" s="5">
-        <v>285.19</v>
+        <v>329.82</v>
       </c>
       <c r="E28" s="5">
-        <v>18.10000000000002</v>
+        <v>61.20000000000005</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -7879,16 +8019,16 @@
         <v>46280.875</v>
       </c>
       <c r="B29" s="5">
-        <v>505.25</v>
+        <v>504.43</v>
       </c>
       <c r="C29" s="5">
-        <v>556.08</v>
+        <v>598.33</v>
       </c>
       <c r="D29" s="5">
-        <v>299.86</v>
+        <v>346.86</v>
       </c>
       <c r="E29" s="5">
-        <v>50.83000000000004</v>
+        <v>93.90000000000003</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -7896,16 +8036,16 @@
         <v>46280.91666666666</v>
       </c>
       <c r="B30" s="5">
-        <v>448.01</v>
+        <v>447.76</v>
       </c>
       <c r="C30" s="5">
-        <v>542.34</v>
+        <v>583.73</v>
       </c>
       <c r="D30" s="5">
-        <v>301.31</v>
+        <v>347</v>
       </c>
       <c r="E30" s="5">
-        <v>94.33000000000004</v>
+        <v>135.97</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -7913,16 +8053,16 @@
         <v>46280.95833333334</v>
       </c>
       <c r="B31" s="5">
-        <v>451.6</v>
+        <v>450.85</v>
       </c>
       <c r="C31" s="5">
-        <v>504.17</v>
+        <v>545.45</v>
       </c>
       <c r="D31" s="5">
-        <v>276.54</v>
+        <v>321.63</v>
       </c>
       <c r="E31" s="5">
-        <v>52.56999999999999</v>
+        <v>94.60000000000002</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -7930,16 +8070,16 @@
         <v>46281</v>
       </c>
       <c r="B32" s="5">
-        <v>506.12</v>
+        <v>507.31</v>
       </c>
       <c r="C32" s="5">
-        <v>491.76</v>
+        <v>532.4</v>
       </c>
       <c r="D32" s="5">
-        <v>275.6</v>
+        <v>319.47</v>
       </c>
       <c r="E32" s="5">
-        <v>-14.36000000000001</v>
+        <v>25.08999999999997</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -7947,16 +8087,16 @@
         <v>46281.04166666666</v>
       </c>
       <c r="B33" s="5">
-        <v>521.11</v>
+        <v>521.25</v>
       </c>
       <c r="C33" s="5">
-        <v>499.74</v>
+        <v>543.24</v>
       </c>
       <c r="D33" s="5">
-        <v>292.96</v>
+        <v>339.02</v>
       </c>
       <c r="E33" s="5">
-        <v>-21.37</v>
+        <v>21.99000000000001</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -7964,16 +8104,16 @@
         <v>46281.08333333334</v>
       </c>
       <c r="B34" s="5">
-        <v>523.3099999999999</v>
+        <v>524.77</v>
       </c>
       <c r="C34" s="5">
-        <v>508.51</v>
+        <v>553.75</v>
       </c>
       <c r="D34" s="5">
-        <v>308.94</v>
+        <v>355.96</v>
       </c>
       <c r="E34" s="5">
-        <v>-14.79999999999995</v>
+        <v>28.98000000000002</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -7981,16 +8121,16 @@
         <v>46281.125</v>
       </c>
       <c r="B35" s="5">
-        <v>529.24</v>
+        <v>529.76</v>
       </c>
       <c r="C35" s="5">
-        <v>510.14</v>
+        <v>555.89</v>
       </c>
       <c r="D35" s="5">
-        <v>315.7</v>
+        <v>362.36</v>
       </c>
       <c r="E35" s="5">
-        <v>-19.10000000000002</v>
+        <v>26.13</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -7998,16 +8138,16 @@
         <v>46281.16666666666</v>
       </c>
       <c r="B36" s="5">
-        <v>538.03</v>
+        <v>537.34</v>
       </c>
       <c r="C36" s="5">
-        <v>511.1</v>
+        <v>557.58</v>
       </c>
       <c r="D36" s="5">
-        <v>319.93</v>
+        <v>366.39</v>
       </c>
       <c r="E36" s="5">
-        <v>-26.92999999999995</v>
+        <v>20.24000000000001</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -8015,16 +8155,16 @@
         <v>46281.20833333334</v>
       </c>
       <c r="B37" s="5">
-        <v>537.1</v>
+        <v>536.9</v>
       </c>
       <c r="C37" s="5">
-        <v>512.33</v>
+        <v>559.6</v>
       </c>
       <c r="D37" s="5">
-        <v>323.03</v>
+        <v>369.31</v>
       </c>
       <c r="E37" s="5">
-        <v>-24.76999999999998</v>
+        <v>22.70000000000005</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -8035,13 +8175,13 @@
         <v>535.3</v>
       </c>
       <c r="C38" s="5">
-        <v>518.65</v>
+        <v>566.16</v>
       </c>
       <c r="D38" s="5">
-        <v>330.44</v>
+        <v>376.06</v>
       </c>
       <c r="E38" s="5">
-        <v>-16.64999999999998</v>
+        <v>30.86000000000001</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -8049,16 +8189,16 @@
         <v>46281.29166666666</v>
       </c>
       <c r="B39" s="5">
-        <v>524.9</v>
+        <v>524.2</v>
       </c>
       <c r="C39" s="5">
-        <v>521.14</v>
+        <v>569.3200000000001</v>
       </c>
       <c r="D39" s="5">
-        <v>333.96</v>
+        <v>379.47</v>
       </c>
       <c r="E39" s="5">
-        <v>-3.759999999999991</v>
+        <v>45.12</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -8066,16 +8206,16 @@
         <v>46281.33333333334</v>
       </c>
       <c r="B40" s="5">
-        <v>535.89</v>
+        <v>535.67</v>
       </c>
       <c r="C40" s="5">
-        <v>519.13</v>
+        <v>567.86</v>
       </c>
       <c r="D40" s="5">
-        <v>334.31</v>
+        <v>379.84</v>
       </c>
       <c r="E40" s="5">
-        <v>-16.75999999999999</v>
+        <v>32.19000000000005</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -8083,16 +8223,16 @@
         <v>46281.375</v>
       </c>
       <c r="B41" s="5">
-        <v>543.8</v>
+        <v>542.09</v>
       </c>
       <c r="C41" s="5">
-        <v>517.6</v>
+        <v>566.54</v>
       </c>
       <c r="D41" s="5">
-        <v>336.22</v>
+        <v>381.65</v>
       </c>
       <c r="E41" s="5">
-        <v>-26.19999999999993</v>
+        <v>24.44999999999993</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -8100,16 +8240,16 @@
         <v>46281.41666666666</v>
       </c>
       <c r="B42" s="5">
-        <v>541.88</v>
+        <v>541.97</v>
       </c>
       <c r="C42" s="5">
-        <v>514.9</v>
+        <v>563.8200000000001</v>
       </c>
       <c r="D42" s="5">
-        <v>336.58</v>
+        <v>381.74</v>
       </c>
       <c r="E42" s="5">
-        <v>-26.98000000000002</v>
+        <v>21.85000000000002</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -8117,16 +8257,16 @@
         <v>46281.45833333334</v>
       </c>
       <c r="B43" s="5">
-        <v>539.33</v>
+        <v>539.6</v>
       </c>
       <c r="C43" s="5">
-        <v>508.02</v>
+        <v>557.27</v>
       </c>
       <c r="D43" s="5">
-        <v>332.67</v>
+        <v>378.02</v>
       </c>
       <c r="E43" s="5">
-        <v>-31.31000000000006</v>
+        <v>17.66999999999996</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -8134,16 +8274,16 @@
         <v>46281.5</v>
       </c>
       <c r="B44" s="5">
-        <v>539.3</v>
+        <v>537.77</v>
       </c>
       <c r="C44" s="5">
-        <v>505.18</v>
+        <v>554.17</v>
       </c>
       <c r="D44" s="5">
-        <v>332.6</v>
+        <v>377.71</v>
       </c>
       <c r="E44" s="5">
-        <v>-34.11999999999995</v>
+        <v>16.39999999999998</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -8151,16 +8291,16 @@
         <v>46281.54166666666</v>
       </c>
       <c r="B45" s="5">
-        <v>562.4</v>
+        <v>560.7</v>
       </c>
       <c r="C45" s="5">
-        <v>502.4</v>
+        <v>550.88</v>
       </c>
       <c r="D45" s="5">
-        <v>333.38</v>
+        <v>378.25</v>
       </c>
       <c r="E45" s="5">
-        <v>-60</v>
+        <v>-9.82000000000005</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -8168,16 +8308,16 @@
         <v>46281.58333333334</v>
       </c>
       <c r="B46" s="5">
-        <v>559.8</v>
+        <v>557.8</v>
       </c>
       <c r="C46" s="5">
-        <v>506.49</v>
+        <v>554.62</v>
       </c>
       <c r="D46" s="5">
-        <v>336.73</v>
+        <v>381.55</v>
       </c>
       <c r="E46" s="5">
-        <v>-53.30999999999995</v>
+        <v>-3.17999999999995</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -8185,16 +8325,16 @@
         <v>46281.625</v>
       </c>
       <c r="B47" s="5">
-        <v>535.9</v>
+        <v>534.5599999999999</v>
       </c>
       <c r="C47" s="5">
-        <v>512.8</v>
+        <v>561.04</v>
       </c>
       <c r="D47" s="5">
-        <v>337.2</v>
+        <v>382.44</v>
       </c>
       <c r="E47" s="5">
-        <v>-23.10000000000002</v>
+        <v>26.48000000000002</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -8202,16 +8342,16 @@
         <v>46281.66666666666</v>
       </c>
       <c r="B48" s="5">
-        <v>527.89</v>
+        <v>528.8</v>
       </c>
       <c r="C48" s="5">
-        <v>523</v>
+        <v>570.72</v>
       </c>
       <c r="D48" s="5">
-        <v>335.99</v>
+        <v>381.05</v>
       </c>
       <c r="E48" s="5">
-        <v>-4.889999999999986</v>
+        <v>41.92000000000007</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -8219,16 +8359,84 @@
         <v>46281.70833333334</v>
       </c>
       <c r="B49" s="5">
-        <v>525.35</v>
+        <v>529.2</v>
       </c>
       <c r="C49" s="5">
-        <v>536.65</v>
+        <v>583.64</v>
       </c>
       <c r="D49" s="5">
-        <v>332.85</v>
+        <v>377.56</v>
       </c>
       <c r="E49" s="5">
-        <v>11.29999999999995</v>
+        <v>54.43999999999994</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6">
+        <v>46281.75</v>
+      </c>
+      <c r="B50" s="5">
+        <v>531.42</v>
+      </c>
+      <c r="C50" s="5">
+        <v>604.42</v>
+      </c>
+      <c r="D50" s="5">
+        <v>377.68</v>
+      </c>
+      <c r="E50" s="5">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6">
+        <v>46281.79166666666</v>
+      </c>
+      <c r="B51" s="5">
+        <v>505.04</v>
+      </c>
+      <c r="C51" s="5">
+        <v>623.3200000000001</v>
+      </c>
+      <c r="D51" s="5">
+        <v>373.72</v>
+      </c>
+      <c r="E51" s="5">
+        <v>118.28</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6">
+        <v>46281.83333333334</v>
+      </c>
+      <c r="B52" s="5">
+        <v>505.5</v>
+      </c>
+      <c r="C52" s="5">
+        <v>636.67</v>
+      </c>
+      <c r="D52" s="5">
+        <v>364.8</v>
+      </c>
+      <c r="E52" s="5">
+        <v>131.17</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6">
+        <v>46281.875</v>
+      </c>
+      <c r="B53" s="5">
+        <v>508.88</v>
+      </c>
+      <c r="C53" s="5">
+        <v>649.9400000000001</v>
+      </c>
+      <c r="D53" s="5">
+        <v>359.37</v>
+      </c>
+      <c r="E53" s="5">
+        <v>141.0600000000001</v>
       </c>
     </row>
   </sheetData>
@@ -8275,19 +8483,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="6">
-        <v>46281.70833333334</v>
+        <v>46281.875</v>
       </c>
       <c r="B2" s="5">
-        <v>2.62</v>
+        <v>2.07</v>
       </c>
       <c r="C2" s="5">
-        <v>-9.56</v>
+        <v>-9.77</v>
       </c>
       <c r="D2" s="5">
-        <v>13.03</v>
+        <v>14.6</v>
       </c>
       <c r="E2" s="5">
-        <v>47.7</v>
+        <v>57.3</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>81</v>
@@ -8298,45 +8506,45 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="6">
-        <v>46281.83333333334</v>
+        <v>46282</v>
       </c>
       <c r="B3" s="5">
-        <v>2.41</v>
+        <v>1.9</v>
       </c>
       <c r="C3" s="5">
-        <v>-11.03</v>
+        <v>-9.77</v>
       </c>
       <c r="D3" s="5">
-        <v>14.27</v>
+        <v>14.41</v>
       </c>
       <c r="E3" s="5">
-        <v>53.9</v>
+        <v>57.9</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>81</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="6">
-        <v>46281.95833333334</v>
+        <v>46282.125</v>
       </c>
       <c r="B4" s="5">
-        <v>2.22</v>
+        <v>1.75</v>
       </c>
       <c r="C4" s="5">
-        <v>-11.61</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="D4" s="5">
-        <v>14.64</v>
+        <v>14.34</v>
       </c>
       <c r="E4" s="5">
-        <v>56.6</v>
+        <v>58.8</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>83</v>
@@ -8344,183 +8552,183 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="6">
-        <v>46282.08333333334</v>
+        <v>46282.25</v>
       </c>
       <c r="B5" s="5">
-        <v>2.04</v>
+        <v>1.61</v>
       </c>
       <c r="C5" s="5">
-        <v>-10.87</v>
+        <v>-10.86</v>
       </c>
       <c r="D5" s="5">
-        <v>13.71</v>
+        <v>15.18</v>
       </c>
       <c r="E5" s="5">
-        <v>54.4</v>
+        <v>63.2</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>81</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="6">
-        <v>46282.20833333334</v>
+        <v>46282.375</v>
       </c>
       <c r="B6" s="5">
-        <v>1.88</v>
+        <v>1.48</v>
       </c>
       <c r="C6" s="5">
-        <v>-12.41</v>
+        <v>-10.97</v>
       </c>
       <c r="D6" s="5">
-        <v>15.07</v>
+        <v>15.14</v>
       </c>
       <c r="E6" s="5">
-        <v>60.8</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="6">
-        <v>46282.33333333334</v>
+        <v>46282.5</v>
       </c>
       <c r="B7" s="5">
-        <v>1.73</v>
+        <v>1.36</v>
       </c>
       <c r="C7" s="5">
-        <v>-12.44</v>
+        <v>-11.11</v>
       </c>
       <c r="D7" s="5">
-        <v>14.94</v>
+        <v>15.15</v>
       </c>
       <c r="E7" s="5">
-        <v>61.5</v>
+        <v>65.2</v>
       </c>
       <c r="F7" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="G7" s="5" t="s">
         <v>84</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="6">
-        <v>46282.45833333334</v>
+        <v>46282.625</v>
       </c>
       <c r="B8" s="5">
-        <v>1.59</v>
+        <v>1.26</v>
       </c>
       <c r="C8" s="5">
-        <v>-12.7</v>
+        <v>-10.36</v>
       </c>
       <c r="D8" s="5">
-        <v>15.05</v>
+        <v>14.28</v>
       </c>
       <c r="E8" s="5">
-        <v>63</v>
+        <v>62.8</v>
       </c>
       <c r="F8" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="G8" s="5" t="s">
         <v>84</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="6">
-        <v>46282.58333333334</v>
+        <v>46282.75</v>
       </c>
       <c r="B9" s="5">
-        <v>1.46</v>
+        <v>1.16</v>
       </c>
       <c r="C9" s="5">
-        <v>-12.53</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="D9" s="5">
-        <v>14.74</v>
+        <v>12.11</v>
       </c>
       <c r="E9" s="5">
-        <v>62.9</v>
+        <v>55.5</v>
       </c>
       <c r="F9" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="G9" s="5" t="s">
         <v>84</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="6">
-        <v>46282.70833333334</v>
+        <v>46282.875</v>
       </c>
       <c r="B10" s="5">
-        <v>1.34</v>
+        <v>1.06</v>
       </c>
       <c r="C10" s="5">
-        <v>-10.83</v>
+        <v>-5.98</v>
       </c>
       <c r="D10" s="5">
-        <v>12.91</v>
+        <v>9.57</v>
       </c>
       <c r="E10" s="5">
-        <v>57</v>
+        <v>46.6</v>
       </c>
       <c r="F10" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G10" s="5" t="s">
         <v>84</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="6">
-        <v>46282.83333333334</v>
+        <v>46283</v>
       </c>
       <c r="B11" s="5">
-        <v>1.24</v>
+        <v>0.98</v>
       </c>
       <c r="C11" s="5">
-        <v>-8.42</v>
+        <v>-4.94</v>
       </c>
       <c r="D11" s="5">
-        <v>10.39</v>
+        <v>7.48</v>
       </c>
       <c r="E11" s="5">
-        <v>48.3</v>
+        <v>39.5</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="6">
-        <v>46282.95833333334</v>
+        <v>46283.125</v>
       </c>
       <c r="B12" s="5">
-        <v>1.14</v>
+        <v>0.9</v>
       </c>
       <c r="C12" s="5">
-        <v>-6.23</v>
+        <v>-4.4</v>
       </c>
       <c r="D12" s="5">
-        <v>8.09</v>
+        <v>6.38</v>
       </c>
       <c r="E12" s="5">
-        <v>40.4</v>
+        <v>36</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>86</v>
@@ -8528,22 +8736,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="6">
-        <v>46283.08333333334</v>
+        <v>46283.25</v>
       </c>
       <c r="B13" s="5">
-        <v>1.05</v>
+        <v>0.83</v>
       </c>
       <c r="C13" s="5">
-        <v>-5.06</v>
+        <v>-5.13</v>
       </c>
       <c r="D13" s="5">
-        <v>6.5</v>
+        <v>7.83</v>
       </c>
       <c r="E13" s="5">
-        <v>35.2</v>
+        <v>42.2</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>86</v>
@@ -8551,275 +8759,275 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="6">
-        <v>46283.20833333334</v>
+        <v>46283.375</v>
       </c>
       <c r="B14" s="5">
-        <v>0.96</v>
+        <v>0.76</v>
       </c>
       <c r="C14" s="5">
-        <v>-5.59</v>
+        <v>-6.59</v>
       </c>
       <c r="D14" s="5">
-        <v>7.25</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="E14" s="5">
-        <v>38.8</v>
+        <v>51</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="6">
-        <v>46283.33333333334</v>
+        <v>46283.5</v>
       </c>
       <c r="B15" s="5">
-        <v>0.89</v>
+        <v>0.7</v>
       </c>
       <c r="C15" s="5">
-        <v>-7.6</v>
+        <v>-9.050000000000001</v>
       </c>
       <c r="D15" s="5">
-        <v>9.18</v>
+        <v>12.36</v>
       </c>
       <c r="E15" s="5">
-        <v>46.9</v>
+        <v>60.6</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>81</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="6">
-        <v>46283.45833333334</v>
+        <v>46283.625</v>
       </c>
       <c r="B16" s="5">
-        <v>0.82</v>
+        <v>0.64</v>
       </c>
       <c r="C16" s="5">
-        <v>-10.07</v>
+        <v>-10.9</v>
       </c>
       <c r="D16" s="5">
-        <v>11.57</v>
+        <v>14.14</v>
       </c>
       <c r="E16" s="5">
-        <v>56.6</v>
+        <v>68</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="6">
-        <v>46283.58333333334</v>
+        <v>46283.75</v>
       </c>
       <c r="B17" s="5">
-        <v>0.75</v>
+        <v>0.59</v>
       </c>
       <c r="C17" s="5">
-        <v>-12.23</v>
+        <v>-11.32</v>
       </c>
       <c r="D17" s="5">
-        <v>13.66</v>
+        <v>14.5</v>
       </c>
       <c r="E17" s="5">
-        <v>65.2</v>
+        <v>69.8</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="6">
-        <v>46283.70833333334</v>
+        <v>46283.875</v>
       </c>
       <c r="B18" s="5">
-        <v>0.6899999999999999</v>
+        <v>0.55</v>
       </c>
       <c r="C18" s="5">
-        <v>-13.19</v>
+        <v>-10.13</v>
       </c>
       <c r="D18" s="5">
-        <v>14.56</v>
+        <v>13.26</v>
       </c>
       <c r="E18" s="5">
-        <v>69.2</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="6">
-        <v>46283.83333333334</v>
+        <v>46284</v>
       </c>
       <c r="B19" s="5">
-        <v>0.63</v>
+        <v>0.5</v>
       </c>
       <c r="C19" s="5">
-        <v>-12.52</v>
+        <v>-7.93</v>
       </c>
       <c r="D19" s="5">
-        <v>13.82</v>
+        <v>11.01</v>
       </c>
       <c r="E19" s="5">
-        <v>66.90000000000001</v>
+        <v>57.5</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="6">
-        <v>46283.95833333334</v>
+        <v>46284.125</v>
       </c>
       <c r="B20" s="5">
-        <v>0.58</v>
+        <v>0.46</v>
       </c>
       <c r="C20" s="5">
-        <v>-10.56</v>
+        <v>-5.62</v>
       </c>
       <c r="D20" s="5">
-        <v>11.81</v>
+        <v>8.66</v>
       </c>
       <c r="E20" s="5">
-        <v>59.8</v>
+        <v>48.9</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="6">
-        <v>46284.08333333334</v>
+        <v>46284.25</v>
       </c>
       <c r="B21" s="5">
-        <v>0.54</v>
+        <v>0.42</v>
       </c>
       <c r="C21" s="5">
-        <v>-8.199999999999999</v>
+        <v>-4.67</v>
       </c>
       <c r="D21" s="5">
-        <v>9.4</v>
+        <v>6.88</v>
       </c>
       <c r="E21" s="5">
-        <v>51</v>
+        <v>42.5</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="6">
-        <v>46284.20833333334</v>
+        <v>46284.375</v>
       </c>
       <c r="B22" s="5">
-        <v>0.52</v>
+        <v>0.41</v>
       </c>
       <c r="C22" s="5">
-        <v>-6.2</v>
+        <v>-4.15</v>
       </c>
       <c r="D22" s="5">
-        <v>7.39</v>
+        <v>5.82</v>
       </c>
       <c r="E22" s="5">
-        <v>43.5</v>
+        <v>38.6</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="6">
-        <v>46284.33333333334</v>
+        <v>46284.5</v>
       </c>
       <c r="B23" s="5">
-        <v>0.52</v>
+        <v>0.41</v>
       </c>
       <c r="C23" s="5">
-        <v>-4.91</v>
+        <v>-3.9</v>
       </c>
       <c r="D23" s="5">
-        <v>6.1</v>
+        <v>5.32</v>
       </c>
       <c r="E23" s="5">
-        <v>38.6</v>
+        <v>36.7</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="6">
-        <v>46284.45833333334</v>
+        <v>46284.625</v>
       </c>
       <c r="B24" s="5">
-        <v>0.52</v>
+        <v>0.41</v>
       </c>
       <c r="C24" s="5">
-        <v>-4.56</v>
+        <v>-3.8</v>
       </c>
       <c r="D24" s="5">
-        <v>5.44</v>
+        <v>5.13</v>
       </c>
       <c r="E24" s="5">
-        <v>36.1</v>
+        <v>36</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="6">
-        <v>46284.58333333334</v>
+        <v>46284.75</v>
       </c>
       <c r="B25" s="5">
-        <v>0.52</v>
+        <v>0.41</v>
       </c>
       <c r="C25" s="5">
-        <v>-4.42</v>
+        <v>-3.76</v>
       </c>
       <c r="D25" s="5">
-        <v>5.17</v>
+        <v>5.05</v>
       </c>
       <c r="E25" s="5">
-        <v>35.1</v>
+        <v>35.7</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G25" s="5" t="s">
         <v>87</v>
@@ -8827,22 +9035,22 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="6">
-        <v>46284.70833333334</v>
+        <v>46284.875</v>
       </c>
       <c r="B26" s="5">
-        <v>0.52</v>
+        <v>0.41</v>
       </c>
       <c r="C26" s="5">
-        <v>-4.38</v>
+        <v>-3.76</v>
       </c>
       <c r="D26" s="5">
-        <v>5.08</v>
+        <v>5.05</v>
       </c>
       <c r="E26" s="5">
-        <v>34.8</v>
+        <v>35.7</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G26" s="5" t="s">
         <v>87</v>
@@ -8938,7 +9146,7 @@
         <v>68</v>
       </c>
       <c r="J2" s="5">
-        <v>94.43000000000001</v>
+        <v>92.79000000000001</v>
       </c>
       <c r="K2" s="5">
         <v>-60</v>
@@ -8982,7 +9190,7 @@
         <v>66.5</v>
       </c>
       <c r="J3" s="5">
-        <v>94.54000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="K3" s="5">
         <v>-38</v>
@@ -9026,7 +9234,7 @@
         <v>352</v>
       </c>
       <c r="J4" s="5">
-        <v>91.47</v>
+        <v>93.37</v>
       </c>
       <c r="K4" s="5">
         <v>-18</v>
@@ -9070,7 +9278,7 @@
         <v>88</v>
       </c>
       <c r="J5" s="5">
-        <v>92.93000000000001</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="K5" s="5">
         <v>-18</v>
@@ -9114,7 +9322,7 @@
         <v>71.2</v>
       </c>
       <c r="J6" s="5">
-        <v>94.19</v>
+        <v>92.56999999999999</v>
       </c>
       <c r="K6" s="5">
         <v>0</v>
@@ -9158,7 +9366,7 @@
         <v>72.8</v>
       </c>
       <c r="J7" s="5">
-        <v>94.06999999999999</v>
+        <v>92.47</v>
       </c>
       <c r="K7" s="5">
         <v>65</v>
@@ -9202,7 +9410,7 @@
         <v>91.2</v>
       </c>
       <c r="J8" s="5">
-        <v>92.68000000000001</v>
+        <v>91.20999999999999</v>
       </c>
       <c r="K8" s="5">
         <v>35</v>
@@ -9246,7 +9454,7 @@
         <v>193.8</v>
       </c>
       <c r="J9" s="5">
-        <v>84.98</v>
+        <v>84.2</v>
       </c>
       <c r="K9" s="5">
         <v>159</v>
@@ -9290,7 +9498,7 @@
         <v>510</v>
       </c>
       <c r="J10" s="5">
-        <v>202.12</v>
+        <v>207.12</v>
       </c>
       <c r="K10" s="5">
         <v>0</v>
@@ -9334,7 +9542,7 @@
         <v>138.5</v>
       </c>
       <c r="J11" s="5">
-        <v>89.13</v>
+        <v>87.98</v>
       </c>
       <c r="K11" s="5">
         <v>122</v>
@@ -9378,7 +9586,7 @@
         <v>282</v>
       </c>
       <c r="J12" s="5">
-        <v>94.09999999999999</v>
+        <v>95.77</v>
       </c>
       <c r="K12" s="5">
         <v>29</v>
@@ -9422,7 +9630,7 @@
         <v>137.2</v>
       </c>
       <c r="J13" s="5">
-        <v>89.23</v>
+        <v>88.06</v>
       </c>
       <c r="K13" s="5">
         <v>134</v>
@@ -9466,7 +9674,7 @@
         <v>116</v>
       </c>
       <c r="J14" s="5">
-        <v>90.81999999999999</v>
+        <v>89.51000000000001</v>
       </c>
       <c r="K14" s="5">
         <v>92</v>
@@ -9510,7 +9718,7 @@
         <v>77</v>
       </c>
       <c r="J15" s="5">
-        <v>93.76000000000001</v>
+        <v>92.18000000000001</v>
       </c>
       <c r="K15" s="5">
         <v>-100</v>
@@ -9527,7 +9735,7 @@
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="5" t="s">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>100</v>
@@ -9554,7 +9762,7 @@
         <v>396.5</v>
       </c>
       <c r="J16" s="5">
-        <v>69.75</v>
+        <v>70.34</v>
       </c>
       <c r="K16" s="5">
         <v>39</v>
@@ -9571,7 +9779,7 @@
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="5" t="s">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>100</v>
@@ -9598,7 +9806,7 @@
         <v>326.2</v>
       </c>
       <c r="J17" s="5">
-        <v>75.03</v>
+        <v>75.14</v>
       </c>
       <c r="K17" s="5">
         <v>39</v>
@@ -9615,7 +9823,7 @@
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>100</v>
@@ -9642,7 +9850,7 @@
         <v>97.8</v>
       </c>
       <c r="J18" s="5">
-        <v>92.2</v>
+        <v>90.76000000000001</v>
       </c>
       <c r="K18" s="5">
         <v>129</v>
@@ -9659,7 +9867,7 @@
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>100</v>
@@ -9686,7 +9894,7 @@
         <v>107</v>
       </c>
       <c r="J19" s="5">
-        <v>91.5</v>
+        <v>90.13</v>
       </c>
       <c r="K19" s="5">
         <v>0</v>
@@ -9703,7 +9911,7 @@
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>100</v>
@@ -9730,7 +9938,7 @@
         <v>55.8</v>
       </c>
       <c r="J20" s="5">
-        <v>95.34999999999999</v>
+        <v>93.63</v>
       </c>
       <c r="K20" s="5">
         <v>88</v>
@@ -9747,7 +9955,7 @@
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>100</v>
@@ -9774,7 +9982,7 @@
         <v>207</v>
       </c>
       <c r="J21" s="5">
-        <v>213.5</v>
+        <v>217.48</v>
       </c>
       <c r="K21" s="5">
         <v>5</v>
@@ -9797,7 +10005,7 @@
         <v>100</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D22" s="5" t="b">
         <v>1</v>
@@ -9818,7 +10026,7 @@
         <v>173.4</v>
       </c>
       <c r="J22" s="5">
-        <v>195.54</v>
+        <v>193.84</v>
       </c>
       <c r="K22" s="5">
         <v>29</v>
@@ -9835,7 +10043,7 @@
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>100</v>
@@ -9862,7 +10070,7 @@
         <v>57</v>
       </c>
       <c r="J23" s="5">
-        <v>95.26000000000001</v>
+        <v>93.55</v>
       </c>
       <c r="K23" s="5">
         <v>-90</v>
@@ -9879,7 +10087,7 @@
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="5" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>100</v>
@@ -9906,7 +10114,7 @@
         <v>76.2</v>
       </c>
       <c r="J24" s="5">
-        <v>93.81</v>
+        <v>92.23</v>
       </c>
       <c r="K24" s="5">
         <v>-86</v>
@@ -9923,7 +10131,7 @@
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>100</v>
@@ -9950,7 +10158,7 @@
         <v>224.2</v>
       </c>
       <c r="J25" s="5">
-        <v>82.69</v>
+        <v>82.11</v>
       </c>
       <c r="K25" s="5">
         <v>39</v>
@@ -9967,7 +10175,7 @@
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>100</v>
@@ -9994,7 +10202,7 @@
         <v>85</v>
       </c>
       <c r="J26" s="5">
-        <v>93.15000000000001</v>
+        <v>91.63</v>
       </c>
       <c r="K26" s="5">
         <v>-80</v>
@@ -10011,7 +10219,7 @@
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>100</v>
@@ -10038,7 +10246,7 @@
         <v>161.2</v>
       </c>
       <c r="J27" s="5">
-        <v>87.42</v>
+        <v>86.42</v>
       </c>
       <c r="K27" s="5">
         <v>39</v>
@@ -10055,7 +10263,7 @@
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="5" t="s">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>100</v>
@@ -10082,7 +10290,7 @@
         <v>1586</v>
       </c>
       <c r="J28" s="5">
-        <v>45.11</v>
+        <v>51.2</v>
       </c>
       <c r="K28" s="5">
         <v>39</v>
@@ -10099,7 +10307,7 @@
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>100</v>
@@ -10126,7 +10334,7 @@
         <v>87.5</v>
       </c>
       <c r="J29" s="5">
-        <v>92.97</v>
+        <v>91.45999999999999</v>
       </c>
       <c r="K29" s="5">
         <v>0</v>
@@ -10143,7 +10351,7 @@
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>100</v>
@@ -10170,7 +10378,7 @@
         <v>57.8</v>
       </c>
       <c r="J30" s="5">
-        <v>95.2</v>
+        <v>93.5</v>
       </c>
       <c r="K30" s="5">
         <v>49</v>
@@ -10187,7 +10395,7 @@
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="5" t="s">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>100</v>
@@ -10214,7 +10422,7 @@
         <v>1305</v>
       </c>
       <c r="J31" s="5">
-        <v>55.67</v>
+        <v>60.81</v>
       </c>
       <c r="K31" s="5">
         <v>39</v>
@@ -10231,7 +10439,7 @@
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>100</v>
@@ -10258,7 +10466,7 @@
         <v>186</v>
       </c>
       <c r="J32" s="5">
-        <v>85.56</v>
+        <v>84.73</v>
       </c>
       <c r="K32" s="5">
         <v>40</v>
@@ -10275,7 +10483,7 @@
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>100</v>
@@ -10302,7 +10510,7 @@
         <v>77.2</v>
       </c>
       <c r="J33" s="5">
-        <v>93.73999999999999</v>
+        <v>92.16</v>
       </c>
       <c r="K33" s="5">
         <v>75</v>
@@ -10319,7 +10527,7 @@
     </row>
     <row r="34" spans="1:14">
       <c r="A34" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>100</v>
@@ -10346,7 +10554,7 @@
         <v>403</v>
       </c>
       <c r="J34" s="5">
-        <v>206.14</v>
+        <v>210.78</v>
       </c>
       <c r="K34" s="5">
         <v>0</v>
@@ -10363,7 +10571,7 @@
     </row>
     <row r="35" spans="1:14">
       <c r="A35" s="5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>100</v>
@@ -10390,7 +10598,7 @@
         <v>84.2</v>
       </c>
       <c r="J35" s="5">
-        <v>93.20999999999999</v>
+        <v>91.68000000000001</v>
       </c>
       <c r="K35" s="5">
         <v>0</v>
@@ -10407,13 +10615,13 @@
     </row>
     <row r="36" spans="1:14">
       <c r="A36" s="5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>100</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D36" s="5" t="b">
         <v>1</v>
@@ -10434,7 +10642,7 @@
         <v>148.1</v>
       </c>
       <c r="J36" s="5">
-        <v>77.72</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="K36" s="5">
         <v>0</v>
@@ -10451,7 +10659,7 @@
     </row>
     <row r="37" spans="1:14">
       <c r="A37" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>100</v>
@@ -10478,7 +10686,7 @@
         <v>897</v>
       </c>
       <c r="J37" s="5">
-        <v>71</v>
+        <v>74.75</v>
       </c>
       <c r="K37" s="5">
         <v>39</v>
@@ -10495,7 +10703,7 @@
     </row>
     <row r="38" spans="1:14">
       <c r="A38" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>100</v>
@@ -10522,7 +10730,7 @@
         <v>744</v>
       </c>
       <c r="J38" s="5">
-        <v>76.75</v>
+        <v>79.98</v>
       </c>
       <c r="K38" s="5">
         <v>40</v>
@@ -10539,7 +10747,7 @@
     </row>
     <row r="39" spans="1:14">
       <c r="A39" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>100</v>
@@ -10566,7 +10774,7 @@
         <v>645</v>
       </c>
       <c r="J39" s="5">
-        <v>80.47</v>
+        <v>83.36</v>
       </c>
       <c r="K39" s="5">
         <v>39</v>
@@ -10583,7 +10791,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>100</v>
@@ -10610,7 +10818,7 @@
         <v>67</v>
       </c>
       <c r="J40" s="5">
-        <v>94.51000000000001</v>
+        <v>92.86</v>
       </c>
       <c r="K40" s="5">
         <v>0</v>
@@ -10627,7 +10835,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>100</v>
@@ -10654,7 +10862,7 @@
         <v>115.2</v>
       </c>
       <c r="J41" s="5">
-        <v>90.88</v>
+        <v>89.56999999999999</v>
       </c>
       <c r="K41" s="5">
         <v>115</v>
@@ -10671,7 +10879,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>100</v>
@@ -10698,7 +10906,7 @@
         <v>79.8</v>
       </c>
       <c r="J42" s="5">
-        <v>93.55</v>
+        <v>91.98999999999999</v>
       </c>
       <c r="K42" s="5">
         <v>0</v>
@@ -10715,7 +10923,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>100</v>
@@ -10742,7 +10950,7 @@
         <v>295</v>
       </c>
       <c r="J43" s="5">
-        <v>210.19</v>
+        <v>214.47</v>
       </c>
       <c r="K43" s="5">
         <v>0</v>
@@ -10759,7 +10967,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="5" t="s">
-        <v>132</v>
+        <v>87</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>100</v>
@@ -10786,7 +10994,7 @@
         <v>98.8</v>
       </c>
       <c r="J44" s="5">
-        <v>92.12</v>
+        <v>90.69</v>
       </c>
       <c r="K44" s="5">
         <v>0</v>
@@ -10808,7 +11016,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -10840,10 +11048,10 @@
         <v>2</v>
       </c>
       <c r="C2" s="5">
-        <v>62.3</v>
+        <v>68.94</v>
       </c>
       <c r="D2" s="5">
-        <v>62.3</v>
+        <v>68.94</v>
       </c>
       <c r="E2" s="5" t="b">
         <v>0</v>
@@ -10857,10 +11065,10 @@
         <v>1</v>
       </c>
       <c r="C3" s="5">
-        <v>274.26</v>
+        <v>285.57</v>
       </c>
       <c r="D3" s="5">
-        <v>274.26</v>
+        <v>285.57</v>
       </c>
       <c r="E3" s="5" t="b">
         <v>0</v>
@@ -10868,7 +11076,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B4" s="5">
         <v>1</v>
@@ -10885,7 +11093,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B5" s="5">
         <v>0</v>
@@ -10964,7 +11172,7 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>110</v>
@@ -10979,10 +11187,10 @@
         <v>560.63</v>
       </c>
       <c r="F12" s="5">
-        <v>834.89</v>
+        <v>846.2</v>
       </c>
       <c r="G12" s="5">
-        <v>274.26</v>
+        <v>285.57</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -10990,7 +11198,7 @@
         <v>111</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C13" s="6">
         <v>46280.80667824074</v>
@@ -11010,7 +11218,7 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>101</v>
@@ -11022,18 +11230,18 @@
         <v>228</v>
       </c>
       <c r="E14" s="5">
-        <v>517.6</v>
+        <v>516.79</v>
       </c>
       <c r="F14" s="5">
         <v>597.75</v>
       </c>
       <c r="G14" s="5">
-        <v>80.15000000000001</v>
+        <v>80.95999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="5" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>101</v>
@@ -11045,18 +11253,18 @@
         <v>305</v>
       </c>
       <c r="E15" s="5">
-        <v>467.46</v>
+        <v>465.01</v>
       </c>
       <c r="F15" s="5">
-        <v>592.53</v>
+        <v>593.0599999999999</v>
       </c>
       <c r="G15" s="5">
-        <v>125.07</v>
+        <v>128.04</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>101</v>
@@ -11068,18 +11276,18 @@
         <v>897</v>
       </c>
       <c r="E16" s="5">
-        <v>500.05</v>
+        <v>500.85</v>
       </c>
       <c r="F16" s="5">
-        <v>586.38</v>
+        <v>593.0599999999999</v>
       </c>
       <c r="G16" s="5">
-        <v>86.33</v>
+        <v>92.20999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>101</v>
@@ -11091,18 +11299,18 @@
         <v>340</v>
       </c>
       <c r="E17" s="5">
-        <v>513.67</v>
+        <v>513.83</v>
       </c>
       <c r="F17" s="5">
-        <v>586.38</v>
+        <v>593.0599999999999</v>
       </c>
       <c r="G17" s="5">
-        <v>72.70999999999999</v>
+        <v>79.23</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>101</v>
@@ -11114,18 +11322,18 @@
         <v>645</v>
       </c>
       <c r="E18" s="5">
-        <v>515.12</v>
+        <v>515.33</v>
       </c>
       <c r="F18" s="5">
-        <v>586.38</v>
+        <v>593.0599999999999</v>
       </c>
       <c r="G18" s="5">
-        <v>71.26000000000001</v>
+        <v>77.73</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="5" t="s">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>104</v>
@@ -11137,18 +11345,18 @@
         <v>1586</v>
       </c>
       <c r="E19" s="5">
-        <v>515.85</v>
+        <v>516.13</v>
       </c>
       <c r="F19" s="5">
-        <v>586.38</v>
+        <v>593.0599999999999</v>
       </c>
       <c r="G19" s="5">
-        <v>70.53</v>
+        <v>76.92</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>101</v>
@@ -11160,18 +11368,18 @@
         <v>350</v>
       </c>
       <c r="E20" s="5">
-        <v>526.13</v>
+        <v>526.27</v>
       </c>
       <c r="F20" s="5">
-        <v>586.38</v>
+        <v>593.0599999999999</v>
       </c>
       <c r="G20" s="5">
-        <v>60.25</v>
+        <v>66.79000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>101</v>
@@ -11183,18 +11391,18 @@
         <v>231</v>
       </c>
       <c r="E21" s="5">
-        <v>528.2</v>
+        <v>528.11</v>
       </c>
       <c r="F21" s="5">
-        <v>586.38</v>
+        <v>593.0599999999999</v>
       </c>
       <c r="G21" s="5">
-        <v>58.18</v>
+        <v>64.95</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="5" t="s">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>104</v>
@@ -11206,18 +11414,18 @@
         <v>1305</v>
       </c>
       <c r="E22" s="5">
-        <v>532.3</v>
+        <v>532.09</v>
       </c>
       <c r="F22" s="5">
-        <v>586.38</v>
+        <v>593.0599999999999</v>
       </c>
       <c r="G22" s="5">
-        <v>54.08</v>
+        <v>60.97</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>101</v>
@@ -11229,13 +11437,36 @@
         <v>744</v>
       </c>
       <c r="E23" s="5">
-        <v>534.4299999999999</v>
+        <v>534.39</v>
       </c>
       <c r="F23" s="5">
         <v>586.38</v>
       </c>
       <c r="G23" s="5">
-        <v>51.95</v>
+        <v>51.99</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C24" s="6">
+        <v>46281.65149305556</v>
+      </c>
+      <c r="D24" s="5">
+        <v>309</v>
+      </c>
+      <c r="E24" s="5">
+        <v>536.45</v>
+      </c>
+      <c r="F24" s="5">
+        <v>566.83</v>
+      </c>
+      <c r="G24" s="5">
+        <v>30.38</v>
       </c>
     </row>
   </sheetData>

--- a/docs/reports/swift_space_weather_report_latest.xlsx
+++ b/docs/reports/swift_space_weather_report_latest.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="163">
   <si>
     <t>SWIFT Space Weather Excel Report</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Updated UTC</t>
   </si>
   <si>
-    <t>2026-09-16T21:26:17Z</t>
+    <t>2026-09-17T05:01:18Z</t>
   </si>
   <si>
     <t>Main URL root</t>
@@ -270,139 +270,139 @@
     <t>MODERATE</t>
   </si>
   <si>
+    <t>2026-09-14T11:08:00-CME-001</t>
+  </si>
+  <si>
+    <t>2026-09-13T21:12:00-CME-001</t>
+  </si>
+  <si>
+    <t>LOW</t>
+  </si>
+  <si>
+    <t>2026-09-13T10:23:00-CME-001</t>
+  </si>
+  <si>
+    <t>2026-09-15T08:36:00-CME-001</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Impact_Class</t>
+  </si>
+  <si>
+    <t>Earth_Candidate</t>
+  </si>
+  <si>
+    <t>Start_UTC</t>
+  </si>
+  <si>
+    <t>Arrival_UTC</t>
+  </si>
+  <si>
+    <t>Transit_h</t>
+  </si>
+  <si>
+    <t>Effective_Speed_km_s</t>
+  </si>
+  <si>
+    <t>Expected_Wind_Increase_km_s</t>
+  </si>
+  <si>
+    <t>Longitude</t>
+  </si>
+  <si>
+    <t>Latitude</t>
+  </si>
+  <si>
+    <t>Angular_Separation_deg</t>
+  </si>
+  <si>
+    <t>2026-09-04T15:24:00-CME-001</t>
+  </si>
+  <si>
+    <t>DONKI</t>
+  </si>
+  <si>
+    <t>MISS</t>
+  </si>
+  <si>
+    <t>2026-09-05T06:38:00-CME-001</t>
+  </si>
+  <si>
+    <t>2026-09-07T09:23:00-CME-001</t>
+  </si>
+  <si>
+    <t>ENLIL-HIT</t>
+  </si>
+  <si>
+    <t>2026-09-06T21:53:00-CME-001</t>
+  </si>
+  <si>
+    <t>2026-09-07T02:48:00-CME-001</t>
+  </si>
+  <si>
+    <t>2026-09-08T13:59:00-CME-001</t>
+  </si>
+  <si>
+    <t>2026-09-10T20:12:00-CME-001</t>
+  </si>
+  <si>
+    <t>2026-09-09T21:45:00-CME-001</t>
+  </si>
+  <si>
+    <t>CORE-HIT</t>
+  </si>
+  <si>
+    <t>2026-09-09T16:00:00-CME-001</t>
+  </si>
+  <si>
+    <t>2026-09-11T05:36:00-CME-001</t>
+  </si>
+  <si>
+    <t>2026-09-10T23:36:00-CME-001</t>
+  </si>
+  <si>
+    <t>2026-09-09T10:36:00-CME-001</t>
+  </si>
+  <si>
+    <t>2026-09-13T19:48:00-CME-001</t>
+  </si>
+  <si>
+    <t>2026-09-11T06:24:00-CME-001</t>
+  </si>
+  <si>
+    <t>2026-09-11T17:12:00-CME-001</t>
+  </si>
+  <si>
+    <t>2026-09-09T07:24:00-CME-001</t>
+  </si>
+  <si>
+    <t>2026-09-09T10:23:00-CME-001</t>
+  </si>
+  <si>
+    <t>BODY-HIT</t>
+  </si>
+  <si>
+    <t>2026-09-09T16:09:00-CME-001</t>
+  </si>
+  <si>
+    <t>2026-09-10T23:30:00-CME-001</t>
+  </si>
+  <si>
+    <t>2026-09-11T16:12:00-CME-001</t>
+  </si>
+  <si>
+    <t>2026-09-11T23:12:00-CME-001</t>
+  </si>
+  <si>
+    <t>2026-09-10T05:24:00-CME-001</t>
+  </si>
+  <si>
+    <t>2026-09-11T14:36:00-CME-001</t>
+  </si>
+  <si>
     <t>2026-09-13T01:24:00-CME-001</t>
-  </si>
-  <si>
-    <t>2026-09-14T11:08:00-CME-001</t>
-  </si>
-  <si>
-    <t>2026-09-13T21:12:00-CME-001</t>
-  </si>
-  <si>
-    <t>LOW</t>
-  </si>
-  <si>
-    <t>2026-09-13T10:23:00-CME-001</t>
-  </si>
-  <si>
-    <t>2026-09-15T08:36:00-CME-001</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Impact_Class</t>
-  </si>
-  <si>
-    <t>Earth_Candidate</t>
-  </si>
-  <si>
-    <t>Start_UTC</t>
-  </si>
-  <si>
-    <t>Arrival_UTC</t>
-  </si>
-  <si>
-    <t>Transit_h</t>
-  </si>
-  <si>
-    <t>Effective_Speed_km_s</t>
-  </si>
-  <si>
-    <t>Expected_Wind_Increase_km_s</t>
-  </si>
-  <si>
-    <t>Longitude</t>
-  </si>
-  <si>
-    <t>Latitude</t>
-  </si>
-  <si>
-    <t>Angular_Separation_deg</t>
-  </si>
-  <si>
-    <t>2026-09-04T15:24:00-CME-001</t>
-  </si>
-  <si>
-    <t>DONKI</t>
-  </si>
-  <si>
-    <t>MISS</t>
-  </si>
-  <si>
-    <t>2026-09-05T06:38:00-CME-001</t>
-  </si>
-  <si>
-    <t>2026-09-07T09:23:00-CME-001</t>
-  </si>
-  <si>
-    <t>ENLIL-HIT</t>
-  </si>
-  <si>
-    <t>2026-09-06T21:53:00-CME-001</t>
-  </si>
-  <si>
-    <t>2026-09-07T02:48:00-CME-001</t>
-  </si>
-  <si>
-    <t>2026-09-08T13:59:00-CME-001</t>
-  </si>
-  <si>
-    <t>2026-09-10T20:12:00-CME-001</t>
-  </si>
-  <si>
-    <t>2026-09-09T21:45:00-CME-001</t>
-  </si>
-  <si>
-    <t>CORE-HIT</t>
-  </si>
-  <si>
-    <t>2026-09-09T16:00:00-CME-001</t>
-  </si>
-  <si>
-    <t>2026-09-11T05:36:00-CME-001</t>
-  </si>
-  <si>
-    <t>2026-09-10T23:36:00-CME-001</t>
-  </si>
-  <si>
-    <t>2026-09-09T10:36:00-CME-001</t>
-  </si>
-  <si>
-    <t>2026-09-13T19:48:00-CME-001</t>
-  </si>
-  <si>
-    <t>2026-09-11T06:24:00-CME-001</t>
-  </si>
-  <si>
-    <t>2026-09-11T17:12:00-CME-001</t>
-  </si>
-  <si>
-    <t>2026-09-09T07:24:00-CME-001</t>
-  </si>
-  <si>
-    <t>2026-09-09T10:23:00-CME-001</t>
-  </si>
-  <si>
-    <t>BODY-HIT</t>
-  </si>
-  <si>
-    <t>2026-09-09T16:09:00-CME-001</t>
-  </si>
-  <si>
-    <t>2026-09-10T23:30:00-CME-001</t>
-  </si>
-  <si>
-    <t>2026-09-11T16:12:00-CME-001</t>
-  </si>
-  <si>
-    <t>2026-09-11T23:12:00-CME-001</t>
-  </si>
-  <si>
-    <t>2026-09-10T05:24:00-CME-001</t>
-  </si>
-  <si>
-    <t>2026-09-11T14:36:00-CME-001</t>
   </si>
   <si>
     <t>2026-09-12T08:38:00-CME-001</t>
@@ -674,10 +674,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>SolarWind_27d!$A$2:$A$36</c:f>
+              <c:f>SolarWind_27d!$A$2:$A$43</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="35"/>
+                <c:ptCount val="42"/>
                 <c:pt idx="0">
                   <c:v>46280.45833333334</c:v>
                 </c:pt>
@@ -782,16 +782,37 @@
                 </c:pt>
                 <c:pt idx="34">
                   <c:v>46281.875</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>46281.91666666666</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>46281.95833333334</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>46282</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>46282.04166666666</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>46282.08333333334</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>46282.125</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>46282.16666666666</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>SolarWind_27d!$B$2:$B$36</c:f>
+              <c:f>SolarWind_27d!$B$2:$B$43</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="35"/>
+                <c:ptCount val="42"/>
                 <c:pt idx="0">
                   <c:v>546.005</c:v>
                 </c:pt>
@@ -823,61 +844,61 @@
                   <c:v>515.75</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>464.39</c:v>
+                  <c:v>466.75</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>446.05</c:v>
+                  <c:v>447.15</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>462.23</c:v>
+                  <c:v>464.55</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>517.345</c:v>
+                  <c:v>516.58</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>522.005</c:v>
+                  <c:v>522.625</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>527.735</c:v>
+                  <c:v>528.05</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>531.665</c:v>
+                  <c:v>532.165</c:v>
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>537.3200000000001</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>536.5</c:v>
+                  <c:v>535.985</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>532.015</c:v>
+                  <c:v>532.09</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>521.465</c:v>
+                  <c:v>522.2</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>542.7</c:v>
+                  <c:v>543.4</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>539.8</c:v>
+                  <c:v>540.0549999999999</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>542.86</c:v>
+                  <c:v>543.045</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>537.5</c:v>
+                  <c:v>537.45</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>549.295</c:v>
+                  <c:v>549.265</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>562.86</c:v>
+                  <c:v>565.405</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>545.145</c:v>
+                  <c:v>545.5</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>534.22</c:v>
+                  <c:v>533.515</c:v>
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>524.6</c:v>
@@ -886,16 +907,37 @@
                   <c:v>535.595</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>524</c:v>
+                  <c:v>527.46</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>501.43</c:v>
+                  <c:v>501.03</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>509.7</c:v>
+                  <c:v>509.36</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>504.155</c:v>
+                  <c:v>502.035</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>514.4</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>508.32</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>501.225</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>505.91</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>548.45</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>516.71</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>506.93</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1019,10 +1061,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>SolarWind_27d!$A$2:$A$36</c:f>
+              <c:f>SolarWind_27d!$A$2:$A$43</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="35"/>
+                <c:ptCount val="42"/>
                 <c:pt idx="0">
                   <c:v>46280.45833333334</c:v>
                 </c:pt>
@@ -1127,16 +1169,37 @@
                 </c:pt>
                 <c:pt idx="34">
                   <c:v>46281.875</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>46281.91666666666</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>46281.95833333334</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>46282</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>46282.04166666666</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>46282.08333333334</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>46282.125</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>46282.16666666666</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>SolarWind_27d!$D$2:$D$36</c:f>
+              <c:f>SolarWind_27d!$D$2:$D$43</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="35"/>
+                <c:ptCount val="42"/>
                 <c:pt idx="0">
                   <c:v>8.85</c:v>
                 </c:pt>
@@ -1174,73 +1237,94 @@
                   <c:v>-2.73</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-4.73</c:v>
+                  <c:v>-4.83</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.87</c:v>
+                  <c:v>1.59</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>5.7</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>3.645</c:v>
+                  <c:v>3.74</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.195</c:v>
+                  <c:v>0.465</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-0.465</c:v>
+                  <c:v>-0.47</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2.175</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>4.84</c:v>
+                  <c:v>4.745</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3.395</c:v>
+                  <c:v>3.425</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>4.47</c:v>
+                  <c:v>4.4</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>2.71</c:v>
+                  <c:v>2.555</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>-2.115</c:v>
+                  <c:v>-2.22</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>-2.31</c:v>
+                  <c:v>-2.32</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.825</c:v>
+                  <c:v>1.005</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>2.8</c:v>
+                  <c:v>2.875</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>4.75</c:v>
+                  <c:v>4.755</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>3.97</c:v>
+                  <c:v>4.2</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>4.115</c:v>
+                  <c:v>4.08</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>4.095</c:v>
+                  <c:v>4.125</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>3.035</c:v>
+                  <c:v>3.02</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>2.18</c:v>
+                  <c:v>2.185</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.58</c:v>
+                  <c:v>0.5649999999999999</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>2.395</c:v>
+                  <c:v>1.945</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>2.22</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>2.375</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.18</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>-0.5</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>2.93</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>2.795</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1257,10 +1341,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>SolarWind_27d!$A$2:$A$36</c:f>
+              <c:f>SolarWind_27d!$A$2:$A$43</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="35"/>
+                <c:ptCount val="42"/>
                 <c:pt idx="0">
                   <c:v>46280.45833333334</c:v>
                 </c:pt>
@@ -1365,16 +1449,37 @@
                 </c:pt>
                 <c:pt idx="34">
                   <c:v>46281.875</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>46281.91666666666</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>46281.95833333334</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>46282</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>46282.04166666666</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>46282.08333333334</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>46282.125</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>46282.16666666666</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>SolarWind_27d!$E$2:$E$36</c:f>
+              <c:f>SolarWind_27d!$E$2:$E$43</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="35"/>
+                <c:ptCount val="42"/>
                 <c:pt idx="0">
                   <c:v>12.92</c:v>
                 </c:pt>
@@ -1412,73 +1517,94 @@
                   <c:v>10.64</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>10.94</c:v>
+                  <c:v>10.98</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>12.745</c:v>
+                  <c:v>12.84</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>10.875</c:v>
+                  <c:v>10.92</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>10.335</c:v>
+                  <c:v>10.315</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>6.895</c:v>
+                  <c:v>6.915</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>7.055</c:v>
+                  <c:v>7.045</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>6.81</c:v>
+                  <c:v>6.825</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>6.46</c:v>
+                  <c:v>6.385</c:v>
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>5.66</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>4.89</c:v>
+                  <c:v>4.85</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>4.67</c:v>
+                  <c:v>4.63</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>4.775</c:v>
+                  <c:v>4.725</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>4.285</c:v>
+                  <c:v>4.39</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>4.505</c:v>
+                  <c:v>4.31</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>4.875</c:v>
+                  <c:v>5.015</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>5.5</c:v>
+                  <c:v>5.44</c:v>
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>5.77</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>5.645</c:v>
+                  <c:v>5.615</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>5.645</c:v>
+                  <c:v>5.63</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>5.44</c:v>
+                  <c:v>5.435</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>4.7</c:v>
+                  <c:v>4.685</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>5.05</c:v>
+                  <c:v>5.025</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>4.9</c:v>
+                  <c:v>4.855</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>4.95</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>4.84</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>5.13</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>5.87</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>7.24</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>6.205</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>5.91</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1607,232 +1733,232 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="76"/>
                 <c:pt idx="0">
-                  <c:v>46281.75</c:v>
+                  <c:v>46282.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>46281.79166666666</c:v>
+                  <c:v>46282.125</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46281.83333333334</c:v>
+                  <c:v>46282.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46281.875</c:v>
+                  <c:v>46282.20833333334</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46281.91666666666</c:v>
+                  <c:v>46282.25</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46281.95833333334</c:v>
+                  <c:v>46282.29166666666</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46282</c:v>
+                  <c:v>46282.33333333334</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>46282.04166666666</c:v>
+                  <c:v>46282.375</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>46282.08333333334</c:v>
+                  <c:v>46282.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>46282.125</c:v>
+                  <c:v>46282.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>46282.16666666666</c:v>
+                  <c:v>46282.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>46282.20833333334</c:v>
+                  <c:v>46282.54166666666</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>46282.25</c:v>
+                  <c:v>46282.58333333334</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>46282.29166666666</c:v>
+                  <c:v>46282.625</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>46282.33333333334</c:v>
+                  <c:v>46282.66666666666</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46282.375</c:v>
+                  <c:v>46282.70833333334</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>46282.41666666666</c:v>
+                  <c:v>46282.75</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>46282.45833333334</c:v>
+                  <c:v>46282.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>46282.5</c:v>
+                  <c:v>46282.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>46282.54166666666</c:v>
+                  <c:v>46282.875</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>46282.58333333334</c:v>
+                  <c:v>46282.91666666666</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>46282.625</c:v>
+                  <c:v>46282.95833333334</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>46282.66666666666</c:v>
+                  <c:v>46283</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>46282.70833333334</c:v>
+                  <c:v>46283.04166666666</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>46282.75</c:v>
+                  <c:v>46283.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>46282.79166666666</c:v>
+                  <c:v>46283.125</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>46282.83333333334</c:v>
+                  <c:v>46283.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>46282.875</c:v>
+                  <c:v>46283.20833333334</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>46282.91666666666</c:v>
+                  <c:v>46283.25</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>46282.95833333334</c:v>
+                  <c:v>46283.29166666666</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>46283</c:v>
+                  <c:v>46283.33333333334</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>46283.04166666666</c:v>
+                  <c:v>46283.375</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>46283.08333333334</c:v>
+                  <c:v>46283.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>46283.125</c:v>
+                  <c:v>46283.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>46283.16666666666</c:v>
+                  <c:v>46283.5</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>46283.20833333334</c:v>
+                  <c:v>46283.54166666666</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>46283.25</c:v>
+                  <c:v>46283.58333333334</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>46283.29166666666</c:v>
+                  <c:v>46283.625</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>46283.33333333334</c:v>
+                  <c:v>46283.66666666666</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>46283.375</c:v>
+                  <c:v>46283.70833333334</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>46283.41666666666</c:v>
+                  <c:v>46283.75</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>46283.45833333334</c:v>
+                  <c:v>46283.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>46283.5</c:v>
+                  <c:v>46283.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>46283.54166666666</c:v>
+                  <c:v>46283.875</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>46283.58333333334</c:v>
+                  <c:v>46283.91666666666</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>46283.625</c:v>
+                  <c:v>46283.95833333334</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>46283.66666666666</c:v>
+                  <c:v>46284</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>46283.70833333334</c:v>
+                  <c:v>46284.04166666666</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>46283.75</c:v>
+                  <c:v>46284.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>46283.79166666666</c:v>
+                  <c:v>46284.125</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>46283.83333333334</c:v>
+                  <c:v>46284.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>46283.875</c:v>
+                  <c:v>46284.20833333334</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>46283.91666666666</c:v>
+                  <c:v>46284.25</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>46283.95833333334</c:v>
+                  <c:v>46284.29166666666</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>46284</c:v>
+                  <c:v>46284.33333333334</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>46284.04166666666</c:v>
+                  <c:v>46284.375</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>46284.08333333334</c:v>
+                  <c:v>46284.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>46284.125</c:v>
+                  <c:v>46284.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>46284.16666666666</c:v>
+                  <c:v>46284.5</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>46284.20833333334</c:v>
+                  <c:v>46284.54166666666</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>46284.25</c:v>
+                  <c:v>46284.58333333334</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>46284.29166666666</c:v>
+                  <c:v>46284.625</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>46284.33333333334</c:v>
+                  <c:v>46284.66666666666</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>46284.375</c:v>
+                  <c:v>46284.70833333334</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>46284.41666666666</c:v>
+                  <c:v>46284.75</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>46284.45833333334</c:v>
+                  <c:v>46284.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>46284.5</c:v>
+                  <c:v>46284.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>46284.54166666666</c:v>
+                  <c:v>46284.875</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>46284.58333333334</c:v>
+                  <c:v>46284.91666666666</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>46284.625</c:v>
+                  <c:v>46284.95833333334</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>46284.66666666666</c:v>
+                  <c:v>46285</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>46284.70833333334</c:v>
+                  <c:v>46285.04166666666</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>46284.75</c:v>
+                  <c:v>46285.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>46284.79166666666</c:v>
+                  <c:v>46285.125</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>46284.83333333334</c:v>
+                  <c:v>46285.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>46284.875</c:v>
+                  <c:v>46285.20833333334</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1844,232 +1970,232 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="76"/>
                 <c:pt idx="0">
-                  <c:v>604.42</c:v>
+                  <c:v>634.0700000000001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>623.3200000000001</c:v>
+                  <c:v>639.17</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>636.67</c:v>
+                  <c:v>637.21</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>649.9400000000001</c:v>
+                  <c:v>645.63</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>654.25</c:v>
+                  <c:v>649.3200000000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>655.86</c:v>
+                  <c:v>654.54</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>655.39</c:v>
+                  <c:v>654.64</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>653.39</c:v>
+                  <c:v>651.98</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>651.72</c:v>
+                  <c:v>647.08</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>649.52</c:v>
+                  <c:v>642.08</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>645.62</c:v>
+                  <c:v>634.4</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>644.9299999999999</c:v>
+                  <c:v>622.72</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>646.13</c:v>
+                  <c:v>609</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>647.36</c:v>
+                  <c:v>594.4400000000001</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>643.6900000000001</c:v>
+                  <c:v>579.76</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>641.37</c:v>
+                  <c:v>565.35</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>637.99</c:v>
+                  <c:v>551.4400000000001</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>632.58</c:v>
+                  <c:v>538.02</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>625.0599999999999</c:v>
+                  <c:v>523.51</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>614.1799999999999</c:v>
+                  <c:v>510.41</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>601.63</c:v>
+                  <c:v>498.46</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>588.42</c:v>
+                  <c:v>487.46</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>575.15</c:v>
+                  <c:v>477.28</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>562.1799999999999</c:v>
+                  <c:v>466.91</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>549.7</c:v>
+                  <c:v>458.63</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>537.6900000000001</c:v>
+                  <c:v>451.86</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>524.95</c:v>
+                  <c:v>446.3</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>513.38</c:v>
+                  <c:v>441.83</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>502.79</c:v>
+                  <c:v>438.49</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>493</c:v>
+                  <c:v>435.58</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>483.95</c:v>
+                  <c:v>433.75</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>474.98</c:v>
+                  <c:v>433.64</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>467.85</c:v>
+                  <c:v>435.8</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>462.11</c:v>
+                  <c:v>436.65</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>457.5</c:v>
+                  <c:v>442</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>453.98</c:v>
+                  <c:v>447.9</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>451.68</c:v>
+                  <c:v>457.2</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>450</c:v>
+                  <c:v>467.79</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>449.75</c:v>
+                  <c:v>477.56</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>451.7</c:v>
+                  <c:v>484.56</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>456.56</c:v>
+                  <c:v>485.68</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>459.6</c:v>
+                  <c:v>480.71</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>468.45</c:v>
+                  <c:v>474.46</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>479.76</c:v>
+                  <c:v>467.62</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>494.65</c:v>
+                  <c:v>458.27</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>510.65</c:v>
+                  <c:v>450.01</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>525.17</c:v>
+                  <c:v>442.59</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>535.79</c:v>
+                  <c:v>433.58</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>538.49</c:v>
+                  <c:v>426.19</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>534.03</c:v>
+                  <c:v>419.93</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>527.33</c:v>
+                  <c:v>414.47</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>519.51</c:v>
+                  <c:v>409.61</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>509.2</c:v>
+                  <c:v>405.22</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>499.72</c:v>
+                  <c:v>401.21</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>490.94</c:v>
+                  <c:v>397.52</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>480.83</c:v>
+                  <c:v>394.1</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>472.21</c:v>
+                  <c:v>390.93</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>464.69</c:v>
+                  <c:v>387.97</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>457.97</c:v>
+                  <c:v>385.21</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>451.9</c:v>
+                  <c:v>382.64</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>446.34</c:v>
+                  <c:v>380.24</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>441.23</c:v>
+                  <c:v>377.99</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>436.49</c:v>
+                  <c:v>375.89</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>432.09</c:v>
+                  <c:v>373.92</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>427.99</c:v>
+                  <c:v>372.08</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>424.17</c:v>
+                  <c:v>370.36</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>420.61</c:v>
+                  <c:v>368.75</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>417.28</c:v>
+                  <c:v>367.25</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>414.17</c:v>
+                  <c:v>365.84</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>411.26</c:v>
+                  <c:v>364.52</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>408.54</c:v>
+                  <c:v>363.29</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>406</c:v>
+                  <c:v>362.14</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>403.62</c:v>
+                  <c:v>361.06</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>401.4</c:v>
+                  <c:v>360.05</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>399.32</c:v>
+                  <c:v>359.11</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>397.38</c:v>
+                  <c:v>358.22</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2091,232 +2217,232 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="76"/>
                 <c:pt idx="0">
-                  <c:v>46281.75</c:v>
+                  <c:v>46282.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>46281.79166666666</c:v>
+                  <c:v>46282.125</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46281.83333333334</c:v>
+                  <c:v>46282.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46281.875</c:v>
+                  <c:v>46282.20833333334</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46281.91666666666</c:v>
+                  <c:v>46282.25</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46281.95833333334</c:v>
+                  <c:v>46282.29166666666</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46282</c:v>
+                  <c:v>46282.33333333334</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>46282.04166666666</c:v>
+                  <c:v>46282.375</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>46282.08333333334</c:v>
+                  <c:v>46282.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>46282.125</c:v>
+                  <c:v>46282.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>46282.16666666666</c:v>
+                  <c:v>46282.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>46282.20833333334</c:v>
+                  <c:v>46282.54166666666</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>46282.25</c:v>
+                  <c:v>46282.58333333334</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>46282.29166666666</c:v>
+                  <c:v>46282.625</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>46282.33333333334</c:v>
+                  <c:v>46282.66666666666</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46282.375</c:v>
+                  <c:v>46282.70833333334</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>46282.41666666666</c:v>
+                  <c:v>46282.75</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>46282.45833333334</c:v>
+                  <c:v>46282.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>46282.5</c:v>
+                  <c:v>46282.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>46282.54166666666</c:v>
+                  <c:v>46282.875</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>46282.58333333334</c:v>
+                  <c:v>46282.91666666666</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>46282.625</c:v>
+                  <c:v>46282.95833333334</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>46282.66666666666</c:v>
+                  <c:v>46283</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>46282.70833333334</c:v>
+                  <c:v>46283.04166666666</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>46282.75</c:v>
+                  <c:v>46283.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>46282.79166666666</c:v>
+                  <c:v>46283.125</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>46282.83333333334</c:v>
+                  <c:v>46283.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>46282.875</c:v>
+                  <c:v>46283.20833333334</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>46282.91666666666</c:v>
+                  <c:v>46283.25</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>46282.95833333334</c:v>
+                  <c:v>46283.29166666666</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>46283</c:v>
+                  <c:v>46283.33333333334</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>46283.04166666666</c:v>
+                  <c:v>46283.375</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>46283.08333333334</c:v>
+                  <c:v>46283.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>46283.125</c:v>
+                  <c:v>46283.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>46283.16666666666</c:v>
+                  <c:v>46283.5</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>46283.20833333334</c:v>
+                  <c:v>46283.54166666666</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>46283.25</c:v>
+                  <c:v>46283.58333333334</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>46283.29166666666</c:v>
+                  <c:v>46283.625</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>46283.33333333334</c:v>
+                  <c:v>46283.66666666666</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>46283.375</c:v>
+                  <c:v>46283.70833333334</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>46283.41666666666</c:v>
+                  <c:v>46283.75</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>46283.45833333334</c:v>
+                  <c:v>46283.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>46283.5</c:v>
+                  <c:v>46283.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>46283.54166666666</c:v>
+                  <c:v>46283.875</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>46283.58333333334</c:v>
+                  <c:v>46283.91666666666</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>46283.625</c:v>
+                  <c:v>46283.95833333334</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>46283.66666666666</c:v>
+                  <c:v>46284</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>46283.70833333334</c:v>
+                  <c:v>46284.04166666666</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>46283.75</c:v>
+                  <c:v>46284.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>46283.79166666666</c:v>
+                  <c:v>46284.125</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>46283.83333333334</c:v>
+                  <c:v>46284.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>46283.875</c:v>
+                  <c:v>46284.20833333334</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>46283.91666666666</c:v>
+                  <c:v>46284.25</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>46283.95833333334</c:v>
+                  <c:v>46284.29166666666</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>46284</c:v>
+                  <c:v>46284.33333333334</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>46284.04166666666</c:v>
+                  <c:v>46284.375</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>46284.08333333334</c:v>
+                  <c:v>46284.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>46284.125</c:v>
+                  <c:v>46284.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>46284.16666666666</c:v>
+                  <c:v>46284.5</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>46284.20833333334</c:v>
+                  <c:v>46284.54166666666</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>46284.25</c:v>
+                  <c:v>46284.58333333334</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>46284.29166666666</c:v>
+                  <c:v>46284.625</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>46284.33333333334</c:v>
+                  <c:v>46284.66666666666</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>46284.375</c:v>
+                  <c:v>46284.70833333334</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>46284.41666666666</c:v>
+                  <c:v>46284.75</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>46284.45833333334</c:v>
+                  <c:v>46284.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>46284.5</c:v>
+                  <c:v>46284.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>46284.54166666666</c:v>
+                  <c:v>46284.875</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>46284.58333333334</c:v>
+                  <c:v>46284.91666666666</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>46284.625</c:v>
+                  <c:v>46284.95833333334</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>46284.66666666666</c:v>
+                  <c:v>46285</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>46284.70833333334</c:v>
+                  <c:v>46285.04166666666</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>46284.75</c:v>
+                  <c:v>46285.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>46284.79166666666</c:v>
+                  <c:v>46285.125</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>46284.83333333334</c:v>
+                  <c:v>46285.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>46284.875</c:v>
+                  <c:v>46285.20833333334</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2328,232 +2454,232 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="76"/>
                 <c:pt idx="0">
-                  <c:v>377.68</c:v>
+                  <c:v>330.02</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>373.72</c:v>
+                  <c:v>331.46</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>364.8</c:v>
+                  <c:v>334.59</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>359.37</c:v>
+                  <c:v>334.76</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>358.92</c:v>
+                  <c:v>335.51</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>357.83</c:v>
+                  <c:v>337.8</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>356.4</c:v>
+                  <c:v>340.04</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>354.54</c:v>
+                  <c:v>338.38</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>353.87</c:v>
+                  <c:v>336.15</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>351.96</c:v>
+                  <c:v>336.6</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>352.66</c:v>
+                  <c:v>337.09</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>352.7</c:v>
+                  <c:v>337.43</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>352.36</c:v>
+                  <c:v>337.68</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>352.14</c:v>
+                  <c:v>337.88</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>352.02</c:v>
+                  <c:v>338.03</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>351.97</c:v>
+                  <c:v>338.16</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>352.13</c:v>
+                  <c:v>338.24</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>352.53</c:v>
+                  <c:v>338.17</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>353.07</c:v>
+                  <c:v>338.01</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>353.54</c:v>
+                  <c:v>337.78</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>353.96</c:v>
+                  <c:v>337.53</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>354.33</c:v>
+                  <c:v>337.25</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>354.69</c:v>
+                  <c:v>336.96</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>355.02</c:v>
+                  <c:v>337.6</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>355.33</c:v>
+                  <c:v>338.82</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>355.51</c:v>
+                  <c:v>340.39</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>355.6</c:v>
+                  <c:v>342.19</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>355.64</c:v>
+                  <c:v>344.12</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>355.63</c:v>
+                  <c:v>346.14</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>355.6</c:v>
+                  <c:v>347.31</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>355.54</c:v>
+                  <c:v>347.95</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>356.4</c:v>
+                  <c:v>348.27</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>357.83</c:v>
+                  <c:v>348.38</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>359.59</c:v>
+                  <c:v>348.36</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>361.57</c:v>
+                  <c:v>348.27</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>363.68</c:v>
+                  <c:v>348.14</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>365.87</c:v>
+                  <c:v>347.98</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>367.21</c:v>
+                  <c:v>347.8</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>368.01</c:v>
+                  <c:v>347.61</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>368.49</c:v>
+                  <c:v>347.41</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>368.75</c:v>
+                  <c:v>347.21</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>368.89</c:v>
+                  <c:v>347.01</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>368.95</c:v>
+                  <c:v>346.8</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>368.95</c:v>
+                  <c:v>346.6</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>368.92</c:v>
+                  <c:v>346.39</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>368.87</c:v>
+                  <c:v>346.19</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>368.81</c:v>
+                  <c:v>345.98</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>368.73</c:v>
+                  <c:v>345.85</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>368.65</c:v>
+                  <c:v>345.77</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>368.55</c:v>
+                  <c:v>345.71</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>368.46</c:v>
+                  <c:v>345.67</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>368.35</c:v>
+                  <c:v>345.64</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>368.24</c:v>
+                  <c:v>345.62</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>368.13</c:v>
+                  <c:v>345.61</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>368.02</c:v>
+                  <c:v>345.59</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>367.97</c:v>
+                  <c:v>345.58</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>367.97</c:v>
+                  <c:v>345.57</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>367.99</c:v>
+                  <c:v>345.56</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>368.03</c:v>
+                  <c:v>345.56</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>368.07</c:v>
+                  <c:v>345.55</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>368.12</c:v>
+                  <c:v>345.54</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>368.17</c:v>
+                  <c:v>345.53</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>368.22</c:v>
+                  <c:v>345.53</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>368.27</c:v>
+                  <c:v>345.52</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>368.31</c:v>
+                  <c:v>345.52</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>368.36</c:v>
+                  <c:v>345.51</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>368.41</c:v>
+                  <c:v>345.5</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>368.45</c:v>
+                  <c:v>345.5</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>368.49</c:v>
+                  <c:v>345.49</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>368.53</c:v>
+                  <c:v>345.49</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>368.57</c:v>
+                  <c:v>345.49</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>368.61</c:v>
+                  <c:v>345.48</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>368.64</c:v>
+                  <c:v>345.48</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>368.68</c:v>
+                  <c:v>345.47</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>368.71</c:v>
+                  <c:v>345.47</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>368.74</c:v>
+                  <c:v>345.47</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2575,232 +2701,232 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="76"/>
                 <c:pt idx="0">
-                  <c:v>46281.75</c:v>
+                  <c:v>46282.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>46281.79166666666</c:v>
+                  <c:v>46282.125</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46281.83333333334</c:v>
+                  <c:v>46282.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46281.875</c:v>
+                  <c:v>46282.20833333334</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46281.91666666666</c:v>
+                  <c:v>46282.25</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46281.95833333334</c:v>
+                  <c:v>46282.29166666666</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46282</c:v>
+                  <c:v>46282.33333333334</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>46282.04166666666</c:v>
+                  <c:v>46282.375</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>46282.08333333334</c:v>
+                  <c:v>46282.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>46282.125</c:v>
+                  <c:v>46282.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>46282.16666666666</c:v>
+                  <c:v>46282.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>46282.20833333334</c:v>
+                  <c:v>46282.54166666666</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>46282.25</c:v>
+                  <c:v>46282.58333333334</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>46282.29166666666</c:v>
+                  <c:v>46282.625</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>46282.33333333334</c:v>
+                  <c:v>46282.66666666666</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46282.375</c:v>
+                  <c:v>46282.70833333334</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>46282.41666666666</c:v>
+                  <c:v>46282.75</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>46282.45833333334</c:v>
+                  <c:v>46282.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>46282.5</c:v>
+                  <c:v>46282.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>46282.54166666666</c:v>
+                  <c:v>46282.875</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>46282.58333333334</c:v>
+                  <c:v>46282.91666666666</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>46282.625</c:v>
+                  <c:v>46282.95833333334</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>46282.66666666666</c:v>
+                  <c:v>46283</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>46282.70833333334</c:v>
+                  <c:v>46283.04166666666</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>46282.75</c:v>
+                  <c:v>46283.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>46282.79166666666</c:v>
+                  <c:v>46283.125</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>46282.83333333334</c:v>
+                  <c:v>46283.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>46282.875</c:v>
+                  <c:v>46283.20833333334</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>46282.91666666666</c:v>
+                  <c:v>46283.25</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>46282.95833333334</c:v>
+                  <c:v>46283.29166666666</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>46283</c:v>
+                  <c:v>46283.33333333334</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>46283.04166666666</c:v>
+                  <c:v>46283.375</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>46283.08333333334</c:v>
+                  <c:v>46283.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>46283.125</c:v>
+                  <c:v>46283.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>46283.16666666666</c:v>
+                  <c:v>46283.5</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>46283.20833333334</c:v>
+                  <c:v>46283.54166666666</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>46283.25</c:v>
+                  <c:v>46283.58333333334</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>46283.29166666666</c:v>
+                  <c:v>46283.625</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>46283.33333333334</c:v>
+                  <c:v>46283.66666666666</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>46283.375</c:v>
+                  <c:v>46283.70833333334</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>46283.41666666666</c:v>
+                  <c:v>46283.75</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>46283.45833333334</c:v>
+                  <c:v>46283.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>46283.5</c:v>
+                  <c:v>46283.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>46283.54166666666</c:v>
+                  <c:v>46283.875</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>46283.58333333334</c:v>
+                  <c:v>46283.91666666666</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>46283.625</c:v>
+                  <c:v>46283.95833333334</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>46283.66666666666</c:v>
+                  <c:v>46284</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>46283.70833333334</c:v>
+                  <c:v>46284.04166666666</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>46283.75</c:v>
+                  <c:v>46284.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>46283.79166666666</c:v>
+                  <c:v>46284.125</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>46283.83333333334</c:v>
+                  <c:v>46284.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>46283.875</c:v>
+                  <c:v>46284.20833333334</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>46283.91666666666</c:v>
+                  <c:v>46284.25</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>46283.95833333334</c:v>
+                  <c:v>46284.29166666666</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>46284</c:v>
+                  <c:v>46284.33333333334</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>46284.04166666666</c:v>
+                  <c:v>46284.375</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>46284.08333333334</c:v>
+                  <c:v>46284.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>46284.125</c:v>
+                  <c:v>46284.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>46284.16666666666</c:v>
+                  <c:v>46284.5</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>46284.20833333334</c:v>
+                  <c:v>46284.54166666666</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>46284.25</c:v>
+                  <c:v>46284.58333333334</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>46284.29166666666</c:v>
+                  <c:v>46284.625</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>46284.33333333334</c:v>
+                  <c:v>46284.66666666666</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>46284.375</c:v>
+                  <c:v>46284.70833333334</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>46284.41666666666</c:v>
+                  <c:v>46284.75</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>46284.45833333334</c:v>
+                  <c:v>46284.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>46284.5</c:v>
+                  <c:v>46284.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>46284.54166666666</c:v>
+                  <c:v>46284.875</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>46284.58333333334</c:v>
+                  <c:v>46284.91666666666</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>46284.625</c:v>
+                  <c:v>46284.95833333334</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>46284.66666666666</c:v>
+                  <c:v>46285</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>46284.70833333334</c:v>
+                  <c:v>46285.04166666666</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>46284.75</c:v>
+                  <c:v>46285.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>46284.79166666666</c:v>
+                  <c:v>46285.125</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>46284.83333333334</c:v>
+                  <c:v>46285.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>46284.875</c:v>
+                  <c:v>46285.20833333334</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2812,232 +2938,232 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="76"/>
                 <c:pt idx="0">
-                  <c:v>299.12</c:v>
+                  <c:v>397.08</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>329.26</c:v>
+                  <c:v>401.85</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>358.66</c:v>
+                  <c:v>395.22</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>383.33</c:v>
+                  <c:v>405.99</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>399.87</c:v>
+                  <c:v>416.08</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>399</c:v>
+                  <c:v>419.92</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>396.46</c:v>
+                  <c:v>406.26</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>393.96</c:v>
+                  <c:v>407.43</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>390.75</c:v>
+                  <c:v>400.35</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>391.92</c:v>
+                  <c:v>387.33</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>376.61</c:v>
+                  <c:v>370.86</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>383.92</c:v>
+                  <c:v>346.95</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>390.85</c:v>
+                  <c:v>324.57</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>392.57</c:v>
+                  <c:v>303.64</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>377.15</c:v>
+                  <c:v>284.06</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>376.88</c:v>
+                  <c:v>265.74</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>369.49</c:v>
+                  <c:v>248.6</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>356.95</c:v>
+                  <c:v>232.57</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>341.44</c:v>
+                  <c:v>211.68</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>319.42</c:v>
+                  <c:v>198.02</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>298.82</c:v>
+                  <c:v>185.25</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>279.55</c:v>
+                  <c:v>173.31</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>261.52</c:v>
+                  <c:v>162.17</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>244.65</c:v>
+                  <c:v>145.44</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>228.88</c:v>
+                  <c:v>136.22</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>214.11</c:v>
+                  <c:v>127.8</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>195.77</c:v>
+                  <c:v>120.29</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>183.14</c:v>
+                  <c:v>113.95</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>171.33</c:v>
+                  <c:v>109.19</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>160.28</c:v>
+                  <c:v>106.56</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>150</c:v>
+                  <c:v>106.78</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>135.26</c:v>
+                  <c:v>110.58</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>126.76</c:v>
+                  <c:v>118.53</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>119.06</c:v>
+                  <c:v>117.16</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>112.36</c:v>
+                  <c:v>133.98</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>107.01</c:v>
+                  <c:v>143.13</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>103.54</c:v>
+                  <c:v>162.81</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>102.74</c:v>
+                  <c:v>179.66</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>105.55</c:v>
+                  <c:v>190.92</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>112.95</c:v>
+                  <c:v>194.45</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>125.72</c:v>
+                  <c:v>183.67</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>125.91</c:v>
+                  <c:v>164.44</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>150.21</c:v>
+                  <c:v>153.84</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>170.52</c:v>
+                  <c:v>143.92</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>197.98</c:v>
+                  <c:v>126.6</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>221.58</c:v>
+                  <c:v>118.44</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>237.67</c:v>
+                  <c:v>110.8</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>243.41</c:v>
+                  <c:v>95.64</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>230.06</c:v>
+                  <c:v>89.47</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>208.88</c:v>
+                  <c:v>83.7</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>195.4</c:v>
+                  <c:v>78.3</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>182.8</c:v>
+                  <c:v>73.25</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>163.99</c:v>
+                  <c:v>68.53</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>153.42</c:v>
+                  <c:v>64.11</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>143.52</c:v>
+                  <c:v>59.97</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>127.19</c:v>
+                  <c:v>56.1</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>118.99</c:v>
+                  <c:v>52.49</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>111.32</c:v>
+                  <c:v>49.1</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>104.14</c:v>
+                  <c:v>45.93</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>97.42</c:v>
+                  <c:v>42.97</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>91.14</c:v>
+                  <c:v>40.2</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>85.26000000000001</c:v>
+                  <c:v>37.61</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>79.76000000000001</c:v>
+                  <c:v>35.18</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>74.62</c:v>
+                  <c:v>32.91</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>69.81</c:v>
+                  <c:v>30.79</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>65.3</c:v>
+                  <c:v>28.81</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>61.09</c:v>
+                  <c:v>26.95</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>57.15</c:v>
+                  <c:v>25.21</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>53.47</c:v>
+                  <c:v>23.58</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>50.02</c:v>
+                  <c:v>22.06</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>46.79</c:v>
+                  <c:v>20.64</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>43.77</c:v>
+                  <c:v>19.31</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>40.95</c:v>
+                  <c:v>18.06</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>38.31</c:v>
+                  <c:v>16.9</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>35.84</c:v>
+                  <c:v>15.81</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>33.53</c:v>
+                  <c:v>14.79</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3166,76 +3292,76 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="24"/>
                 <c:pt idx="0">
-                  <c:v>46281.875</c:v>
+                  <c:v>46282.25</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>46282</c:v>
+                  <c:v>46282.375</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46282.125</c:v>
+                  <c:v>46282.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46282.25</c:v>
+                  <c:v>46282.625</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46282.375</c:v>
+                  <c:v>46282.75</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46282.5</c:v>
+                  <c:v>46282.875</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46282.625</c:v>
+                  <c:v>46283</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>46282.75</c:v>
+                  <c:v>46283.125</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>46282.875</c:v>
+                  <c:v>46283.25</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>46283</c:v>
+                  <c:v>46283.375</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>46283.125</c:v>
+                  <c:v>46283.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>46283.25</c:v>
+                  <c:v>46283.625</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>46283.375</c:v>
+                  <c:v>46283.75</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>46283.5</c:v>
+                  <c:v>46283.875</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>46283.625</c:v>
+                  <c:v>46284</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46283.75</c:v>
+                  <c:v>46284.125</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>46283.875</c:v>
+                  <c:v>46284.25</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>46284</c:v>
+                  <c:v>46284.375</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>46284.125</c:v>
+                  <c:v>46284.5</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>46284.25</c:v>
+                  <c:v>46284.625</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>46284.375</c:v>
+                  <c:v>46284.75</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>46284.5</c:v>
+                  <c:v>46284.875</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>46284.625</c:v>
+                  <c:v>46285</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>46284.75</c:v>
+                  <c:v>46285.125</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3247,76 +3373,76 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="24"/>
                 <c:pt idx="0">
-                  <c:v>1.67</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.67</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.67</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3</c:v>
+                  <c:v>1.67</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.33</c:v>
+                  <c:v>1.33</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3</c:v>
+                  <c:v>0.67</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2</c:v>
+                  <c:v>0.67</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>0.67</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.67</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>1.33</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="11">
+                  <c:v>1.67</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.67</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="14">
                   <c:v>0.67</c:v>
                 </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.67</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>1.67</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>2.33</c:v>
-                </c:pt>
                 <c:pt idx="15">
-                  <c:v>2.67</c:v>
+                  <c:v>0.33</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.33</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.67</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.67</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.33</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.33</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.33</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3445,79 +3571,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>46281.875</c:v>
+                  <c:v>46282.20833333334</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>46282</c:v>
+                  <c:v>46282.33333333334</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46282.125</c:v>
+                  <c:v>46282.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46282.25</c:v>
+                  <c:v>46282.58333333334</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46282.375</c:v>
+                  <c:v>46282.70833333334</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46282.5</c:v>
+                  <c:v>46282.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46282.625</c:v>
+                  <c:v>46282.95833333334</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>46282.75</c:v>
+                  <c:v>46283.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>46282.875</c:v>
+                  <c:v>46283.20833333334</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>46283</c:v>
+                  <c:v>46283.33333333334</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>46283.125</c:v>
+                  <c:v>46283.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>46283.25</c:v>
+                  <c:v>46283.58333333334</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>46283.375</c:v>
+                  <c:v>46283.70833333334</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>46283.5</c:v>
+                  <c:v>46283.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>46283.625</c:v>
+                  <c:v>46283.95833333334</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46283.75</c:v>
+                  <c:v>46284.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>46283.875</c:v>
+                  <c:v>46284.20833333334</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>46284</c:v>
+                  <c:v>46284.33333333334</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>46284.125</c:v>
+                  <c:v>46284.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>46284.25</c:v>
+                  <c:v>46284.58333333334</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>46284.375</c:v>
+                  <c:v>46284.70833333334</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>46284.5</c:v>
+                  <c:v>46284.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>46284.625</c:v>
+                  <c:v>46284.95833333334</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>46284.75</c:v>
+                  <c:v>46285.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>46284.875</c:v>
+                  <c:v>46285.20833333334</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3529,79 +3655,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>2.07</c:v>
+                  <c:v>1.61</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.9</c:v>
+                  <c:v>1.48</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.75</c:v>
+                  <c:v>1.36</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.61</c:v>
+                  <c:v>1.26</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.48</c:v>
+                  <c:v>1.16</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.36</c:v>
+                  <c:v>1.06</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.26</c:v>
+                  <c:v>0.98</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.16</c:v>
+                  <c:v>0.9</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.06</c:v>
+                  <c:v>0.83</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.98</c:v>
+                  <c:v>0.76</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.9</c:v>
+                  <c:v>0.7</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.83</c:v>
+                  <c:v>0.64</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.76</c:v>
+                  <c:v>0.59</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.7</c:v>
+                  <c:v>0.55</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.64</c:v>
+                  <c:v>0.5</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.59</c:v>
+                  <c:v>0.46</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.55</c:v>
+                  <c:v>0.43</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.5</c:v>
+                  <c:v>0.39</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.46</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.42</c:v>
+                  <c:v>0.33</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.41</c:v>
+                  <c:v>0.32</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.41</c:v>
+                  <c:v>0.32</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.41</c:v>
+                  <c:v>0.32</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.41</c:v>
+                  <c:v>0.32</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.41</c:v>
+                  <c:v>0.32</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3623,79 +3749,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>46281.875</c:v>
+                  <c:v>46282.20833333334</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>46282</c:v>
+                  <c:v>46282.33333333334</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46282.125</c:v>
+                  <c:v>46282.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46282.25</c:v>
+                  <c:v>46282.58333333334</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46282.375</c:v>
+                  <c:v>46282.70833333334</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46282.5</c:v>
+                  <c:v>46282.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46282.625</c:v>
+                  <c:v>46282.95833333334</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>46282.75</c:v>
+                  <c:v>46283.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>46282.875</c:v>
+                  <c:v>46283.20833333334</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>46283</c:v>
+                  <c:v>46283.33333333334</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>46283.125</c:v>
+                  <c:v>46283.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>46283.25</c:v>
+                  <c:v>46283.58333333334</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>46283.375</c:v>
+                  <c:v>46283.70833333334</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>46283.5</c:v>
+                  <c:v>46283.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>46283.625</c:v>
+                  <c:v>46283.95833333334</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46283.75</c:v>
+                  <c:v>46284.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>46283.875</c:v>
+                  <c:v>46284.20833333334</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>46284</c:v>
+                  <c:v>46284.33333333334</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>46284.125</c:v>
+                  <c:v>46284.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>46284.25</c:v>
+                  <c:v>46284.58333333334</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>46284.375</c:v>
+                  <c:v>46284.70833333334</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>46284.5</c:v>
+                  <c:v>46284.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>46284.625</c:v>
+                  <c:v>46284.95833333334</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>46284.75</c:v>
+                  <c:v>46285.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>46284.875</c:v>
+                  <c:v>46285.20833333334</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3707,79 +3833,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>-9.77</c:v>
+                  <c:v>-12.3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-9.77</c:v>
+                  <c:v>-12.3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-9.859999999999999</c:v>
+                  <c:v>-12.55</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-10.86</c:v>
+                  <c:v>-12.36</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-10.97</c:v>
+                  <c:v>-10.64</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-11.11</c:v>
+                  <c:v>-8.220000000000001</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-10.36</c:v>
+                  <c:v>-6.01</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-8.300000000000001</c:v>
+                  <c:v>-4.52</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-5.98</c:v>
+                  <c:v>-5.35</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-4.94</c:v>
+                  <c:v>-7.35</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-4.4</c:v>
+                  <c:v>-9.81</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-5.13</c:v>
+                  <c:v>-11.96</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-6.59</c:v>
+                  <c:v>-12.91</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-9.050000000000001</c:v>
+                  <c:v>-12.23</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-10.9</c:v>
+                  <c:v>-10.26</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-11.32</c:v>
+                  <c:v>-7.9</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-10.13</c:v>
+                  <c:v>-5.92</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-7.93</c:v>
+                  <c:v>-4.67</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-5.62</c:v>
+                  <c:v>-4.04</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-4.67</c:v>
+                  <c:v>-3.8</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-4.15</c:v>
+                  <c:v>-3.72</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>-3.9</c:v>
+                  <c:v>-3.69</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>-3.8</c:v>
+                  <c:v>-3.69</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>-3.76</c:v>
+                  <c:v>-3.69</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>-3.76</c:v>
+                  <c:v>-3.69</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3801,79 +3927,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>46281.875</c:v>
+                  <c:v>46282.20833333334</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>46282</c:v>
+                  <c:v>46282.33333333334</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46282.125</c:v>
+                  <c:v>46282.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46282.25</c:v>
+                  <c:v>46282.58333333334</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46282.375</c:v>
+                  <c:v>46282.70833333334</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46282.5</c:v>
+                  <c:v>46282.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46282.625</c:v>
+                  <c:v>46282.95833333334</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>46282.75</c:v>
+                  <c:v>46283.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>46282.875</c:v>
+                  <c:v>46283.20833333334</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>46283</c:v>
+                  <c:v>46283.33333333334</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>46283.125</c:v>
+                  <c:v>46283.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>46283.25</c:v>
+                  <c:v>46283.58333333334</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>46283.375</c:v>
+                  <c:v>46283.70833333334</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>46283.5</c:v>
+                  <c:v>46283.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>46283.625</c:v>
+                  <c:v>46283.95833333334</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46283.75</c:v>
+                  <c:v>46284.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>46283.875</c:v>
+                  <c:v>46284.20833333334</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>46284</c:v>
+                  <c:v>46284.33333333334</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>46284.125</c:v>
+                  <c:v>46284.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>46284.25</c:v>
+                  <c:v>46284.58333333334</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>46284.375</c:v>
+                  <c:v>46284.70833333334</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>46284.5</c:v>
+                  <c:v>46284.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>46284.625</c:v>
+                  <c:v>46284.95833333334</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>46284.75</c:v>
+                  <c:v>46285.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>46284.875</c:v>
+                  <c:v>46285.20833333334</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3885,79 +4011,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>14.6</c:v>
+                  <c:v>15.43</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>14.41</c:v>
+                  <c:v>15.27</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>14.34</c:v>
+                  <c:v>15.35</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>15.18</c:v>
+                  <c:v>15.02</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>15.14</c:v>
+                  <c:v>13.17</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>15.15</c:v>
+                  <c:v>10.62</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>14.28</c:v>
+                  <c:v>8.300000000000001</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>12.11</c:v>
+                  <c:v>6.71</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9.57</c:v>
+                  <c:v>7.44</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>9.35</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11.73</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>13.81</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>14.69</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>13.95</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>11.92</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>9.5</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>7.48</c:v>
                 </c:pt>
-                <c:pt idx="10">
-                  <c:v>6.38</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>7.83</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>9.960000000000001</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>12.36</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>14.14</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>14.5</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>13.26</c:v>
-                </c:pt>
                 <c:pt idx="17">
-                  <c:v>11.01</c:v>
+                  <c:v>6.18</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>8.66</c:v>
+                  <c:v>5.51</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>6.88</c:v>
+                  <c:v>5.23</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>5.82</c:v>
+                  <c:v>5.14</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>5.32</c:v>
+                  <c:v>5.11</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>5.13</c:v>
+                  <c:v>5.11</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>5.05</c:v>
+                  <c:v>5.11</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>5.05</c:v>
+                  <c:v>5.11</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4086,79 +4212,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>46281.875</c:v>
+                  <c:v>46282.20833333334</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>46282</c:v>
+                  <c:v>46282.33333333334</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46282.125</c:v>
+                  <c:v>46282.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46282.25</c:v>
+                  <c:v>46282.58333333334</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46282.375</c:v>
+                  <c:v>46282.70833333334</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46282.5</c:v>
+                  <c:v>46282.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46282.625</c:v>
+                  <c:v>46282.95833333334</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>46282.75</c:v>
+                  <c:v>46283.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>46282.875</c:v>
+                  <c:v>46283.20833333334</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>46283</c:v>
+                  <c:v>46283.33333333334</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>46283.125</c:v>
+                  <c:v>46283.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>46283.25</c:v>
+                  <c:v>46283.58333333334</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>46283.375</c:v>
+                  <c:v>46283.70833333334</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>46283.5</c:v>
+                  <c:v>46283.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>46283.625</c:v>
+                  <c:v>46283.95833333334</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46283.75</c:v>
+                  <c:v>46284.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>46283.875</c:v>
+                  <c:v>46284.20833333334</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>46284</c:v>
+                  <c:v>46284.33333333334</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>46284.125</c:v>
+                  <c:v>46284.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>46284.25</c:v>
+                  <c:v>46284.58333333334</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>46284.375</c:v>
+                  <c:v>46284.70833333334</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>46284.5</c:v>
+                  <c:v>46284.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>46284.625</c:v>
+                  <c:v>46284.95833333334</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>46284.75</c:v>
+                  <c:v>46285.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>46284.875</c:v>
+                  <c:v>46285.20833333334</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4170,79 +4296,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>57.3</c:v>
+                  <c:v>62.8</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>57.9</c:v>
+                  <c:v>63.4</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>58.8</c:v>
+                  <c:v>64.8</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>63.2</c:v>
+                  <c:v>64.59999999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>64.09999999999999</c:v>
+                  <c:v>58.5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>65.2</c:v>
+                  <c:v>49.8</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>62.8</c:v>
+                  <c:v>41.8</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>55.5</c:v>
+                  <c:v>36.5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>46.6</c:v>
+                  <c:v>40.1</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>39.5</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>36</c:v>
+                  <c:v>57.7</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>42.2</c:v>
+                  <c:v>66.2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>51</c:v>
+                  <c:v>70.09999999999999</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>60.6</c:v>
+                  <c:v>67.7</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>68</c:v>
+                  <c:v>60.5</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>69.8</c:v>
+                  <c:v>51.8</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>65.59999999999999</c:v>
+                  <c:v>44.5</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>57.5</c:v>
+                  <c:v>39.9</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>48.9</c:v>
+                  <c:v>37.7</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>42.5</c:v>
+                  <c:v>36.9</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>38.6</c:v>
+                  <c:v>36.7</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>36.7</c:v>
+                  <c:v>36.6</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>36</c:v>
+                  <c:v>36.6</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>35.7</c:v>
+                  <c:v>36.6</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>35.7</c:v>
+                  <c:v>36.6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4898,7 +5024,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="5">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>25</v>
@@ -4907,16 +5033,16 @@
         <v>24</v>
       </c>
       <c r="F9" s="5">
-        <v>48.483</v>
+        <v>59.571</v>
       </c>
       <c r="G9" s="5">
-        <v>47.4</v>
+        <v>55.268</v>
       </c>
       <c r="H9" s="5">
-        <v>70.8</v>
+        <v>54.2</v>
       </c>
       <c r="I9" s="5">
-        <v>83.3</v>
+        <v>66.7</v>
       </c>
       <c r="J9" s="5" t="s">
         <v>26</v>
@@ -4927,25 +5053,25 @@
         <v>10</v>
       </c>
       <c r="B10" s="5">
-        <v>3271</v>
+        <v>3789</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>27</v>
       </c>
       <c r="E10" s="5">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="F10" s="5">
-        <v>66.477</v>
+        <v>59.281</v>
       </c>
       <c r="G10" s="5">
-        <v>57.005</v>
+        <v>38.641</v>
       </c>
       <c r="H10" s="5">
-        <v>54.3</v>
+        <v>53.5</v>
       </c>
       <c r="I10" s="5">
-        <v>74.3</v>
+        <v>69.8</v>
       </c>
       <c r="J10" s="5" t="s">
         <v>26</v>
@@ -4956,25 +5082,25 @@
         <v>11</v>
       </c>
       <c r="B11" s="5">
-        <v>3259</v>
+        <v>3779</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>28</v>
       </c>
       <c r="E11" s="5">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="F11" s="5">
-        <v>66.477</v>
+        <v>59.281</v>
       </c>
       <c r="G11" s="5">
-        <v>57.005</v>
+        <v>38.641</v>
       </c>
       <c r="H11" s="5">
-        <v>54.3</v>
+        <v>53.5</v>
       </c>
       <c r="I11" s="5">
-        <v>74.3</v>
+        <v>69.8</v>
       </c>
       <c r="J11" s="5" t="s">
         <v>26</v>
@@ -5064,7 +5190,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="5">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -5077,7 +5203,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.7109375" customWidth="1"/>
@@ -5276,10 +5402,10 @@
         <v>46280.875</v>
       </c>
       <c r="B12" s="5">
-        <v>464.39</v>
+        <v>466.75</v>
       </c>
       <c r="C12" s="5">
-        <v>3.91</v>
+        <v>3.535</v>
       </c>
       <c r="D12" s="5">
         <v>0.44</v>
@@ -5293,10 +5419,10 @@
         <v>46280.91666666666</v>
       </c>
       <c r="B13" s="5">
-        <v>446.05</v>
+        <v>447.15</v>
       </c>
       <c r="C13" s="5">
-        <v>7.54</v>
+        <v>8.255000000000001</v>
       </c>
       <c r="D13" s="5">
         <v>-2.73</v>
@@ -5310,16 +5436,16 @@
         <v>46280.95833333334</v>
       </c>
       <c r="B14" s="5">
-        <v>462.23</v>
+        <v>464.55</v>
       </c>
       <c r="C14" s="5">
         <v>9.300000000000001</v>
       </c>
       <c r="D14" s="5">
-        <v>-4.73</v>
+        <v>-4.83</v>
       </c>
       <c r="E14" s="5">
-        <v>10.94</v>
+        <v>10.98</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -5327,16 +5453,16 @@
         <v>46281</v>
       </c>
       <c r="B15" s="5">
-        <v>517.345</v>
+        <v>516.58</v>
       </c>
       <c r="C15" s="5">
-        <v>20.685</v>
+        <v>21.725</v>
       </c>
       <c r="D15" s="5">
-        <v>1.87</v>
+        <v>1.59</v>
       </c>
       <c r="E15" s="5">
-        <v>12.745</v>
+        <v>12.84</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -5344,16 +5470,16 @@
         <v>46281.04166666666</v>
       </c>
       <c r="B16" s="5">
-        <v>522.005</v>
+        <v>522.625</v>
       </c>
       <c r="C16" s="5">
-        <v>13.335</v>
+        <v>13.445</v>
       </c>
       <c r="D16" s="5">
         <v>5.7</v>
       </c>
       <c r="E16" s="5">
-        <v>10.875</v>
+        <v>10.92</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -5361,16 +5487,16 @@
         <v>46281.08333333334</v>
       </c>
       <c r="B17" s="5">
-        <v>527.735</v>
+        <v>528.05</v>
       </c>
       <c r="C17" s="5">
-        <v>8.984999999999999</v>
+        <v>8.805</v>
       </c>
       <c r="D17" s="5">
-        <v>3.645</v>
+        <v>3.74</v>
       </c>
       <c r="E17" s="5">
-        <v>10.335</v>
+        <v>10.315</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -5378,16 +5504,16 @@
         <v>46281.125</v>
       </c>
       <c r="B18" s="5">
-        <v>531.665</v>
+        <v>532.165</v>
       </c>
       <c r="C18" s="5">
-        <v>6.48</v>
+        <v>6.305</v>
       </c>
       <c r="D18" s="5">
-        <v>0.195</v>
+        <v>0.465</v>
       </c>
       <c r="E18" s="5">
-        <v>6.895</v>
+        <v>6.915</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -5398,13 +5524,13 @@
         <v>537.3200000000001</v>
       </c>
       <c r="C19" s="5">
-        <v>5.49</v>
+        <v>5.47</v>
       </c>
       <c r="D19" s="5">
-        <v>-0.465</v>
+        <v>-0.47</v>
       </c>
       <c r="E19" s="5">
-        <v>7.055</v>
+        <v>7.045</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -5412,16 +5538,16 @@
         <v>46281.20833333334</v>
       </c>
       <c r="B20" s="5">
-        <v>536.5</v>
+        <v>535.985</v>
       </c>
       <c r="C20" s="5">
-        <v>5.47</v>
+        <v>5.49</v>
       </c>
       <c r="D20" s="5">
-        <v>2.175</v>
+        <v>2</v>
       </c>
       <c r="E20" s="5">
-        <v>6.81</v>
+        <v>6.825</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -5429,16 +5555,16 @@
         <v>46281.25</v>
       </c>
       <c r="B21" s="5">
-        <v>532.015</v>
+        <v>532.09</v>
       </c>
       <c r="C21" s="5">
-        <v>5.57</v>
+        <v>5.54</v>
       </c>
       <c r="D21" s="5">
-        <v>4.84</v>
+        <v>4.745</v>
       </c>
       <c r="E21" s="5">
-        <v>6.46</v>
+        <v>6.385</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -5446,13 +5572,13 @@
         <v>46281.29166666666</v>
       </c>
       <c r="B22" s="5">
-        <v>521.465</v>
+        <v>522.2</v>
       </c>
       <c r="C22" s="5">
-        <v>5.2</v>
+        <v>5.245</v>
       </c>
       <c r="D22" s="5">
-        <v>3.395</v>
+        <v>3.425</v>
       </c>
       <c r="E22" s="5">
         <v>5.66</v>
@@ -5463,16 +5589,16 @@
         <v>46281.33333333334</v>
       </c>
       <c r="B23" s="5">
-        <v>542.7</v>
+        <v>543.4</v>
       </c>
       <c r="C23" s="5">
-        <v>4.7</v>
+        <v>4.74</v>
       </c>
       <c r="D23" s="5">
-        <v>4.47</v>
+        <v>4.4</v>
       </c>
       <c r="E23" s="5">
-        <v>4.89</v>
+        <v>4.85</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -5480,16 +5606,16 @@
         <v>46281.375</v>
       </c>
       <c r="B24" s="5">
-        <v>539.8</v>
+        <v>540.0549999999999</v>
       </c>
       <c r="C24" s="5">
-        <v>0.61</v>
+        <v>0.66</v>
       </c>
       <c r="D24" s="5">
-        <v>2.71</v>
+        <v>2.555</v>
       </c>
       <c r="E24" s="5">
-        <v>4.67</v>
+        <v>4.63</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -5497,16 +5623,16 @@
         <v>46281.41666666666</v>
       </c>
       <c r="B25" s="5">
-        <v>542.86</v>
+        <v>543.045</v>
       </c>
       <c r="C25" s="5">
-        <v>0.985</v>
+        <v>0.67</v>
       </c>
       <c r="D25" s="5">
-        <v>-2.115</v>
+        <v>-2.22</v>
       </c>
       <c r="E25" s="5">
-        <v>4.775</v>
+        <v>4.725</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -5514,16 +5640,16 @@
         <v>46281.45833333334</v>
       </c>
       <c r="B26" s="5">
-        <v>537.5</v>
+        <v>537.45</v>
       </c>
       <c r="C26" s="5">
-        <v>0.33</v>
+        <v>0.235</v>
       </c>
       <c r="D26" s="5">
-        <v>-2.31</v>
+        <v>-2.32</v>
       </c>
       <c r="E26" s="5">
-        <v>4.285</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -5531,16 +5657,16 @@
         <v>46281.5</v>
       </c>
       <c r="B27" s="5">
-        <v>549.295</v>
+        <v>549.265</v>
       </c>
       <c r="C27" s="5">
-        <v>0.1</v>
+        <v>0.105</v>
       </c>
       <c r="D27" s="5">
-        <v>0.825</v>
+        <v>1.005</v>
       </c>
       <c r="E27" s="5">
-        <v>4.505</v>
+        <v>4.31</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -5548,16 +5674,16 @@
         <v>46281.54166666666</v>
       </c>
       <c r="B28" s="5">
-        <v>562.86</v>
+        <v>565.405</v>
       </c>
       <c r="C28" s="5">
-        <v>0.05</v>
+        <v>0.045</v>
       </c>
       <c r="D28" s="5">
-        <v>2.8</v>
+        <v>2.875</v>
       </c>
       <c r="E28" s="5">
-        <v>4.875</v>
+        <v>5.015</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -5565,16 +5691,16 @@
         <v>46281.58333333334</v>
       </c>
       <c r="B29" s="5">
-        <v>545.145</v>
+        <v>545.5</v>
       </c>
       <c r="C29" s="5">
-        <v>0.08</v>
+        <v>0.075</v>
       </c>
       <c r="D29" s="5">
-        <v>4.75</v>
+        <v>4.755</v>
       </c>
       <c r="E29" s="5">
-        <v>5.5</v>
+        <v>5.44</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -5582,13 +5708,13 @@
         <v>46281.625</v>
       </c>
       <c r="B30" s="5">
-        <v>534.22</v>
+        <v>533.515</v>
       </c>
       <c r="C30" s="5">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="D30" s="5">
-        <v>3.97</v>
+        <v>4.2</v>
       </c>
       <c r="E30" s="5">
         <v>5.77</v>
@@ -5602,13 +5728,13 @@
         <v>524.6</v>
       </c>
       <c r="C31" s="5">
-        <v>0.17</v>
+        <v>0.145</v>
       </c>
       <c r="D31" s="5">
-        <v>4.115</v>
+        <v>4.08</v>
       </c>
       <c r="E31" s="5">
-        <v>5.645</v>
+        <v>5.615</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -5622,10 +5748,10 @@
         <v>0.2</v>
       </c>
       <c r="D32" s="5">
-        <v>4.095</v>
+        <v>4.125</v>
       </c>
       <c r="E32" s="5">
-        <v>5.645</v>
+        <v>5.63</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -5633,16 +5759,16 @@
         <v>46281.75</v>
       </c>
       <c r="B33" s="5">
-        <v>524</v>
+        <v>527.46</v>
       </c>
       <c r="C33" s="5">
         <v>2.55</v>
       </c>
       <c r="D33" s="5">
-        <v>3.035</v>
+        <v>3.02</v>
       </c>
       <c r="E33" s="5">
-        <v>5.44</v>
+        <v>5.435</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -5650,16 +5776,16 @@
         <v>46281.79166666666</v>
       </c>
       <c r="B34" s="5">
-        <v>501.43</v>
+        <v>501.03</v>
       </c>
       <c r="C34" s="5">
-        <v>3.785</v>
+        <v>3.77</v>
       </c>
       <c r="D34" s="5">
-        <v>2.18</v>
+        <v>2.185</v>
       </c>
       <c r="E34" s="5">
-        <v>4.7</v>
+        <v>4.685</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -5667,16 +5793,16 @@
         <v>46281.83333333334</v>
       </c>
       <c r="B35" s="5">
-        <v>509.7</v>
+        <v>509.36</v>
       </c>
       <c r="C35" s="5">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="D35" s="5">
-        <v>0.58</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="E35" s="5">
-        <v>5.05</v>
+        <v>5.025</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -5684,16 +5810,135 @@
         <v>46281.875</v>
       </c>
       <c r="B36" s="5">
-        <v>504.155</v>
+        <v>502.035</v>
       </c>
       <c r="C36" s="5">
-        <v>3.02</v>
+        <v>2.975</v>
       </c>
       <c r="D36" s="5">
-        <v>2.395</v>
+        <v>1.945</v>
       </c>
       <c r="E36" s="5">
-        <v>4.9</v>
+        <v>4.855</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6">
+        <v>46281.91666666666</v>
+      </c>
+      <c r="B37" s="5">
+        <v>514.4</v>
+      </c>
+      <c r="C37" s="5">
+        <v>2.72</v>
+      </c>
+      <c r="D37" s="5">
+        <v>2.22</v>
+      </c>
+      <c r="E37" s="5">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6">
+        <v>46281.95833333334</v>
+      </c>
+      <c r="B38" s="5">
+        <v>508.32</v>
+      </c>
+      <c r="C38" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="D38" s="5">
+        <v>2.375</v>
+      </c>
+      <c r="E38" s="5">
+        <v>4.84</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6">
+        <v>46282</v>
+      </c>
+      <c r="B39" s="5">
+        <v>501.225</v>
+      </c>
+      <c r="C39" s="5">
+        <v>0.875</v>
+      </c>
+      <c r="D39" s="5">
+        <v>0.18</v>
+      </c>
+      <c r="E39" s="5">
+        <v>5.13</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6">
+        <v>46282.04166666666</v>
+      </c>
+      <c r="B40" s="5">
+        <v>505.91</v>
+      </c>
+      <c r="C40" s="5">
+        <v>1.11</v>
+      </c>
+      <c r="D40" s="5">
+        <v>-0.5</v>
+      </c>
+      <c r="E40" s="5">
+        <v>5.87</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6">
+        <v>46282.08333333334</v>
+      </c>
+      <c r="B41" s="5">
+        <v>548.45</v>
+      </c>
+      <c r="C41" s="5">
+        <v>2.05</v>
+      </c>
+      <c r="D41" s="5">
+        <v>2.93</v>
+      </c>
+      <c r="E41" s="5">
+        <v>7.24</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6">
+        <v>46282.125</v>
+      </c>
+      <c r="B42" s="5">
+        <v>516.71</v>
+      </c>
+      <c r="C42" s="5">
+        <v>1.43</v>
+      </c>
+      <c r="D42" s="5">
+        <v>2.795</v>
+      </c>
+      <c r="E42" s="5">
+        <v>6.205</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6">
+        <v>46282.16666666666</v>
+      </c>
+      <c r="B43" s="5">
+        <v>506.93</v>
+      </c>
+      <c r="C43" s="5">
+        <v>1.23</v>
+      </c>
+      <c r="D43" s="5">
+        <v>2</v>
+      </c>
+      <c r="E43" s="5">
+        <v>5.91</v>
       </c>
     </row>
   </sheetData>
@@ -5737,19 +5982,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="6">
-        <v>46281.75</v>
+        <v>46282.08333333334</v>
       </c>
       <c r="B2" s="5">
-        <v>604.42</v>
+        <v>634.0700000000001</v>
       </c>
       <c r="C2" s="5">
-        <v>377.68</v>
+        <v>330.02</v>
       </c>
       <c r="D2" s="5">
-        <v>531.42</v>
+        <v>546.05</v>
       </c>
       <c r="E2" s="5">
-        <v>299.12</v>
+        <v>397.08</v>
       </c>
       <c r="F2" s="5"/>
       <c r="G2" s="5" t="s">
@@ -5758,19 +6003,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="6">
-        <v>46281.79166666666</v>
+        <v>46282.125</v>
       </c>
       <c r="B3" s="5">
-        <v>623.3200000000001</v>
+        <v>639.17</v>
       </c>
       <c r="C3" s="5">
-        <v>373.72</v>
+        <v>331.46</v>
       </c>
       <c r="D3" s="5">
-        <v>505.04</v>
+        <v>537.7</v>
       </c>
       <c r="E3" s="5">
-        <v>329.26</v>
+        <v>401.85</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5" t="s">
@@ -5779,19 +6024,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="6">
-        <v>46281.83333333334</v>
+        <v>46282.16666666666</v>
       </c>
       <c r="B4" s="5">
-        <v>636.67</v>
+        <v>637.21</v>
       </c>
       <c r="C4" s="5">
-        <v>364.8</v>
+        <v>334.59</v>
       </c>
       <c r="D4" s="5">
-        <v>505.5</v>
+        <v>509.66</v>
       </c>
       <c r="E4" s="5">
-        <v>358.66</v>
+        <v>395.22</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="5" t="s">
@@ -5800,19 +6045,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="6">
-        <v>46281.875</v>
+        <v>46282.20833333334</v>
       </c>
       <c r="B5" s="5">
-        <v>649.9400000000001</v>
+        <v>645.63</v>
       </c>
       <c r="C5" s="5">
-        <v>359.37</v>
+        <v>334.76</v>
       </c>
       <c r="D5" s="5">
-        <v>508.88</v>
+        <v>505.05</v>
       </c>
       <c r="E5" s="5">
-        <v>383.33</v>
+        <v>405.99</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5" t="s">
@@ -5821,17 +6066,17 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="6">
-        <v>46281.91666666666</v>
+        <v>46282.25</v>
       </c>
       <c r="B6" s="5">
-        <v>654.25</v>
+        <v>649.3200000000001</v>
       </c>
       <c r="C6" s="5">
-        <v>358.92</v>
+        <v>335.51</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5">
-        <v>399.87</v>
+        <v>416.08</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="5" t="s">
@@ -5840,17 +6085,17 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="6">
-        <v>46281.95833333334</v>
+        <v>46282.29166666666</v>
       </c>
       <c r="B7" s="5">
-        <v>655.86</v>
+        <v>654.54</v>
       </c>
       <c r="C7" s="5">
-        <v>357.83</v>
+        <v>337.8</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5">
-        <v>399</v>
+        <v>419.92</v>
       </c>
       <c r="F7" s="5"/>
       <c r="G7" s="5" t="s">
@@ -5859,17 +6104,17 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="6">
-        <v>46282</v>
+        <v>46282.33333333334</v>
       </c>
       <c r="B8" s="5">
-        <v>655.39</v>
+        <v>654.64</v>
       </c>
       <c r="C8" s="5">
-        <v>356.4</v>
+        <v>340.04</v>
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="5">
-        <v>396.46</v>
+        <v>406.26</v>
       </c>
       <c r="F8" s="5"/>
       <c r="G8" s="5" t="s">
@@ -5878,17 +6123,17 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="6">
-        <v>46282.04166666666</v>
+        <v>46282.375</v>
       </c>
       <c r="B9" s="5">
-        <v>653.39</v>
+        <v>651.98</v>
       </c>
       <c r="C9" s="5">
-        <v>354.54</v>
+        <v>338.38</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="5">
-        <v>393.96</v>
+        <v>407.43</v>
       </c>
       <c r="F9" s="5"/>
       <c r="G9" s="5" t="s">
@@ -5897,17 +6142,17 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="6">
-        <v>46282.08333333334</v>
+        <v>46282.41666666666</v>
       </c>
       <c r="B10" s="5">
-        <v>651.72</v>
+        <v>647.08</v>
       </c>
       <c r="C10" s="5">
-        <v>353.87</v>
+        <v>336.15</v>
       </c>
       <c r="D10" s="5"/>
       <c r="E10" s="5">
-        <v>390.75</v>
+        <v>400.35</v>
       </c>
       <c r="F10" s="5"/>
       <c r="G10" s="5" t="s">
@@ -5916,17 +6161,17 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="6">
-        <v>46282.125</v>
+        <v>46282.45833333334</v>
       </c>
       <c r="B11" s="5">
-        <v>649.52</v>
+        <v>642.08</v>
       </c>
       <c r="C11" s="5">
-        <v>351.96</v>
+        <v>336.6</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="5">
-        <v>391.92</v>
+        <v>387.33</v>
       </c>
       <c r="F11" s="5"/>
       <c r="G11" s="5" t="s">
@@ -5935,17 +6180,17 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="6">
-        <v>46282.16666666666</v>
+        <v>46282.5</v>
       </c>
       <c r="B12" s="5">
-        <v>645.62</v>
+        <v>634.4</v>
       </c>
       <c r="C12" s="5">
-        <v>352.66</v>
+        <v>337.09</v>
       </c>
       <c r="D12" s="5"/>
       <c r="E12" s="5">
-        <v>376.61</v>
+        <v>370.86</v>
       </c>
       <c r="F12" s="5"/>
       <c r="G12" s="5" t="s">
@@ -5954,17 +6199,17 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="6">
-        <v>46282.20833333334</v>
+        <v>46282.54166666666</v>
       </c>
       <c r="B13" s="5">
-        <v>644.9299999999999</v>
+        <v>622.72</v>
       </c>
       <c r="C13" s="5">
-        <v>352.7</v>
+        <v>337.43</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="5">
-        <v>383.92</v>
+        <v>346.95</v>
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="5" t="s">
@@ -5973,17 +6218,17 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="6">
-        <v>46282.25</v>
+        <v>46282.58333333334</v>
       </c>
       <c r="B14" s="5">
-        <v>646.13</v>
+        <v>609</v>
       </c>
       <c r="C14" s="5">
-        <v>352.36</v>
+        <v>337.68</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="5">
-        <v>390.85</v>
+        <v>324.57</v>
       </c>
       <c r="F14" s="5"/>
       <c r="G14" s="5" t="s">
@@ -5992,17 +6237,17 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="6">
-        <v>46282.29166666666</v>
+        <v>46282.625</v>
       </c>
       <c r="B15" s="5">
-        <v>647.36</v>
+        <v>594.4400000000001</v>
       </c>
       <c r="C15" s="5">
-        <v>352.14</v>
+        <v>337.88</v>
       </c>
       <c r="D15" s="5"/>
       <c r="E15" s="5">
-        <v>392.57</v>
+        <v>303.64</v>
       </c>
       <c r="F15" s="5"/>
       <c r="G15" s="5" t="s">
@@ -6011,17 +6256,17 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="6">
-        <v>46282.33333333334</v>
+        <v>46282.66666666666</v>
       </c>
       <c r="B16" s="5">
-        <v>643.6900000000001</v>
+        <v>579.76</v>
       </c>
       <c r="C16" s="5">
-        <v>352.02</v>
+        <v>338.03</v>
       </c>
       <c r="D16" s="5"/>
       <c r="E16" s="5">
-        <v>377.15</v>
+        <v>284.06</v>
       </c>
       <c r="F16" s="5"/>
       <c r="G16" s="5" t="s">
@@ -6030,17 +6275,17 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="6">
-        <v>46282.375</v>
+        <v>46282.70833333334</v>
       </c>
       <c r="B17" s="5">
-        <v>641.37</v>
+        <v>565.35</v>
       </c>
       <c r="C17" s="5">
-        <v>351.97</v>
+        <v>338.16</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="5">
-        <v>376.88</v>
+        <v>265.74</v>
       </c>
       <c r="F17" s="5"/>
       <c r="G17" s="5" t="s">
@@ -6049,17 +6294,17 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="6">
-        <v>46282.41666666666</v>
+        <v>46282.75</v>
       </c>
       <c r="B18" s="5">
-        <v>637.99</v>
+        <v>551.4400000000001</v>
       </c>
       <c r="C18" s="5">
-        <v>352.13</v>
+        <v>338.24</v>
       </c>
       <c r="D18" s="5"/>
       <c r="E18" s="5">
-        <v>369.49</v>
+        <v>248.6</v>
       </c>
       <c r="F18" s="5"/>
       <c r="G18" s="5" t="s">
@@ -6068,17 +6313,17 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="6">
-        <v>46282.45833333334</v>
+        <v>46282.79166666666</v>
       </c>
       <c r="B19" s="5">
-        <v>632.58</v>
+        <v>538.02</v>
       </c>
       <c r="C19" s="5">
-        <v>352.53</v>
+        <v>338.17</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="5">
-        <v>356.95</v>
+        <v>232.57</v>
       </c>
       <c r="F19" s="5"/>
       <c r="G19" s="5" t="s">
@@ -6087,17 +6332,17 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="6">
-        <v>46282.5</v>
+        <v>46282.83333333334</v>
       </c>
       <c r="B20" s="5">
-        <v>625.0599999999999</v>
+        <v>523.51</v>
       </c>
       <c r="C20" s="5">
-        <v>353.07</v>
+        <v>338.01</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="5">
-        <v>341.44</v>
+        <v>211.68</v>
       </c>
       <c r="F20" s="5"/>
       <c r="G20" s="5" t="s">
@@ -6106,17 +6351,17 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="6">
-        <v>46282.54166666666</v>
+        <v>46282.875</v>
       </c>
       <c r="B21" s="5">
-        <v>614.1799999999999</v>
+        <v>510.41</v>
       </c>
       <c r="C21" s="5">
-        <v>353.54</v>
+        <v>337.78</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5">
-        <v>319.42</v>
+        <v>198.02</v>
       </c>
       <c r="F21" s="5"/>
       <c r="G21" s="5" t="s">
@@ -6125,17 +6370,17 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="6">
-        <v>46282.58333333334</v>
+        <v>46282.91666666666</v>
       </c>
       <c r="B22" s="5">
-        <v>601.63</v>
+        <v>498.46</v>
       </c>
       <c r="C22" s="5">
-        <v>353.96</v>
+        <v>337.53</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="5">
-        <v>298.82</v>
+        <v>185.25</v>
       </c>
       <c r="F22" s="5"/>
       <c r="G22" s="5" t="s">
@@ -6144,17 +6389,17 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="6">
-        <v>46282.625</v>
+        <v>46282.95833333334</v>
       </c>
       <c r="B23" s="5">
-        <v>588.42</v>
+        <v>487.46</v>
       </c>
       <c r="C23" s="5">
-        <v>354.33</v>
+        <v>337.25</v>
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="5">
-        <v>279.55</v>
+        <v>173.31</v>
       </c>
       <c r="F23" s="5"/>
       <c r="G23" s="5" t="s">
@@ -6163,17 +6408,17 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="6">
-        <v>46282.66666666666</v>
+        <v>46283</v>
       </c>
       <c r="B24" s="5">
-        <v>575.15</v>
+        <v>477.28</v>
       </c>
       <c r="C24" s="5">
-        <v>354.69</v>
+        <v>336.96</v>
       </c>
       <c r="D24" s="5"/>
       <c r="E24" s="5">
-        <v>261.52</v>
+        <v>162.17</v>
       </c>
       <c r="F24" s="5"/>
       <c r="G24" s="5" t="s">
@@ -6182,17 +6427,17 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="6">
-        <v>46282.70833333334</v>
+        <v>46283.04166666666</v>
       </c>
       <c r="B25" s="5">
-        <v>562.1799999999999</v>
+        <v>466.91</v>
       </c>
       <c r="C25" s="5">
-        <v>355.02</v>
+        <v>337.6</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="5">
-        <v>244.65</v>
+        <v>145.44</v>
       </c>
       <c r="F25" s="5"/>
       <c r="G25" s="5" t="s">
@@ -6201,17 +6446,17 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="6">
-        <v>46282.75</v>
+        <v>46283.08333333334</v>
       </c>
       <c r="B26" s="5">
-        <v>549.7</v>
+        <v>458.63</v>
       </c>
       <c r="C26" s="5">
-        <v>355.33</v>
+        <v>338.82</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5">
-        <v>228.88</v>
+        <v>136.22</v>
       </c>
       <c r="F26" s="5"/>
       <c r="G26" s="5" t="s">
@@ -6220,17 +6465,17 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="6">
-        <v>46282.79166666666</v>
+        <v>46283.125</v>
       </c>
       <c r="B27" s="5">
-        <v>537.6900000000001</v>
+        <v>451.86</v>
       </c>
       <c r="C27" s="5">
-        <v>355.51</v>
+        <v>340.39</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="5">
-        <v>214.11</v>
+        <v>127.8</v>
       </c>
       <c r="F27" s="5"/>
       <c r="G27" s="5" t="s">
@@ -6239,17 +6484,17 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="6">
-        <v>46282.83333333334</v>
+        <v>46283.16666666666</v>
       </c>
       <c r="B28" s="5">
-        <v>524.95</v>
+        <v>446.3</v>
       </c>
       <c r="C28" s="5">
-        <v>355.6</v>
+        <v>342.19</v>
       </c>
       <c r="D28" s="5"/>
       <c r="E28" s="5">
-        <v>195.77</v>
+        <v>120.29</v>
       </c>
       <c r="F28" s="5"/>
       <c r="G28" s="5" t="s">
@@ -6258,17 +6503,17 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="6">
-        <v>46282.875</v>
+        <v>46283.20833333334</v>
       </c>
       <c r="B29" s="5">
-        <v>513.38</v>
+        <v>441.83</v>
       </c>
       <c r="C29" s="5">
-        <v>355.64</v>
+        <v>344.12</v>
       </c>
       <c r="D29" s="5"/>
       <c r="E29" s="5">
-        <v>183.14</v>
+        <v>113.95</v>
       </c>
       <c r="F29" s="5"/>
       <c r="G29" s="5" t="s">
@@ -6277,17 +6522,17 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="6">
-        <v>46282.91666666666</v>
+        <v>46283.25</v>
       </c>
       <c r="B30" s="5">
-        <v>502.79</v>
+        <v>438.49</v>
       </c>
       <c r="C30" s="5">
-        <v>355.63</v>
+        <v>346.14</v>
       </c>
       <c r="D30" s="5"/>
       <c r="E30" s="5">
-        <v>171.33</v>
+        <v>109.19</v>
       </c>
       <c r="F30" s="5"/>
       <c r="G30" s="5" t="s">
@@ -6296,17 +6541,17 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="6">
-        <v>46282.95833333334</v>
+        <v>46283.29166666666</v>
       </c>
       <c r="B31" s="5">
-        <v>493</v>
+        <v>435.58</v>
       </c>
       <c r="C31" s="5">
-        <v>355.6</v>
+        <v>347.31</v>
       </c>
       <c r="D31" s="5"/>
       <c r="E31" s="5">
-        <v>160.28</v>
+        <v>106.56</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="5" t="s">
@@ -6315,17 +6560,17 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="6">
-        <v>46283</v>
+        <v>46283.33333333334</v>
       </c>
       <c r="B32" s="5">
-        <v>483.95</v>
+        <v>433.75</v>
       </c>
       <c r="C32" s="5">
-        <v>355.54</v>
+        <v>347.95</v>
       </c>
       <c r="D32" s="5"/>
       <c r="E32" s="5">
-        <v>150</v>
+        <v>106.78</v>
       </c>
       <c r="F32" s="5"/>
       <c r="G32" s="5" t="s">
@@ -6334,17 +6579,17 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="6">
-        <v>46283.04166666666</v>
+        <v>46283.375</v>
       </c>
       <c r="B33" s="5">
-        <v>474.98</v>
+        <v>433.64</v>
       </c>
       <c r="C33" s="5">
-        <v>356.4</v>
+        <v>348.27</v>
       </c>
       <c r="D33" s="5"/>
       <c r="E33" s="5">
-        <v>135.26</v>
+        <v>110.58</v>
       </c>
       <c r="F33" s="5"/>
       <c r="G33" s="5" t="s">
@@ -6353,17 +6598,17 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="6">
-        <v>46283.08333333334</v>
+        <v>46283.41666666666</v>
       </c>
       <c r="B34" s="5">
-        <v>467.85</v>
+        <v>435.8</v>
       </c>
       <c r="C34" s="5">
-        <v>357.83</v>
+        <v>348.38</v>
       </c>
       <c r="D34" s="5"/>
       <c r="E34" s="5">
-        <v>126.76</v>
+        <v>118.53</v>
       </c>
       <c r="F34" s="5"/>
       <c r="G34" s="5" t="s">
@@ -6372,17 +6617,17 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="6">
-        <v>46283.125</v>
+        <v>46283.45833333334</v>
       </c>
       <c r="B35" s="5">
-        <v>462.11</v>
+        <v>436.65</v>
       </c>
       <c r="C35" s="5">
-        <v>359.59</v>
+        <v>348.36</v>
       </c>
       <c r="D35" s="5"/>
       <c r="E35" s="5">
-        <v>119.06</v>
+        <v>117.16</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="5" t="s">
@@ -6391,17 +6636,17 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="6">
-        <v>46283.16666666666</v>
+        <v>46283.5</v>
       </c>
       <c r="B36" s="5">
-        <v>457.5</v>
+        <v>442</v>
       </c>
       <c r="C36" s="5">
-        <v>361.57</v>
+        <v>348.27</v>
       </c>
       <c r="D36" s="5"/>
       <c r="E36" s="5">
-        <v>112.36</v>
+        <v>133.98</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="5" t="s">
@@ -6410,17 +6655,17 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="6">
-        <v>46283.20833333334</v>
+        <v>46283.54166666666</v>
       </c>
       <c r="B37" s="5">
-        <v>453.98</v>
+        <v>447.9</v>
       </c>
       <c r="C37" s="5">
-        <v>363.68</v>
+        <v>348.14</v>
       </c>
       <c r="D37" s="5"/>
       <c r="E37" s="5">
-        <v>107.01</v>
+        <v>143.13</v>
       </c>
       <c r="F37" s="5"/>
       <c r="G37" s="5" t="s">
@@ -6429,17 +6674,17 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="6">
-        <v>46283.25</v>
+        <v>46283.58333333334</v>
       </c>
       <c r="B38" s="5">
-        <v>451.68</v>
+        <v>457.2</v>
       </c>
       <c r="C38" s="5">
-        <v>365.87</v>
+        <v>347.98</v>
       </c>
       <c r="D38" s="5"/>
       <c r="E38" s="5">
-        <v>103.54</v>
+        <v>162.81</v>
       </c>
       <c r="F38" s="5"/>
       <c r="G38" s="5" t="s">
@@ -6448,17 +6693,17 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="6">
-        <v>46283.29166666666</v>
+        <v>46283.625</v>
       </c>
       <c r="B39" s="5">
-        <v>450</v>
+        <v>467.79</v>
       </c>
       <c r="C39" s="5">
-        <v>367.21</v>
+        <v>347.8</v>
       </c>
       <c r="D39" s="5"/>
       <c r="E39" s="5">
-        <v>102.74</v>
+        <v>179.66</v>
       </c>
       <c r="F39" s="5"/>
       <c r="G39" s="5" t="s">
@@ -6467,17 +6712,17 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="6">
-        <v>46283.33333333334</v>
+        <v>46283.66666666666</v>
       </c>
       <c r="B40" s="5">
-        <v>449.75</v>
+        <v>477.56</v>
       </c>
       <c r="C40" s="5">
-        <v>368.01</v>
+        <v>347.61</v>
       </c>
       <c r="D40" s="5"/>
       <c r="E40" s="5">
-        <v>105.55</v>
+        <v>190.92</v>
       </c>
       <c r="F40" s="5"/>
       <c r="G40" s="5" t="s">
@@ -6486,17 +6731,17 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="6">
-        <v>46283.375</v>
+        <v>46283.70833333334</v>
       </c>
       <c r="B41" s="5">
-        <v>451.7</v>
+        <v>484.56</v>
       </c>
       <c r="C41" s="5">
-        <v>368.49</v>
+        <v>347.41</v>
       </c>
       <c r="D41" s="5"/>
       <c r="E41" s="5">
-        <v>112.95</v>
+        <v>194.45</v>
       </c>
       <c r="F41" s="5"/>
       <c r="G41" s="5" t="s">
@@ -6505,17 +6750,17 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="6">
-        <v>46283.41666666666</v>
+        <v>46283.75</v>
       </c>
       <c r="B42" s="5">
-        <v>456.56</v>
+        <v>485.68</v>
       </c>
       <c r="C42" s="5">
-        <v>368.75</v>
+        <v>347.21</v>
       </c>
       <c r="D42" s="5"/>
       <c r="E42" s="5">
-        <v>125.72</v>
+        <v>183.67</v>
       </c>
       <c r="F42" s="5"/>
       <c r="G42" s="5" t="s">
@@ -6524,17 +6769,17 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="6">
-        <v>46283.45833333334</v>
+        <v>46283.79166666666</v>
       </c>
       <c r="B43" s="5">
-        <v>459.6</v>
+        <v>480.71</v>
       </c>
       <c r="C43" s="5">
-        <v>368.89</v>
+        <v>347.01</v>
       </c>
       <c r="D43" s="5"/>
       <c r="E43" s="5">
-        <v>125.91</v>
+        <v>164.44</v>
       </c>
       <c r="F43" s="5"/>
       <c r="G43" s="5" t="s">
@@ -6543,17 +6788,17 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="6">
-        <v>46283.5</v>
+        <v>46283.83333333334</v>
       </c>
       <c r="B44" s="5">
-        <v>468.45</v>
+        <v>474.46</v>
       </c>
       <c r="C44" s="5">
-        <v>368.95</v>
+        <v>346.8</v>
       </c>
       <c r="D44" s="5"/>
       <c r="E44" s="5">
-        <v>150.21</v>
+        <v>153.84</v>
       </c>
       <c r="F44" s="5"/>
       <c r="G44" s="5" t="s">
@@ -6562,17 +6807,17 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="6">
-        <v>46283.54166666666</v>
+        <v>46283.875</v>
       </c>
       <c r="B45" s="5">
-        <v>479.76</v>
+        <v>467.62</v>
       </c>
       <c r="C45" s="5">
-        <v>368.95</v>
+        <v>346.6</v>
       </c>
       <c r="D45" s="5"/>
       <c r="E45" s="5">
-        <v>170.52</v>
+        <v>143.92</v>
       </c>
       <c r="F45" s="5"/>
       <c r="G45" s="5" t="s">
@@ -6581,17 +6826,17 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="6">
-        <v>46283.58333333334</v>
+        <v>46283.91666666666</v>
       </c>
       <c r="B46" s="5">
-        <v>494.65</v>
+        <v>458.27</v>
       </c>
       <c r="C46" s="5">
-        <v>368.92</v>
+        <v>346.39</v>
       </c>
       <c r="D46" s="5"/>
       <c r="E46" s="5">
-        <v>197.98</v>
+        <v>126.6</v>
       </c>
       <c r="F46" s="5"/>
       <c r="G46" s="5" t="s">
@@ -6600,17 +6845,17 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="6">
-        <v>46283.625</v>
+        <v>46283.95833333334</v>
       </c>
       <c r="B47" s="5">
-        <v>510.65</v>
+        <v>450.01</v>
       </c>
       <c r="C47" s="5">
-        <v>368.87</v>
+        <v>346.19</v>
       </c>
       <c r="D47" s="5"/>
       <c r="E47" s="5">
-        <v>221.58</v>
+        <v>118.44</v>
       </c>
       <c r="F47" s="5"/>
       <c r="G47" s="5" t="s">
@@ -6619,17 +6864,17 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="6">
-        <v>46283.66666666666</v>
+        <v>46284</v>
       </c>
       <c r="B48" s="5">
-        <v>525.17</v>
+        <v>442.59</v>
       </c>
       <c r="C48" s="5">
-        <v>368.81</v>
+        <v>345.98</v>
       </c>
       <c r="D48" s="5"/>
       <c r="E48" s="5">
-        <v>237.67</v>
+        <v>110.8</v>
       </c>
       <c r="F48" s="5"/>
       <c r="G48" s="5" t="s">
@@ -6638,17 +6883,17 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="6">
-        <v>46283.70833333334</v>
+        <v>46284.04166666666</v>
       </c>
       <c r="B49" s="5">
-        <v>535.79</v>
+        <v>433.58</v>
       </c>
       <c r="C49" s="5">
-        <v>368.73</v>
+        <v>345.85</v>
       </c>
       <c r="D49" s="5"/>
       <c r="E49" s="5">
-        <v>243.41</v>
+        <v>95.64</v>
       </c>
       <c r="F49" s="5"/>
       <c r="G49" s="5" t="s">
@@ -6657,17 +6902,17 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="6">
-        <v>46283.75</v>
+        <v>46284.08333333334</v>
       </c>
       <c r="B50" s="5">
-        <v>538.49</v>
+        <v>426.19</v>
       </c>
       <c r="C50" s="5">
-        <v>368.65</v>
+        <v>345.77</v>
       </c>
       <c r="D50" s="5"/>
       <c r="E50" s="5">
-        <v>230.06</v>
+        <v>89.47</v>
       </c>
       <c r="F50" s="5"/>
       <c r="G50" s="5" t="s">
@@ -6676,17 +6921,17 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="6">
-        <v>46283.79166666666</v>
+        <v>46284.125</v>
       </c>
       <c r="B51" s="5">
-        <v>534.03</v>
+        <v>419.93</v>
       </c>
       <c r="C51" s="5">
-        <v>368.55</v>
+        <v>345.71</v>
       </c>
       <c r="D51" s="5"/>
       <c r="E51" s="5">
-        <v>208.88</v>
+        <v>83.7</v>
       </c>
       <c r="F51" s="5"/>
       <c r="G51" s="5" t="s">
@@ -6695,17 +6940,17 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="6">
-        <v>46283.83333333334</v>
+        <v>46284.16666666666</v>
       </c>
       <c r="B52" s="5">
-        <v>527.33</v>
+        <v>414.47</v>
       </c>
       <c r="C52" s="5">
-        <v>368.46</v>
+        <v>345.67</v>
       </c>
       <c r="D52" s="5"/>
       <c r="E52" s="5">
-        <v>195.4</v>
+        <v>78.3</v>
       </c>
       <c r="F52" s="5"/>
       <c r="G52" s="5" t="s">
@@ -6714,17 +6959,17 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="6">
-        <v>46283.875</v>
+        <v>46284.20833333334</v>
       </c>
       <c r="B53" s="5">
-        <v>519.51</v>
+        <v>409.61</v>
       </c>
       <c r="C53" s="5">
-        <v>368.35</v>
+        <v>345.64</v>
       </c>
       <c r="D53" s="5"/>
       <c r="E53" s="5">
-        <v>182.8</v>
+        <v>73.25</v>
       </c>
       <c r="F53" s="5"/>
       <c r="G53" s="5" t="s">
@@ -6733,17 +6978,17 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="6">
-        <v>46283.91666666666</v>
+        <v>46284.25</v>
       </c>
       <c r="B54" s="5">
-        <v>509.2</v>
+        <v>405.22</v>
       </c>
       <c r="C54" s="5">
-        <v>368.24</v>
+        <v>345.62</v>
       </c>
       <c r="D54" s="5"/>
       <c r="E54" s="5">
-        <v>163.99</v>
+        <v>68.53</v>
       </c>
       <c r="F54" s="5"/>
       <c r="G54" s="5" t="s">
@@ -6752,17 +6997,17 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="6">
-        <v>46283.95833333334</v>
+        <v>46284.29166666666</v>
       </c>
       <c r="B55" s="5">
-        <v>499.72</v>
+        <v>401.21</v>
       </c>
       <c r="C55" s="5">
-        <v>368.13</v>
+        <v>345.61</v>
       </c>
       <c r="D55" s="5"/>
       <c r="E55" s="5">
-        <v>153.42</v>
+        <v>64.11</v>
       </c>
       <c r="F55" s="5"/>
       <c r="G55" s="5" t="s">
@@ -6771,17 +7016,17 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="6">
-        <v>46284</v>
+        <v>46284.33333333334</v>
       </c>
       <c r="B56" s="5">
-        <v>490.94</v>
+        <v>397.52</v>
       </c>
       <c r="C56" s="5">
-        <v>368.02</v>
+        <v>345.59</v>
       </c>
       <c r="D56" s="5"/>
       <c r="E56" s="5">
-        <v>143.52</v>
+        <v>59.97</v>
       </c>
       <c r="F56" s="5"/>
       <c r="G56" s="5" t="s">
@@ -6790,17 +7035,17 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="6">
-        <v>46284.04166666666</v>
+        <v>46284.375</v>
       </c>
       <c r="B57" s="5">
-        <v>480.83</v>
+        <v>394.1</v>
       </c>
       <c r="C57" s="5">
-        <v>367.97</v>
+        <v>345.58</v>
       </c>
       <c r="D57" s="5"/>
       <c r="E57" s="5">
-        <v>127.19</v>
+        <v>56.1</v>
       </c>
       <c r="F57" s="5"/>
       <c r="G57" s="5" t="s">
@@ -6809,17 +7054,17 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="6">
-        <v>46284.08333333334</v>
+        <v>46284.41666666666</v>
       </c>
       <c r="B58" s="5">
-        <v>472.21</v>
+        <v>390.93</v>
       </c>
       <c r="C58" s="5">
-        <v>367.97</v>
+        <v>345.57</v>
       </c>
       <c r="D58" s="5"/>
       <c r="E58" s="5">
-        <v>118.99</v>
+        <v>52.49</v>
       </c>
       <c r="F58" s="5"/>
       <c r="G58" s="5" t="s">
@@ -6828,17 +7073,17 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="6">
-        <v>46284.125</v>
+        <v>46284.45833333334</v>
       </c>
       <c r="B59" s="5">
-        <v>464.69</v>
+        <v>387.97</v>
       </c>
       <c r="C59" s="5">
-        <v>367.99</v>
+        <v>345.56</v>
       </c>
       <c r="D59" s="5"/>
       <c r="E59" s="5">
-        <v>111.32</v>
+        <v>49.1</v>
       </c>
       <c r="F59" s="5"/>
       <c r="G59" s="5" t="s">
@@ -6847,17 +7092,17 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="6">
-        <v>46284.16666666666</v>
+        <v>46284.5</v>
       </c>
       <c r="B60" s="5">
-        <v>457.97</v>
+        <v>385.21</v>
       </c>
       <c r="C60" s="5">
-        <v>368.03</v>
+        <v>345.56</v>
       </c>
       <c r="D60" s="5"/>
       <c r="E60" s="5">
-        <v>104.14</v>
+        <v>45.93</v>
       </c>
       <c r="F60" s="5"/>
       <c r="G60" s="5" t="s">
@@ -6866,17 +7111,17 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="6">
-        <v>46284.20833333334</v>
+        <v>46284.54166666666</v>
       </c>
       <c r="B61" s="5">
-        <v>451.9</v>
+        <v>382.64</v>
       </c>
       <c r="C61" s="5">
-        <v>368.07</v>
+        <v>345.55</v>
       </c>
       <c r="D61" s="5"/>
       <c r="E61" s="5">
-        <v>97.42</v>
+        <v>42.97</v>
       </c>
       <c r="F61" s="5"/>
       <c r="G61" s="5" t="s">
@@ -6885,17 +7130,17 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="6">
-        <v>46284.25</v>
+        <v>46284.58333333334</v>
       </c>
       <c r="B62" s="5">
-        <v>446.34</v>
+        <v>380.24</v>
       </c>
       <c r="C62" s="5">
-        <v>368.12</v>
+        <v>345.54</v>
       </c>
       <c r="D62" s="5"/>
       <c r="E62" s="5">
-        <v>91.14</v>
+        <v>40.2</v>
       </c>
       <c r="F62" s="5"/>
       <c r="G62" s="5" t="s">
@@ -6904,17 +7149,17 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="6">
-        <v>46284.29166666666</v>
+        <v>46284.625</v>
       </c>
       <c r="B63" s="5">
-        <v>441.23</v>
+        <v>377.99</v>
       </c>
       <c r="C63" s="5">
-        <v>368.17</v>
+        <v>345.53</v>
       </c>
       <c r="D63" s="5"/>
       <c r="E63" s="5">
-        <v>85.26000000000001</v>
+        <v>37.61</v>
       </c>
       <c r="F63" s="5"/>
       <c r="G63" s="5" t="s">
@@ -6923,17 +7168,17 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="6">
-        <v>46284.33333333334</v>
+        <v>46284.66666666666</v>
       </c>
       <c r="B64" s="5">
-        <v>436.49</v>
+        <v>375.89</v>
       </c>
       <c r="C64" s="5">
-        <v>368.22</v>
+        <v>345.53</v>
       </c>
       <c r="D64" s="5"/>
       <c r="E64" s="5">
-        <v>79.76000000000001</v>
+        <v>35.18</v>
       </c>
       <c r="F64" s="5"/>
       <c r="G64" s="5" t="s">
@@ -6942,17 +7187,17 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="6">
-        <v>46284.375</v>
+        <v>46284.70833333334</v>
       </c>
       <c r="B65" s="5">
-        <v>432.09</v>
+        <v>373.92</v>
       </c>
       <c r="C65" s="5">
-        <v>368.27</v>
+        <v>345.52</v>
       </c>
       <c r="D65" s="5"/>
       <c r="E65" s="5">
-        <v>74.62</v>
+        <v>32.91</v>
       </c>
       <c r="F65" s="5"/>
       <c r="G65" s="5" t="s">
@@ -6961,17 +7206,17 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="6">
-        <v>46284.41666666666</v>
+        <v>46284.75</v>
       </c>
       <c r="B66" s="5">
-        <v>427.99</v>
+        <v>372.08</v>
       </c>
       <c r="C66" s="5">
-        <v>368.31</v>
+        <v>345.52</v>
       </c>
       <c r="D66" s="5"/>
       <c r="E66" s="5">
-        <v>69.81</v>
+        <v>30.79</v>
       </c>
       <c r="F66" s="5"/>
       <c r="G66" s="5" t="s">
@@ -6980,17 +7225,17 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="6">
-        <v>46284.45833333334</v>
+        <v>46284.79166666666</v>
       </c>
       <c r="B67" s="5">
-        <v>424.17</v>
+        <v>370.36</v>
       </c>
       <c r="C67" s="5">
-        <v>368.36</v>
+        <v>345.51</v>
       </c>
       <c r="D67" s="5"/>
       <c r="E67" s="5">
-        <v>65.3</v>
+        <v>28.81</v>
       </c>
       <c r="F67" s="5"/>
       <c r="G67" s="5" t="s">
@@ -6999,17 +7244,17 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="6">
-        <v>46284.5</v>
+        <v>46284.83333333334</v>
       </c>
       <c r="B68" s="5">
-        <v>420.61</v>
+        <v>368.75</v>
       </c>
       <c r="C68" s="5">
-        <v>368.41</v>
+        <v>345.5</v>
       </c>
       <c r="D68" s="5"/>
       <c r="E68" s="5">
-        <v>61.09</v>
+        <v>26.95</v>
       </c>
       <c r="F68" s="5"/>
       <c r="G68" s="5" t="s">
@@ -7018,17 +7263,17 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="6">
-        <v>46284.54166666666</v>
+        <v>46284.875</v>
       </c>
       <c r="B69" s="5">
-        <v>417.28</v>
+        <v>367.25</v>
       </c>
       <c r="C69" s="5">
-        <v>368.45</v>
+        <v>345.5</v>
       </c>
       <c r="D69" s="5"/>
       <c r="E69" s="5">
-        <v>57.15</v>
+        <v>25.21</v>
       </c>
       <c r="F69" s="5"/>
       <c r="G69" s="5" t="s">
@@ -7037,17 +7282,17 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="6">
-        <v>46284.58333333334</v>
+        <v>46284.91666666666</v>
       </c>
       <c r="B70" s="5">
-        <v>414.17</v>
+        <v>365.84</v>
       </c>
       <c r="C70" s="5">
-        <v>368.49</v>
+        <v>345.49</v>
       </c>
       <c r="D70" s="5"/>
       <c r="E70" s="5">
-        <v>53.47</v>
+        <v>23.58</v>
       </c>
       <c r="F70" s="5"/>
       <c r="G70" s="5" t="s">
@@ -7056,17 +7301,17 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="6">
-        <v>46284.625</v>
+        <v>46284.95833333334</v>
       </c>
       <c r="B71" s="5">
-        <v>411.26</v>
+        <v>364.52</v>
       </c>
       <c r="C71" s="5">
-        <v>368.53</v>
+        <v>345.49</v>
       </c>
       <c r="D71" s="5"/>
       <c r="E71" s="5">
-        <v>50.02</v>
+        <v>22.06</v>
       </c>
       <c r="F71" s="5"/>
       <c r="G71" s="5" t="s">
@@ -7075,17 +7320,17 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="6">
-        <v>46284.66666666666</v>
+        <v>46285</v>
       </c>
       <c r="B72" s="5">
-        <v>408.54</v>
+        <v>363.29</v>
       </c>
       <c r="C72" s="5">
-        <v>368.57</v>
+        <v>345.49</v>
       </c>
       <c r="D72" s="5"/>
       <c r="E72" s="5">
-        <v>46.79</v>
+        <v>20.64</v>
       </c>
       <c r="F72" s="5"/>
       <c r="G72" s="5" t="s">
@@ -7094,17 +7339,17 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="6">
-        <v>46284.70833333334</v>
+        <v>46285.04166666666</v>
       </c>
       <c r="B73" s="5">
-        <v>406</v>
+        <v>362.14</v>
       </c>
       <c r="C73" s="5">
-        <v>368.61</v>
+        <v>345.48</v>
       </c>
       <c r="D73" s="5"/>
       <c r="E73" s="5">
-        <v>43.77</v>
+        <v>19.31</v>
       </c>
       <c r="F73" s="5"/>
       <c r="G73" s="5" t="s">
@@ -7113,17 +7358,17 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="6">
-        <v>46284.75</v>
+        <v>46285.08333333334</v>
       </c>
       <c r="B74" s="5">
-        <v>403.62</v>
+        <v>361.06</v>
       </c>
       <c r="C74" s="5">
-        <v>368.64</v>
+        <v>345.48</v>
       </c>
       <c r="D74" s="5"/>
       <c r="E74" s="5">
-        <v>40.95</v>
+        <v>18.06</v>
       </c>
       <c r="F74" s="5"/>
       <c r="G74" s="5" t="s">
@@ -7132,17 +7377,17 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="6">
-        <v>46284.79166666666</v>
+        <v>46285.125</v>
       </c>
       <c r="B75" s="5">
-        <v>401.4</v>
+        <v>360.05</v>
       </c>
       <c r="C75" s="5">
-        <v>368.68</v>
+        <v>345.47</v>
       </c>
       <c r="D75" s="5"/>
       <c r="E75" s="5">
-        <v>38.31</v>
+        <v>16.9</v>
       </c>
       <c r="F75" s="5"/>
       <c r="G75" s="5" t="s">
@@ -7151,17 +7396,17 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="6">
-        <v>46284.83333333334</v>
+        <v>46285.16666666666</v>
       </c>
       <c r="B76" s="5">
-        <v>399.32</v>
+        <v>359.11</v>
       </c>
       <c r="C76" s="5">
-        <v>368.71</v>
+        <v>345.47</v>
       </c>
       <c r="D76" s="5"/>
       <c r="E76" s="5">
-        <v>35.84</v>
+        <v>15.81</v>
       </c>
       <c r="F76" s="5"/>
       <c r="G76" s="5" t="s">
@@ -7170,17 +7415,17 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="6">
-        <v>46284.875</v>
+        <v>46285.20833333334</v>
       </c>
       <c r="B77" s="5">
-        <v>397.38</v>
+        <v>358.22</v>
       </c>
       <c r="C77" s="5">
-        <v>368.74</v>
+        <v>345.47</v>
       </c>
       <c r="D77" s="5"/>
       <c r="E77" s="5">
-        <v>33.53</v>
+        <v>14.79</v>
       </c>
       <c r="F77" s="5"/>
       <c r="G77" s="5" t="s">
@@ -7222,10 +7467,10 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="6">
-        <v>46281.875</v>
+        <v>46282.25</v>
       </c>
       <c r="B2" s="5">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>48</v>
@@ -7237,10 +7482,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="6">
-        <v>46282</v>
+        <v>46282.375</v>
       </c>
       <c r="B3" s="5">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>48</v>
@@ -7252,7 +7497,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="6">
-        <v>46282.125</v>
+        <v>46282.5</v>
       </c>
       <c r="B4" s="5">
         <v>2</v>
@@ -7267,10 +7512,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="6">
-        <v>46282.25</v>
+        <v>46282.625</v>
       </c>
       <c r="B5" s="5">
-        <v>2.67</v>
+        <v>2</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>48</v>
@@ -7282,10 +7527,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="6">
-        <v>46282.375</v>
+        <v>46282.75</v>
       </c>
       <c r="B6" s="5">
-        <v>3</v>
+        <v>1.67</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>48</v>
@@ -7297,10 +7542,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="6">
-        <v>46282.5</v>
+        <v>46282.875</v>
       </c>
       <c r="B7" s="5">
-        <v>3.33</v>
+        <v>1.33</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>48</v>
@@ -7312,10 +7557,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="6">
-        <v>46282.625</v>
+        <v>46283</v>
       </c>
       <c r="B8" s="5">
-        <v>3</v>
+        <v>0.67</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>48</v>
@@ -7327,10 +7572,10 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="6">
-        <v>46282.75</v>
+        <v>46283.125</v>
       </c>
       <c r="B9" s="5">
-        <v>2</v>
+        <v>0.67</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>48</v>
@@ -7342,10 +7587,10 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="6">
-        <v>46282.875</v>
+        <v>46283.25</v>
       </c>
       <c r="B10" s="5">
-        <v>1.33</v>
+        <v>0.67</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>48</v>
@@ -7357,10 +7602,10 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="6">
-        <v>46283</v>
+        <v>46283.375</v>
       </c>
       <c r="B11" s="5">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>48</v>
@@ -7372,10 +7617,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="6">
-        <v>46283.125</v>
+        <v>46283.5</v>
       </c>
       <c r="B12" s="5">
-        <v>0.67</v>
+        <v>1.33</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>48</v>
@@ -7387,10 +7632,10 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="6">
-        <v>46283.25</v>
+        <v>46283.625</v>
       </c>
       <c r="B13" s="5">
-        <v>0.67</v>
+        <v>1.67</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>48</v>
@@ -7402,10 +7647,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="6">
-        <v>46283.375</v>
+        <v>46283.75</v>
       </c>
       <c r="B14" s="5">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>48</v>
@@ -7417,10 +7662,10 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="6">
-        <v>46283.5</v>
+        <v>46283.875</v>
       </c>
       <c r="B15" s="5">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>48</v>
@@ -7432,10 +7677,10 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="6">
-        <v>46283.625</v>
+        <v>46284</v>
       </c>
       <c r="B16" s="5">
-        <v>2.33</v>
+        <v>0.67</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>48</v>
@@ -7447,10 +7692,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="6">
-        <v>46283.75</v>
+        <v>46284.125</v>
       </c>
       <c r="B17" s="5">
-        <v>2.67</v>
+        <v>0.33</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>48</v>
@@ -7462,10 +7707,10 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="6">
-        <v>46283.875</v>
+        <v>46284.25</v>
       </c>
       <c r="B18" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>48</v>
@@ -7477,10 +7722,10 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="6">
-        <v>46284</v>
+        <v>46284.375</v>
       </c>
       <c r="B19" s="5">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>48</v>
@@ -7492,10 +7737,10 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="6">
-        <v>46284.125</v>
+        <v>46284.5</v>
       </c>
       <c r="B20" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>48</v>
@@ -7507,10 +7752,10 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="6">
-        <v>46284.25</v>
+        <v>46284.625</v>
       </c>
       <c r="B21" s="5">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>48</v>
@@ -7522,10 +7767,10 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="6">
-        <v>46284.375</v>
+        <v>46284.75</v>
       </c>
       <c r="B22" s="5">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>48</v>
@@ -7537,10 +7782,10 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="6">
-        <v>46284.5</v>
+        <v>46284.875</v>
       </c>
       <c r="B23" s="5">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>48</v>
@@ -7552,10 +7797,10 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="6">
-        <v>46284.625</v>
+        <v>46285</v>
       </c>
       <c r="B24" s="5">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>48</v>
@@ -7567,10 +7812,10 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="6">
-        <v>46284.75</v>
+        <v>46285.125</v>
       </c>
       <c r="B25" s="5">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>48</v>
@@ -7588,7 +7833,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:M61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="9" width="16.7109375" customWidth="1"/>
@@ -7642,19 +7887,19 @@
         <v>24</v>
       </c>
       <c r="D4" s="5">
-        <v>48.483</v>
+        <v>59.571</v>
       </c>
       <c r="E4" s="5">
-        <v>64.10599999999999</v>
+        <v>77.83</v>
       </c>
       <c r="F4" s="5">
-        <v>47.4</v>
+        <v>55.268</v>
       </c>
       <c r="G4" s="5">
-        <v>70.8</v>
+        <v>54.2</v>
       </c>
       <c r="H4" s="5">
-        <v>83.3</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -7665,22 +7910,22 @@
         <v>61</v>
       </c>
       <c r="C5" s="5">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D5" s="5">
-        <v>66.477</v>
+        <v>59.281</v>
       </c>
       <c r="E5" s="5">
-        <v>86.486</v>
+        <v>76.304</v>
       </c>
       <c r="F5" s="5">
-        <v>57.005</v>
+        <v>38.641</v>
       </c>
       <c r="G5" s="5">
-        <v>54.3</v>
+        <v>53.5</v>
       </c>
       <c r="H5" s="5">
-        <v>74.3</v>
+        <v>69.8</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -7691,22 +7936,22 @@
         <v>62</v>
       </c>
       <c r="C6" s="5">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D6" s="5">
-        <v>66.477</v>
+        <v>59.281</v>
       </c>
       <c r="E6" s="5">
-        <v>86.486</v>
+        <v>76.304</v>
       </c>
       <c r="F6" s="5">
-        <v>57.005</v>
+        <v>38.641</v>
       </c>
       <c r="G6" s="5">
-        <v>54.3</v>
+        <v>53.5</v>
       </c>
       <c r="H6" s="5">
-        <v>74.3</v>
+        <v>69.8</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -7852,13 +8097,13 @@
         <v>524.8200000000001</v>
       </c>
       <c r="C19" s="5">
-        <v>470.85</v>
+        <v>428.06</v>
       </c>
       <c r="D19" s="5">
-        <v>360.49</v>
+        <v>336.29</v>
       </c>
       <c r="E19" s="5">
-        <v>-53.97000000000003</v>
+        <v>-96.76000000000005</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -7869,13 +8114,13 @@
         <v>566.89</v>
       </c>
       <c r="C20" s="5">
-        <v>536.28</v>
+        <v>487.63</v>
       </c>
       <c r="D20" s="5">
-        <v>397.56</v>
+        <v>373.6</v>
       </c>
       <c r="E20" s="5">
-        <v>-30.61000000000001</v>
+        <v>-79.25999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -7886,13 +8131,13 @@
         <v>561.75</v>
       </c>
       <c r="C21" s="5">
-        <v>584.85</v>
+        <v>531.21</v>
       </c>
       <c r="D21" s="5">
-        <v>408.34</v>
+        <v>384.49</v>
       </c>
       <c r="E21" s="5">
-        <v>23.10000000000002</v>
+        <v>-30.53999999999996</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -7903,13 +8148,13 @@
         <v>482.62</v>
       </c>
       <c r="C22" s="5">
-        <v>605.11</v>
+        <v>547.12</v>
       </c>
       <c r="D22" s="5">
-        <v>391.17</v>
+        <v>367.14</v>
       </c>
       <c r="E22" s="5">
-        <v>122.49</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -7920,13 +8165,13 @@
         <v>443.5</v>
       </c>
       <c r="C23" s="5">
-        <v>609.13</v>
+        <v>548.22</v>
       </c>
       <c r="D23" s="5">
-        <v>361.97</v>
+        <v>337.65</v>
       </c>
       <c r="E23" s="5">
-        <v>165.63</v>
+        <v>104.72</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -7937,13 +8182,13 @@
         <v>451.89</v>
       </c>
       <c r="C24" s="5">
-        <v>626.14</v>
+        <v>564.58</v>
       </c>
       <c r="D24" s="5">
-        <v>354.05</v>
+        <v>329.64</v>
       </c>
       <c r="E24" s="5">
-        <v>174.25</v>
+        <v>112.6900000000001</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -7954,13 +8199,13 @@
         <v>431.62</v>
       </c>
       <c r="C25" s="5">
-        <v>630.77</v>
+        <v>572.09</v>
       </c>
       <c r="D25" s="5">
-        <v>350.74</v>
+        <v>326.3</v>
       </c>
       <c r="E25" s="5">
-        <v>199.15</v>
+        <v>140.47</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -7971,13 +8216,13 @@
         <v>453.4</v>
       </c>
       <c r="C26" s="5">
-        <v>624.02</v>
+        <v>567.92</v>
       </c>
       <c r="D26" s="5">
-        <v>340.1</v>
+        <v>315.55</v>
       </c>
       <c r="E26" s="5">
-        <v>170.62</v>
+        <v>114.52</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -7988,13 +8233,13 @@
         <v>666.5</v>
       </c>
       <c r="C27" s="5">
-        <v>598.3200000000001</v>
+        <v>544.42</v>
       </c>
       <c r="D27" s="5">
-        <v>316.62</v>
+        <v>291.83</v>
       </c>
       <c r="E27" s="5">
-        <v>-68.17999999999995</v>
+        <v>-122.08</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -8005,13 +8250,13 @@
         <v>536.49</v>
       </c>
       <c r="C28" s="5">
-        <v>597.6900000000001</v>
+        <v>546.03</v>
       </c>
       <c r="D28" s="5">
-        <v>329.82</v>
+        <v>305.17</v>
       </c>
       <c r="E28" s="5">
-        <v>61.20000000000005</v>
+        <v>9.539999999999964</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -8019,16 +8264,16 @@
         <v>46280.875</v>
       </c>
       <c r="B29" s="5">
-        <v>504.43</v>
+        <v>502.61</v>
       </c>
       <c r="C29" s="5">
-        <v>598.33</v>
+        <v>548.85</v>
       </c>
       <c r="D29" s="5">
-        <v>346.86</v>
+        <v>322.38</v>
       </c>
       <c r="E29" s="5">
-        <v>93.90000000000003</v>
+        <v>46.24000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -8036,16 +8281,16 @@
         <v>46280.91666666666</v>
       </c>
       <c r="B30" s="5">
-        <v>447.76</v>
+        <v>449.1</v>
       </c>
       <c r="C30" s="5">
-        <v>583.73</v>
+        <v>535.4400000000001</v>
       </c>
       <c r="D30" s="5">
-        <v>347</v>
+        <v>321.65</v>
       </c>
       <c r="E30" s="5">
-        <v>135.97</v>
+        <v>86.34000000000003</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -8053,16 +8298,16 @@
         <v>46280.95833333334</v>
       </c>
       <c r="B31" s="5">
-        <v>450.85</v>
+        <v>453.2</v>
       </c>
       <c r="C31" s="5">
-        <v>545.45</v>
+        <v>501.43</v>
       </c>
       <c r="D31" s="5">
-        <v>321.63</v>
+        <v>298.34</v>
       </c>
       <c r="E31" s="5">
-        <v>94.60000000000002</v>
+        <v>48.23000000000002</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -8070,16 +8315,16 @@
         <v>46281</v>
       </c>
       <c r="B32" s="5">
-        <v>507.31</v>
+        <v>506.78</v>
       </c>
       <c r="C32" s="5">
-        <v>532.4</v>
+        <v>491.28</v>
       </c>
       <c r="D32" s="5">
-        <v>319.47</v>
+        <v>296.68</v>
       </c>
       <c r="E32" s="5">
-        <v>25.08999999999997</v>
+        <v>-15.5</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -8087,16 +8332,16 @@
         <v>46281.04166666666</v>
       </c>
       <c r="B33" s="5">
-        <v>521.25</v>
+        <v>521.5599999999999</v>
       </c>
       <c r="C33" s="5">
-        <v>543.24</v>
+        <v>503.41</v>
       </c>
       <c r="D33" s="5">
-        <v>339.02</v>
+        <v>314.82</v>
       </c>
       <c r="E33" s="5">
-        <v>21.99000000000001</v>
+        <v>-18.14999999999992</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -8104,16 +8349,16 @@
         <v>46281.08333333334</v>
       </c>
       <c r="B34" s="5">
-        <v>524.77</v>
+        <v>525.3</v>
       </c>
       <c r="C34" s="5">
-        <v>553.75</v>
+        <v>516.4299999999999</v>
       </c>
       <c r="D34" s="5">
-        <v>355.96</v>
+        <v>331.28</v>
       </c>
       <c r="E34" s="5">
-        <v>28.98000000000002</v>
+        <v>-8.870000000000005</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -8121,16 +8366,16 @@
         <v>46281.125</v>
       </c>
       <c r="B35" s="5">
-        <v>529.76</v>
+        <v>530.12</v>
       </c>
       <c r="C35" s="5">
-        <v>555.89</v>
+        <v>522.52</v>
       </c>
       <c r="D35" s="5">
-        <v>362.36</v>
+        <v>338.3</v>
       </c>
       <c r="E35" s="5">
-        <v>26.13</v>
+        <v>-7.600000000000023</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -8138,16 +8383,16 @@
         <v>46281.16666666666</v>
       </c>
       <c r="B36" s="5">
-        <v>537.34</v>
+        <v>537.58</v>
       </c>
       <c r="C36" s="5">
-        <v>557.58</v>
+        <v>527.62</v>
       </c>
       <c r="D36" s="5">
-        <v>366.39</v>
+        <v>342.21</v>
       </c>
       <c r="E36" s="5">
-        <v>20.24000000000001</v>
+        <v>-9.960000000000036</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -8155,16 +8400,16 @@
         <v>46281.20833333334</v>
       </c>
       <c r="B37" s="5">
-        <v>536.9</v>
+        <v>536.5</v>
       </c>
       <c r="C37" s="5">
-        <v>559.6</v>
+        <v>533.1</v>
       </c>
       <c r="D37" s="5">
-        <v>369.31</v>
+        <v>345</v>
       </c>
       <c r="E37" s="5">
-        <v>22.70000000000005</v>
+        <v>-3.399999999999977</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -8175,13 +8420,13 @@
         <v>535.3</v>
       </c>
       <c r="C38" s="5">
-        <v>566.16</v>
+        <v>543.53</v>
       </c>
       <c r="D38" s="5">
-        <v>376.06</v>
+        <v>352.16</v>
       </c>
       <c r="E38" s="5">
-        <v>30.86000000000001</v>
+        <v>8.230000000000018</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -8189,16 +8434,16 @@
         <v>46281.29166666666</v>
       </c>
       <c r="B39" s="5">
-        <v>524.2</v>
+        <v>524.23</v>
       </c>
       <c r="C39" s="5">
-        <v>569.3200000000001</v>
+        <v>549.3200000000001</v>
       </c>
       <c r="D39" s="5">
-        <v>379.47</v>
+        <v>355.11</v>
       </c>
       <c r="E39" s="5">
-        <v>45.12</v>
+        <v>25.09000000000003</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -8206,16 +8451,16 @@
         <v>46281.33333333334</v>
       </c>
       <c r="B40" s="5">
-        <v>535.67</v>
+        <v>537.3</v>
       </c>
       <c r="C40" s="5">
-        <v>567.86</v>
+        <v>550.22</v>
       </c>
       <c r="D40" s="5">
-        <v>379.84</v>
+        <v>355.62</v>
       </c>
       <c r="E40" s="5">
-        <v>32.19000000000005</v>
+        <v>12.92000000000007</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -8223,16 +8468,16 @@
         <v>46281.375</v>
       </c>
       <c r="B41" s="5">
-        <v>542.09</v>
+        <v>543.02</v>
       </c>
       <c r="C41" s="5">
-        <v>566.54</v>
+        <v>550.38</v>
       </c>
       <c r="D41" s="5">
-        <v>381.65</v>
+        <v>357.49</v>
       </c>
       <c r="E41" s="5">
-        <v>24.44999999999993</v>
+        <v>7.360000000000014</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -8240,16 +8485,16 @@
         <v>46281.41666666666</v>
       </c>
       <c r="B42" s="5">
-        <v>541.97</v>
+        <v>540.4</v>
       </c>
       <c r="C42" s="5">
-        <v>563.8200000000001</v>
+        <v>548.77</v>
       </c>
       <c r="D42" s="5">
-        <v>381.74</v>
+        <v>357.64</v>
       </c>
       <c r="E42" s="5">
-        <v>21.85000000000002</v>
+        <v>8.370000000000005</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -8257,16 +8502,16 @@
         <v>46281.45833333334</v>
       </c>
       <c r="B43" s="5">
-        <v>539.6</v>
+        <v>540.14</v>
       </c>
       <c r="C43" s="5">
-        <v>557.27</v>
+        <v>542.72</v>
       </c>
       <c r="D43" s="5">
-        <v>378.02</v>
+        <v>354.02</v>
       </c>
       <c r="E43" s="5">
-        <v>17.66999999999996</v>
+        <v>2.580000000000041</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -8277,13 +8522,13 @@
         <v>537.77</v>
       </c>
       <c r="C44" s="5">
-        <v>554.17</v>
+        <v>539.24</v>
       </c>
       <c r="D44" s="5">
-        <v>377.71</v>
+        <v>353.8</v>
       </c>
       <c r="E44" s="5">
-        <v>16.39999999999998</v>
+        <v>1.470000000000027</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -8291,16 +8536,16 @@
         <v>46281.54166666666</v>
       </c>
       <c r="B45" s="5">
-        <v>560.7</v>
+        <v>561.9</v>
       </c>
       <c r="C45" s="5">
-        <v>550.88</v>
+        <v>534.34</v>
       </c>
       <c r="D45" s="5">
-        <v>378.25</v>
+        <v>354.7</v>
       </c>
       <c r="E45" s="5">
-        <v>-9.82000000000005</v>
+        <v>-27.55999999999995</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -8308,16 +8553,16 @@
         <v>46281.58333333334</v>
       </c>
       <c r="B46" s="5">
-        <v>557.8</v>
+        <v>559.27</v>
       </c>
       <c r="C46" s="5">
-        <v>554.62</v>
+        <v>535.1900000000001</v>
       </c>
       <c r="D46" s="5">
-        <v>381.55</v>
+        <v>357.56</v>
       </c>
       <c r="E46" s="5">
-        <v>-3.17999999999995</v>
+        <v>-24.07999999999993</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -8325,16 +8570,16 @@
         <v>46281.625</v>
       </c>
       <c r="B47" s="5">
-        <v>534.5599999999999</v>
+        <v>535.9</v>
       </c>
       <c r="C47" s="5">
-        <v>561.04</v>
+        <v>538.34</v>
       </c>
       <c r="D47" s="5">
-        <v>382.44</v>
+        <v>358.18</v>
       </c>
       <c r="E47" s="5">
-        <v>26.48000000000002</v>
+        <v>2.440000000000055</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -8342,16 +8587,16 @@
         <v>46281.66666666666</v>
       </c>
       <c r="B48" s="5">
-        <v>528.8</v>
+        <v>528.14</v>
       </c>
       <c r="C48" s="5">
-        <v>570.72</v>
+        <v>545.02</v>
       </c>
       <c r="D48" s="5">
-        <v>381.05</v>
+        <v>357.21</v>
       </c>
       <c r="E48" s="5">
-        <v>41.92000000000007</v>
+        <v>16.88</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -8359,16 +8604,16 @@
         <v>46281.70833333334</v>
       </c>
       <c r="B49" s="5">
-        <v>529.2</v>
+        <v>528.46</v>
       </c>
       <c r="C49" s="5">
-        <v>583.64</v>
+        <v>554.25</v>
       </c>
       <c r="D49" s="5">
-        <v>377.56</v>
+        <v>353.67</v>
       </c>
       <c r="E49" s="5">
-        <v>54.43999999999994</v>
+        <v>25.78999999999996</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -8376,16 +8621,16 @@
         <v>46281.75</v>
       </c>
       <c r="B50" s="5">
-        <v>531.42</v>
+        <v>532.26</v>
       </c>
       <c r="C50" s="5">
-        <v>604.42</v>
+        <v>571.4</v>
       </c>
       <c r="D50" s="5">
-        <v>377.68</v>
+        <v>353.57</v>
       </c>
       <c r="E50" s="5">
-        <v>73</v>
+        <v>39.13999999999999</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -8393,16 +8638,16 @@
         <v>46281.79166666666</v>
       </c>
       <c r="B51" s="5">
-        <v>505.04</v>
+        <v>504.91</v>
       </c>
       <c r="C51" s="5">
-        <v>623.3200000000001</v>
+        <v>587.55</v>
       </c>
       <c r="D51" s="5">
-        <v>373.72</v>
+        <v>349.49</v>
       </c>
       <c r="E51" s="5">
-        <v>118.28</v>
+        <v>82.63999999999993</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -8410,16 +8655,16 @@
         <v>46281.83333333334</v>
       </c>
       <c r="B52" s="5">
-        <v>505.5</v>
+        <v>505.2</v>
       </c>
       <c r="C52" s="5">
-        <v>636.67</v>
+        <v>599.91</v>
       </c>
       <c r="D52" s="5">
-        <v>364.8</v>
+        <v>340.83</v>
       </c>
       <c r="E52" s="5">
-        <v>131.17</v>
+        <v>94.70999999999998</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -8427,16 +8672,152 @@
         <v>46281.875</v>
       </c>
       <c r="B53" s="5">
-        <v>508.88</v>
+        <v>506.1</v>
       </c>
       <c r="C53" s="5">
-        <v>649.9400000000001</v>
+        <v>613.38</v>
       </c>
       <c r="D53" s="5">
-        <v>359.37</v>
+        <v>335.05</v>
       </c>
       <c r="E53" s="5">
-        <v>141.0600000000001</v>
+        <v>107.28</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6">
+        <v>46281.91666666666</v>
+      </c>
+      <c r="B54" s="5">
+        <v>508.95</v>
+      </c>
+      <c r="C54" s="5">
+        <v>622.67</v>
+      </c>
+      <c r="D54" s="5">
+        <v>329.28</v>
+      </c>
+      <c r="E54" s="5">
+        <v>113.72</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6">
+        <v>46281.95833333334</v>
+      </c>
+      <c r="B55" s="5">
+        <v>512.02</v>
+      </c>
+      <c r="C55" s="5">
+        <v>627.73</v>
+      </c>
+      <c r="D55" s="5">
+        <v>329.34</v>
+      </c>
+      <c r="E55" s="5">
+        <v>115.71</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="6">
+        <v>46282</v>
+      </c>
+      <c r="B56" s="5">
+        <v>507.89</v>
+      </c>
+      <c r="C56" s="5">
+        <v>630.77</v>
+      </c>
+      <c r="D56" s="5">
+        <v>328.88</v>
+      </c>
+      <c r="E56" s="5">
+        <v>122.88</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="6">
+        <v>46282.04166666666</v>
+      </c>
+      <c r="B57" s="5">
+        <v>498.8</v>
+      </c>
+      <c r="C57" s="5">
+        <v>632.04</v>
+      </c>
+      <c r="D57" s="5">
+        <v>328</v>
+      </c>
+      <c r="E57" s="5">
+        <v>133.24</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="6">
+        <v>46282.08333333334</v>
+      </c>
+      <c r="B58" s="5">
+        <v>546.05</v>
+      </c>
+      <c r="C58" s="5">
+        <v>634.0700000000001</v>
+      </c>
+      <c r="D58" s="5">
+        <v>330.02</v>
+      </c>
+      <c r="E58" s="5">
+        <v>88.0200000000001</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="6">
+        <v>46282.125</v>
+      </c>
+      <c r="B59" s="5">
+        <v>537.7</v>
+      </c>
+      <c r="C59" s="5">
+        <v>639.17</v>
+      </c>
+      <c r="D59" s="5">
+        <v>331.46</v>
+      </c>
+      <c r="E59" s="5">
+        <v>101.4699999999999</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="6">
+        <v>46282.16666666666</v>
+      </c>
+      <c r="B60" s="5">
+        <v>509.66</v>
+      </c>
+      <c r="C60" s="5">
+        <v>637.21</v>
+      </c>
+      <c r="D60" s="5">
+        <v>334.59</v>
+      </c>
+      <c r="E60" s="5">
+        <v>127.55</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="6">
+        <v>46282.20833333334</v>
+      </c>
+      <c r="B61" s="5">
+        <v>505.05</v>
+      </c>
+      <c r="C61" s="5">
+        <v>645.63</v>
+      </c>
+      <c r="D61" s="5">
+        <v>334.76</v>
+      </c>
+      <c r="E61" s="5">
+        <v>140.58</v>
       </c>
     </row>
   </sheetData>
@@ -8483,19 +8864,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="6">
-        <v>46281.875</v>
+        <v>46282.20833333334</v>
       </c>
       <c r="B2" s="5">
-        <v>2.07</v>
+        <v>1.61</v>
       </c>
       <c r="C2" s="5">
-        <v>-9.77</v>
+        <v>-12.3</v>
       </c>
       <c r="D2" s="5">
-        <v>14.6</v>
+        <v>15.43</v>
       </c>
       <c r="E2" s="5">
-        <v>57.3</v>
+        <v>62.8</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>81</v>
@@ -8506,19 +8887,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="6">
-        <v>46282</v>
+        <v>46282.33333333334</v>
       </c>
       <c r="B3" s="5">
-        <v>1.9</v>
+        <v>1.48</v>
       </c>
       <c r="C3" s="5">
-        <v>-9.77</v>
+        <v>-12.3</v>
       </c>
       <c r="D3" s="5">
-        <v>14.41</v>
+        <v>15.27</v>
       </c>
       <c r="E3" s="5">
-        <v>57.9</v>
+        <v>63.4</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>81</v>
@@ -8529,19 +8910,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="6">
-        <v>46282.125</v>
+        <v>46282.45833333334</v>
       </c>
       <c r="B4" s="5">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="C4" s="5">
-        <v>-9.859999999999999</v>
+        <v>-12.55</v>
       </c>
       <c r="D4" s="5">
-        <v>14.34</v>
+        <v>15.35</v>
       </c>
       <c r="E4" s="5">
-        <v>58.8</v>
+        <v>64.8</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>81</v>
@@ -8552,19 +8933,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="6">
-        <v>46282.25</v>
+        <v>46282.58333333334</v>
       </c>
       <c r="B5" s="5">
-        <v>1.61</v>
+        <v>1.26</v>
       </c>
       <c r="C5" s="5">
-        <v>-10.86</v>
+        <v>-12.36</v>
       </c>
       <c r="D5" s="5">
-        <v>15.18</v>
+        <v>15.02</v>
       </c>
       <c r="E5" s="5">
-        <v>63.2</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>81</v>
@@ -8575,19 +8956,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="6">
-        <v>46282.375</v>
+        <v>46282.70833333334</v>
       </c>
       <c r="B6" s="5">
-        <v>1.48</v>
+        <v>1.16</v>
       </c>
       <c r="C6" s="5">
-        <v>-10.97</v>
+        <v>-10.64</v>
       </c>
       <c r="D6" s="5">
-        <v>15.14</v>
+        <v>13.17</v>
       </c>
       <c r="E6" s="5">
-        <v>64.09999999999999</v>
+        <v>58.5</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>81</v>
@@ -8598,390 +8979,390 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="6">
-        <v>46282.5</v>
+        <v>46282.83333333334</v>
       </c>
       <c r="B7" s="5">
-        <v>1.36</v>
+        <v>1.06</v>
       </c>
       <c r="C7" s="5">
-        <v>-11.11</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="D7" s="5">
-        <v>15.15</v>
+        <v>10.62</v>
       </c>
       <c r="E7" s="5">
-        <v>65.2</v>
+        <v>49.8</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="6">
-        <v>46282.625</v>
+        <v>46282.95833333334</v>
       </c>
       <c r="B8" s="5">
-        <v>1.26</v>
+        <v>0.98</v>
       </c>
       <c r="C8" s="5">
-        <v>-10.36</v>
+        <v>-6.01</v>
       </c>
       <c r="D8" s="5">
-        <v>14.28</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E8" s="5">
-        <v>62.8</v>
+        <v>41.8</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="6">
-        <v>46282.75</v>
+        <v>46283.08333333334</v>
       </c>
       <c r="B9" s="5">
-        <v>1.16</v>
+        <v>0.9</v>
       </c>
       <c r="C9" s="5">
-        <v>-8.300000000000001</v>
+        <v>-4.52</v>
       </c>
       <c r="D9" s="5">
-        <v>12.11</v>
+        <v>6.71</v>
       </c>
       <c r="E9" s="5">
-        <v>55.5</v>
+        <v>36.5</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="6">
-        <v>46282.875</v>
+        <v>46283.20833333334</v>
       </c>
       <c r="B10" s="5">
-        <v>1.06</v>
+        <v>0.83</v>
       </c>
       <c r="C10" s="5">
-        <v>-5.98</v>
+        <v>-5.35</v>
       </c>
       <c r="D10" s="5">
-        <v>9.57</v>
+        <v>7.44</v>
       </c>
       <c r="E10" s="5">
-        <v>46.6</v>
+        <v>40.1</v>
       </c>
       <c r="F10" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="G10" s="5" t="s">
         <v>85</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="6">
-        <v>46283</v>
+        <v>46283.33333333334</v>
       </c>
       <c r="B11" s="5">
-        <v>0.98</v>
+        <v>0.76</v>
       </c>
       <c r="C11" s="5">
-        <v>-4.94</v>
+        <v>-7.35</v>
       </c>
       <c r="D11" s="5">
-        <v>7.48</v>
+        <v>9.35</v>
       </c>
       <c r="E11" s="5">
-        <v>39.5</v>
+        <v>48</v>
       </c>
       <c r="F11" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="G11" s="5" t="s">
         <v>85</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="6">
-        <v>46283.125</v>
+        <v>46283.45833333334</v>
       </c>
       <c r="B12" s="5">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="C12" s="5">
-        <v>-4.4</v>
+        <v>-9.81</v>
       </c>
       <c r="D12" s="5">
-        <v>6.38</v>
+        <v>11.73</v>
       </c>
       <c r="E12" s="5">
-        <v>36</v>
+        <v>57.7</v>
       </c>
       <c r="F12" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="G12" s="5" t="s">
         <v>85</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="6">
-        <v>46283.25</v>
+        <v>46283.58333333334</v>
       </c>
       <c r="B13" s="5">
-        <v>0.83</v>
+        <v>0.64</v>
       </c>
       <c r="C13" s="5">
-        <v>-5.13</v>
+        <v>-11.96</v>
       </c>
       <c r="D13" s="5">
-        <v>7.83</v>
+        <v>13.81</v>
       </c>
       <c r="E13" s="5">
-        <v>42.2</v>
+        <v>66.2</v>
       </c>
       <c r="F13" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="G13" s="5" t="s">
         <v>85</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="6">
-        <v>46283.375</v>
+        <v>46283.70833333334</v>
       </c>
       <c r="B14" s="5">
-        <v>0.76</v>
+        <v>0.59</v>
       </c>
       <c r="C14" s="5">
-        <v>-6.59</v>
+        <v>-12.91</v>
       </c>
       <c r="D14" s="5">
-        <v>9.960000000000001</v>
+        <v>14.69</v>
       </c>
       <c r="E14" s="5">
-        <v>51</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F14" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="G14" s="5" t="s">
         <v>85</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="6">
-        <v>46283.5</v>
+        <v>46283.83333333334</v>
       </c>
       <c r="B15" s="5">
-        <v>0.7</v>
+        <v>0.55</v>
       </c>
       <c r="C15" s="5">
-        <v>-9.050000000000001</v>
+        <v>-12.23</v>
       </c>
       <c r="D15" s="5">
-        <v>12.36</v>
+        <v>13.95</v>
       </c>
       <c r="E15" s="5">
-        <v>60.6</v>
+        <v>67.7</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>81</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="6">
-        <v>46283.625</v>
+        <v>46283.95833333334</v>
       </c>
       <c r="B16" s="5">
-        <v>0.64</v>
+        <v>0.5</v>
       </c>
       <c r="C16" s="5">
-        <v>-10.9</v>
+        <v>-10.26</v>
       </c>
       <c r="D16" s="5">
-        <v>14.14</v>
+        <v>11.92</v>
       </c>
       <c r="E16" s="5">
-        <v>68</v>
+        <v>60.5</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>81</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="6">
-        <v>46283.75</v>
+        <v>46284.08333333334</v>
       </c>
       <c r="B17" s="5">
-        <v>0.59</v>
+        <v>0.46</v>
       </c>
       <c r="C17" s="5">
-        <v>-11.32</v>
+        <v>-7.9</v>
       </c>
       <c r="D17" s="5">
-        <v>14.5</v>
+        <v>9.5</v>
       </c>
       <c r="E17" s="5">
-        <v>69.8</v>
+        <v>51.8</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="6">
-        <v>46283.875</v>
+        <v>46284.20833333334</v>
       </c>
       <c r="B18" s="5">
-        <v>0.55</v>
+        <v>0.43</v>
       </c>
       <c r="C18" s="5">
-        <v>-10.13</v>
+        <v>-5.92</v>
       </c>
       <c r="D18" s="5">
-        <v>13.26</v>
+        <v>7.48</v>
       </c>
       <c r="E18" s="5">
-        <v>65.59999999999999</v>
+        <v>44.5</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="6">
-        <v>46284</v>
+        <v>46284.33333333334</v>
       </c>
       <c r="B19" s="5">
-        <v>0.5</v>
+        <v>0.39</v>
       </c>
       <c r="C19" s="5">
-        <v>-7.93</v>
+        <v>-4.67</v>
       </c>
       <c r="D19" s="5">
-        <v>11.01</v>
+        <v>6.18</v>
       </c>
       <c r="E19" s="5">
-        <v>57.5</v>
+        <v>39.9</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="6">
-        <v>46284.125</v>
+        <v>46284.45833333334</v>
       </c>
       <c r="B20" s="5">
-        <v>0.46</v>
+        <v>0.36</v>
       </c>
       <c r="C20" s="5">
-        <v>-5.62</v>
+        <v>-4.04</v>
       </c>
       <c r="D20" s="5">
-        <v>8.66</v>
+        <v>5.51</v>
       </c>
       <c r="E20" s="5">
-        <v>48.9</v>
+        <v>37.7</v>
       </c>
       <c r="F20" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="G20" s="5" t="s">
         <v>85</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="6">
-        <v>46284.25</v>
+        <v>46284.58333333334</v>
       </c>
       <c r="B21" s="5">
-        <v>0.42</v>
+        <v>0.33</v>
       </c>
       <c r="C21" s="5">
-        <v>-4.67</v>
+        <v>-3.8</v>
       </c>
       <c r="D21" s="5">
-        <v>6.88</v>
+        <v>5.23</v>
       </c>
       <c r="E21" s="5">
-        <v>42.5</v>
+        <v>36.9</v>
       </c>
       <c r="F21" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="G21" s="5" t="s">
         <v>85</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="6">
-        <v>46284.375</v>
+        <v>46284.70833333334</v>
       </c>
       <c r="B22" s="5">
-        <v>0.41</v>
+        <v>0.32</v>
       </c>
       <c r="C22" s="5">
-        <v>-4.15</v>
+        <v>-3.72</v>
       </c>
       <c r="D22" s="5">
-        <v>5.82</v>
+        <v>5.14</v>
       </c>
       <c r="E22" s="5">
-        <v>38.6</v>
+        <v>36.7</v>
       </c>
       <c r="F22" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="G22" s="5" t="s">
         <v>85</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="6">
-        <v>46284.5</v>
+        <v>46284.83333333334</v>
       </c>
       <c r="B23" s="5">
-        <v>0.41</v>
+        <v>0.32</v>
       </c>
       <c r="C23" s="5">
-        <v>-3.9</v>
+        <v>-3.69</v>
       </c>
       <c r="D23" s="5">
-        <v>5.32</v>
+        <v>5.11</v>
       </c>
       <c r="E23" s="5">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G23" s="5" t="s">
         <v>86</v>
@@ -8989,22 +9370,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="6">
-        <v>46284.625</v>
+        <v>46284.95833333334</v>
       </c>
       <c r="B24" s="5">
-        <v>0.41</v>
+        <v>0.32</v>
       </c>
       <c r="C24" s="5">
-        <v>-3.8</v>
+        <v>-3.69</v>
       </c>
       <c r="D24" s="5">
-        <v>5.13</v>
+        <v>5.11</v>
       </c>
       <c r="E24" s="5">
-        <v>36</v>
+        <v>36.6</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G24" s="5" t="s">
         <v>86</v>
@@ -9012,48 +9393,48 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="6">
-        <v>46284.75</v>
+        <v>46285.08333333334</v>
       </c>
       <c r="B25" s="5">
-        <v>0.41</v>
+        <v>0.32</v>
       </c>
       <c r="C25" s="5">
-        <v>-3.76</v>
+        <v>-3.69</v>
       </c>
       <c r="D25" s="5">
-        <v>5.05</v>
+        <v>5.11</v>
       </c>
       <c r="E25" s="5">
-        <v>35.7</v>
+        <v>36.6</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="6">
-        <v>46284.875</v>
+        <v>46285.20833333334</v>
       </c>
       <c r="B26" s="5">
-        <v>0.41</v>
+        <v>0.32</v>
       </c>
       <c r="C26" s="5">
-        <v>-3.76</v>
+        <v>-3.69</v>
       </c>
       <c r="D26" s="5">
-        <v>5.05</v>
+        <v>5.11</v>
       </c>
       <c r="E26" s="5">
-        <v>35.7</v>
+        <v>36.6</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -9075,43 +9456,43 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>44</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>92</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>93</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>35</v>
       </c>
       <c r="I1" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>97</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>98</v>
       </c>
       <c r="N1" s="4" t="s">
         <v>47</v>
@@ -9119,13 +9500,13 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="C2" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>101</v>
       </c>
       <c r="D2" s="5" t="b">
         <v>0</v>
@@ -9146,7 +9527,7 @@
         <v>68</v>
       </c>
       <c r="J2" s="5">
-        <v>92.79000000000001</v>
+        <v>94.78</v>
       </c>
       <c r="K2" s="5">
         <v>-60</v>
@@ -9163,13 +9544,13 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>101</v>
       </c>
       <c r="D3" s="5" t="b">
         <v>0</v>
@@ -9190,7 +9571,7 @@
         <v>66.5</v>
       </c>
       <c r="J3" s="5">
-        <v>92.90000000000001</v>
+        <v>94.87</v>
       </c>
       <c r="K3" s="5">
         <v>-38</v>
@@ -9207,13 +9588,13 @@
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>103</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>104</v>
       </c>
       <c r="D4" s="5" t="b">
         <v>1</v>
@@ -9234,7 +9615,7 @@
         <v>352</v>
       </c>
       <c r="J4" s="5">
-        <v>93.37</v>
+        <v>103.19</v>
       </c>
       <c r="K4" s="5">
         <v>-18</v>
@@ -9251,13 +9632,13 @@
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>101</v>
       </c>
       <c r="D5" s="5" t="b">
         <v>0</v>
@@ -9278,7 +9659,7 @@
         <v>88</v>
       </c>
       <c r="J5" s="5">
-        <v>91.43000000000001</v>
+        <v>93.59</v>
       </c>
       <c r="K5" s="5">
         <v>-18</v>
@@ -9295,13 +9676,13 @@
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>101</v>
       </c>
       <c r="D6" s="5" t="b">
         <v>0</v>
@@ -9322,7 +9703,7 @@
         <v>71.2</v>
       </c>
       <c r="J6" s="5">
-        <v>92.56999999999999</v>
+        <v>94.59</v>
       </c>
       <c r="K6" s="5">
         <v>0</v>
@@ -9339,13 +9720,13 @@
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>101</v>
       </c>
       <c r="D7" s="5" t="b">
         <v>0</v>
@@ -9366,7 +9747,7 @@
         <v>72.8</v>
       </c>
       <c r="J7" s="5">
-        <v>92.47</v>
+        <v>94.5</v>
       </c>
       <c r="K7" s="5">
         <v>65</v>
@@ -9383,13 +9764,13 @@
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>101</v>
       </c>
       <c r="D8" s="5" t="b">
         <v>0</v>
@@ -9410,7 +9791,7 @@
         <v>91.2</v>
       </c>
       <c r="J8" s="5">
-        <v>91.20999999999999</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="K8" s="5">
         <v>35</v>
@@ -9427,13 +9808,13 @@
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B9" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>101</v>
       </c>
       <c r="D9" s="5" t="b">
         <v>0</v>
@@ -9454,7 +9835,7 @@
         <v>193.8</v>
       </c>
       <c r="J9" s="5">
-        <v>84.2</v>
+        <v>87.3</v>
       </c>
       <c r="K9" s="5">
         <v>159</v>
@@ -9471,13 +9852,13 @@
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>109</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>110</v>
       </c>
       <c r="D10" s="5" t="b">
         <v>1</v>
@@ -9498,7 +9879,7 @@
         <v>510</v>
       </c>
       <c r="J10" s="5">
-        <v>207.12</v>
+        <v>154.86</v>
       </c>
       <c r="K10" s="5">
         <v>0</v>
@@ -9515,13 +9896,13 @@
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B11" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>101</v>
       </c>
       <c r="D11" s="5" t="b">
         <v>0</v>
@@ -9542,7 +9923,7 @@
         <v>138.5</v>
       </c>
       <c r="J11" s="5">
-        <v>87.98</v>
+        <v>90.59</v>
       </c>
       <c r="K11" s="5">
         <v>122</v>
@@ -9559,13 +9940,13 @@
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D12" s="5" t="b">
         <v>1</v>
@@ -9586,7 +9967,7 @@
         <v>282</v>
       </c>
       <c r="J12" s="5">
-        <v>95.77</v>
+        <v>105.27</v>
       </c>
       <c r="K12" s="5">
         <v>29</v>
@@ -9603,13 +9984,13 @@
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B13" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>101</v>
       </c>
       <c r="D13" s="5" t="b">
         <v>0</v>
@@ -9630,7 +10011,7 @@
         <v>137.2</v>
       </c>
       <c r="J13" s="5">
-        <v>88.06</v>
+        <v>90.66</v>
       </c>
       <c r="K13" s="5">
         <v>134</v>
@@ -9647,13 +10028,13 @@
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B14" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>101</v>
       </c>
       <c r="D14" s="5" t="b">
         <v>0</v>
@@ -9674,7 +10055,7 @@
         <v>116</v>
       </c>
       <c r="J14" s="5">
-        <v>89.51000000000001</v>
+        <v>91.93000000000001</v>
       </c>
       <c r="K14" s="5">
         <v>92</v>
@@ -9691,13 +10072,13 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B15" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>101</v>
       </c>
       <c r="D15" s="5" t="b">
         <v>0</v>
@@ -9718,7 +10099,7 @@
         <v>77</v>
       </c>
       <c r="J15" s="5">
-        <v>92.18000000000001</v>
+        <v>94.25</v>
       </c>
       <c r="K15" s="5">
         <v>-100</v>
@@ -9735,13 +10116,13 @@
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B16" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>101</v>
       </c>
       <c r="D16" s="5" t="b">
         <v>0</v>
@@ -9762,7 +10143,7 @@
         <v>396.5</v>
       </c>
       <c r="J16" s="5">
-        <v>70.34</v>
+        <v>75.23</v>
       </c>
       <c r="K16" s="5">
         <v>39</v>
@@ -9779,13 +10160,13 @@
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B17" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>101</v>
       </c>
       <c r="D17" s="5" t="b">
         <v>0</v>
@@ -9806,7 +10187,7 @@
         <v>326.2</v>
       </c>
       <c r="J17" s="5">
-        <v>75.14</v>
+        <v>79.41</v>
       </c>
       <c r="K17" s="5">
         <v>39</v>
@@ -9823,13 +10204,13 @@
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B18" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>101</v>
       </c>
       <c r="D18" s="5" t="b">
         <v>0</v>
@@ -9850,7 +10231,7 @@
         <v>97.8</v>
       </c>
       <c r="J18" s="5">
-        <v>90.76000000000001</v>
+        <v>93.01000000000001</v>
       </c>
       <c r="K18" s="5">
         <v>129</v>
@@ -9867,13 +10248,13 @@
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B19" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>101</v>
       </c>
       <c r="D19" s="5" t="b">
         <v>0</v>
@@ -9894,7 +10275,7 @@
         <v>107</v>
       </c>
       <c r="J19" s="5">
-        <v>90.13</v>
+        <v>92.45999999999999</v>
       </c>
       <c r="K19" s="5">
         <v>0</v>
@@ -9911,13 +10292,13 @@
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B20" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>101</v>
       </c>
       <c r="D20" s="5" t="b">
         <v>0</v>
@@ -9938,7 +10319,7 @@
         <v>55.8</v>
       </c>
       <c r="J20" s="5">
-        <v>93.63</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="K20" s="5">
         <v>88</v>
@@ -9955,13 +10336,13 @@
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D21" s="5" t="b">
         <v>1</v>
@@ -9982,7 +10363,7 @@
         <v>207</v>
       </c>
       <c r="J21" s="5">
-        <v>217.48</v>
+        <v>163.88</v>
       </c>
       <c r="K21" s="5">
         <v>5</v>
@@ -9999,13 +10380,13 @@
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D22" s="5" t="b">
         <v>1</v>
@@ -10026,7 +10407,7 @@
         <v>173.4</v>
       </c>
       <c r="J22" s="5">
-        <v>193.84</v>
+        <v>195.74</v>
       </c>
       <c r="K22" s="5">
         <v>29</v>
@@ -10043,13 +10424,13 @@
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B23" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C23" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>101</v>
       </c>
       <c r="D23" s="5" t="b">
         <v>0</v>
@@ -10070,7 +10451,7 @@
         <v>57</v>
       </c>
       <c r="J23" s="5">
-        <v>93.55</v>
+        <v>95.44</v>
       </c>
       <c r="K23" s="5">
         <v>-90</v>
@@ -10087,13 +10468,13 @@
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B24" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C24" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>101</v>
       </c>
       <c r="D24" s="5" t="b">
         <v>0</v>
@@ -10114,7 +10495,7 @@
         <v>76.2</v>
       </c>
       <c r="J24" s="5">
-        <v>92.23</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="K24" s="5">
         <v>-86</v>
@@ -10131,13 +10512,13 @@
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B25" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C25" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>101</v>
       </c>
       <c r="D25" s="5" t="b">
         <v>0</v>
@@ -10158,7 +10539,7 @@
         <v>224.2</v>
       </c>
       <c r="J25" s="5">
-        <v>82.11</v>
+        <v>85.48</v>
       </c>
       <c r="K25" s="5">
         <v>39</v>
@@ -10175,13 +10556,13 @@
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B26" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C26" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>101</v>
       </c>
       <c r="D26" s="5" t="b">
         <v>0</v>
@@ -10202,7 +10583,7 @@
         <v>85</v>
       </c>
       <c r="J26" s="5">
-        <v>91.63</v>
+        <v>93.77</v>
       </c>
       <c r="K26" s="5">
         <v>-80</v>
@@ -10219,13 +10600,13 @@
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B27" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C27" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>101</v>
       </c>
       <c r="D27" s="5" t="b">
         <v>0</v>
@@ -10246,7 +10627,7 @@
         <v>161.2</v>
       </c>
       <c r="J27" s="5">
-        <v>86.42</v>
+        <v>89.23</v>
       </c>
       <c r="K27" s="5">
         <v>39</v>
@@ -10263,13 +10644,13 @@
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D28" s="5" t="b">
         <v>1</v>
@@ -10290,7 +10671,7 @@
         <v>1586</v>
       </c>
       <c r="J28" s="5">
-        <v>51.2</v>
+        <v>66.45999999999999</v>
       </c>
       <c r="K28" s="5">
         <v>39</v>
@@ -10307,13 +10688,13 @@
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B29" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C29" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>101</v>
       </c>
       <c r="D29" s="5" t="b">
         <v>0</v>
@@ -10334,7 +10715,7 @@
         <v>87.5</v>
       </c>
       <c r="J29" s="5">
-        <v>91.45999999999999</v>
+        <v>93.62</v>
       </c>
       <c r="K29" s="5">
         <v>0</v>
@@ -10351,13 +10732,13 @@
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B30" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C30" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>101</v>
       </c>
       <c r="D30" s="5" t="b">
         <v>0</v>
@@ -10378,7 +10759,7 @@
         <v>57.8</v>
       </c>
       <c r="J30" s="5">
-        <v>93.5</v>
+        <v>95.39</v>
       </c>
       <c r="K30" s="5">
         <v>49</v>
@@ -10395,13 +10776,13 @@
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D31" s="5" t="b">
         <v>1</v>
@@ -10422,7 +10803,7 @@
         <v>1305</v>
       </c>
       <c r="J31" s="5">
-        <v>60.81</v>
+        <v>74.81999999999999</v>
       </c>
       <c r="K31" s="5">
         <v>39</v>
@@ -10439,13 +10820,13 @@
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B32" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C32" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>101</v>
       </c>
       <c r="D32" s="5" t="b">
         <v>0</v>
@@ -10466,7 +10847,7 @@
         <v>186</v>
       </c>
       <c r="J32" s="5">
-        <v>84.73</v>
+        <v>87.76000000000001</v>
       </c>
       <c r="K32" s="5">
         <v>40</v>
@@ -10483,13 +10864,13 @@
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B33" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C33" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>101</v>
       </c>
       <c r="D33" s="5" t="b">
         <v>0</v>
@@ -10510,7 +10891,7 @@
         <v>77.2</v>
       </c>
       <c r="J33" s="5">
-        <v>92.16</v>
+        <v>94.23</v>
       </c>
       <c r="K33" s="5">
         <v>75</v>
@@ -10527,13 +10908,13 @@
     </row>
     <row r="34" spans="1:14">
       <c r="A34" s="5" t="s">
-        <v>82</v>
+        <v>126</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D34" s="5" t="b">
         <v>1</v>
@@ -10554,7 +10935,7 @@
         <v>403</v>
       </c>
       <c r="J34" s="5">
-        <v>210.78</v>
+        <v>158.04</v>
       </c>
       <c r="K34" s="5">
         <v>0</v>
@@ -10574,10 +10955,10 @@
         <v>127</v>
       </c>
       <c r="B35" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C35" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>101</v>
       </c>
       <c r="D35" s="5" t="b">
         <v>0</v>
@@ -10598,7 +10979,7 @@
         <v>84.2</v>
       </c>
       <c r="J35" s="5">
-        <v>91.68000000000001</v>
+        <v>93.81999999999999</v>
       </c>
       <c r="K35" s="5">
         <v>0</v>
@@ -10618,7 +10999,7 @@
         <v>128</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>129</v>
@@ -10642,7 +11023,7 @@
         <v>148.1</v>
       </c>
       <c r="J36" s="5">
-        <v>76.34999999999999</v>
+        <v>110.57</v>
       </c>
       <c r="K36" s="5">
         <v>0</v>
@@ -10659,13 +11040,13 @@
     </row>
     <row r="37" spans="1:14">
       <c r="A37" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D37" s="5" t="b">
         <v>1</v>
@@ -10686,7 +11067,7 @@
         <v>897</v>
       </c>
       <c r="J37" s="5">
-        <v>74.75</v>
+        <v>86.97</v>
       </c>
       <c r="K37" s="5">
         <v>39</v>
@@ -10703,13 +11084,13 @@
     </row>
     <row r="38" spans="1:14">
       <c r="A38" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D38" s="5" t="b">
         <v>1</v>
@@ -10730,7 +11111,7 @@
         <v>744</v>
       </c>
       <c r="J38" s="5">
-        <v>79.98</v>
+        <v>91.52</v>
       </c>
       <c r="K38" s="5">
         <v>40</v>
@@ -10747,13 +11128,13 @@
     </row>
     <row r="39" spans="1:14">
       <c r="A39" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D39" s="5" t="b">
         <v>1</v>
@@ -10774,7 +11155,7 @@
         <v>645</v>
       </c>
       <c r="J39" s="5">
-        <v>83.36</v>
+        <v>94.47</v>
       </c>
       <c r="K39" s="5">
         <v>39</v>
@@ -10794,10 +11175,10 @@
         <v>130</v>
       </c>
       <c r="B40" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C40" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>101</v>
       </c>
       <c r="D40" s="5" t="b">
         <v>0</v>
@@ -10818,7 +11199,7 @@
         <v>67</v>
       </c>
       <c r="J40" s="5">
-        <v>92.86</v>
+        <v>94.84</v>
       </c>
       <c r="K40" s="5">
         <v>0</v>
@@ -10838,10 +11219,10 @@
         <v>131</v>
       </c>
       <c r="B41" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C41" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>101</v>
       </c>
       <c r="D41" s="5" t="b">
         <v>0</v>
@@ -10862,7 +11243,7 @@
         <v>115.2</v>
       </c>
       <c r="J41" s="5">
-        <v>89.56999999999999</v>
+        <v>91.97</v>
       </c>
       <c r="K41" s="5">
         <v>115</v>
@@ -10882,10 +11263,10 @@
         <v>132</v>
       </c>
       <c r="B42" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C42" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>101</v>
       </c>
       <c r="D42" s="5" t="b">
         <v>0</v>
@@ -10906,7 +11287,7 @@
         <v>79.8</v>
       </c>
       <c r="J42" s="5">
-        <v>91.98999999999999</v>
+        <v>94.08</v>
       </c>
       <c r="K42" s="5">
         <v>0</v>
@@ -10923,13 +11304,13 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D43" s="5" t="b">
         <v>1</v>
@@ -10950,7 +11331,7 @@
         <v>295</v>
       </c>
       <c r="J43" s="5">
-        <v>214.47</v>
+        <v>161.26</v>
       </c>
       <c r="K43" s="5">
         <v>0</v>
@@ -10967,13 +11348,13 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B44" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C44" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>101</v>
       </c>
       <c r="D44" s="5" t="b">
         <v>0</v>
@@ -10994,7 +11375,7 @@
         <v>98.8</v>
       </c>
       <c r="J44" s="5">
-        <v>90.69</v>
+        <v>92.95</v>
       </c>
       <c r="K44" s="5">
         <v>0</v>
@@ -11016,7 +11397,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -11025,7 +11406,7 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>19</v>
@@ -11042,16 +11423,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B2" s="5">
         <v>2</v>
       </c>
       <c r="C2" s="5">
-        <v>68.94</v>
+        <v>83.44</v>
       </c>
       <c r="D2" s="5">
-        <v>68.94</v>
+        <v>83.44</v>
       </c>
       <c r="E2" s="5" t="b">
         <v>0</v>
@@ -11059,16 +11440,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B3" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="5">
-        <v>285.57</v>
+        <v>185.94</v>
       </c>
       <c r="D3" s="5">
-        <v>285.57</v>
+        <v>185.94</v>
       </c>
       <c r="E3" s="5" t="b">
         <v>0</v>
@@ -11076,7 +11457,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B4" s="5">
         <v>1</v>
@@ -11096,16 +11477,16 @@
         <v>129</v>
       </c>
       <c r="B5" s="5">
+        <v>1</v>
+      </c>
+      <c r="C5" s="5">
+        <v>102.97</v>
+      </c>
+      <c r="D5" s="5">
+        <v>102.97</v>
+      </c>
+      <c r="E5" s="5" t="b">
         <v>0</v>
-      </c>
-      <c r="C5" s="5">
-        <v>45</v>
-      </c>
-      <c r="D5" s="5">
-        <v>45</v>
-      </c>
-      <c r="E5" s="5" t="b">
-        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -11149,13 +11530,13 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>89</v>
-      </c>
       <c r="C11" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>35</v>
@@ -11172,10 +11553,10 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C12" s="6">
         <v>46280.66598379629</v>
@@ -11195,10 +11576,10 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C13" s="6">
         <v>46280.80667824074</v>
@@ -11218,10 +11599,10 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C14" s="6">
         <v>46280.90626157408</v>
@@ -11233,18 +11614,18 @@
         <v>516.79</v>
       </c>
       <c r="F14" s="5">
-        <v>597.75</v>
+        <v>593.0599999999999</v>
       </c>
       <c r="G14" s="5">
-        <v>80.95999999999999</v>
+        <v>76.27</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C15" s="6">
         <v>46281.08846064815</v>
@@ -11253,21 +11634,21 @@
         <v>305</v>
       </c>
       <c r="E15" s="5">
-        <v>465.01</v>
+        <v>466.42</v>
       </c>
       <c r="F15" s="5">
         <v>593.0599999999999</v>
       </c>
       <c r="G15" s="5">
-        <v>128.04</v>
+        <v>126.63</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C16" s="6">
         <v>46281.20115740741</v>
@@ -11287,10 +11668,10 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C17" s="6">
         <v>46281.25833333333</v>
@@ -11299,21 +11680,21 @@
         <v>340</v>
       </c>
       <c r="E17" s="5">
-        <v>513.83</v>
+        <v>513.9</v>
       </c>
       <c r="F17" s="5">
         <v>593.0599999999999</v>
       </c>
       <c r="G17" s="5">
-        <v>79.23</v>
+        <v>79.16</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C18" s="6">
         <v>46281.29935185185</v>
@@ -11322,21 +11703,21 @@
         <v>645</v>
       </c>
       <c r="E18" s="5">
-        <v>515.33</v>
+        <v>515.4</v>
       </c>
       <c r="F18" s="5">
         <v>593.0599999999999</v>
       </c>
       <c r="G18" s="5">
-        <v>77.73</v>
+        <v>77.66</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C19" s="6">
         <v>46281.31875</v>
@@ -11345,21 +11726,21 @@
         <v>1586</v>
       </c>
       <c r="E19" s="5">
-        <v>516.13</v>
+        <v>516.1</v>
       </c>
       <c r="F19" s="5">
         <v>593.0599999999999</v>
       </c>
       <c r="G19" s="5">
-        <v>76.92</v>
+        <v>76.95999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C20" s="6">
         <v>46281.41905092593</v>
@@ -11371,18 +11752,18 @@
         <v>526.27</v>
       </c>
       <c r="F20" s="5">
-        <v>593.0599999999999</v>
+        <v>615.95</v>
       </c>
       <c r="G20" s="5">
-        <v>66.79000000000001</v>
+        <v>89.68000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C21" s="6">
         <v>46281.45834490741</v>
@@ -11391,21 +11772,21 @@
         <v>231</v>
       </c>
       <c r="E21" s="5">
-        <v>528.11</v>
+        <v>528.17</v>
       </c>
       <c r="F21" s="5">
-        <v>593.0599999999999</v>
+        <v>622</v>
       </c>
       <c r="G21" s="5">
-        <v>64.95</v>
+        <v>93.83</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C22" s="6">
         <v>46281.5</v>
@@ -11417,18 +11798,18 @@
         <v>532.09</v>
       </c>
       <c r="F22" s="5">
-        <v>593.0599999999999</v>
+        <v>622</v>
       </c>
       <c r="G22" s="5">
-        <v>60.97</v>
+        <v>89.91</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C23" s="6">
         <v>46281.55842592593</v>
@@ -11437,21 +11818,21 @@
         <v>744</v>
       </c>
       <c r="E23" s="5">
-        <v>534.39</v>
+        <v>534.3</v>
       </c>
       <c r="F23" s="5">
-        <v>586.38</v>
+        <v>622</v>
       </c>
       <c r="G23" s="5">
-        <v>51.99</v>
+        <v>87.7</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C24" s="6">
         <v>46281.65149305556</v>
@@ -11460,13 +11841,82 @@
         <v>309</v>
       </c>
       <c r="E24" s="5">
-        <v>536.45</v>
+        <v>536.4</v>
       </c>
       <c r="F24" s="5">
-        <v>566.83</v>
+        <v>622</v>
       </c>
       <c r="G24" s="5">
-        <v>30.38</v>
+        <v>85.59999999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C25" s="6">
+        <v>46281.92517361111</v>
+      </c>
+      <c r="D25" s="5">
+        <v>403</v>
+      </c>
+      <c r="E25" s="5">
+        <v>535.7</v>
+      </c>
+      <c r="F25" s="5">
+        <v>622</v>
+      </c>
+      <c r="G25" s="5">
+        <v>86.3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="C26" s="6">
+        <v>46281.98386574074</v>
+      </c>
+      <c r="D26" s="5">
+        <v>337</v>
+      </c>
+      <c r="E26" s="5">
+        <v>528.38</v>
+      </c>
+      <c r="F26" s="5">
+        <v>622</v>
+      </c>
+      <c r="G26" s="5">
+        <v>93.62</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="C27" s="6">
+        <v>46282.03425925926</v>
+      </c>
+      <c r="D27" s="5">
+        <v>404</v>
+      </c>
+      <c r="E27" s="5">
+        <v>519.03</v>
+      </c>
+      <c r="F27" s="5">
+        <v>622</v>
+      </c>
+      <c r="G27" s="5">
+        <v>102.97</v>
       </c>
     </row>
   </sheetData>

--- a/docs/reports/swift_space_weather_report_latest.xlsx
+++ b/docs/reports/swift_space_weather_report_latest.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="162">
   <si>
     <t>SWIFT Space Weather Excel Report</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Updated UTC</t>
   </si>
   <si>
-    <t>2026-09-17T11:52:17Z</t>
+    <t>2026-09-17T21:30:52Z</t>
   </si>
   <si>
     <t>Main URL root</t>
@@ -267,16 +267,16 @@
     <t>Risk</t>
   </si>
   <si>
+    <t>LOW</t>
+  </si>
+  <si>
+    <t>2026-09-13T21:12:00-CME-001</t>
+  </si>
+  <si>
+    <t>2026-09-13T10:23:00-CME-001</t>
+  </si>
+  <si>
     <t>MODERATE</t>
-  </si>
-  <si>
-    <t>2026-09-13T21:12:00-CME-001</t>
-  </si>
-  <si>
-    <t>LOW</t>
-  </si>
-  <si>
-    <t>2026-09-13T10:23:00-CME-001</t>
   </si>
   <si>
     <t>2026-09-15T08:36:00-CME-001</t>
@@ -671,10 +671,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>SolarWind_27d!$A$2:$A$50</c:f>
+              <c:f>SolarWind_27d!$A$2:$A$60</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="49"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>46280.45833333334</c:v>
                 </c:pt>
@@ -821,16 +821,46 @@
                 </c:pt>
                 <c:pt idx="48">
                   <c:v>46282.45833333334</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>46282.5</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>46282.54166666666</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>46282.58333333334</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>46282.625</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>46282.66666666666</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46282.70833333334</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46282.75</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46282.79166666666</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46282.83333333334</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46282.875</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>SolarWind_27d!$B$2:$B$50</c:f>
+              <c:f>SolarWind_27d!$B$2:$B$60</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="49"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>546.005</c:v>
                 </c:pt>
@@ -904,79 +934,109 @@
                   <c:v>544.0549999999999</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>537.5</c:v>
+                  <c:v>537.65</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>550.22</c:v>
+                  <c:v>549.265</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>563.34</c:v>
+                  <c:v>561.3150000000001</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>545.0650000000001</c:v>
+                  <c:v>545.145</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>533.05</c:v>
+                  <c:v>534.4299999999999</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>524.975</c:v>
+                  <c:v>524.6</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>535.105</c:v>
+                  <c:v>537.705</c:v>
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>523.22</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>501.2</c:v>
+                  <c:v>501.75</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>509.625</c:v>
+                  <c:v>509.8</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>501.875</c:v>
+                  <c:v>502.215</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>514.26</c:v>
+                  <c:v>512.5599999999999</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>506.995</c:v>
+                  <c:v>505.765</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>504.07</c:v>
+                  <c:v>504.475</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>496.04</c:v>
+                  <c:v>506.52</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>550.135</c:v>
+                  <c:v>547.45</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>512.7</c:v>
+                  <c:v>509.5</c:v>
                 </c:pt>
                 <c:pt idx="41">
                   <c:v>495.15</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>497.73</c:v>
+                  <c:v>497.57</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>476.33</c:v>
+                  <c:v>476.755</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>484.215</c:v>
+                  <c:v>485.05</c:v>
                 </c:pt>
                 <c:pt idx="45">
                   <c:v>476.55</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>475.22</c:v>
+                  <c:v>475.84</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>486.615</c:v>
+                  <c:v>488.935</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>484.775</c:v>
+                  <c:v>482.74</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>474.85</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>464.35</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>459.115</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>450.13</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>460.725</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>465.735</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>475.8</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>479.955</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>469.35</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>462.12</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1100,10 +1160,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>SolarWind_27d!$A$2:$A$50</c:f>
+              <c:f>SolarWind_27d!$A$2:$A$60</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="49"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>46280.45833333334</c:v>
                 </c:pt>
@@ -1250,16 +1310,46 @@
                 </c:pt>
                 <c:pt idx="48">
                   <c:v>46282.45833333334</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>46282.5</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>46282.54166666666</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>46282.58333333334</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>46282.625</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>46282.66666666666</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46282.70833333334</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46282.75</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46282.79166666666</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46282.83333333334</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46282.875</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>SolarWind_27d!$D$2:$D$50</c:f>
+              <c:f>SolarWind_27d!$D$2:$D$60</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="49"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>8.85</c:v>
                 </c:pt>
@@ -1333,79 +1423,109 @@
                   <c:v>-2.22</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>-2.38</c:v>
+                  <c:v>-2.33</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.955</c:v>
+                  <c:v>0.605</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>3.095</c:v>
+                  <c:v>2.99</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>4.83</c:v>
+                  <c:v>4.82</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>4.315</c:v>
+                  <c:v>4.235</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>4.11</c:v>
+                  <c:v>4.14</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>4.115</c:v>
+                  <c:v>4.15</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>2.985</c:v>
+                  <c:v>3.02</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>2.11</c:v>
+                  <c:v>2.185</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.655</c:v>
+                  <c:v>0.54</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>1.945</c:v>
+                  <c:v>1.965</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>2.27</c:v>
+                  <c:v>2.29</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>2.49</c:v>
+                  <c:v>3.02</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.18</c:v>
+                  <c:v>0.005</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>-0.16</c:v>
+                  <c:v>-0.28</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>3.01</c:v>
+                  <c:v>3.5</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>2.925</c:v>
+                  <c:v>3.145</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>2.205</c:v>
+                  <c:v>2.24</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.1</c:v>
+                  <c:v>-0.09</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.775</c:v>
+                  <c:v>1.17</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>1.525</c:v>
+                  <c:v>1.6</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>2.285</c:v>
+                  <c:v>2.265</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>2.09</c:v>
+                  <c:v>2.04</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>-2.61</c:v>
+                  <c:v>-2.655</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>-2.79</c:v>
+                  <c:v>-2.42</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>-0.045</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>-0.23</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.115</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.37</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>-0.305</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.44</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>2.46</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1.63</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-1.71</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.03</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1422,10 +1542,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>SolarWind_27d!$A$2:$A$50</c:f>
+              <c:f>SolarWind_27d!$A$2:$A$60</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="49"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>46280.45833333334</c:v>
                 </c:pt>
@@ -1572,16 +1692,46 @@
                 </c:pt>
                 <c:pt idx="48">
                   <c:v>46282.45833333334</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>46282.5</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>46282.54166666666</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>46282.58333333334</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>46282.625</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>46282.66666666666</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46282.70833333334</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46282.75</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46282.79166666666</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46282.83333333334</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46282.875</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>SolarWind_27d!$E$2:$E$50</c:f>
+              <c:f>SolarWind_27d!$E$2:$E$60</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="49"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>12.92</c:v>
                 </c:pt>
@@ -1655,58 +1805,58 @@
                   <c:v>4.725</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>4.37</c:v>
+                  <c:v>4.26</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>4.465</c:v>
+                  <c:v>4.39</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>4.9</c:v>
+                  <c:v>4.97</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>5.475</c:v>
+                  <c:v>5.47</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>5.835</c:v>
+                  <c:v>5.82</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>5.62</c:v>
+                  <c:v>5.61</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>5.63</c:v>
+                  <c:v>5.73</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>5.45</c:v>
+                  <c:v>5.42</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>4.685</c:v>
+                  <c:v>4.68</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>5.03</c:v>
+                  <c:v>5.01</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>4.905</c:v>
+                  <c:v>4.91</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>5.01</c:v>
+                  <c:v>4.98</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>4.755</c:v>
+                  <c:v>4.92</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>5.165</c:v>
+                  <c:v>5.1</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>6.08</c:v>
+                  <c:v>5.84</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>7.25</c:v>
+                  <c:v>7.2</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>6.175</c:v>
+                  <c:v>6.075</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>5.735</c:v>
+                  <c:v>5.725</c:v>
                 </c:pt>
                 <c:pt idx="42">
                   <c:v>4.63</c:v>
@@ -1715,19 +1865,49 @@
                   <c:v>4.33</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>4.21</c:v>
+                  <c:v>4.23</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>3.76</c:v>
+                  <c:v>3.81</c:v>
                 </c:pt>
                 <c:pt idx="46">
                   <c:v>3.69</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>3.625</c:v>
+                  <c:v>3.665</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>3.88</c:v>
+                  <c:v>3.85</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>3.695</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>3.62</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>3.415</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>3.55</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>3.76</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>3.7</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>4.49</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>4.435</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>3.53</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>3.39</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1856,232 +2036,232 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="76"/>
                 <c:pt idx="0">
-                  <c:v>46282.33333333334</c:v>
+                  <c:v>46282.75</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>46282.375</c:v>
+                  <c:v>46282.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46282.41666666666</c:v>
+                  <c:v>46282.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46282.45833333334</c:v>
+                  <c:v>46282.875</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46282.5</c:v>
+                  <c:v>46282.91666666666</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46282.54166666666</c:v>
+                  <c:v>46282.95833333334</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46282.58333333334</c:v>
+                  <c:v>46283</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>46282.625</c:v>
+                  <c:v>46283.04166666666</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>46282.66666666666</c:v>
+                  <c:v>46283.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>46282.70833333334</c:v>
+                  <c:v>46283.125</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>46282.75</c:v>
+                  <c:v>46283.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>46282.79166666666</c:v>
+                  <c:v>46283.20833333334</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>46282.83333333334</c:v>
+                  <c:v>46283.25</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>46282.875</c:v>
+                  <c:v>46283.29166666666</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>46282.91666666666</c:v>
+                  <c:v>46283.33333333334</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46282.95833333334</c:v>
+                  <c:v>46283.375</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>46283</c:v>
+                  <c:v>46283.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>46283.04166666666</c:v>
+                  <c:v>46283.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>46283.08333333334</c:v>
+                  <c:v>46283.5</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>46283.125</c:v>
+                  <c:v>46283.54166666666</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>46283.16666666666</c:v>
+                  <c:v>46283.58333333334</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>46283.20833333334</c:v>
+                  <c:v>46283.625</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>46283.25</c:v>
+                  <c:v>46283.66666666666</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>46283.29166666666</c:v>
+                  <c:v>46283.70833333334</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>46283.33333333334</c:v>
+                  <c:v>46283.75</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>46283.375</c:v>
+                  <c:v>46283.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>46283.41666666666</c:v>
+                  <c:v>46283.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>46283.45833333334</c:v>
+                  <c:v>46283.875</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>46283.5</c:v>
+                  <c:v>46283.91666666666</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>46283.54166666666</c:v>
+                  <c:v>46283.95833333334</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>46283.58333333334</c:v>
+                  <c:v>46284</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>46283.625</c:v>
+                  <c:v>46284.04166666666</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>46283.66666666666</c:v>
+                  <c:v>46284.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>46283.70833333334</c:v>
+                  <c:v>46284.125</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>46283.75</c:v>
+                  <c:v>46284.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>46283.79166666666</c:v>
+                  <c:v>46284.20833333334</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>46283.83333333334</c:v>
+                  <c:v>46284.25</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>46283.875</c:v>
+                  <c:v>46284.29166666666</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>46283.91666666666</c:v>
+                  <c:v>46284.33333333334</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>46283.95833333334</c:v>
+                  <c:v>46284.375</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>46284</c:v>
+                  <c:v>46284.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>46284.04166666666</c:v>
+                  <c:v>46284.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>46284.08333333334</c:v>
+                  <c:v>46284.5</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>46284.125</c:v>
+                  <c:v>46284.54166666666</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>46284.16666666666</c:v>
+                  <c:v>46284.58333333334</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>46284.20833333334</c:v>
+                  <c:v>46284.625</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>46284.25</c:v>
+                  <c:v>46284.66666666666</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>46284.29166666666</c:v>
+                  <c:v>46284.70833333334</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>46284.33333333334</c:v>
+                  <c:v>46284.75</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>46284.375</c:v>
+                  <c:v>46284.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>46284.41666666666</c:v>
+                  <c:v>46284.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>46284.45833333334</c:v>
+                  <c:v>46284.875</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>46284.5</c:v>
+                  <c:v>46284.91666666666</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>46284.54166666666</c:v>
+                  <c:v>46284.95833333334</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>46284.58333333334</c:v>
+                  <c:v>46285</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>46284.625</c:v>
+                  <c:v>46285.04166666666</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>46284.66666666666</c:v>
+                  <c:v>46285.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>46284.70833333334</c:v>
+                  <c:v>46285.125</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>46284.75</c:v>
+                  <c:v>46285.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>46284.79166666666</c:v>
+                  <c:v>46285.20833333334</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>46284.83333333334</c:v>
+                  <c:v>46285.25</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>46284.875</c:v>
+                  <c:v>46285.29166666666</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>46284.91666666666</c:v>
+                  <c:v>46285.33333333334</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>46284.95833333334</c:v>
+                  <c:v>46285.375</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>46285</c:v>
+                  <c:v>46285.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>46285.04166666666</c:v>
+                  <c:v>46285.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>46285.08333333334</c:v>
+                  <c:v>46285.5</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>46285.125</c:v>
+                  <c:v>46285.54166666666</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>46285.16666666666</c:v>
+                  <c:v>46285.58333333334</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>46285.20833333334</c:v>
+                  <c:v>46285.625</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>46285.25</c:v>
+                  <c:v>46285.66666666666</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>46285.29166666666</c:v>
+                  <c:v>46285.70833333334</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>46285.33333333334</c:v>
+                  <c:v>46285.75</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>46285.375</c:v>
+                  <c:v>46285.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>46285.41666666666</c:v>
+                  <c:v>46285.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>46285.45833333334</c:v>
+                  <c:v>46285.875</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2093,232 +2273,232 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="76"/>
                 <c:pt idx="0">
-                  <c:v>565.8</c:v>
+                  <c:v>421.89</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>561.1900000000001</c:v>
+                  <c:v>411.97</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>552.84</c:v>
+                  <c:v>402.67</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>543.51</c:v>
+                  <c:v>395.15</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>540.49</c:v>
+                  <c:v>393.13</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>532.5</c:v>
+                  <c:v>390.41</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>521.25</c:v>
+                  <c:v>386.64</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>509.07</c:v>
+                  <c:v>381.23</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>497.46</c:v>
+                  <c:v>375.31</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>485.15</c:v>
+                  <c:v>368.64</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>471.84</c:v>
+                  <c:v>364.24</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>459.23</c:v>
+                  <c:v>360.9</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>446.35</c:v>
+                  <c:v>358.68</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>434.62</c:v>
+                  <c:v>356.85</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>423.84</c:v>
+                  <c:v>356.11</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>413.88</c:v>
+                  <c:v>357.13</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>404.68</c:v>
+                  <c:v>360.52</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>396.08</c:v>
+                  <c:v>362.56</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>389.34</c:v>
+                  <c:v>369.28</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>383.97</c:v>
+                  <c:v>376.3</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>379.7</c:v>
+                  <c:v>386.88</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>376.43</c:v>
+                  <c:v>398.76</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>374.24</c:v>
+                  <c:v>409.73</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>372.44</c:v>
+                  <c:v>417.73</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>371.73</c:v>
+                  <c:v>419.47</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>372.77</c:v>
+                  <c:v>415.66</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>376.15</c:v>
+                  <c:v>410.09</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>378.11</c:v>
+                  <c:v>403.62</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>384.76</c:v>
+                  <c:v>395.21</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>391.69</c:v>
+                  <c:v>387.44</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>402.18</c:v>
+                  <c:v>380.23</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>413.99</c:v>
+                  <c:v>371.98</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>424.88</c:v>
+                  <c:v>364.94</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>432.81</c:v>
+                  <c:v>358.77</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>434.46</c:v>
+                  <c:v>353.25</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>430.31</c:v>
+                  <c:v>348.25</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>424.5</c:v>
+                  <c:v>343.67</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>417.86</c:v>
+                  <c:v>339.43</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>409.08</c:v>
+                  <c:v>335.5</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>401.08</c:v>
+                  <c:v>331.84</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>393.73</c:v>
+                  <c:v>328.43</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>385.14</c:v>
+                  <c:v>325.23</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>377.91</c:v>
+                  <c:v>322.24</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>371.64</c:v>
+                  <c:v>319.55</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>366.08</c:v>
+                  <c:v>317.11</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>361.06</c:v>
+                  <c:v>314.88</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>356.49</c:v>
+                  <c:v>312.82</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>352.27</c:v>
+                  <c:v>310.93</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>348.36</c:v>
+                  <c:v>309.18</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>344.73</c:v>
+                  <c:v>307.6</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>341.34</c:v>
+                  <c:v>306.17</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>338.18</c:v>
+                  <c:v>304.87</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>335.22</c:v>
+                  <c:v>303.69</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>332.56</c:v>
+                  <c:v>302.6</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>330.15</c:v>
+                  <c:v>301.61</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>327.95</c:v>
+                  <c:v>300.6</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>325.92</c:v>
+                  <c:v>299.59</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>324.05</c:v>
+                  <c:v>298.61</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>322.32</c:v>
+                  <c:v>297.68</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>320.77</c:v>
+                  <c:v>296.79</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>319.37</c:v>
+                  <c:v>291.71</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>318.09</c:v>
+                  <c:v>288.56</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>316.93</c:v>
+                  <c:v>286.61</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>315.86</c:v>
+                  <c:v>285.41</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>314.89</c:v>
+                  <c:v>284.67</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>313.9</c:v>
+                  <c:v>284.21</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>312.91</c:v>
+                  <c:v>283.93</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>311.95</c:v>
+                  <c:v>283.77</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>311.04</c:v>
+                  <c:v>283.67</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>310.17</c:v>
+                  <c:v>283.61</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>305.08</c:v>
+                  <c:v>283.57</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>301.94</c:v>
+                  <c:v>283.56</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>300.01</c:v>
+                  <c:v>283.55</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>298.82</c:v>
+                  <c:v>283.55</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>298.09</c:v>
+                  <c:v>283.55</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>297.65</c:v>
+                  <c:v>283.56</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2340,232 +2520,232 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="76"/>
                 <c:pt idx="0">
-                  <c:v>46282.33333333334</c:v>
+                  <c:v>46282.75</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>46282.375</c:v>
+                  <c:v>46282.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46282.41666666666</c:v>
+                  <c:v>46282.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46282.45833333334</c:v>
+                  <c:v>46282.875</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46282.5</c:v>
+                  <c:v>46282.91666666666</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46282.54166666666</c:v>
+                  <c:v>46282.95833333334</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46282.58333333334</c:v>
+                  <c:v>46283</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>46282.625</c:v>
+                  <c:v>46283.04166666666</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>46282.66666666666</c:v>
+                  <c:v>46283.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>46282.70833333334</c:v>
+                  <c:v>46283.125</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>46282.75</c:v>
+                  <c:v>46283.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>46282.79166666666</c:v>
+                  <c:v>46283.20833333334</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>46282.83333333334</c:v>
+                  <c:v>46283.25</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>46282.875</c:v>
+                  <c:v>46283.29166666666</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>46282.91666666666</c:v>
+                  <c:v>46283.33333333334</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46282.95833333334</c:v>
+                  <c:v>46283.375</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>46283</c:v>
+                  <c:v>46283.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>46283.04166666666</c:v>
+                  <c:v>46283.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>46283.08333333334</c:v>
+                  <c:v>46283.5</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>46283.125</c:v>
+                  <c:v>46283.54166666666</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>46283.16666666666</c:v>
+                  <c:v>46283.58333333334</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>46283.20833333334</c:v>
+                  <c:v>46283.625</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>46283.25</c:v>
+                  <c:v>46283.66666666666</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>46283.29166666666</c:v>
+                  <c:v>46283.70833333334</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>46283.33333333334</c:v>
+                  <c:v>46283.75</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>46283.375</c:v>
+                  <c:v>46283.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>46283.41666666666</c:v>
+                  <c:v>46283.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>46283.45833333334</c:v>
+                  <c:v>46283.875</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>46283.5</c:v>
+                  <c:v>46283.91666666666</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>46283.54166666666</c:v>
+                  <c:v>46283.95833333334</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>46283.58333333334</c:v>
+                  <c:v>46284</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>46283.625</c:v>
+                  <c:v>46284.04166666666</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>46283.66666666666</c:v>
+                  <c:v>46284.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>46283.70833333334</c:v>
+                  <c:v>46284.125</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>46283.75</c:v>
+                  <c:v>46284.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>46283.79166666666</c:v>
+                  <c:v>46284.20833333334</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>46283.83333333334</c:v>
+                  <c:v>46284.25</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>46283.875</c:v>
+                  <c:v>46284.29166666666</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>46283.91666666666</c:v>
+                  <c:v>46284.33333333334</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>46283.95833333334</c:v>
+                  <c:v>46284.375</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>46284</c:v>
+                  <c:v>46284.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>46284.04166666666</c:v>
+                  <c:v>46284.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>46284.08333333334</c:v>
+                  <c:v>46284.5</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>46284.125</c:v>
+                  <c:v>46284.54166666666</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>46284.16666666666</c:v>
+                  <c:v>46284.58333333334</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>46284.20833333334</c:v>
+                  <c:v>46284.625</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>46284.25</c:v>
+                  <c:v>46284.66666666666</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>46284.29166666666</c:v>
+                  <c:v>46284.70833333334</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>46284.33333333334</c:v>
+                  <c:v>46284.75</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>46284.375</c:v>
+                  <c:v>46284.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>46284.41666666666</c:v>
+                  <c:v>46284.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>46284.45833333334</c:v>
+                  <c:v>46284.875</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>46284.5</c:v>
+                  <c:v>46284.91666666666</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>46284.54166666666</c:v>
+                  <c:v>46284.95833333334</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>46284.58333333334</c:v>
+                  <c:v>46285</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>46284.625</c:v>
+                  <c:v>46285.04166666666</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>46284.66666666666</c:v>
+                  <c:v>46285.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>46284.70833333334</c:v>
+                  <c:v>46285.125</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>46284.75</c:v>
+                  <c:v>46285.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>46284.79166666666</c:v>
+                  <c:v>46285.20833333334</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>46284.83333333334</c:v>
+                  <c:v>46285.25</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>46284.875</c:v>
+                  <c:v>46285.29166666666</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>46284.91666666666</c:v>
+                  <c:v>46285.33333333334</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>46284.95833333334</c:v>
+                  <c:v>46285.375</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>46285</c:v>
+                  <c:v>46285.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>46285.04166666666</c:v>
+                  <c:v>46285.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>46285.08333333334</c:v>
+                  <c:v>46285.5</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>46285.125</c:v>
+                  <c:v>46285.54166666666</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>46285.16666666666</c:v>
+                  <c:v>46285.58333333334</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>46285.20833333334</c:v>
+                  <c:v>46285.625</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>46285.25</c:v>
+                  <c:v>46285.66666666666</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>46285.29166666666</c:v>
+                  <c:v>46285.70833333334</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>46285.33333333334</c:v>
+                  <c:v>46285.75</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>46285.375</c:v>
+                  <c:v>46285.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>46285.41666666666</c:v>
+                  <c:v>46285.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>46285.45833333334</c:v>
+                  <c:v>46285.875</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2577,232 +2757,232 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="76"/>
                 <c:pt idx="0">
-                  <c:v>292.82</c:v>
+                  <c:v>272.13</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>289.22</c:v>
+                  <c:v>271.87</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>286.72</c:v>
+                  <c:v>273.53</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>286.72</c:v>
+                  <c:v>274.35</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>288.02</c:v>
+                  <c:v>275.29</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>288.72</c:v>
+                  <c:v>277.17</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>288.48</c:v>
+                  <c:v>278.83</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>288.4</c:v>
+                  <c:v>280.17</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>289.22</c:v>
+                  <c:v>280.59</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>289.21</c:v>
+                  <c:v>279.8</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>287.84</c:v>
+                  <c:v>280.77</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>286.67</c:v>
+                  <c:v>282.15</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>285.64</c:v>
+                  <c:v>283.8</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>284.72</c:v>
+                  <c:v>284.7</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>283.89</c:v>
+                  <c:v>285.13</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>283.12</c:v>
+                  <c:v>285.29</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>282.45</c:v>
+                  <c:v>285.31</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>282.99</c:v>
+                  <c:v>285.27</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>284.27</c:v>
+                  <c:v>285.21</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>286.02</c:v>
+                  <c:v>285.03</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>288.05</c:v>
+                  <c:v>284.79</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>290.24</c:v>
+                  <c:v>284.5</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>292.54</c:v>
+                  <c:v>284.19</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>293.98</c:v>
+                  <c:v>283.85</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>294.88</c:v>
+                  <c:v>283.51</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>295.45</c:v>
+                  <c:v>283.19</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>295.8</c:v>
+                  <c:v>282.88</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>296.02</c:v>
+                  <c:v>282.59</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>296.15</c:v>
+                  <c:v>282.3</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>296.14</c:v>
+                  <c:v>282.01</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>296.04</c:v>
+                  <c:v>281.73</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>295.87</c:v>
+                  <c:v>281.52</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>295.67</c:v>
+                  <c:v>281.36</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>295.44</c:v>
+                  <c:v>281.24</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>295.19</c:v>
+                  <c:v>281.13</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>294.96</c:v>
+                  <c:v>281.03</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>294.74</c:v>
+                  <c:v>280.93</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>294.53</c:v>
+                  <c:v>280.84</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>294.32</c:v>
+                  <c:v>280.75</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>294.11</c:v>
+                  <c:v>280.66</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>293.9</c:v>
+                  <c:v>280.56</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>293.76</c:v>
+                  <c:v>280.47</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>293.67</c:v>
+                  <c:v>280.37</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>293.6</c:v>
+                  <c:v>280.39</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>293.55</c:v>
+                  <c:v>280.48</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>293.51</c:v>
+                  <c:v>280.61</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>293.47</c:v>
+                  <c:v>280.77</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>293.44</c:v>
+                  <c:v>280.94</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>293.39</c:v>
+                  <c:v>281.12</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>293.35</c:v>
+                  <c:v>281.36</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>293.3</c:v>
+                  <c:v>281.62</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>293.26</c:v>
+                  <c:v>281.91</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>293.2</c:v>
+                  <c:v>282.2</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>293.26</c:v>
+                  <c:v>282.5</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>293.39</c:v>
+                  <c:v>282.81</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>293.56</c:v>
+                  <c:v>283</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>293.75</c:v>
+                  <c:v>283.13</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>293.96</c:v>
+                  <c:v>283.22</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>294.17</c:v>
+                  <c:v>283.28</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>294.44</c:v>
+                  <c:v>283.32</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>294.73</c:v>
+                  <c:v>283.35</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>295.04</c:v>
+                  <c:v>283.38</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>295.37</c:v>
+                  <c:v>283.4</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>295.69</c:v>
+                  <c:v>283.42</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>296.02</c:v>
+                  <c:v>283.43</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>296.24</c:v>
+                  <c:v>283.45</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>296.4</c:v>
+                  <c:v>283.46</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>296.5</c:v>
+                  <c:v>283.47</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>296.59</c:v>
+                  <c:v>283.48</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>296.65</c:v>
+                  <c:v>283.49</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>296.7</c:v>
+                  <c:v>283.5</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>296.75</c:v>
+                  <c:v>283.51</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>296.79</c:v>
+                  <c:v>283.52</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>296.82</c:v>
+                  <c:v>283.53</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>296.85</c:v>
+                  <c:v>283.54</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>296.88</c:v>
+                  <c:v>283.55</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2824,232 +3004,232 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="76"/>
                 <c:pt idx="0">
-                  <c:v>46282.33333333334</c:v>
+                  <c:v>46282.75</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>46282.375</c:v>
+                  <c:v>46282.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46282.41666666666</c:v>
+                  <c:v>46282.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46282.45833333334</c:v>
+                  <c:v>46282.875</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46282.5</c:v>
+                  <c:v>46282.91666666666</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46282.54166666666</c:v>
+                  <c:v>46282.95833333334</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46282.58333333334</c:v>
+                  <c:v>46283</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>46282.625</c:v>
+                  <c:v>46283.04166666666</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>46282.66666666666</c:v>
+                  <c:v>46283.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>46282.70833333334</c:v>
+                  <c:v>46283.125</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>46282.75</c:v>
+                  <c:v>46283.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>46282.79166666666</c:v>
+                  <c:v>46283.20833333334</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>46282.83333333334</c:v>
+                  <c:v>46283.25</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>46282.875</c:v>
+                  <c:v>46283.29166666666</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>46282.91666666666</c:v>
+                  <c:v>46283.33333333334</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46282.95833333334</c:v>
+                  <c:v>46283.375</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>46283</c:v>
+                  <c:v>46283.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>46283.04166666666</c:v>
+                  <c:v>46283.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>46283.08333333334</c:v>
+                  <c:v>46283.5</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>46283.125</c:v>
+                  <c:v>46283.54166666666</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>46283.16666666666</c:v>
+                  <c:v>46283.58333333334</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>46283.20833333334</c:v>
+                  <c:v>46283.625</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>46283.25</c:v>
+                  <c:v>46283.66666666666</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>46283.29166666666</c:v>
+                  <c:v>46283.70833333334</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>46283.33333333334</c:v>
+                  <c:v>46283.75</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>46283.375</c:v>
+                  <c:v>46283.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>46283.41666666666</c:v>
+                  <c:v>46283.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>46283.45833333334</c:v>
+                  <c:v>46283.875</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>46283.5</c:v>
+                  <c:v>46283.91666666666</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>46283.54166666666</c:v>
+                  <c:v>46283.95833333334</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>46283.58333333334</c:v>
+                  <c:v>46284</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>46283.625</c:v>
+                  <c:v>46284.04166666666</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>46283.66666666666</c:v>
+                  <c:v>46284.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>46283.70833333334</c:v>
+                  <c:v>46284.125</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>46283.75</c:v>
+                  <c:v>46284.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>46283.79166666666</c:v>
+                  <c:v>46284.20833333334</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>46283.83333333334</c:v>
+                  <c:v>46284.25</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>46283.875</c:v>
+                  <c:v>46284.29166666666</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>46283.91666666666</c:v>
+                  <c:v>46284.33333333334</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>46283.95833333334</c:v>
+                  <c:v>46284.375</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>46284</c:v>
+                  <c:v>46284.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>46284.04166666666</c:v>
+                  <c:v>46284.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>46284.08333333334</c:v>
+                  <c:v>46284.5</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>46284.125</c:v>
+                  <c:v>46284.54166666666</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>46284.16666666666</c:v>
+                  <c:v>46284.58333333334</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>46284.20833333334</c:v>
+                  <c:v>46284.625</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>46284.25</c:v>
+                  <c:v>46284.66666666666</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>46284.29166666666</c:v>
+                  <c:v>46284.70833333334</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>46284.33333333334</c:v>
+                  <c:v>46284.75</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>46284.375</c:v>
+                  <c:v>46284.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>46284.41666666666</c:v>
+                  <c:v>46284.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>46284.45833333334</c:v>
+                  <c:v>46284.875</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>46284.5</c:v>
+                  <c:v>46284.91666666666</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>46284.54166666666</c:v>
+                  <c:v>46284.95833333334</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>46284.58333333334</c:v>
+                  <c:v>46285</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>46284.625</c:v>
+                  <c:v>46285.04166666666</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>46284.66666666666</c:v>
+                  <c:v>46285.08333333334</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>46284.70833333334</c:v>
+                  <c:v>46285.125</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>46284.75</c:v>
+                  <c:v>46285.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>46284.79166666666</c:v>
+                  <c:v>46285.20833333334</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>46284.83333333334</c:v>
+                  <c:v>46285.25</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>46284.875</c:v>
+                  <c:v>46285.29166666666</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>46284.91666666666</c:v>
+                  <c:v>46285.33333333334</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>46284.95833333334</c:v>
+                  <c:v>46285.375</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>46285</c:v>
+                  <c:v>46285.41666666666</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>46285.04166666666</c:v>
+                  <c:v>46285.45833333334</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>46285.08333333334</c:v>
+                  <c:v>46285.5</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>46285.125</c:v>
+                  <c:v>46285.54166666666</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>46285.16666666666</c:v>
+                  <c:v>46285.58333333334</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>46285.20833333334</c:v>
+                  <c:v>46285.625</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>46285.25</c:v>
+                  <c:v>46285.66666666666</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>46285.29166666666</c:v>
+                  <c:v>46285.70833333334</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>46285.33333333334</c:v>
+                  <c:v>46285.75</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>46285.375</c:v>
+                  <c:v>46285.79166666666</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>46285.41666666666</c:v>
+                  <c:v>46285.83333333334</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>46285.45833333334</c:v>
+                  <c:v>46285.875</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3061,214 +3241,214 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="76"/>
                 <c:pt idx="0">
-                  <c:v>351.75</c:v>
+                  <c:v>192.1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>350.44</c:v>
+                  <c:v>179.71</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>342.91</c:v>
+                  <c:v>165.65</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>330.87</c:v>
+                  <c:v>154.97</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>316.24</c:v>
+                  <c:v>144.98</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>295.85</c:v>
+                  <c:v>135.63</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>276.77</c:v>
+                  <c:v>126.93</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>258.92</c:v>
+                  <c:v>115.52</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>242.22</c:v>
+                  <c:v>108.24</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>226.6</c:v>
+                  <c:v>101.64</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>211.98</c:v>
+                  <c:v>95.84</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>198.31</c:v>
+                  <c:v>91.14</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>182.17</c:v>
+                  <c:v>87.94</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>170.42</c:v>
+                  <c:v>86.84999999999999</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>159.43</c:v>
+                  <c:v>88.61</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>149.15</c:v>
+                  <c:v>93.98</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>139.57</c:v>
+                  <c:v>103.55</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>126.51</c:v>
+                  <c:v>103.46</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>118.52</c:v>
+                  <c:v>122.07</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>111.25</c:v>
+                  <c:v>132.13</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>104.85</c:v>
+                  <c:v>153.6</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>99.56999999999999</c:v>
+                  <c:v>172.06</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>95.84999999999999</c:v>
+                  <c:v>184.65</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>94.29000000000001</c:v>
+                  <c:v>189.18</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>95.62</c:v>
+                  <c:v>178.8</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>100.63</c:v>
+                  <c:v>162.63</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>109.9</c:v>
+                  <c:v>152.14</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>109.45</c:v>
+                  <c:v>142.33</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>127.88</c:v>
+                  <c:v>127.84</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>137.7</c:v>
+                  <c:v>119.59</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>159.05</c:v>
+                  <c:v>111.88</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>177.38</c:v>
+                  <c:v>99.19</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>189.82</c:v>
+                  <c:v>92.8</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>194.15</c:v>
+                  <c:v>86.81</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>183.47</c:v>
+                  <c:v>81.20999999999999</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>166.15</c:v>
+                  <c:v>75.98</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>155.43</c:v>
+                  <c:v>71.08</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>145.41</c:v>
+                  <c:v>66.48999999999999</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>129.84</c:v>
+                  <c:v>62.2</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>121.47</c:v>
+                  <c:v>58.19</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>113.63</c:v>
+                  <c:v>54.44</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>99.98999999999999</c:v>
+                  <c:v>50.93</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>93.54000000000001</c:v>
+                  <c:v>47.64</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>87.51000000000001</c:v>
+                  <c:v>44.57</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>81.86</c:v>
+                  <c:v>41.7</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>76.58</c:v>
+                  <c:v>39.01</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>71.65000000000001</c:v>
+                  <c:v>36.49</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>67.03</c:v>
+                  <c:v>34.14</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>62.7</c:v>
+                  <c:v>31.94</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>58.66</c:v>
+                  <c:v>29.88</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>54.88</c:v>
+                  <c:v>27.95</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>51.34</c:v>
+                  <c:v>26.15</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>48.03</c:v>
+                  <c:v>24.46</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>44.93</c:v>
+                  <c:v>22.88</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>42.03</c:v>
+                  <c:v>21.41</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>39.32</c:v>
+                  <c:v>20.03</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>36.78</c:v>
+                  <c:v>18.74</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>34.41</c:v>
+                  <c:v>17.53</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>32.19</c:v>
+                  <c:v>16.4</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>30.12</c:v>
+                  <c:v>15.34</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>28.17</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>26.36</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>24.66</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>23.07</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>21.58</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>20.19</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>18.89</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>17.67</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>16.53</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>15.46</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="70">
                   <c:v>0</c:v>
@@ -3415,76 +3595,76 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="24"/>
                 <c:pt idx="0">
-                  <c:v>46282.5</c:v>
+                  <c:v>46283</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>46282.625</c:v>
+                  <c:v>46283.125</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46282.75</c:v>
+                  <c:v>46283.25</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46282.875</c:v>
+                  <c:v>46283.375</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46283</c:v>
+                  <c:v>46283.5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46283.125</c:v>
+                  <c:v>46283.625</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46283.25</c:v>
+                  <c:v>46283.75</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>46283.375</c:v>
+                  <c:v>46283.875</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>46283.5</c:v>
+                  <c:v>46284</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>46283.625</c:v>
+                  <c:v>46284.125</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>46283.75</c:v>
+                  <c:v>46284.25</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>46283.875</c:v>
+                  <c:v>46284.375</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>46284</c:v>
+                  <c:v>46284.5</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>46284.125</c:v>
+                  <c:v>46284.625</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>46284.25</c:v>
+                  <c:v>46284.75</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46284.375</c:v>
+                  <c:v>46284.875</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>46284.5</c:v>
+                  <c:v>46285</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>46284.625</c:v>
+                  <c:v>46285.125</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>46284.75</c:v>
+                  <c:v>46285.25</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>46284.875</c:v>
+                  <c:v>46285.375</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>46285</c:v>
+                  <c:v>46285.5</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>46285.125</c:v>
+                  <c:v>46285.625</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>46285.25</c:v>
+                  <c:v>46285.75</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>46285.375</c:v>
+                  <c:v>46285.875</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3496,43 +3676,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="24"/>
                 <c:pt idx="0">
+                  <c:v>0.67</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.33</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.33</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.33</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.67</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>1.33</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="6">
+                  <c:v>1.33</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.67</c:v>
-                </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="8">
                   <c:v>0.33</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="9">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="10">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.33</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.67</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1.33</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>1.33</c:v>
-                </c:pt>
                 <c:pt idx="11">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.33</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>0</c:v>
@@ -3694,79 +3874,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>46282.45833333334</c:v>
+                  <c:v>46282.875</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>46282.58333333334</c:v>
+                  <c:v>46283</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46282.70833333334</c:v>
+                  <c:v>46283.125</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46282.83333333334</c:v>
+                  <c:v>46283.25</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46282.95833333334</c:v>
+                  <c:v>46283.375</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46283.08333333334</c:v>
+                  <c:v>46283.5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46283.20833333334</c:v>
+                  <c:v>46283.625</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>46283.33333333334</c:v>
+                  <c:v>46283.75</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>46283.45833333334</c:v>
+                  <c:v>46283.875</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>46283.58333333334</c:v>
+                  <c:v>46284</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>46283.70833333334</c:v>
+                  <c:v>46284.125</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>46283.83333333334</c:v>
+                  <c:v>46284.25</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>46283.95833333334</c:v>
+                  <c:v>46284.375</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>46284.08333333334</c:v>
+                  <c:v>46284.5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>46284.20833333334</c:v>
+                  <c:v>46284.625</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46284.33333333334</c:v>
+                  <c:v>46284.75</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>46284.45833333334</c:v>
+                  <c:v>46284.875</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>46284.58333333334</c:v>
+                  <c:v>46285</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>46284.70833333334</c:v>
+                  <c:v>46285.125</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>46284.83333333334</c:v>
+                  <c:v>46285.25</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>46284.95833333334</c:v>
+                  <c:v>46285.375</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>46285.08333333334</c:v>
+                  <c:v>46285.5</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>46285.20833333334</c:v>
+                  <c:v>46285.625</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>46285.33333333334</c:v>
+                  <c:v>46285.75</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>46285.45833333334</c:v>
+                  <c:v>46285.875</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3778,79 +3958,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>0.59</c:v>
+                  <c:v>0.28</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.54</c:v>
+                  <c:v>0.26</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.5</c:v>
+                  <c:v>0.23</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.46</c:v>
+                  <c:v>0.22</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.42</c:v>
+                  <c:v>0.2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.39</c:v>
+                  <c:v>0.18</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.36</c:v>
+                  <c:v>0.17</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.33</c:v>
+                  <c:v>0.15</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.3</c:v>
+                  <c:v>0.14</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.28</c:v>
+                  <c:v>0.13</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.26</c:v>
+                  <c:v>0.12</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.24</c:v>
+                  <c:v>0.11</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.22</c:v>
+                  <c:v>0.1</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.2</c:v>
+                  <c:v>0.09</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.18</c:v>
+                  <c:v>0.09</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.17</c:v>
+                  <c:v>0.08</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.16</c:v>
+                  <c:v>0.07000000000000001</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.14</c:v>
+                  <c:v>0.07000000000000001</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.13</c:v>
+                  <c:v>0.06</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.12</c:v>
+                  <c:v>0.06</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.12</c:v>
+                  <c:v>0.06</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.12</c:v>
+                  <c:v>0.06</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.12</c:v>
+                  <c:v>0.06</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.12</c:v>
+                  <c:v>0.06</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.12</c:v>
+                  <c:v>0.06</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3872,79 +4052,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>46282.45833333334</c:v>
+                  <c:v>46282.875</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>46282.58333333334</c:v>
+                  <c:v>46283</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46282.70833333334</c:v>
+                  <c:v>46283.125</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46282.83333333334</c:v>
+                  <c:v>46283.25</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46282.95833333334</c:v>
+                  <c:v>46283.375</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46283.08333333334</c:v>
+                  <c:v>46283.5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46283.20833333334</c:v>
+                  <c:v>46283.625</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>46283.33333333334</c:v>
+                  <c:v>46283.75</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>46283.45833333334</c:v>
+                  <c:v>46283.875</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>46283.58333333334</c:v>
+                  <c:v>46284</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>46283.70833333334</c:v>
+                  <c:v>46284.125</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>46283.83333333334</c:v>
+                  <c:v>46284.25</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>46283.95833333334</c:v>
+                  <c:v>46284.375</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>46284.08333333334</c:v>
+                  <c:v>46284.5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>46284.20833333334</c:v>
+                  <c:v>46284.625</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46284.33333333334</c:v>
+                  <c:v>46284.75</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>46284.45833333334</c:v>
+                  <c:v>46284.875</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>46284.58333333334</c:v>
+                  <c:v>46285</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>46284.70833333334</c:v>
+                  <c:v>46285.125</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>46284.83333333334</c:v>
+                  <c:v>46285.25</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>46284.95833333334</c:v>
+                  <c:v>46285.375</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>46285.08333333334</c:v>
+                  <c:v>46285.5</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>46285.20833333334</c:v>
+                  <c:v>46285.625</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>46285.33333333334</c:v>
+                  <c:v>46285.75</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>46285.45833333334</c:v>
+                  <c:v>46285.875</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3956,79 +4136,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>-13.06</c:v>
+                  <c:v>-6.9</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-12.81</c:v>
+                  <c:v>-4.84</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-11.04</c:v>
+                  <c:v>-3.77</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-8.56</c:v>
+                  <c:v>-5.24</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-6.31</c:v>
+                  <c:v>-7.41</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-4.77</c:v>
+                  <c:v>-9.82</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-5.56</c:v>
+                  <c:v>-11.63</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-7.52</c:v>
+                  <c:v>-12.01</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-9.94</c:v>
+                  <c:v>-10.79</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-12.07</c:v>
+                  <c:v>-8.550000000000001</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-12.99</c:v>
+                  <c:v>-6.22</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-12.28</c:v>
+                  <c:v>-4.45</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-10.29</c:v>
+                  <c:v>-3.4</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-7.9</c:v>
+                  <c:v>-2.91</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-5.91</c:v>
+                  <c:v>-2.72</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-4.63</c:v>
+                  <c:v>-2.66</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-3.99</c:v>
+                  <c:v>-2.66</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-3.73</c:v>
+                  <c:v>-2.66</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-3.65</c:v>
+                  <c:v>-2.67</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-3.63</c:v>
+                  <c:v>-2.67</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-3.63</c:v>
+                  <c:v>-2.67</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>-3.63</c:v>
+                  <c:v>-2.67</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>-3.63</c:v>
+                  <c:v>-2.67</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>-3.63</c:v>
+                  <c:v>-2.67</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>-3.63</c:v>
+                  <c:v>-2.67</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4050,79 +4230,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>46282.45833333334</c:v>
+                  <c:v>46282.875</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>46282.58333333334</c:v>
+                  <c:v>46283</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46282.70833333334</c:v>
+                  <c:v>46283.125</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46282.83333333334</c:v>
+                  <c:v>46283.25</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46282.95833333334</c:v>
+                  <c:v>46283.375</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46283.08333333334</c:v>
+                  <c:v>46283.5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46283.20833333334</c:v>
+                  <c:v>46283.625</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>46283.33333333334</c:v>
+                  <c:v>46283.75</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>46283.45833333334</c:v>
+                  <c:v>46283.875</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>46283.58333333334</c:v>
+                  <c:v>46284</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>46283.70833333334</c:v>
+                  <c:v>46284.125</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>46283.83333333334</c:v>
+                  <c:v>46284.25</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>46283.95833333334</c:v>
+                  <c:v>46284.375</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>46284.08333333334</c:v>
+                  <c:v>46284.5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>46284.20833333334</c:v>
+                  <c:v>46284.625</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46284.33333333334</c:v>
+                  <c:v>46284.75</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>46284.45833333334</c:v>
+                  <c:v>46284.875</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>46284.58333333334</c:v>
+                  <c:v>46285</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>46284.70833333334</c:v>
+                  <c:v>46285.125</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>46284.83333333334</c:v>
+                  <c:v>46285.25</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>46284.95833333334</c:v>
+                  <c:v>46285.375</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>46285.08333333334</c:v>
+                  <c:v>46285.5</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>46285.20833333334</c:v>
+                  <c:v>46285.625</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>46285.33333333334</c:v>
+                  <c:v>46285.75</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>46285.45833333334</c:v>
+                  <c:v>46285.875</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4134,79 +4314,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>14.17</c:v>
+                  <c:v>8.56</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>13.93</c:v>
+                  <c:v>6.55</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>12.17</c:v>
+                  <c:v>5.52</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>9.699999999999999</c:v>
+                  <c:v>7.04</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>7.46</c:v>
+                  <c:v>9.24</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5.92</c:v>
+                  <c:v>11.69</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>6.72</c:v>
+                  <c:v>13.52</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8.69</c:v>
+                  <c:v>13.94</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>11.12</c:v>
+                  <c:v>12.74</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>13.25</c:v>
+                  <c:v>10.53</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>14.18</c:v>
+                  <c:v>8.220000000000001</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>13.47</c:v>
+                  <c:v>6.47</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>11.49</c:v>
+                  <c:v>5.45</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>9.1</c:v>
+                  <c:v>4.97</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>7.11</c:v>
+                  <c:v>4.8</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>5.84</c:v>
+                  <c:v>4.75</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>5.2</c:v>
+                  <c:v>4.77</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>4.95</c:v>
+                  <c:v>4.79</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>4.87</c:v>
+                  <c:v>4.8</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>4.85</c:v>
+                  <c:v>4.82</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>4.86</c:v>
+                  <c:v>4.82</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>4.85</c:v>
+                  <c:v>4.82</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>4.85</c:v>
+                  <c:v>4.82</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>4.85</c:v>
+                  <c:v>4.82</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>4.85</c:v>
+                  <c:v>4.82</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4335,79 +4515,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>46282.45833333334</c:v>
+                  <c:v>46282.875</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>46282.58333333334</c:v>
+                  <c:v>46283</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46282.70833333334</c:v>
+                  <c:v>46283.125</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46282.83333333334</c:v>
+                  <c:v>46283.25</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46282.95833333334</c:v>
+                  <c:v>46283.375</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46283.08333333334</c:v>
+                  <c:v>46283.5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46283.20833333334</c:v>
+                  <c:v>46283.625</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>46283.33333333334</c:v>
+                  <c:v>46283.75</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>46283.45833333334</c:v>
+                  <c:v>46283.875</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>46283.58333333334</c:v>
+                  <c:v>46284</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>46283.70833333334</c:v>
+                  <c:v>46284.125</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>46283.83333333334</c:v>
+                  <c:v>46284.25</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>46283.95833333334</c:v>
+                  <c:v>46284.375</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>46284.08333333334</c:v>
+                  <c:v>46284.5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>46284.20833333334</c:v>
+                  <c:v>46284.625</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46284.33333333334</c:v>
+                  <c:v>46284.75</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>46284.45833333334</c:v>
+                  <c:v>46284.875</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>46284.58333333334</c:v>
+                  <c:v>46285</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>46284.70833333334</c:v>
+                  <c:v>46285.125</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>46284.83333333334</c:v>
+                  <c:v>46285.25</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>46284.95833333334</c:v>
+                  <c:v>46285.375</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>46285.08333333334</c:v>
+                  <c:v>46285.5</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>46285.20833333334</c:v>
+                  <c:v>46285.625</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>46285.33333333334</c:v>
+                  <c:v>46285.75</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>46285.45833333334</c:v>
+                  <c:v>46285.875</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4419,79 +4599,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>71.7</c:v>
+                  <c:v>53.9</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>71</c:v>
+                  <c:v>46.2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>64.5</c:v>
+                  <c:v>42.3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>55.3</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46.9</c:v>
+                  <c:v>56.3</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>41.3</c:v>
+                  <c:v>65.59999999999999</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>44.5</c:v>
+                  <c:v>72.5</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>52.1</c:v>
+                  <c:v>74</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>61.4</c:v>
+                  <c:v>69.5</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>69.7</c:v>
+                  <c:v>61.1</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>73.3</c:v>
+                  <c:v>52.3</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>70.7</c:v>
+                  <c:v>45.6</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>63.3</c:v>
+                  <c:v>41.7</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>54.3</c:v>
+                  <c:v>39.8</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>46.8</c:v>
+                  <c:v>39.2</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>42.1</c:v>
+                  <c:v>39</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>39.7</c:v>
+                  <c:v>39</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>38.8</c:v>
+                  <c:v>39.1</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>38.6</c:v>
+                  <c:v>39.1</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>38.6</c:v>
+                  <c:v>39.2</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>38.6</c:v>
+                  <c:v>39.2</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>38.6</c:v>
+                  <c:v>39.2</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>38.6</c:v>
+                  <c:v>39.2</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>38.6</c:v>
+                  <c:v>39.2</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>38.6</c:v>
+                  <c:v>39.2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5147,7 +5327,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="5">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>25</v>
@@ -5156,16 +5336,16 @@
         <v>24</v>
       </c>
       <c r="F9" s="5">
-        <v>69.16500000000001</v>
+        <v>53.951</v>
       </c>
       <c r="G9" s="5">
-        <v>44.453</v>
+        <v>29.293</v>
       </c>
       <c r="H9" s="5">
-        <v>20.8</v>
+        <v>41.7</v>
       </c>
       <c r="I9" s="5">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="J9" s="5" t="s">
         <v>26</v>
@@ -5176,25 +5356,25 @@
         <v>10</v>
       </c>
       <c r="B10" s="5">
-        <v>4570</v>
+        <v>5265</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>27</v>
       </c>
       <c r="E10" s="5">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="F10" s="5">
-        <v>64.83499999999999</v>
+        <v>58.967</v>
       </c>
       <c r="G10" s="5">
-        <v>15.12</v>
+        <v>-0.672</v>
       </c>
       <c r="H10" s="5">
-        <v>42.9</v>
+        <v>44.1</v>
       </c>
       <c r="I10" s="5">
-        <v>85.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="J10" s="5" t="s">
         <v>26</v>
@@ -5205,25 +5385,25 @@
         <v>11</v>
       </c>
       <c r="B11" s="5">
-        <v>4558</v>
+        <v>5261</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>28</v>
       </c>
       <c r="E11" s="5">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="F11" s="5">
-        <v>64.83499999999999</v>
+        <v>58.967</v>
       </c>
       <c r="G11" s="5">
-        <v>15.12</v>
+        <v>-0.672</v>
       </c>
       <c r="H11" s="5">
-        <v>42.9</v>
+        <v>44.1</v>
       </c>
       <c r="I11" s="5">
-        <v>85.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="J11" s="5" t="s">
         <v>26</v>
@@ -5313,7 +5493,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="5">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -5326,7 +5506,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E60"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.7109375" customWidth="1"/>
@@ -5763,16 +5943,16 @@
         <v>46281.45833333334</v>
       </c>
       <c r="B26" s="5">
-        <v>537.5</v>
+        <v>537.65</v>
       </c>
       <c r="C26" s="5">
-        <v>0.31</v>
+        <v>0.295</v>
       </c>
       <c r="D26" s="5">
-        <v>-2.38</v>
+        <v>-2.33</v>
       </c>
       <c r="E26" s="5">
-        <v>4.37</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -5780,16 +5960,16 @@
         <v>46281.5</v>
       </c>
       <c r="B27" s="5">
-        <v>550.22</v>
+        <v>549.265</v>
       </c>
       <c r="C27" s="5">
         <v>0.1</v>
       </c>
       <c r="D27" s="5">
-        <v>0.955</v>
+        <v>0.605</v>
       </c>
       <c r="E27" s="5">
-        <v>4.465</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -5797,16 +5977,16 @@
         <v>46281.54166666666</v>
       </c>
       <c r="B28" s="5">
-        <v>563.34</v>
+        <v>561.3150000000001</v>
       </c>
       <c r="C28" s="5">
         <v>0.05</v>
       </c>
       <c r="D28" s="5">
-        <v>3.095</v>
+        <v>2.99</v>
       </c>
       <c r="E28" s="5">
-        <v>4.9</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -5814,16 +5994,16 @@
         <v>46281.58333333334</v>
       </c>
       <c r="B29" s="5">
-        <v>545.0650000000001</v>
+        <v>545.145</v>
       </c>
       <c r="C29" s="5">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="D29" s="5">
-        <v>4.83</v>
+        <v>4.82</v>
       </c>
       <c r="E29" s="5">
-        <v>5.475</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -5831,16 +6011,16 @@
         <v>46281.625</v>
       </c>
       <c r="B30" s="5">
-        <v>533.05</v>
+        <v>534.4299999999999</v>
       </c>
       <c r="C30" s="5">
-        <v>0.155</v>
+        <v>0.15</v>
       </c>
       <c r="D30" s="5">
-        <v>4.315</v>
+        <v>4.235</v>
       </c>
       <c r="E30" s="5">
-        <v>5.835</v>
+        <v>5.82</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -5848,16 +6028,16 @@
         <v>46281.66666666666</v>
       </c>
       <c r="B31" s="5">
-        <v>524.975</v>
+        <v>524.6</v>
       </c>
       <c r="C31" s="5">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="D31" s="5">
-        <v>4.11</v>
+        <v>4.14</v>
       </c>
       <c r="E31" s="5">
-        <v>5.62</v>
+        <v>5.61</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -5865,16 +6045,16 @@
         <v>46281.70833333334</v>
       </c>
       <c r="B32" s="5">
-        <v>535.105</v>
+        <v>537.705</v>
       </c>
       <c r="C32" s="5">
-        <v>0.225</v>
+        <v>0.19</v>
       </c>
       <c r="D32" s="5">
-        <v>4.115</v>
+        <v>4.15</v>
       </c>
       <c r="E32" s="5">
-        <v>5.63</v>
+        <v>5.73</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -5885,13 +6065,13 @@
         <v>523.22</v>
       </c>
       <c r="C33" s="5">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="D33" s="5">
-        <v>2.985</v>
+        <v>3.02</v>
       </c>
       <c r="E33" s="5">
-        <v>5.45</v>
+        <v>5.42</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -5899,16 +6079,16 @@
         <v>46281.79166666666</v>
       </c>
       <c r="B34" s="5">
-        <v>501.2</v>
+        <v>501.75</v>
       </c>
       <c r="C34" s="5">
-        <v>3.79</v>
+        <v>3.765</v>
       </c>
       <c r="D34" s="5">
-        <v>2.11</v>
+        <v>2.185</v>
       </c>
       <c r="E34" s="5">
-        <v>4.685</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -5916,16 +6096,16 @@
         <v>46281.83333333334</v>
       </c>
       <c r="B35" s="5">
-        <v>509.625</v>
+        <v>509.8</v>
       </c>
       <c r="C35" s="5">
         <v>3.065</v>
       </c>
       <c r="D35" s="5">
-        <v>0.655</v>
+        <v>0.54</v>
       </c>
       <c r="E35" s="5">
-        <v>5.03</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -5933,16 +6113,16 @@
         <v>46281.875</v>
       </c>
       <c r="B36" s="5">
-        <v>501.875</v>
+        <v>502.215</v>
       </c>
       <c r="C36" s="5">
-        <v>2.935</v>
+        <v>2.9</v>
       </c>
       <c r="D36" s="5">
-        <v>1.945</v>
+        <v>1.965</v>
       </c>
       <c r="E36" s="5">
-        <v>4.905</v>
+        <v>4.91</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -5950,16 +6130,16 @@
         <v>46281.91666666666</v>
       </c>
       <c r="B37" s="5">
-        <v>514.26</v>
+        <v>512.5599999999999</v>
       </c>
       <c r="C37" s="5">
-        <v>2.85</v>
+        <v>2.68</v>
       </c>
       <c r="D37" s="5">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="E37" s="5">
-        <v>5.01</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -5967,16 +6147,16 @@
         <v>46281.95833333334</v>
       </c>
       <c r="B38" s="5">
-        <v>506.995</v>
+        <v>505.765</v>
       </c>
       <c r="C38" s="5">
-        <v>0.455</v>
+        <v>0.485</v>
       </c>
       <c r="D38" s="5">
-        <v>2.49</v>
+        <v>3.02</v>
       </c>
       <c r="E38" s="5">
-        <v>4.755</v>
+        <v>4.92</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -5984,16 +6164,16 @@
         <v>46282</v>
       </c>
       <c r="B39" s="5">
-        <v>504.07</v>
+        <v>504.475</v>
       </c>
       <c r="C39" s="5">
-        <v>1.015</v>
+        <v>0.525</v>
       </c>
       <c r="D39" s="5">
-        <v>0.18</v>
+        <v>0.005</v>
       </c>
       <c r="E39" s="5">
-        <v>5.165</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -6001,16 +6181,16 @@
         <v>46282.04166666666</v>
       </c>
       <c r="B40" s="5">
-        <v>496.04</v>
+        <v>506.52</v>
       </c>
       <c r="C40" s="5">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="D40" s="5">
-        <v>-0.16</v>
+        <v>-0.28</v>
       </c>
       <c r="E40" s="5">
-        <v>6.08</v>
+        <v>5.84</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -6018,16 +6198,16 @@
         <v>46282.08333333334</v>
       </c>
       <c r="B41" s="5">
-        <v>550.135</v>
+        <v>547.45</v>
       </c>
       <c r="C41" s="5">
-        <v>0.9</v>
+        <v>1.935</v>
       </c>
       <c r="D41" s="5">
-        <v>3.01</v>
+        <v>3.5</v>
       </c>
       <c r="E41" s="5">
-        <v>7.25</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -6035,16 +6215,16 @@
         <v>46282.125</v>
       </c>
       <c r="B42" s="5">
-        <v>512.7</v>
+        <v>509.5</v>
       </c>
       <c r="C42" s="5">
-        <v>1.43</v>
+        <v>1.76</v>
       </c>
       <c r="D42" s="5">
-        <v>2.925</v>
+        <v>3.145</v>
       </c>
       <c r="E42" s="5">
-        <v>6.175</v>
+        <v>6.075</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -6055,13 +6235,13 @@
         <v>495.15</v>
       </c>
       <c r="C43" s="5">
-        <v>3.435</v>
+        <v>3.635</v>
       </c>
       <c r="D43" s="5">
-        <v>2.205</v>
+        <v>2.24</v>
       </c>
       <c r="E43" s="5">
-        <v>5.735</v>
+        <v>5.725</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -6069,13 +6249,13 @@
         <v>46282.20833333334</v>
       </c>
       <c r="B44" s="5">
-        <v>497.73</v>
+        <v>497.57</v>
       </c>
       <c r="C44" s="5">
-        <v>3.445</v>
+        <v>3.42</v>
       </c>
       <c r="D44" s="5">
-        <v>0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="E44" s="5">
         <v>4.63</v>
@@ -6086,13 +6266,13 @@
         <v>46282.25</v>
       </c>
       <c r="B45" s="5">
-        <v>476.33</v>
+        <v>476.755</v>
       </c>
       <c r="C45" s="5">
-        <v>3.295</v>
+        <v>3.33</v>
       </c>
       <c r="D45" s="5">
-        <v>0.775</v>
+        <v>1.17</v>
       </c>
       <c r="E45" s="5">
         <v>4.33</v>
@@ -6103,16 +6283,16 @@
         <v>46282.29166666666</v>
       </c>
       <c r="B46" s="5">
-        <v>484.215</v>
+        <v>485.05</v>
       </c>
       <c r="C46" s="5">
-        <v>3.185</v>
+        <v>3.195</v>
       </c>
       <c r="D46" s="5">
-        <v>1.525</v>
+        <v>1.6</v>
       </c>
       <c r="E46" s="5">
-        <v>4.21</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -6126,10 +6306,10 @@
         <v>3.21</v>
       </c>
       <c r="D47" s="5">
-        <v>2.285</v>
+        <v>2.265</v>
       </c>
       <c r="E47" s="5">
-        <v>3.76</v>
+        <v>3.81</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -6137,13 +6317,13 @@
         <v>46282.375</v>
       </c>
       <c r="B48" s="5">
-        <v>475.22</v>
+        <v>475.84</v>
       </c>
       <c r="C48" s="5">
-        <v>3.235</v>
+        <v>3.205</v>
       </c>
       <c r="D48" s="5">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="E48" s="5">
         <v>3.69</v>
@@ -6154,16 +6334,16 @@
         <v>46282.41666666666</v>
       </c>
       <c r="B49" s="5">
-        <v>486.615</v>
+        <v>488.935</v>
       </c>
       <c r="C49" s="5">
         <v>2.76</v>
       </c>
       <c r="D49" s="5">
-        <v>-2.61</v>
+        <v>-2.655</v>
       </c>
       <c r="E49" s="5">
-        <v>3.625</v>
+        <v>3.665</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -6171,16 +6351,186 @@
         <v>46282.45833333334</v>
       </c>
       <c r="B50" s="5">
-        <v>484.775</v>
+        <v>482.74</v>
       </c>
       <c r="C50" s="5">
         <v>2.7</v>
       </c>
       <c r="D50" s="5">
-        <v>-2.79</v>
+        <v>-2.42</v>
       </c>
       <c r="E50" s="5">
-        <v>3.88</v>
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6">
+        <v>46282.5</v>
+      </c>
+      <c r="B51" s="5">
+        <v>474.85</v>
+      </c>
+      <c r="C51" s="5">
+        <v>0.51</v>
+      </c>
+      <c r="D51" s="5">
+        <v>-0.045</v>
+      </c>
+      <c r="E51" s="5">
+        <v>3.695</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6">
+        <v>46282.54166666666</v>
+      </c>
+      <c r="B52" s="5">
+        <v>464.35</v>
+      </c>
+      <c r="C52" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="D52" s="5">
+        <v>-0.23</v>
+      </c>
+      <c r="E52" s="5">
+        <v>3.62</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6">
+        <v>46282.58333333334</v>
+      </c>
+      <c r="B53" s="5">
+        <v>459.115</v>
+      </c>
+      <c r="C53" s="5">
+        <v>1.015</v>
+      </c>
+      <c r="D53" s="5">
+        <v>0.115</v>
+      </c>
+      <c r="E53" s="5">
+        <v>3.415</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6">
+        <v>46282.625</v>
+      </c>
+      <c r="B54" s="5">
+        <v>450.13</v>
+      </c>
+      <c r="C54" s="5">
+        <v>2.32</v>
+      </c>
+      <c r="D54" s="5">
+        <v>0.37</v>
+      </c>
+      <c r="E54" s="5">
+        <v>3.55</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6">
+        <v>46282.66666666666</v>
+      </c>
+      <c r="B55" s="5">
+        <v>460.725</v>
+      </c>
+      <c r="C55" s="5">
+        <v>2.75</v>
+      </c>
+      <c r="D55" s="5">
+        <v>-0.305</v>
+      </c>
+      <c r="E55" s="5">
+        <v>3.76</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="6">
+        <v>46282.70833333334</v>
+      </c>
+      <c r="B56" s="5">
+        <v>465.735</v>
+      </c>
+      <c r="C56" s="5">
+        <v>2.505</v>
+      </c>
+      <c r="D56" s="5">
+        <v>0.44</v>
+      </c>
+      <c r="E56" s="5">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="6">
+        <v>46282.75</v>
+      </c>
+      <c r="B57" s="5">
+        <v>475.8</v>
+      </c>
+      <c r="C57" s="5">
+        <v>0.7</v>
+      </c>
+      <c r="D57" s="5">
+        <v>2.46</v>
+      </c>
+      <c r="E57" s="5">
+        <v>4.49</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="6">
+        <v>46282.79166666666</v>
+      </c>
+      <c r="B58" s="5">
+        <v>479.955</v>
+      </c>
+      <c r="C58" s="5">
+        <v>1.315</v>
+      </c>
+      <c r="D58" s="5">
+        <v>1.63</v>
+      </c>
+      <c r="E58" s="5">
+        <v>4.435</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="6">
+        <v>46282.83333333334</v>
+      </c>
+      <c r="B59" s="5">
+        <v>469.35</v>
+      </c>
+      <c r="C59" s="5">
+        <v>1.23</v>
+      </c>
+      <c r="D59" s="5">
+        <v>-1.71</v>
+      </c>
+      <c r="E59" s="5">
+        <v>3.53</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="6">
+        <v>46282.875</v>
+      </c>
+      <c r="B60" s="5">
+        <v>462.12</v>
+      </c>
+      <c r="C60" s="5">
+        <v>1.27</v>
+      </c>
+      <c r="D60" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="E60" s="5">
+        <v>3.39</v>
       </c>
     </row>
   </sheetData>
@@ -6224,19 +6574,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="6">
-        <v>46282.33333333334</v>
+        <v>46282.75</v>
       </c>
       <c r="B2" s="5">
-        <v>565.8</v>
+        <v>421.89</v>
       </c>
       <c r="C2" s="5">
-        <v>292.82</v>
+        <v>272.13</v>
       </c>
       <c r="D2" s="5">
-        <v>480.17</v>
+        <v>473.8</v>
       </c>
       <c r="E2" s="5">
-        <v>351.75</v>
+        <v>192.1</v>
       </c>
       <c r="F2" s="5"/>
       <c r="G2" s="5" t="s">
@@ -6245,19 +6595,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="6">
-        <v>46282.375</v>
+        <v>46282.79166666666</v>
       </c>
       <c r="B3" s="5">
-        <v>561.1900000000001</v>
+        <v>411.97</v>
       </c>
       <c r="C3" s="5">
-        <v>289.22</v>
+        <v>271.87</v>
       </c>
       <c r="D3" s="5">
-        <v>476.7</v>
+        <v>480.4</v>
       </c>
       <c r="E3" s="5">
-        <v>350.44</v>
+        <v>179.71</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5" t="s">
@@ -6266,19 +6616,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="6">
-        <v>46282.41666666666</v>
+        <v>46282.83333333334</v>
       </c>
       <c r="B4" s="5">
-        <v>552.84</v>
+        <v>402.67</v>
       </c>
       <c r="C4" s="5">
-        <v>286.72</v>
+        <v>273.53</v>
       </c>
       <c r="D4" s="5">
-        <v>476.4</v>
+        <v>474.5</v>
       </c>
       <c r="E4" s="5">
-        <v>342.91</v>
+        <v>165.65</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="5" t="s">
@@ -6287,19 +6637,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="6">
-        <v>46282.45833333334</v>
+        <v>46282.875</v>
       </c>
       <c r="B5" s="5">
-        <v>543.51</v>
+        <v>395.15</v>
       </c>
       <c r="C5" s="5">
-        <v>286.72</v>
+        <v>274.35</v>
       </c>
       <c r="D5" s="5">
-        <v>487.45</v>
+        <v>466.25</v>
       </c>
       <c r="E5" s="5">
-        <v>330.87</v>
+        <v>154.97</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5" t="s">
@@ -6308,17 +6658,17 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="6">
-        <v>46282.5</v>
+        <v>46282.91666666666</v>
       </c>
       <c r="B6" s="5">
-        <v>540.49</v>
+        <v>393.13</v>
       </c>
       <c r="C6" s="5">
-        <v>288.02</v>
+        <v>275.29</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5">
-        <v>316.24</v>
+        <v>144.98</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="5" t="s">
@@ -6327,17 +6677,17 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="6">
-        <v>46282.54166666666</v>
+        <v>46282.95833333334</v>
       </c>
       <c r="B7" s="5">
-        <v>532.5</v>
+        <v>390.41</v>
       </c>
       <c r="C7" s="5">
-        <v>288.72</v>
+        <v>277.17</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5">
-        <v>295.85</v>
+        <v>135.63</v>
       </c>
       <c r="F7" s="5"/>
       <c r="G7" s="5" t="s">
@@ -6346,17 +6696,17 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="6">
-        <v>46282.58333333334</v>
+        <v>46283</v>
       </c>
       <c r="B8" s="5">
-        <v>521.25</v>
+        <v>386.64</v>
       </c>
       <c r="C8" s="5">
-        <v>288.48</v>
+        <v>278.83</v>
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="5">
-        <v>276.77</v>
+        <v>126.93</v>
       </c>
       <c r="F8" s="5"/>
       <c r="G8" s="5" t="s">
@@ -6365,17 +6715,17 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="6">
-        <v>46282.625</v>
+        <v>46283.04166666666</v>
       </c>
       <c r="B9" s="5">
-        <v>509.07</v>
+        <v>381.23</v>
       </c>
       <c r="C9" s="5">
-        <v>288.4</v>
+        <v>280.17</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="5">
-        <v>258.92</v>
+        <v>115.52</v>
       </c>
       <c r="F9" s="5"/>
       <c r="G9" s="5" t="s">
@@ -6384,17 +6734,17 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="6">
-        <v>46282.66666666666</v>
+        <v>46283.08333333334</v>
       </c>
       <c r="B10" s="5">
-        <v>497.46</v>
+        <v>375.31</v>
       </c>
       <c r="C10" s="5">
-        <v>289.22</v>
+        <v>280.59</v>
       </c>
       <c r="D10" s="5"/>
       <c r="E10" s="5">
-        <v>242.22</v>
+        <v>108.24</v>
       </c>
       <c r="F10" s="5"/>
       <c r="G10" s="5" t="s">
@@ -6403,17 +6753,17 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="6">
-        <v>46282.70833333334</v>
+        <v>46283.125</v>
       </c>
       <c r="B11" s="5">
-        <v>485.15</v>
+        <v>368.64</v>
       </c>
       <c r="C11" s="5">
-        <v>289.21</v>
+        <v>279.8</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="5">
-        <v>226.6</v>
+        <v>101.64</v>
       </c>
       <c r="F11" s="5"/>
       <c r="G11" s="5" t="s">
@@ -6422,17 +6772,17 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="6">
-        <v>46282.75</v>
+        <v>46283.16666666666</v>
       </c>
       <c r="B12" s="5">
-        <v>471.84</v>
+        <v>364.24</v>
       </c>
       <c r="C12" s="5">
-        <v>287.84</v>
+        <v>280.77</v>
       </c>
       <c r="D12" s="5"/>
       <c r="E12" s="5">
-        <v>211.98</v>
+        <v>95.84</v>
       </c>
       <c r="F12" s="5"/>
       <c r="G12" s="5" t="s">
@@ -6441,17 +6791,17 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="6">
-        <v>46282.79166666666</v>
+        <v>46283.20833333334</v>
       </c>
       <c r="B13" s="5">
-        <v>459.23</v>
+        <v>360.9</v>
       </c>
       <c r="C13" s="5">
-        <v>286.67</v>
+        <v>282.15</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="5">
-        <v>198.31</v>
+        <v>91.14</v>
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="5" t="s">
@@ -6460,17 +6810,17 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="6">
-        <v>46282.83333333334</v>
+        <v>46283.25</v>
       </c>
       <c r="B14" s="5">
-        <v>446.35</v>
+        <v>358.68</v>
       </c>
       <c r="C14" s="5">
-        <v>285.64</v>
+        <v>283.8</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="5">
-        <v>182.17</v>
+        <v>87.94</v>
       </c>
       <c r="F14" s="5"/>
       <c r="G14" s="5" t="s">
@@ -6479,17 +6829,17 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="6">
-        <v>46282.875</v>
+        <v>46283.29166666666</v>
       </c>
       <c r="B15" s="5">
-        <v>434.62</v>
+        <v>356.85</v>
       </c>
       <c r="C15" s="5">
-        <v>284.72</v>
+        <v>284.7</v>
       </c>
       <c r="D15" s="5"/>
       <c r="E15" s="5">
-        <v>170.42</v>
+        <v>86.84999999999999</v>
       </c>
       <c r="F15" s="5"/>
       <c r="G15" s="5" t="s">
@@ -6498,17 +6848,17 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="6">
-        <v>46282.91666666666</v>
+        <v>46283.33333333334</v>
       </c>
       <c r="B16" s="5">
-        <v>423.84</v>
+        <v>356.11</v>
       </c>
       <c r="C16" s="5">
-        <v>283.89</v>
+        <v>285.13</v>
       </c>
       <c r="D16" s="5"/>
       <c r="E16" s="5">
-        <v>159.43</v>
+        <v>88.61</v>
       </c>
       <c r="F16" s="5"/>
       <c r="G16" s="5" t="s">
@@ -6517,17 +6867,17 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="6">
-        <v>46282.95833333334</v>
+        <v>46283.375</v>
       </c>
       <c r="B17" s="5">
-        <v>413.88</v>
+        <v>357.13</v>
       </c>
       <c r="C17" s="5">
-        <v>283.12</v>
+        <v>285.29</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="5">
-        <v>149.15</v>
+        <v>93.98</v>
       </c>
       <c r="F17" s="5"/>
       <c r="G17" s="5" t="s">
@@ -6536,17 +6886,17 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="6">
-        <v>46283</v>
+        <v>46283.41666666666</v>
       </c>
       <c r="B18" s="5">
-        <v>404.68</v>
+        <v>360.52</v>
       </c>
       <c r="C18" s="5">
-        <v>282.45</v>
+        <v>285.31</v>
       </c>
       <c r="D18" s="5"/>
       <c r="E18" s="5">
-        <v>139.57</v>
+        <v>103.55</v>
       </c>
       <c r="F18" s="5"/>
       <c r="G18" s="5" t="s">
@@ -6555,17 +6905,17 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="6">
-        <v>46283.04166666666</v>
+        <v>46283.45833333334</v>
       </c>
       <c r="B19" s="5">
-        <v>396.08</v>
+        <v>362.56</v>
       </c>
       <c r="C19" s="5">
-        <v>282.99</v>
+        <v>285.27</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="5">
-        <v>126.51</v>
+        <v>103.46</v>
       </c>
       <c r="F19" s="5"/>
       <c r="G19" s="5" t="s">
@@ -6574,17 +6924,17 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="6">
-        <v>46283.08333333334</v>
+        <v>46283.5</v>
       </c>
       <c r="B20" s="5">
-        <v>389.34</v>
+        <v>369.28</v>
       </c>
       <c r="C20" s="5">
-        <v>284.27</v>
+        <v>285.21</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="5">
-        <v>118.52</v>
+        <v>122.07</v>
       </c>
       <c r="F20" s="5"/>
       <c r="G20" s="5" t="s">
@@ -6593,17 +6943,17 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="6">
-        <v>46283.125</v>
+        <v>46283.54166666666</v>
       </c>
       <c r="B21" s="5">
-        <v>383.97</v>
+        <v>376.3</v>
       </c>
       <c r="C21" s="5">
-        <v>286.02</v>
+        <v>285.03</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5">
-        <v>111.25</v>
+        <v>132.13</v>
       </c>
       <c r="F21" s="5"/>
       <c r="G21" s="5" t="s">
@@ -6612,17 +6962,17 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="6">
-        <v>46283.16666666666</v>
+        <v>46283.58333333334</v>
       </c>
       <c r="B22" s="5">
-        <v>379.7</v>
+        <v>386.88</v>
       </c>
       <c r="C22" s="5">
-        <v>288.05</v>
+        <v>284.79</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="5">
-        <v>104.85</v>
+        <v>153.6</v>
       </c>
       <c r="F22" s="5"/>
       <c r="G22" s="5" t="s">
@@ -6631,17 +6981,17 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="6">
-        <v>46283.20833333334</v>
+        <v>46283.625</v>
       </c>
       <c r="B23" s="5">
-        <v>376.43</v>
+        <v>398.76</v>
       </c>
       <c r="C23" s="5">
-        <v>290.24</v>
+        <v>284.5</v>
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="5">
-        <v>99.56999999999999</v>
+        <v>172.06</v>
       </c>
       <c r="F23" s="5"/>
       <c r="G23" s="5" t="s">
@@ -6650,17 +7000,17 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="6">
-        <v>46283.25</v>
+        <v>46283.66666666666</v>
       </c>
       <c r="B24" s="5">
-        <v>374.24</v>
+        <v>409.73</v>
       </c>
       <c r="C24" s="5">
-        <v>292.54</v>
+        <v>284.19</v>
       </c>
       <c r="D24" s="5"/>
       <c r="E24" s="5">
-        <v>95.84999999999999</v>
+        <v>184.65</v>
       </c>
       <c r="F24" s="5"/>
       <c r="G24" s="5" t="s">
@@ -6669,17 +7019,17 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="6">
-        <v>46283.29166666666</v>
+        <v>46283.70833333334</v>
       </c>
       <c r="B25" s="5">
-        <v>372.44</v>
+        <v>417.73</v>
       </c>
       <c r="C25" s="5">
-        <v>293.98</v>
+        <v>283.85</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="5">
-        <v>94.29000000000001</v>
+        <v>189.18</v>
       </c>
       <c r="F25" s="5"/>
       <c r="G25" s="5" t="s">
@@ -6688,17 +7038,17 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="6">
-        <v>46283.33333333334</v>
+        <v>46283.75</v>
       </c>
       <c r="B26" s="5">
-        <v>371.73</v>
+        <v>419.47</v>
       </c>
       <c r="C26" s="5">
-        <v>294.88</v>
+        <v>283.51</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5">
-        <v>95.62</v>
+        <v>178.8</v>
       </c>
       <c r="F26" s="5"/>
       <c r="G26" s="5" t="s">
@@ -6707,17 +7057,17 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="6">
-        <v>46283.375</v>
+        <v>46283.79166666666</v>
       </c>
       <c r="B27" s="5">
-        <v>372.77</v>
+        <v>415.66</v>
       </c>
       <c r="C27" s="5">
-        <v>295.45</v>
+        <v>283.19</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="5">
-        <v>100.63</v>
+        <v>162.63</v>
       </c>
       <c r="F27" s="5"/>
       <c r="G27" s="5" t="s">
@@ -6726,17 +7076,17 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="6">
-        <v>46283.41666666666</v>
+        <v>46283.83333333334</v>
       </c>
       <c r="B28" s="5">
-        <v>376.15</v>
+        <v>410.09</v>
       </c>
       <c r="C28" s="5">
-        <v>295.8</v>
+        <v>282.88</v>
       </c>
       <c r="D28" s="5"/>
       <c r="E28" s="5">
-        <v>109.9</v>
+        <v>152.14</v>
       </c>
       <c r="F28" s="5"/>
       <c r="G28" s="5" t="s">
@@ -6745,17 +7095,17 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="6">
-        <v>46283.45833333334</v>
+        <v>46283.875</v>
       </c>
       <c r="B29" s="5">
-        <v>378.11</v>
+        <v>403.62</v>
       </c>
       <c r="C29" s="5">
-        <v>296.02</v>
+        <v>282.59</v>
       </c>
       <c r="D29" s="5"/>
       <c r="E29" s="5">
-        <v>109.45</v>
+        <v>142.33</v>
       </c>
       <c r="F29" s="5"/>
       <c r="G29" s="5" t="s">
@@ -6764,17 +7114,17 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="6">
-        <v>46283.5</v>
+        <v>46283.91666666666</v>
       </c>
       <c r="B30" s="5">
-        <v>384.76</v>
+        <v>395.21</v>
       </c>
       <c r="C30" s="5">
-        <v>296.15</v>
+        <v>282.3</v>
       </c>
       <c r="D30" s="5"/>
       <c r="E30" s="5">
-        <v>127.88</v>
+        <v>127.84</v>
       </c>
       <c r="F30" s="5"/>
       <c r="G30" s="5" t="s">
@@ -6783,17 +7133,17 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="6">
-        <v>46283.54166666666</v>
+        <v>46283.95833333334</v>
       </c>
       <c r="B31" s="5">
-        <v>391.69</v>
+        <v>387.44</v>
       </c>
       <c r="C31" s="5">
-        <v>296.14</v>
+        <v>282.01</v>
       </c>
       <c r="D31" s="5"/>
       <c r="E31" s="5">
-        <v>137.7</v>
+        <v>119.59</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="5" t="s">
@@ -6802,17 +7152,17 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="6">
-        <v>46283.58333333334</v>
+        <v>46284</v>
       </c>
       <c r="B32" s="5">
-        <v>402.18</v>
+        <v>380.23</v>
       </c>
       <c r="C32" s="5">
-        <v>296.04</v>
+        <v>281.73</v>
       </c>
       <c r="D32" s="5"/>
       <c r="E32" s="5">
-        <v>159.05</v>
+        <v>111.88</v>
       </c>
       <c r="F32" s="5"/>
       <c r="G32" s="5" t="s">
@@ -6821,17 +7171,17 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="6">
-        <v>46283.625</v>
+        <v>46284.04166666666</v>
       </c>
       <c r="B33" s="5">
-        <v>413.99</v>
+        <v>371.98</v>
       </c>
       <c r="C33" s="5">
-        <v>295.87</v>
+        <v>281.52</v>
       </c>
       <c r="D33" s="5"/>
       <c r="E33" s="5">
-        <v>177.38</v>
+        <v>99.19</v>
       </c>
       <c r="F33" s="5"/>
       <c r="G33" s="5" t="s">
@@ -6840,17 +7190,17 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="6">
-        <v>46283.66666666666</v>
+        <v>46284.08333333334</v>
       </c>
       <c r="B34" s="5">
-        <v>424.88</v>
+        <v>364.94</v>
       </c>
       <c r="C34" s="5">
-        <v>295.67</v>
+        <v>281.36</v>
       </c>
       <c r="D34" s="5"/>
       <c r="E34" s="5">
-        <v>189.82</v>
+        <v>92.8</v>
       </c>
       <c r="F34" s="5"/>
       <c r="G34" s="5" t="s">
@@ -6859,17 +7209,17 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="6">
-        <v>46283.70833333334</v>
+        <v>46284.125</v>
       </c>
       <c r="B35" s="5">
-        <v>432.81</v>
+        <v>358.77</v>
       </c>
       <c r="C35" s="5">
-        <v>295.44</v>
+        <v>281.24</v>
       </c>
       <c r="D35" s="5"/>
       <c r="E35" s="5">
-        <v>194.15</v>
+        <v>86.81</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="5" t="s">
@@ -6878,17 +7228,17 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="6">
-        <v>46283.75</v>
+        <v>46284.16666666666</v>
       </c>
       <c r="B36" s="5">
-        <v>434.46</v>
+        <v>353.25</v>
       </c>
       <c r="C36" s="5">
-        <v>295.19</v>
+        <v>281.13</v>
       </c>
       <c r="D36" s="5"/>
       <c r="E36" s="5">
-        <v>183.47</v>
+        <v>81.20999999999999</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="5" t="s">
@@ -6897,17 +7247,17 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="6">
-        <v>46283.79166666666</v>
+        <v>46284.20833333334</v>
       </c>
       <c r="B37" s="5">
-        <v>430.31</v>
+        <v>348.25</v>
       </c>
       <c r="C37" s="5">
-        <v>294.96</v>
+        <v>281.03</v>
       </c>
       <c r="D37" s="5"/>
       <c r="E37" s="5">
-        <v>166.15</v>
+        <v>75.98</v>
       </c>
       <c r="F37" s="5"/>
       <c r="G37" s="5" t="s">
@@ -6916,17 +7266,17 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="6">
-        <v>46283.83333333334</v>
+        <v>46284.25</v>
       </c>
       <c r="B38" s="5">
-        <v>424.5</v>
+        <v>343.67</v>
       </c>
       <c r="C38" s="5">
-        <v>294.74</v>
+        <v>280.93</v>
       </c>
       <c r="D38" s="5"/>
       <c r="E38" s="5">
-        <v>155.43</v>
+        <v>71.08</v>
       </c>
       <c r="F38" s="5"/>
       <c r="G38" s="5" t="s">
@@ -6935,17 +7285,17 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="6">
-        <v>46283.875</v>
+        <v>46284.29166666666</v>
       </c>
       <c r="B39" s="5">
-        <v>417.86</v>
+        <v>339.43</v>
       </c>
       <c r="C39" s="5">
-        <v>294.53</v>
+        <v>280.84</v>
       </c>
       <c r="D39" s="5"/>
       <c r="E39" s="5">
-        <v>145.41</v>
+        <v>66.48999999999999</v>
       </c>
       <c r="F39" s="5"/>
       <c r="G39" s="5" t="s">
@@ -6954,17 +7304,17 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="6">
-        <v>46283.91666666666</v>
+        <v>46284.33333333334</v>
       </c>
       <c r="B40" s="5">
-        <v>409.08</v>
+        <v>335.5</v>
       </c>
       <c r="C40" s="5">
-        <v>294.32</v>
+        <v>280.75</v>
       </c>
       <c r="D40" s="5"/>
       <c r="E40" s="5">
-        <v>129.84</v>
+        <v>62.2</v>
       </c>
       <c r="F40" s="5"/>
       <c r="G40" s="5" t="s">
@@ -6973,17 +7323,17 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="6">
-        <v>46283.95833333334</v>
+        <v>46284.375</v>
       </c>
       <c r="B41" s="5">
-        <v>401.08</v>
+        <v>331.84</v>
       </c>
       <c r="C41" s="5">
-        <v>294.11</v>
+        <v>280.66</v>
       </c>
       <c r="D41" s="5"/>
       <c r="E41" s="5">
-        <v>121.47</v>
+        <v>58.19</v>
       </c>
       <c r="F41" s="5"/>
       <c r="G41" s="5" t="s">
@@ -6992,17 +7342,17 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="6">
-        <v>46284</v>
+        <v>46284.41666666666</v>
       </c>
       <c r="B42" s="5">
-        <v>393.73</v>
+        <v>328.43</v>
       </c>
       <c r="C42" s="5">
-        <v>293.9</v>
+        <v>280.56</v>
       </c>
       <c r="D42" s="5"/>
       <c r="E42" s="5">
-        <v>113.63</v>
+        <v>54.44</v>
       </c>
       <c r="F42" s="5"/>
       <c r="G42" s="5" t="s">
@@ -7011,17 +7361,17 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="6">
-        <v>46284.04166666666</v>
+        <v>46284.45833333334</v>
       </c>
       <c r="B43" s="5">
-        <v>385.14</v>
+        <v>325.23</v>
       </c>
       <c r="C43" s="5">
-        <v>293.76</v>
+        <v>280.47</v>
       </c>
       <c r="D43" s="5"/>
       <c r="E43" s="5">
-        <v>99.98999999999999</v>
+        <v>50.93</v>
       </c>
       <c r="F43" s="5"/>
       <c r="G43" s="5" t="s">
@@ -7030,17 +7380,17 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="6">
-        <v>46284.08333333334</v>
+        <v>46284.5</v>
       </c>
       <c r="B44" s="5">
-        <v>377.91</v>
+        <v>322.24</v>
       </c>
       <c r="C44" s="5">
-        <v>293.67</v>
+        <v>280.37</v>
       </c>
       <c r="D44" s="5"/>
       <c r="E44" s="5">
-        <v>93.54000000000001</v>
+        <v>47.64</v>
       </c>
       <c r="F44" s="5"/>
       <c r="G44" s="5" t="s">
@@ -7049,17 +7399,17 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="6">
-        <v>46284.125</v>
+        <v>46284.54166666666</v>
       </c>
       <c r="B45" s="5">
-        <v>371.64</v>
+        <v>319.55</v>
       </c>
       <c r="C45" s="5">
-        <v>293.6</v>
+        <v>280.39</v>
       </c>
       <c r="D45" s="5"/>
       <c r="E45" s="5">
-        <v>87.51000000000001</v>
+        <v>44.57</v>
       </c>
       <c r="F45" s="5"/>
       <c r="G45" s="5" t="s">
@@ -7068,17 +7418,17 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="6">
-        <v>46284.16666666666</v>
+        <v>46284.58333333334</v>
       </c>
       <c r="B46" s="5">
-        <v>366.08</v>
+        <v>317.11</v>
       </c>
       <c r="C46" s="5">
-        <v>293.55</v>
+        <v>280.48</v>
       </c>
       <c r="D46" s="5"/>
       <c r="E46" s="5">
-        <v>81.86</v>
+        <v>41.7</v>
       </c>
       <c r="F46" s="5"/>
       <c r="G46" s="5" t="s">
@@ -7087,17 +7437,17 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="6">
-        <v>46284.20833333334</v>
+        <v>46284.625</v>
       </c>
       <c r="B47" s="5">
-        <v>361.06</v>
+        <v>314.88</v>
       </c>
       <c r="C47" s="5">
-        <v>293.51</v>
+        <v>280.61</v>
       </c>
       <c r="D47" s="5"/>
       <c r="E47" s="5">
-        <v>76.58</v>
+        <v>39.01</v>
       </c>
       <c r="F47" s="5"/>
       <c r="G47" s="5" t="s">
@@ -7106,17 +7456,17 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="6">
-        <v>46284.25</v>
+        <v>46284.66666666666</v>
       </c>
       <c r="B48" s="5">
-        <v>356.49</v>
+        <v>312.82</v>
       </c>
       <c r="C48" s="5">
-        <v>293.47</v>
+        <v>280.77</v>
       </c>
       <c r="D48" s="5"/>
       <c r="E48" s="5">
-        <v>71.65000000000001</v>
+        <v>36.49</v>
       </c>
       <c r="F48" s="5"/>
       <c r="G48" s="5" t="s">
@@ -7125,17 +7475,17 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="6">
-        <v>46284.29166666666</v>
+        <v>46284.70833333334</v>
       </c>
       <c r="B49" s="5">
-        <v>352.27</v>
+        <v>310.93</v>
       </c>
       <c r="C49" s="5">
-        <v>293.44</v>
+        <v>280.94</v>
       </c>
       <c r="D49" s="5"/>
       <c r="E49" s="5">
-        <v>67.03</v>
+        <v>34.14</v>
       </c>
       <c r="F49" s="5"/>
       <c r="G49" s="5" t="s">
@@ -7144,17 +7494,17 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="6">
-        <v>46284.33333333334</v>
+        <v>46284.75</v>
       </c>
       <c r="B50" s="5">
-        <v>348.36</v>
+        <v>309.18</v>
       </c>
       <c r="C50" s="5">
-        <v>293.39</v>
+        <v>281.12</v>
       </c>
       <c r="D50" s="5"/>
       <c r="E50" s="5">
-        <v>62.7</v>
+        <v>31.94</v>
       </c>
       <c r="F50" s="5"/>
       <c r="G50" s="5" t="s">
@@ -7163,17 +7513,17 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="6">
-        <v>46284.375</v>
+        <v>46284.79166666666</v>
       </c>
       <c r="B51" s="5">
-        <v>344.73</v>
+        <v>307.6</v>
       </c>
       <c r="C51" s="5">
-        <v>293.35</v>
+        <v>281.36</v>
       </c>
       <c r="D51" s="5"/>
       <c r="E51" s="5">
-        <v>58.66</v>
+        <v>29.88</v>
       </c>
       <c r="F51" s="5"/>
       <c r="G51" s="5" t="s">
@@ -7182,17 +7532,17 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="6">
-        <v>46284.41666666666</v>
+        <v>46284.83333333334</v>
       </c>
       <c r="B52" s="5">
-        <v>341.34</v>
+        <v>306.17</v>
       </c>
       <c r="C52" s="5">
-        <v>293.3</v>
+        <v>281.62</v>
       </c>
       <c r="D52" s="5"/>
       <c r="E52" s="5">
-        <v>54.88</v>
+        <v>27.95</v>
       </c>
       <c r="F52" s="5"/>
       <c r="G52" s="5" t="s">
@@ -7201,17 +7551,17 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="6">
-        <v>46284.45833333334</v>
+        <v>46284.875</v>
       </c>
       <c r="B53" s="5">
-        <v>338.18</v>
+        <v>304.87</v>
       </c>
       <c r="C53" s="5">
-        <v>293.26</v>
+        <v>281.91</v>
       </c>
       <c r="D53" s="5"/>
       <c r="E53" s="5">
-        <v>51.34</v>
+        <v>26.15</v>
       </c>
       <c r="F53" s="5"/>
       <c r="G53" s="5" t="s">
@@ -7220,17 +7570,17 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="6">
-        <v>46284.5</v>
+        <v>46284.91666666666</v>
       </c>
       <c r="B54" s="5">
-        <v>335.22</v>
+        <v>303.69</v>
       </c>
       <c r="C54" s="5">
-        <v>293.2</v>
+        <v>282.2</v>
       </c>
       <c r="D54" s="5"/>
       <c r="E54" s="5">
-        <v>48.03</v>
+        <v>24.46</v>
       </c>
       <c r="F54" s="5"/>
       <c r="G54" s="5" t="s">
@@ -7239,17 +7589,17 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="6">
-        <v>46284.54166666666</v>
+        <v>46284.95833333334</v>
       </c>
       <c r="B55" s="5">
-        <v>332.56</v>
+        <v>302.6</v>
       </c>
       <c r="C55" s="5">
-        <v>293.26</v>
+        <v>282.5</v>
       </c>
       <c r="D55" s="5"/>
       <c r="E55" s="5">
-        <v>44.93</v>
+        <v>22.88</v>
       </c>
       <c r="F55" s="5"/>
       <c r="G55" s="5" t="s">
@@ -7258,17 +7608,17 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="6">
-        <v>46284.58333333334</v>
+        <v>46285</v>
       </c>
       <c r="B56" s="5">
-        <v>330.15</v>
+        <v>301.61</v>
       </c>
       <c r="C56" s="5">
-        <v>293.39</v>
+        <v>282.81</v>
       </c>
       <c r="D56" s="5"/>
       <c r="E56" s="5">
-        <v>42.03</v>
+        <v>21.41</v>
       </c>
       <c r="F56" s="5"/>
       <c r="G56" s="5" t="s">
@@ -7277,17 +7627,17 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="6">
-        <v>46284.625</v>
+        <v>46285.04166666666</v>
       </c>
       <c r="B57" s="5">
-        <v>327.95</v>
+        <v>300.6</v>
       </c>
       <c r="C57" s="5">
-        <v>293.56</v>
+        <v>283</v>
       </c>
       <c r="D57" s="5"/>
       <c r="E57" s="5">
-        <v>39.32</v>
+        <v>20.03</v>
       </c>
       <c r="F57" s="5"/>
       <c r="G57" s="5" t="s">
@@ -7296,17 +7646,17 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="6">
-        <v>46284.66666666666</v>
+        <v>46285.08333333334</v>
       </c>
       <c r="B58" s="5">
-        <v>325.92</v>
+        <v>299.59</v>
       </c>
       <c r="C58" s="5">
-        <v>293.75</v>
+        <v>283.13</v>
       </c>
       <c r="D58" s="5"/>
       <c r="E58" s="5">
-        <v>36.78</v>
+        <v>18.74</v>
       </c>
       <c r="F58" s="5"/>
       <c r="G58" s="5" t="s">
@@ -7315,17 +7665,17 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="6">
-        <v>46284.70833333334</v>
+        <v>46285.125</v>
       </c>
       <c r="B59" s="5">
-        <v>324.05</v>
+        <v>298.61</v>
       </c>
       <c r="C59" s="5">
-        <v>293.96</v>
+        <v>283.22</v>
       </c>
       <c r="D59" s="5"/>
       <c r="E59" s="5">
-        <v>34.41</v>
+        <v>17.53</v>
       </c>
       <c r="F59" s="5"/>
       <c r="G59" s="5" t="s">
@@ -7334,17 +7684,17 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="6">
-        <v>46284.75</v>
+        <v>46285.16666666666</v>
       </c>
       <c r="B60" s="5">
-        <v>322.32</v>
+        <v>297.68</v>
       </c>
       <c r="C60" s="5">
-        <v>294.17</v>
+        <v>283.28</v>
       </c>
       <c r="D60" s="5"/>
       <c r="E60" s="5">
-        <v>32.19</v>
+        <v>16.4</v>
       </c>
       <c r="F60" s="5"/>
       <c r="G60" s="5" t="s">
@@ -7353,17 +7703,17 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="6">
-        <v>46284.79166666666</v>
+        <v>46285.20833333334</v>
       </c>
       <c r="B61" s="5">
-        <v>320.77</v>
+        <v>296.79</v>
       </c>
       <c r="C61" s="5">
-        <v>294.44</v>
+        <v>283.32</v>
       </c>
       <c r="D61" s="5"/>
       <c r="E61" s="5">
-        <v>30.12</v>
+        <v>15.34</v>
       </c>
       <c r="F61" s="5"/>
       <c r="G61" s="5" t="s">
@@ -7372,17 +7722,17 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="6">
-        <v>46284.83333333334</v>
+        <v>46285.25</v>
       </c>
       <c r="B62" s="5">
-        <v>319.37</v>
+        <v>291.71</v>
       </c>
       <c r="C62" s="5">
-        <v>294.73</v>
+        <v>283.35</v>
       </c>
       <c r="D62" s="5"/>
       <c r="E62" s="5">
-        <v>28.17</v>
+        <v>0</v>
       </c>
       <c r="F62" s="5"/>
       <c r="G62" s="5" t="s">
@@ -7391,17 +7741,17 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="6">
-        <v>46284.875</v>
+        <v>46285.29166666666</v>
       </c>
       <c r="B63" s="5">
-        <v>318.09</v>
+        <v>288.56</v>
       </c>
       <c r="C63" s="5">
-        <v>295.04</v>
+        <v>283.38</v>
       </c>
       <c r="D63" s="5"/>
       <c r="E63" s="5">
-        <v>26.36</v>
+        <v>0</v>
       </c>
       <c r="F63" s="5"/>
       <c r="G63" s="5" t="s">
@@ -7410,17 +7760,17 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="6">
-        <v>46284.91666666666</v>
+        <v>46285.33333333334</v>
       </c>
       <c r="B64" s="5">
-        <v>316.93</v>
+        <v>286.61</v>
       </c>
       <c r="C64" s="5">
-        <v>295.37</v>
+        <v>283.4</v>
       </c>
       <c r="D64" s="5"/>
       <c r="E64" s="5">
-        <v>24.66</v>
+        <v>0</v>
       </c>
       <c r="F64" s="5"/>
       <c r="G64" s="5" t="s">
@@ -7429,17 +7779,17 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="6">
-        <v>46284.95833333334</v>
+        <v>46285.375</v>
       </c>
       <c r="B65" s="5">
-        <v>315.86</v>
+        <v>285.41</v>
       </c>
       <c r="C65" s="5">
-        <v>295.69</v>
+        <v>283.42</v>
       </c>
       <c r="D65" s="5"/>
       <c r="E65" s="5">
-        <v>23.07</v>
+        <v>0</v>
       </c>
       <c r="F65" s="5"/>
       <c r="G65" s="5" t="s">
@@ -7448,17 +7798,17 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="6">
-        <v>46285</v>
+        <v>46285.41666666666</v>
       </c>
       <c r="B66" s="5">
-        <v>314.89</v>
+        <v>284.67</v>
       </c>
       <c r="C66" s="5">
-        <v>296.02</v>
+        <v>283.43</v>
       </c>
       <c r="D66" s="5"/>
       <c r="E66" s="5">
-        <v>21.58</v>
+        <v>0</v>
       </c>
       <c r="F66" s="5"/>
       <c r="G66" s="5" t="s">
@@ -7467,17 +7817,17 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="6">
-        <v>46285.04166666666</v>
+        <v>46285.45833333334</v>
       </c>
       <c r="B67" s="5">
-        <v>313.9</v>
+        <v>284.21</v>
       </c>
       <c r="C67" s="5">
-        <v>296.24</v>
+        <v>283.45</v>
       </c>
       <c r="D67" s="5"/>
       <c r="E67" s="5">
-        <v>20.19</v>
+        <v>0</v>
       </c>
       <c r="F67" s="5"/>
       <c r="G67" s="5" t="s">
@@ -7486,17 +7836,17 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="6">
-        <v>46285.08333333334</v>
+        <v>46285.5</v>
       </c>
       <c r="B68" s="5">
-        <v>312.91</v>
+        <v>283.93</v>
       </c>
       <c r="C68" s="5">
-        <v>296.4</v>
+        <v>283.46</v>
       </c>
       <c r="D68" s="5"/>
       <c r="E68" s="5">
-        <v>18.89</v>
+        <v>0</v>
       </c>
       <c r="F68" s="5"/>
       <c r="G68" s="5" t="s">
@@ -7505,17 +7855,17 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="6">
-        <v>46285.125</v>
+        <v>46285.54166666666</v>
       </c>
       <c r="B69" s="5">
-        <v>311.95</v>
+        <v>283.77</v>
       </c>
       <c r="C69" s="5">
-        <v>296.5</v>
+        <v>283.47</v>
       </c>
       <c r="D69" s="5"/>
       <c r="E69" s="5">
-        <v>17.67</v>
+        <v>0</v>
       </c>
       <c r="F69" s="5"/>
       <c r="G69" s="5" t="s">
@@ -7524,17 +7874,17 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="6">
-        <v>46285.16666666666</v>
+        <v>46285.58333333334</v>
       </c>
       <c r="B70" s="5">
-        <v>311.04</v>
+        <v>283.67</v>
       </c>
       <c r="C70" s="5">
-        <v>296.59</v>
+        <v>283.48</v>
       </c>
       <c r="D70" s="5"/>
       <c r="E70" s="5">
-        <v>16.53</v>
+        <v>0</v>
       </c>
       <c r="F70" s="5"/>
       <c r="G70" s="5" t="s">
@@ -7543,17 +7893,17 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="6">
-        <v>46285.20833333334</v>
+        <v>46285.625</v>
       </c>
       <c r="B71" s="5">
-        <v>310.17</v>
+        <v>283.61</v>
       </c>
       <c r="C71" s="5">
-        <v>296.65</v>
+        <v>283.49</v>
       </c>
       <c r="D71" s="5"/>
       <c r="E71" s="5">
-        <v>15.46</v>
+        <v>0</v>
       </c>
       <c r="F71" s="5"/>
       <c r="G71" s="5" t="s">
@@ -7562,13 +7912,13 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="6">
-        <v>46285.25</v>
+        <v>46285.66666666666</v>
       </c>
       <c r="B72" s="5">
-        <v>305.08</v>
+        <v>283.57</v>
       </c>
       <c r="C72" s="5">
-        <v>296.7</v>
+        <v>283.5</v>
       </c>
       <c r="D72" s="5"/>
       <c r="E72" s="5">
@@ -7581,13 +7931,13 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="6">
-        <v>46285.29166666666</v>
+        <v>46285.70833333334</v>
       </c>
       <c r="B73" s="5">
-        <v>301.94</v>
+        <v>283.56</v>
       </c>
       <c r="C73" s="5">
-        <v>296.75</v>
+        <v>283.51</v>
       </c>
       <c r="D73" s="5"/>
       <c r="E73" s="5">
@@ -7600,13 +7950,13 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="6">
-        <v>46285.33333333334</v>
+        <v>46285.75</v>
       </c>
       <c r="B74" s="5">
-        <v>300.01</v>
+        <v>283.55</v>
       </c>
       <c r="C74" s="5">
-        <v>296.79</v>
+        <v>283.52</v>
       </c>
       <c r="D74" s="5"/>
       <c r="E74" s="5">
@@ -7619,13 +7969,13 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="6">
-        <v>46285.375</v>
+        <v>46285.79166666666</v>
       </c>
       <c r="B75" s="5">
-        <v>298.82</v>
+        <v>283.55</v>
       </c>
       <c r="C75" s="5">
-        <v>296.82</v>
+        <v>283.53</v>
       </c>
       <c r="D75" s="5"/>
       <c r="E75" s="5">
@@ -7638,13 +7988,13 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="6">
-        <v>46285.41666666666</v>
+        <v>46285.83333333334</v>
       </c>
       <c r="B76" s="5">
-        <v>298.09</v>
+        <v>283.55</v>
       </c>
       <c r="C76" s="5">
-        <v>296.85</v>
+        <v>283.54</v>
       </c>
       <c r="D76" s="5"/>
       <c r="E76" s="5">
@@ -7657,13 +8007,13 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="6">
-        <v>46285.45833333334</v>
+        <v>46285.875</v>
       </c>
       <c r="B77" s="5">
-        <v>297.65</v>
+        <v>283.56</v>
       </c>
       <c r="C77" s="5">
-        <v>296.88</v>
+        <v>283.55</v>
       </c>
       <c r="D77" s="5"/>
       <c r="E77" s="5">
@@ -7709,10 +8059,10 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="6">
-        <v>46282.5</v>
+        <v>46283</v>
       </c>
       <c r="B2" s="5">
-        <v>1.33</v>
+        <v>0.67</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>48</v>
@@ -7724,10 +8074,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="6">
-        <v>46282.625</v>
+        <v>46283.125</v>
       </c>
       <c r="B3" s="5">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>48</v>
@@ -7739,10 +8089,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="6">
-        <v>46282.75</v>
+        <v>46283.25</v>
       </c>
       <c r="B4" s="5">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>48</v>
@@ -7754,10 +8104,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="6">
-        <v>46282.875</v>
+        <v>46283.375</v>
       </c>
       <c r="B5" s="5">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>48</v>
@@ -7769,10 +8119,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="6">
-        <v>46283</v>
+        <v>46283.5</v>
       </c>
       <c r="B6" s="5">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>48</v>
@@ -7784,10 +8134,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="6">
-        <v>46283.125</v>
+        <v>46283.625</v>
       </c>
       <c r="B7" s="5">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>48</v>
@@ -7799,10 +8149,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="6">
-        <v>46283.25</v>
+        <v>46283.75</v>
       </c>
       <c r="B8" s="5">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>48</v>
@@ -7814,10 +8164,10 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="6">
-        <v>46283.375</v>
+        <v>46283.875</v>
       </c>
       <c r="B9" s="5">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>48</v>
@@ -7829,10 +8179,10 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="6">
-        <v>46283.5</v>
+        <v>46284</v>
       </c>
       <c r="B10" s="5">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>48</v>
@@ -7844,10 +8194,10 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="6">
-        <v>46283.625</v>
+        <v>46284.125</v>
       </c>
       <c r="B11" s="5">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>48</v>
@@ -7859,10 +8209,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="6">
-        <v>46283.75</v>
+        <v>46284.25</v>
       </c>
       <c r="B12" s="5">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>48</v>
@@ -7874,10 +8224,10 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="6">
-        <v>46283.875</v>
+        <v>46284.375</v>
       </c>
       <c r="B13" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>48</v>
@@ -7889,10 +8239,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="6">
-        <v>46284</v>
+        <v>46284.5</v>
       </c>
       <c r="B14" s="5">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>48</v>
@@ -7904,7 +8254,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="6">
-        <v>46284.125</v>
+        <v>46284.625</v>
       </c>
       <c r="B15" s="5">
         <v>0</v>
@@ -7919,7 +8269,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="6">
-        <v>46284.25</v>
+        <v>46284.75</v>
       </c>
       <c r="B16" s="5">
         <v>0</v>
@@ -7934,7 +8284,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="6">
-        <v>46284.375</v>
+        <v>46284.875</v>
       </c>
       <c r="B17" s="5">
         <v>0</v>
@@ -7949,7 +8299,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="6">
-        <v>46284.5</v>
+        <v>46285</v>
       </c>
       <c r="B18" s="5">
         <v>0</v>
@@ -7964,7 +8314,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="6">
-        <v>46284.625</v>
+        <v>46285.125</v>
       </c>
       <c r="B19" s="5">
         <v>0</v>
@@ -7979,7 +8329,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="6">
-        <v>46284.75</v>
+        <v>46285.25</v>
       </c>
       <c r="B20" s="5">
         <v>0</v>
@@ -7994,7 +8344,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="6">
-        <v>46284.875</v>
+        <v>46285.375</v>
       </c>
       <c r="B21" s="5">
         <v>0</v>
@@ -8009,7 +8359,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="6">
-        <v>46285</v>
+        <v>46285.5</v>
       </c>
       <c r="B22" s="5">
         <v>0</v>
@@ -8024,7 +8374,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="6">
-        <v>46285.125</v>
+        <v>46285.625</v>
       </c>
       <c r="B23" s="5">
         <v>0</v>
@@ -8039,7 +8389,7 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="6">
-        <v>46285.25</v>
+        <v>46285.75</v>
       </c>
       <c r="B24" s="5">
         <v>0</v>
@@ -8054,7 +8404,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="6">
-        <v>46285.375</v>
+        <v>46285.875</v>
       </c>
       <c r="B25" s="5">
         <v>0</v>
@@ -8075,7 +8425,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M67"/>
+  <dimension ref="A1:M77"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="9" width="16.7109375" customWidth="1"/>
@@ -8129,19 +8479,19 @@
         <v>24</v>
       </c>
       <c r="D4" s="5">
-        <v>69.16500000000001</v>
+        <v>53.951</v>
       </c>
       <c r="E4" s="5">
-        <v>74.327</v>
+        <v>59.192</v>
       </c>
       <c r="F4" s="5">
-        <v>44.453</v>
+        <v>29.293</v>
       </c>
       <c r="G4" s="5">
-        <v>20.8</v>
+        <v>41.7</v>
       </c>
       <c r="H4" s="5">
-        <v>87.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -8152,22 +8502,22 @@
         <v>61</v>
       </c>
       <c r="C5" s="5">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="D5" s="5">
-        <v>64.83499999999999</v>
+        <v>58.967</v>
       </c>
       <c r="E5" s="5">
-        <v>72.41200000000001</v>
+        <v>66.24299999999999</v>
       </c>
       <c r="F5" s="5">
-        <v>15.12</v>
+        <v>-0.672</v>
       </c>
       <c r="G5" s="5">
-        <v>42.9</v>
+        <v>44.1</v>
       </c>
       <c r="H5" s="5">
-        <v>85.7</v>
+        <v>94.90000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -8178,22 +8528,22 @@
         <v>62</v>
       </c>
       <c r="C6" s="5">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="D6" s="5">
-        <v>64.83499999999999</v>
+        <v>58.967</v>
       </c>
       <c r="E6" s="5">
-        <v>72.41200000000001</v>
+        <v>66.24299999999999</v>
       </c>
       <c r="F6" s="5">
-        <v>15.12</v>
+        <v>-0.672</v>
       </c>
       <c r="G6" s="5">
-        <v>42.9</v>
+        <v>44.1</v>
       </c>
       <c r="H6" s="5">
-        <v>85.7</v>
+        <v>94.90000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -8339,13 +8689,13 @@
         <v>524.8200000000001</v>
       </c>
       <c r="C19" s="5">
-        <v>384.54</v>
+        <v>369.73</v>
       </c>
       <c r="D19" s="5">
-        <v>289.35</v>
+        <v>275.49</v>
       </c>
       <c r="E19" s="5">
-        <v>-140.28</v>
+        <v>-155.09</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -8356,13 +8706,13 @@
         <v>566.89</v>
       </c>
       <c r="C20" s="5">
-        <v>470.37</v>
+        <v>468.13</v>
       </c>
       <c r="D20" s="5">
-        <v>350.43</v>
+        <v>348.55</v>
       </c>
       <c r="E20" s="5">
-        <v>-96.51999999999998</v>
+        <v>-98.75999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -8373,13 +8723,13 @@
         <v>561.75</v>
       </c>
       <c r="C21" s="5">
-        <v>515.54</v>
+        <v>513.25</v>
       </c>
       <c r="D21" s="5">
-        <v>361.47</v>
+        <v>359.64</v>
       </c>
       <c r="E21" s="5">
-        <v>-46.21000000000004</v>
+        <v>-48.5</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -8390,13 +8740,13 @@
         <v>482.62</v>
       </c>
       <c r="C22" s="5">
-        <v>532.55</v>
+        <v>530.09</v>
       </c>
       <c r="D22" s="5">
-        <v>343.89</v>
+        <v>341.97</v>
       </c>
       <c r="E22" s="5">
-        <v>49.92999999999995</v>
+        <v>47.47000000000003</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -8407,13 +8757,13 @@
         <v>443.5</v>
       </c>
       <c r="C23" s="5">
-        <v>534.33</v>
+        <v>531.66</v>
       </c>
       <c r="D23" s="5">
-        <v>314</v>
+        <v>311.95</v>
       </c>
       <c r="E23" s="5">
-        <v>90.83000000000004</v>
+        <v>88.15999999999997</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -8424,13 +8774,13 @@
         <v>451.89</v>
       </c>
       <c r="C24" s="5">
-        <v>551.25</v>
+        <v>548.47</v>
       </c>
       <c r="D24" s="5">
-        <v>305.88</v>
+        <v>303.8</v>
       </c>
       <c r="E24" s="5">
-        <v>99.36000000000001</v>
+        <v>96.58000000000004</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -8441,13 +8791,13 @@
         <v>431.62</v>
       </c>
       <c r="C25" s="5">
-        <v>558.59</v>
+        <v>555.78</v>
       </c>
       <c r="D25" s="5">
-        <v>302.49</v>
+        <v>300.4</v>
       </c>
       <c r="E25" s="5">
-        <v>126.97</v>
+        <v>124.16</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -8458,13 +8808,13 @@
         <v>453.4</v>
       </c>
       <c r="C26" s="5">
-        <v>554.03</v>
+        <v>551.15</v>
       </c>
       <c r="D26" s="5">
-        <v>291.6</v>
+        <v>289.45</v>
       </c>
       <c r="E26" s="5">
-        <v>100.63</v>
+        <v>97.75</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -8475,13 +8825,13 @@
         <v>666.5</v>
       </c>
       <c r="C27" s="5">
-        <v>529.76</v>
+        <v>526.74</v>
       </c>
       <c r="D27" s="5">
-        <v>267.55</v>
+        <v>265.29</v>
       </c>
       <c r="E27" s="5">
-        <v>-136.74</v>
+        <v>-139.76</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -8492,13 +8842,13 @@
         <v>536.49</v>
       </c>
       <c r="C28" s="5">
-        <v>530.74</v>
+        <v>527.71</v>
       </c>
       <c r="D28" s="5">
-        <v>281.06</v>
+        <v>278.86</v>
       </c>
       <c r="E28" s="5">
-        <v>-5.75</v>
+        <v>-8.779999999999973</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -8509,13 +8859,13 @@
         <v>502.61</v>
       </c>
       <c r="C29" s="5">
-        <v>532.73</v>
+        <v>529.66</v>
       </c>
       <c r="D29" s="5">
-        <v>298.48</v>
+        <v>296.36</v>
       </c>
       <c r="E29" s="5">
-        <v>30.12</v>
+        <v>27.04999999999995</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -8526,13 +8876,13 @@
         <v>449.1</v>
       </c>
       <c r="C30" s="5">
-        <v>517.99</v>
+        <v>514.7</v>
       </c>
       <c r="D30" s="5">
-        <v>297.72</v>
+        <v>295.6</v>
       </c>
       <c r="E30" s="5">
-        <v>68.88999999999999</v>
+        <v>65.60000000000002</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -8543,13 +8893,13 @@
         <v>453.2</v>
       </c>
       <c r="C31" s="5">
-        <v>481.95</v>
+        <v>478.17</v>
       </c>
       <c r="D31" s="5">
-        <v>274.09</v>
+        <v>271.86</v>
       </c>
       <c r="E31" s="5">
-        <v>28.75</v>
+        <v>24.97000000000003</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -8560,13 +8910,13 @@
         <v>506.78</v>
       </c>
       <c r="C32" s="5">
-        <v>469.56</v>
+        <v>465.18</v>
       </c>
       <c r="D32" s="5">
-        <v>272.39</v>
+        <v>270.15</v>
       </c>
       <c r="E32" s="5">
-        <v>-37.21999999999997</v>
+        <v>-41.59999999999997</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -8577,13 +8927,13 @@
         <v>521.5599999999999</v>
       </c>
       <c r="C33" s="5">
-        <v>479.1</v>
+        <v>473.98</v>
       </c>
       <c r="D33" s="5">
-        <v>290.79</v>
+        <v>288.64</v>
       </c>
       <c r="E33" s="5">
-        <v>-42.45999999999992</v>
+        <v>-47.57999999999993</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -8594,13 +8944,13 @@
         <v>525.3</v>
       </c>
       <c r="C34" s="5">
-        <v>488.83</v>
+        <v>482.69</v>
       </c>
       <c r="D34" s="5">
-        <v>307.48</v>
+        <v>305.41</v>
       </c>
       <c r="E34" s="5">
-        <v>-36.46999999999997</v>
+        <v>-42.60999999999996</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -8611,13 +8961,13 @@
         <v>530.12</v>
       </c>
       <c r="C35" s="5">
-        <v>490.84</v>
+        <v>483.39</v>
       </c>
       <c r="D35" s="5">
-        <v>314.61</v>
+        <v>312.57</v>
       </c>
       <c r="E35" s="5">
-        <v>-39.28000000000003</v>
+        <v>-46.73000000000002</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -8628,13 +8978,13 @@
         <v>537.58</v>
       </c>
       <c r="C36" s="5">
-        <v>491.34</v>
+        <v>482.36</v>
       </c>
       <c r="D36" s="5">
-        <v>318.59</v>
+        <v>316.57</v>
       </c>
       <c r="E36" s="5">
-        <v>-46.24000000000007</v>
+        <v>-55.22000000000003</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -8645,13 +8995,13 @@
         <v>536.9</v>
       </c>
       <c r="C37" s="5">
-        <v>491.97</v>
+        <v>481.35</v>
       </c>
       <c r="D37" s="5">
-        <v>321.43</v>
+        <v>319.41</v>
       </c>
       <c r="E37" s="5">
-        <v>-44.92999999999995</v>
+        <v>-55.54999999999995</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -8662,13 +9012,13 @@
         <v>535.1</v>
       </c>
       <c r="C38" s="5">
-        <v>497.83</v>
+        <v>485.62</v>
       </c>
       <c r="D38" s="5">
-        <v>328.76</v>
+        <v>326.78</v>
       </c>
       <c r="E38" s="5">
-        <v>-37.27000000000004</v>
+        <v>-49.48000000000002</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -8679,13 +9029,13 @@
         <v>524.8</v>
       </c>
       <c r="C39" s="5">
-        <v>499.44</v>
+        <v>485.79</v>
       </c>
       <c r="D39" s="5">
-        <v>331.7</v>
+        <v>329.73</v>
       </c>
       <c r="E39" s="5">
-        <v>-25.35999999999996</v>
+        <v>-39.00999999999993</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -8696,13 +9046,13 @@
         <v>533.77</v>
       </c>
       <c r="C40" s="5">
-        <v>497.48</v>
+        <v>482.86</v>
       </c>
       <c r="D40" s="5">
-        <v>332.14</v>
+        <v>330.17</v>
       </c>
       <c r="E40" s="5">
-        <v>-36.28999999999996</v>
+        <v>-50.90999999999997</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -8713,13 +9063,13 @@
         <v>543.22</v>
       </c>
       <c r="C41" s="5">
-        <v>495.93</v>
+        <v>480.76</v>
       </c>
       <c r="D41" s="5">
-        <v>333.85</v>
+        <v>331.89</v>
       </c>
       <c r="E41" s="5">
-        <v>-47.29000000000002</v>
+        <v>-62.46000000000004</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -8730,13 +9080,13 @@
         <v>541.97</v>
       </c>
       <c r="C42" s="5">
-        <v>493.1</v>
+        <v>477.52</v>
       </c>
       <c r="D42" s="5">
-        <v>333.96</v>
+        <v>332.01</v>
       </c>
       <c r="E42" s="5">
-        <v>-48.87</v>
+        <v>-64.45000000000005</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -8747,13 +9097,13 @@
         <v>540.8</v>
       </c>
       <c r="C43" s="5">
-        <v>486.52</v>
+        <v>470.76</v>
       </c>
       <c r="D43" s="5">
-        <v>330.25</v>
+        <v>328.28</v>
       </c>
       <c r="E43" s="5">
-        <v>-54.27999999999997</v>
+        <v>-70.03999999999996</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -8761,16 +9111,16 @@
         <v>46281.5</v>
       </c>
       <c r="B44" s="5">
-        <v>537.9</v>
+        <v>538.5</v>
       </c>
       <c r="C44" s="5">
-        <v>483.25</v>
+        <v>467.92</v>
       </c>
       <c r="D44" s="5">
-        <v>329.67</v>
+        <v>327.95</v>
       </c>
       <c r="E44" s="5">
-        <v>-54.64999999999998</v>
+        <v>-70.57999999999998</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -8778,16 +9128,16 @@
         <v>46281.54166666666</v>
       </c>
       <c r="B45" s="5">
-        <v>562.3</v>
+        <v>563.6</v>
       </c>
       <c r="C45" s="5">
-        <v>480.96</v>
+        <v>466.45</v>
       </c>
       <c r="D45" s="5">
-        <v>330.75</v>
+        <v>328.98</v>
       </c>
       <c r="E45" s="5">
-        <v>-81.33999999999997</v>
+        <v>-97.15000000000003</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -8795,16 +9145,16 @@
         <v>46281.58333333334</v>
       </c>
       <c r="B46" s="5">
-        <v>557.5</v>
+        <v>557.3099999999999</v>
       </c>
       <c r="C46" s="5">
-        <v>484.97</v>
+        <v>471.06</v>
       </c>
       <c r="D46" s="5">
-        <v>334.27</v>
+        <v>332.32</v>
       </c>
       <c r="E46" s="5">
-        <v>-72.52999999999997</v>
+        <v>-86.24999999999994</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -8815,13 +9165,13 @@
         <v>535.9</v>
       </c>
       <c r="C47" s="5">
-        <v>491.09</v>
+        <v>478.07</v>
       </c>
       <c r="D47" s="5">
-        <v>335.21</v>
+        <v>333.46</v>
       </c>
       <c r="E47" s="5">
-        <v>-44.81</v>
+        <v>-57.82999999999998</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -8829,16 +9179,16 @@
         <v>46281.66666666666</v>
       </c>
       <c r="B48" s="5">
-        <v>528.14</v>
+        <v>526.76</v>
       </c>
       <c r="C48" s="5">
-        <v>499.84</v>
+        <v>487.36</v>
       </c>
       <c r="D48" s="5">
-        <v>333.51</v>
+        <v>331.66</v>
       </c>
       <c r="E48" s="5">
-        <v>-28.30000000000001</v>
+        <v>-39.39999999999998</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -8846,16 +9196,16 @@
         <v>46281.70833333334</v>
       </c>
       <c r="B49" s="5">
-        <v>527.75</v>
+        <v>528.46</v>
       </c>
       <c r="C49" s="5">
-        <v>512.84</v>
+        <v>500.7</v>
       </c>
       <c r="D49" s="5">
-        <v>330.72</v>
+        <v>328.67</v>
       </c>
       <c r="E49" s="5">
-        <v>-14.90999999999997</v>
+        <v>-27.76000000000005</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -8866,13 +9216,13 @@
         <v>529.48</v>
       </c>
       <c r="C50" s="5">
-        <v>532.53</v>
+        <v>521.52</v>
       </c>
       <c r="D50" s="5">
-        <v>330.01</v>
+        <v>328.65</v>
       </c>
       <c r="E50" s="5">
-        <v>3.049999999999955</v>
+        <v>-7.960000000000036</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -8880,16 +9230,16 @@
         <v>46281.79166666666</v>
       </c>
       <c r="B51" s="5">
-        <v>505.47</v>
+        <v>505.04</v>
       </c>
       <c r="C51" s="5">
-        <v>551.48</v>
+        <v>540.23</v>
       </c>
       <c r="D51" s="5">
-        <v>325.59</v>
+        <v>323.66</v>
       </c>
       <c r="E51" s="5">
-        <v>46.00999999999999</v>
+        <v>35.19</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -8897,16 +9247,16 @@
         <v>46281.83333333334</v>
       </c>
       <c r="B52" s="5">
-        <v>505.4</v>
+        <v>505.04</v>
       </c>
       <c r="C52" s="5">
-        <v>566.02</v>
+        <v>554.85</v>
       </c>
       <c r="D52" s="5">
-        <v>316.21</v>
+        <v>314.16</v>
       </c>
       <c r="E52" s="5">
-        <v>60.62</v>
+        <v>49.81</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -8914,16 +9264,16 @@
         <v>46281.875</v>
       </c>
       <c r="B53" s="5">
-        <v>505.4</v>
+        <v>506.6</v>
       </c>
       <c r="C53" s="5">
-        <v>582.01</v>
+        <v>570.63</v>
       </c>
       <c r="D53" s="5">
-        <v>310.63</v>
+        <v>308.33</v>
       </c>
       <c r="E53" s="5">
-        <v>76.61000000000001</v>
+        <v>64.02999999999997</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -8931,16 +9281,16 @@
         <v>46281.91666666666</v>
       </c>
       <c r="B54" s="5">
-        <v>508.08</v>
+        <v>506.75</v>
       </c>
       <c r="C54" s="5">
-        <v>592.53</v>
+        <v>581.53</v>
       </c>
       <c r="D54" s="5">
-        <v>304.66</v>
+        <v>302.93</v>
       </c>
       <c r="E54" s="5">
-        <v>84.44999999999999</v>
+        <v>74.77999999999997</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -8948,16 +9298,16 @@
         <v>46281.95833333334</v>
       </c>
       <c r="B55" s="5">
-        <v>512.12</v>
+        <v>510.56</v>
       </c>
       <c r="C55" s="5">
-        <v>597.21</v>
+        <v>585.42</v>
       </c>
       <c r="D55" s="5">
-        <v>304.36</v>
+        <v>302.27</v>
       </c>
       <c r="E55" s="5">
-        <v>85.09000000000003</v>
+        <v>74.85999999999996</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -8965,16 +9315,16 @@
         <v>46282</v>
       </c>
       <c r="B56" s="5">
-        <v>505.65</v>
+        <v>507.4</v>
       </c>
       <c r="C56" s="5">
-        <v>598.98</v>
+        <v>586.3200000000001</v>
       </c>
       <c r="D56" s="5">
-        <v>303.87</v>
+        <v>301.65</v>
       </c>
       <c r="E56" s="5">
-        <v>93.33000000000004</v>
+        <v>78.92000000000007</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -8982,16 +9332,16 @@
         <v>46282.04166666666</v>
       </c>
       <c r="B57" s="5">
-        <v>496.42</v>
+        <v>500.7</v>
       </c>
       <c r="C57" s="5">
-        <v>597.92</v>
+        <v>584.1799999999999</v>
       </c>
       <c r="D57" s="5">
-        <v>303.25</v>
+        <v>301.04</v>
       </c>
       <c r="E57" s="5">
-        <v>101.4999999999999</v>
+        <v>83.47999999999996</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -8999,16 +9349,16 @@
         <v>46282.08333333334</v>
       </c>
       <c r="B58" s="5">
-        <v>541.66</v>
+        <v>543.55</v>
       </c>
       <c r="C58" s="5">
-        <v>595.65</v>
+        <v>580.8200000000001</v>
       </c>
       <c r="D58" s="5">
-        <v>304.94</v>
+        <v>303.07</v>
       </c>
       <c r="E58" s="5">
-        <v>53.99000000000001</v>
+        <v>37.2700000000001</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -9016,16 +9366,16 @@
         <v>46282.125</v>
       </c>
       <c r="B59" s="5">
-        <v>536.22</v>
+        <v>530.17</v>
       </c>
       <c r="C59" s="5">
-        <v>596.6799999999999</v>
+        <v>580.05</v>
       </c>
       <c r="D59" s="5">
-        <v>306.82</v>
+        <v>304.88</v>
       </c>
       <c r="E59" s="5">
-        <v>60.45999999999992</v>
+        <v>49.88</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -9033,16 +9383,16 @@
         <v>46282.16666666666</v>
       </c>
       <c r="B60" s="5">
-        <v>504.07</v>
+        <v>503.26</v>
       </c>
       <c r="C60" s="5">
-        <v>589.73</v>
+        <v>570.13</v>
       </c>
       <c r="D60" s="5">
-        <v>310.47</v>
+        <v>307.42</v>
       </c>
       <c r="E60" s="5">
-        <v>85.66000000000003</v>
+        <v>66.87</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -9050,16 +9400,16 @@
         <v>46282.20833333334</v>
       </c>
       <c r="B61" s="5">
-        <v>498.87</v>
+        <v>497.91</v>
       </c>
       <c r="C61" s="5">
-        <v>592.4299999999999</v>
+        <v>571.71</v>
       </c>
       <c r="D61" s="5">
-        <v>309.61</v>
+        <v>307.4</v>
       </c>
       <c r="E61" s="5">
-        <v>93.55999999999995</v>
+        <v>73.80000000000001</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -9067,16 +9417,16 @@
         <v>46282.25</v>
       </c>
       <c r="B62" s="5">
-        <v>478.75</v>
+        <v>479.3</v>
       </c>
       <c r="C62" s="5">
-        <v>593.73</v>
+        <v>571.37</v>
       </c>
       <c r="D62" s="5">
-        <v>307.47</v>
+        <v>305.39</v>
       </c>
       <c r="E62" s="5">
-        <v>114.98</v>
+        <v>92.06999999999999</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -9084,16 +9434,16 @@
         <v>46282.29166666666</v>
       </c>
       <c r="B63" s="5">
-        <v>482.61</v>
+        <v>482.23</v>
       </c>
       <c r="C63" s="5">
-        <v>584.1</v>
+        <v>561.0599999999999</v>
       </c>
       <c r="D63" s="5">
-        <v>297.75</v>
+        <v>296.18</v>
       </c>
       <c r="E63" s="5">
-        <v>101.49</v>
+        <v>78.82999999999993</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -9101,16 +9451,16 @@
         <v>46282.33333333334</v>
       </c>
       <c r="B64" s="5">
-        <v>480.17</v>
+        <v>479.81</v>
       </c>
       <c r="C64" s="5">
-        <v>565.8</v>
+        <v>541.0599999999999</v>
       </c>
       <c r="D64" s="5">
-        <v>292.82</v>
+        <v>290.59</v>
       </c>
       <c r="E64" s="5">
-        <v>85.62999999999994</v>
+        <v>61.24999999999994</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -9118,16 +9468,16 @@
         <v>46282.375</v>
       </c>
       <c r="B65" s="5">
-        <v>476.7</v>
+        <v>476.6</v>
       </c>
       <c r="C65" s="5">
-        <v>561.1900000000001</v>
+        <v>536.25</v>
       </c>
       <c r="D65" s="5">
-        <v>289.22</v>
+        <v>287.55</v>
       </c>
       <c r="E65" s="5">
-        <v>84.49000000000007</v>
+        <v>59.64999999999998</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -9135,16 +9485,16 @@
         <v>46282.41666666666</v>
       </c>
       <c r="B66" s="5">
-        <v>476.4</v>
+        <v>478.17</v>
       </c>
       <c r="C66" s="5">
-        <v>552.84</v>
+        <v>527.9299999999999</v>
       </c>
       <c r="D66" s="5">
-        <v>286.72</v>
+        <v>285.11</v>
       </c>
       <c r="E66" s="5">
-        <v>76.44000000000005</v>
+        <v>49.75999999999993</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -9152,16 +9502,186 @@
         <v>46282.45833333334</v>
       </c>
       <c r="B67" s="5">
-        <v>487.45</v>
+        <v>488.02</v>
       </c>
       <c r="C67" s="5">
-        <v>543.51</v>
+        <v>519.5700000000001</v>
       </c>
       <c r="D67" s="5">
-        <v>286.72</v>
+        <v>285.61</v>
       </c>
       <c r="E67" s="5">
-        <v>56.06</v>
+        <v>31.55000000000007</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="6">
+        <v>46282.5</v>
+      </c>
+      <c r="B68" s="5">
+        <v>480.16</v>
+      </c>
+      <c r="C68" s="5">
+        <v>509.01</v>
+      </c>
+      <c r="D68" s="5">
+        <v>285.61</v>
+      </c>
+      <c r="E68" s="5">
+        <v>28.84999999999997</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="6">
+        <v>46282.54166666666</v>
+      </c>
+      <c r="B69" s="5">
+        <v>469.65</v>
+      </c>
+      <c r="C69" s="5">
+        <v>494.6</v>
+      </c>
+      <c r="D69" s="5">
+        <v>285.61</v>
+      </c>
+      <c r="E69" s="5">
+        <v>24.95000000000005</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="6">
+        <v>46282.58333333334</v>
+      </c>
+      <c r="B70" s="5">
+        <v>461.13</v>
+      </c>
+      <c r="C70" s="5">
+        <v>479.5</v>
+      </c>
+      <c r="D70" s="5">
+        <v>283.99</v>
+      </c>
+      <c r="E70" s="5">
+        <v>18.37</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="6">
+        <v>46282.625</v>
+      </c>
+      <c r="B71" s="5">
+        <v>452.9</v>
+      </c>
+      <c r="C71" s="5">
+        <v>466.69</v>
+      </c>
+      <c r="D71" s="5">
+        <v>283.79</v>
+      </c>
+      <c r="E71" s="5">
+        <v>13.79000000000002</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="6">
+        <v>46282.66666666666</v>
+      </c>
+      <c r="B72" s="5">
+        <v>455.09</v>
+      </c>
+      <c r="C72" s="5">
+        <v>451.47</v>
+      </c>
+      <c r="D72" s="5">
+        <v>280.36</v>
+      </c>
+      <c r="E72" s="5">
+        <v>-3.619999999999948</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="6">
+        <v>46282.70833333334</v>
+      </c>
+      <c r="B73" s="5">
+        <v>462.1</v>
+      </c>
+      <c r="C73" s="5">
+        <v>433.1</v>
+      </c>
+      <c r="D73" s="5">
+        <v>273.02</v>
+      </c>
+      <c r="E73" s="5">
+        <v>-29</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="6">
+        <v>46282.75</v>
+      </c>
+      <c r="B74" s="5">
+        <v>473.8</v>
+      </c>
+      <c r="C74" s="5">
+        <v>421.89</v>
+      </c>
+      <c r="D74" s="5">
+        <v>272.13</v>
+      </c>
+      <c r="E74" s="5">
+        <v>-51.91000000000003</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="6">
+        <v>46282.79166666666</v>
+      </c>
+      <c r="B75" s="5">
+        <v>480.4</v>
+      </c>
+      <c r="C75" s="5">
+        <v>411.97</v>
+      </c>
+      <c r="D75" s="5">
+        <v>271.87</v>
+      </c>
+      <c r="E75" s="5">
+        <v>-68.42999999999995</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="6">
+        <v>46282.83333333334</v>
+      </c>
+      <c r="B76" s="5">
+        <v>474.5</v>
+      </c>
+      <c r="C76" s="5">
+        <v>402.67</v>
+      </c>
+      <c r="D76" s="5">
+        <v>273.53</v>
+      </c>
+      <c r="E76" s="5">
+        <v>-71.82999999999998</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="6">
+        <v>46282.875</v>
+      </c>
+      <c r="B77" s="5">
+        <v>466.25</v>
+      </c>
+      <c r="C77" s="5">
+        <v>395.15</v>
+      </c>
+      <c r="D77" s="5">
+        <v>274.35</v>
+      </c>
+      <c r="E77" s="5">
+        <v>-71.10000000000002</v>
       </c>
     </row>
   </sheetData>
@@ -9208,19 +9728,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="6">
-        <v>46282.45833333334</v>
+        <v>46282.875</v>
       </c>
       <c r="B2" s="5">
-        <v>0.59</v>
+        <v>0.28</v>
       </c>
       <c r="C2" s="5">
-        <v>-13.06</v>
+        <v>-6.9</v>
       </c>
       <c r="D2" s="5">
-        <v>14.17</v>
+        <v>8.56</v>
       </c>
       <c r="E2" s="5">
-        <v>71.7</v>
+        <v>53.9</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>81</v>
@@ -9231,19 +9751,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="6">
-        <v>46282.58333333334</v>
+        <v>46283</v>
       </c>
       <c r="B3" s="5">
-        <v>0.54</v>
+        <v>0.26</v>
       </c>
       <c r="C3" s="5">
-        <v>-12.81</v>
+        <v>-4.84</v>
       </c>
       <c r="D3" s="5">
-        <v>13.93</v>
+        <v>6.55</v>
       </c>
       <c r="E3" s="5">
-        <v>71</v>
+        <v>46.2</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>81</v>
@@ -9254,413 +9774,413 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="6">
-        <v>46282.70833333334</v>
+        <v>46283.125</v>
       </c>
       <c r="B4" s="5">
-        <v>0.5</v>
+        <v>0.23</v>
       </c>
       <c r="C4" s="5">
-        <v>-11.04</v>
+        <v>-3.77</v>
       </c>
       <c r="D4" s="5">
-        <v>12.17</v>
+        <v>5.52</v>
       </c>
       <c r="E4" s="5">
-        <v>64.5</v>
+        <v>42.3</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>81</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="6">
-        <v>46282.83333333334</v>
+        <v>46283.25</v>
       </c>
       <c r="B5" s="5">
-        <v>0.46</v>
+        <v>0.22</v>
       </c>
       <c r="C5" s="5">
-        <v>-8.56</v>
+        <v>-5.24</v>
       </c>
       <c r="D5" s="5">
-        <v>9.699999999999999</v>
+        <v>7.04</v>
       </c>
       <c r="E5" s="5">
-        <v>55.3</v>
+        <v>48</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>81</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="6">
-        <v>46282.95833333334</v>
+        <v>46283.375</v>
       </c>
       <c r="B6" s="5">
-        <v>0.42</v>
+        <v>0.2</v>
       </c>
       <c r="C6" s="5">
-        <v>-6.31</v>
+        <v>-7.41</v>
       </c>
       <c r="D6" s="5">
-        <v>7.46</v>
+        <v>9.24</v>
       </c>
       <c r="E6" s="5">
-        <v>46.9</v>
+        <v>56.3</v>
       </c>
       <c r="F6" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="G6" s="5" t="s">
         <v>83</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="6">
-        <v>46283.08333333334</v>
+        <v>46283.5</v>
       </c>
       <c r="B7" s="5">
-        <v>0.39</v>
+        <v>0.18</v>
       </c>
       <c r="C7" s="5">
-        <v>-4.77</v>
+        <v>-9.82</v>
       </c>
       <c r="D7" s="5">
-        <v>5.92</v>
+        <v>11.69</v>
       </c>
       <c r="E7" s="5">
-        <v>41.3</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="F7" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="G7" s="5" t="s">
         <v>83</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="6">
-        <v>46283.20833333334</v>
+        <v>46283.625</v>
       </c>
       <c r="B8" s="5">
-        <v>0.36</v>
+        <v>0.17</v>
       </c>
       <c r="C8" s="5">
-        <v>-5.56</v>
+        <v>-11.63</v>
       </c>
       <c r="D8" s="5">
-        <v>6.72</v>
+        <v>13.52</v>
       </c>
       <c r="E8" s="5">
-        <v>44.5</v>
+        <v>72.5</v>
       </c>
       <c r="F8" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="G8" s="5" t="s">
         <v>83</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="6">
-        <v>46283.33333333334</v>
+        <v>46283.75</v>
       </c>
       <c r="B9" s="5">
-        <v>0.33</v>
+        <v>0.15</v>
       </c>
       <c r="C9" s="5">
-        <v>-7.52</v>
+        <v>-12.01</v>
       </c>
       <c r="D9" s="5">
-        <v>8.69</v>
+        <v>13.94</v>
       </c>
       <c r="E9" s="5">
-        <v>52.1</v>
+        <v>74</v>
       </c>
       <c r="F9" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="G9" s="5" t="s">
         <v>83</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="6">
-        <v>46283.45833333334</v>
+        <v>46283.875</v>
       </c>
       <c r="B10" s="5">
-        <v>0.3</v>
+        <v>0.14</v>
       </c>
       <c r="C10" s="5">
-        <v>-9.94</v>
+        <v>-10.79</v>
       </c>
       <c r="D10" s="5">
-        <v>11.12</v>
+        <v>12.74</v>
       </c>
       <c r="E10" s="5">
-        <v>61.4</v>
+        <v>69.5</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="6">
-        <v>46283.58333333334</v>
+        <v>46284</v>
       </c>
       <c r="B11" s="5">
-        <v>0.28</v>
+        <v>0.13</v>
       </c>
       <c r="C11" s="5">
-        <v>-12.07</v>
+        <v>-8.550000000000001</v>
       </c>
       <c r="D11" s="5">
-        <v>13.25</v>
+        <v>10.53</v>
       </c>
       <c r="E11" s="5">
-        <v>69.7</v>
+        <v>61.1</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="6">
-        <v>46283.70833333334</v>
+        <v>46284.125</v>
       </c>
       <c r="B12" s="5">
-        <v>0.26</v>
+        <v>0.12</v>
       </c>
       <c r="C12" s="5">
-        <v>-12.99</v>
+        <v>-6.22</v>
       </c>
       <c r="D12" s="5">
-        <v>14.18</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="E12" s="5">
-        <v>73.3</v>
+        <v>52.3</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>81</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="6">
-        <v>46283.83333333334</v>
+        <v>46284.25</v>
       </c>
       <c r="B13" s="5">
-        <v>0.24</v>
+        <v>0.11</v>
       </c>
       <c r="C13" s="5">
-        <v>-12.28</v>
+        <v>-4.45</v>
       </c>
       <c r="D13" s="5">
-        <v>13.47</v>
+        <v>6.47</v>
       </c>
       <c r="E13" s="5">
-        <v>70.7</v>
+        <v>45.6</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>81</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="6">
-        <v>46283.95833333334</v>
+        <v>46284.375</v>
       </c>
       <c r="B14" s="5">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="C14" s="5">
-        <v>-10.29</v>
+        <v>-3.4</v>
       </c>
       <c r="D14" s="5">
-        <v>11.49</v>
+        <v>5.45</v>
       </c>
       <c r="E14" s="5">
-        <v>63.3</v>
+        <v>41.7</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>81</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="6">
-        <v>46284.08333333334</v>
+        <v>46284.5</v>
       </c>
       <c r="B15" s="5">
-        <v>0.2</v>
+        <v>0.09</v>
       </c>
       <c r="C15" s="5">
-        <v>-7.9</v>
+        <v>-2.91</v>
       </c>
       <c r="D15" s="5">
-        <v>9.1</v>
+        <v>4.97</v>
       </c>
       <c r="E15" s="5">
-        <v>54.3</v>
+        <v>39.8</v>
       </c>
       <c r="F15" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="G15" s="5" t="s">
         <v>83</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="6">
-        <v>46284.20833333334</v>
+        <v>46284.625</v>
       </c>
       <c r="B16" s="5">
-        <v>0.18</v>
+        <v>0.09</v>
       </c>
       <c r="C16" s="5">
-        <v>-5.91</v>
+        <v>-2.72</v>
       </c>
       <c r="D16" s="5">
-        <v>7.11</v>
+        <v>4.8</v>
       </c>
       <c r="E16" s="5">
-        <v>46.8</v>
+        <v>39.2</v>
       </c>
       <c r="F16" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="G16" s="5" t="s">
         <v>83</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="6">
-        <v>46284.33333333334</v>
+        <v>46284.75</v>
       </c>
       <c r="B17" s="5">
-        <v>0.17</v>
+        <v>0.08</v>
       </c>
       <c r="C17" s="5">
-        <v>-4.63</v>
+        <v>-2.66</v>
       </c>
       <c r="D17" s="5">
-        <v>5.84</v>
+        <v>4.75</v>
       </c>
       <c r="E17" s="5">
-        <v>42.1</v>
+        <v>39</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="6">
-        <v>46284.45833333334</v>
+        <v>46284.875</v>
       </c>
       <c r="B18" s="5">
-        <v>0.16</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C18" s="5">
-        <v>-3.99</v>
+        <v>-2.66</v>
       </c>
       <c r="D18" s="5">
-        <v>5.2</v>
+        <v>4.77</v>
       </c>
       <c r="E18" s="5">
-        <v>39.7</v>
+        <v>39</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="6">
-        <v>46284.58333333334</v>
+        <v>46285</v>
       </c>
       <c r="B19" s="5">
-        <v>0.14</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C19" s="5">
-        <v>-3.73</v>
+        <v>-2.66</v>
       </c>
       <c r="D19" s="5">
-        <v>4.95</v>
+        <v>4.79</v>
       </c>
       <c r="E19" s="5">
-        <v>38.8</v>
+        <v>39.1</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="6">
-        <v>46284.70833333334</v>
+        <v>46285.125</v>
       </c>
       <c r="B20" s="5">
-        <v>0.13</v>
+        <v>0.06</v>
       </c>
       <c r="C20" s="5">
-        <v>-3.65</v>
+        <v>-2.67</v>
       </c>
       <c r="D20" s="5">
-        <v>4.87</v>
+        <v>4.8</v>
       </c>
       <c r="E20" s="5">
-        <v>38.6</v>
+        <v>39.1</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="6">
-        <v>46284.83333333334</v>
+        <v>46285.25</v>
       </c>
       <c r="B21" s="5">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="C21" s="5">
-        <v>-3.63</v>
+        <v>-2.67</v>
       </c>
       <c r="D21" s="5">
-        <v>4.85</v>
+        <v>4.82</v>
       </c>
       <c r="E21" s="5">
-        <v>38.6</v>
+        <v>39.2</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G21" s="5" t="s">
         <v>85</v>
@@ -9668,112 +10188,106 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="6">
-        <v>46284.95833333334</v>
+        <v>46285.375</v>
       </c>
       <c r="B22" s="5">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="C22" s="5">
-        <v>-3.63</v>
+        <v>-2.67</v>
       </c>
       <c r="D22" s="5">
-        <v>4.86</v>
+        <v>4.82</v>
       </c>
       <c r="E22" s="5">
-        <v>38.6</v>
+        <v>39.2</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>85</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="G22" s="5"/>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="6">
-        <v>46285.08333333334</v>
+        <v>46285.5</v>
       </c>
       <c r="B23" s="5">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="C23" s="5">
-        <v>-3.63</v>
+        <v>-2.67</v>
       </c>
       <c r="D23" s="5">
-        <v>4.85</v>
+        <v>4.82</v>
       </c>
       <c r="E23" s="5">
-        <v>38.6</v>
+        <v>39.2</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>85</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="G23" s="5"/>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="6">
-        <v>46285.20833333334</v>
+        <v>46285.625</v>
       </c>
       <c r="B24" s="5">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="C24" s="5">
-        <v>-3.63</v>
+        <v>-2.67</v>
       </c>
       <c r="D24" s="5">
-        <v>4.85</v>
+        <v>4.82</v>
       </c>
       <c r="E24" s="5">
-        <v>38.6</v>
+        <v>39.2</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>85</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="G24" s="5"/>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="6">
-        <v>46285.33333333334</v>
+        <v>46285.75</v>
       </c>
       <c r="B25" s="5">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="C25" s="5">
-        <v>-3.63</v>
+        <v>-2.67</v>
       </c>
       <c r="D25" s="5">
-        <v>4.85</v>
+        <v>4.82</v>
       </c>
       <c r="E25" s="5">
-        <v>38.6</v>
+        <v>39.2</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G25" s="5"/>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="6">
-        <v>46285.45833333334</v>
+        <v>46285.875</v>
       </c>
       <c r="B26" s="5">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="C26" s="5">
-        <v>-3.63</v>
+        <v>-2.67</v>
       </c>
       <c r="D26" s="5">
-        <v>4.85</v>
+        <v>4.82</v>
       </c>
       <c r="E26" s="5">
-        <v>38.6</v>
+        <v>39.2</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G26" s="5"/>
     </row>
@@ -9867,7 +10381,7 @@
         <v>66.5</v>
       </c>
       <c r="J2" s="5">
-        <v>96.42</v>
+        <v>95.14</v>
       </c>
       <c r="K2" s="5">
         <v>-38</v>
@@ -9911,7 +10425,7 @@
         <v>352</v>
       </c>
       <c r="J3" s="5">
-        <v>85.79000000000001</v>
+        <v>75.83</v>
       </c>
       <c r="K3" s="5">
         <v>-18</v>
@@ -9955,7 +10469,7 @@
         <v>88</v>
       </c>
       <c r="J4" s="5">
-        <v>94.75</v>
+        <v>93.47</v>
       </c>
       <c r="K4" s="5">
         <v>-18</v>
@@ -9999,7 +10513,7 @@
         <v>71.2</v>
       </c>
       <c r="J5" s="5">
-        <v>96.05</v>
+        <v>94.77</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
@@ -10043,7 +10557,7 @@
         <v>72.8</v>
       </c>
       <c r="J6" s="5">
-        <v>95.93000000000001</v>
+        <v>94.65000000000001</v>
       </c>
       <c r="K6" s="5">
         <v>65</v>
@@ -10087,7 +10601,7 @@
         <v>91.2</v>
       </c>
       <c r="J7" s="5">
-        <v>94.48999999999999</v>
+        <v>93.20999999999999</v>
       </c>
       <c r="K7" s="5">
         <v>35</v>
@@ -10131,7 +10645,7 @@
         <v>193.8</v>
       </c>
       <c r="J8" s="5">
-        <v>86.53</v>
+        <v>85.25</v>
       </c>
       <c r="K8" s="5">
         <v>159</v>
@@ -10175,7 +10689,7 @@
         <v>510</v>
       </c>
       <c r="J9" s="5">
-        <v>160.25</v>
+        <v>158.9</v>
       </c>
       <c r="K9" s="5">
         <v>0</v>
@@ -10219,7 +10733,7 @@
         <v>138.5</v>
       </c>
       <c r="J10" s="5">
-        <v>90.81999999999999</v>
+        <v>89.54000000000001</v>
       </c>
       <c r="K10" s="5">
         <v>122</v>
@@ -10263,7 +10777,7 @@
         <v>282</v>
       </c>
       <c r="J11" s="5">
-        <v>88.51000000000001</v>
+        <v>78.55</v>
       </c>
       <c r="K11" s="5">
         <v>29</v>
@@ -10307,7 +10821,7 @@
         <v>137.2</v>
       </c>
       <c r="J12" s="5">
-        <v>90.92</v>
+        <v>89.64</v>
       </c>
       <c r="K12" s="5">
         <v>134</v>
@@ -10351,7 +10865,7 @@
         <v>116</v>
       </c>
       <c r="J13" s="5">
-        <v>92.56999999999999</v>
+        <v>91.29000000000001</v>
       </c>
       <c r="K13" s="5">
         <v>92</v>
@@ -10395,7 +10909,7 @@
         <v>77</v>
       </c>
       <c r="J14" s="5">
-        <v>95.59999999999999</v>
+        <v>94.31999999999999</v>
       </c>
       <c r="K14" s="5">
         <v>-100</v>
@@ -10439,7 +10953,7 @@
         <v>396.5</v>
       </c>
       <c r="J15" s="5">
-        <v>70.78</v>
+        <v>69.48</v>
       </c>
       <c r="K15" s="5">
         <v>39</v>
@@ -10483,7 +10997,7 @@
         <v>326.2</v>
       </c>
       <c r="J16" s="5">
-        <v>76.23999999999999</v>
+        <v>74.94</v>
       </c>
       <c r="K16" s="5">
         <v>39</v>
@@ -10527,7 +11041,7 @@
         <v>97.8</v>
       </c>
       <c r="J17" s="5">
-        <v>93.98999999999999</v>
+        <v>92.70999999999999</v>
       </c>
       <c r="K17" s="5">
         <v>129</v>
@@ -10571,7 +11085,7 @@
         <v>107</v>
       </c>
       <c r="J18" s="5">
-        <v>93.27</v>
+        <v>91.98999999999999</v>
       </c>
       <c r="K18" s="5">
         <v>0</v>
@@ -10615,7 +11129,7 @@
         <v>55.8</v>
       </c>
       <c r="J19" s="5">
-        <v>97.25</v>
+        <v>95.97</v>
       </c>
       <c r="K19" s="5">
         <v>88</v>
@@ -10659,7 +11173,7 @@
         <v>207</v>
       </c>
       <c r="J20" s="5">
-        <v>172.02</v>
+        <v>170.68</v>
       </c>
       <c r="K20" s="5">
         <v>5</v>
@@ -10703,7 +11217,7 @@
         <v>173.4</v>
       </c>
       <c r="J21" s="5">
-        <v>197.44</v>
+        <v>196.16</v>
       </c>
       <c r="K21" s="5">
         <v>29</v>
@@ -10747,7 +11261,7 @@
         <v>57</v>
       </c>
       <c r="J22" s="5">
-        <v>97.16</v>
+        <v>95.88</v>
       </c>
       <c r="K22" s="5">
         <v>-90</v>
@@ -10791,7 +11305,7 @@
         <v>76.2</v>
       </c>
       <c r="J23" s="5">
-        <v>95.66</v>
+        <v>94.38</v>
       </c>
       <c r="K23" s="5">
         <v>-86</v>
@@ -10835,7 +11349,7 @@
         <v>224.2</v>
       </c>
       <c r="J24" s="5">
-        <v>84.16</v>
+        <v>82.87</v>
       </c>
       <c r="K24" s="5">
         <v>39</v>
@@ -10879,7 +11393,7 @@
         <v>85</v>
       </c>
       <c r="J25" s="5">
-        <v>94.98</v>
+        <v>93.7</v>
       </c>
       <c r="K25" s="5">
         <v>-80</v>
@@ -10923,7 +11437,7 @@
         <v>161.2</v>
       </c>
       <c r="J26" s="5">
-        <v>89.06</v>
+        <v>87.77</v>
       </c>
       <c r="K26" s="5">
         <v>39</v>
@@ -10967,7 +11481,7 @@
         <v>1586</v>
       </c>
       <c r="J27" s="5">
-        <v>37.85</v>
+        <v>27.86</v>
       </c>
       <c r="K27" s="5">
         <v>39</v>
@@ -11011,7 +11525,7 @@
         <v>87.5</v>
       </c>
       <c r="J28" s="5">
-        <v>94.79000000000001</v>
+        <v>93.51000000000001</v>
       </c>
       <c r="K28" s="5">
         <v>0</v>
@@ -11055,7 +11569,7 @@
         <v>57.8</v>
       </c>
       <c r="J29" s="5">
-        <v>97.09999999999999</v>
+        <v>95.81999999999999</v>
       </c>
       <c r="K29" s="5">
         <v>49</v>
@@ -11099,7 +11613,7 @@
         <v>1305</v>
       </c>
       <c r="J30" s="5">
-        <v>48.77</v>
+        <v>38.78</v>
       </c>
       <c r="K30" s="5">
         <v>39</v>
@@ -11143,7 +11657,7 @@
         <v>186</v>
       </c>
       <c r="J31" s="5">
-        <v>87.13</v>
+        <v>85.84999999999999</v>
       </c>
       <c r="K31" s="5">
         <v>40</v>
@@ -11187,7 +11701,7 @@
         <v>77.2</v>
       </c>
       <c r="J32" s="5">
-        <v>95.58</v>
+        <v>94.3</v>
       </c>
       <c r="K32" s="5">
         <v>75</v>
@@ -11231,7 +11745,7 @@
         <v>403</v>
       </c>
       <c r="J33" s="5">
-        <v>164.41</v>
+        <v>163.06</v>
       </c>
       <c r="K33" s="5">
         <v>0</v>
@@ -11275,7 +11789,7 @@
         <v>84.2</v>
       </c>
       <c r="J34" s="5">
-        <v>95.04000000000001</v>
+        <v>93.76000000000001</v>
       </c>
       <c r="K34" s="5">
         <v>0</v>
@@ -11319,7 +11833,7 @@
         <v>148.1</v>
       </c>
       <c r="J35" s="5">
-        <v>121.53</v>
+        <v>120.49</v>
       </c>
       <c r="K35" s="5">
         <v>0</v>
@@ -11363,7 +11877,7 @@
         <v>897</v>
       </c>
       <c r="J36" s="5">
-        <v>64.62</v>
+        <v>54.64</v>
       </c>
       <c r="K36" s="5">
         <v>39</v>
@@ -11407,7 +11921,7 @@
         <v>744</v>
       </c>
       <c r="J37" s="5">
-        <v>70.56</v>
+        <v>60.59</v>
       </c>
       <c r="K37" s="5">
         <v>40</v>
@@ -11451,7 +11965,7 @@
         <v>645</v>
       </c>
       <c r="J38" s="5">
-        <v>74.41</v>
+        <v>64.44</v>
       </c>
       <c r="K38" s="5">
         <v>39</v>
@@ -11495,7 +12009,7 @@
         <v>67</v>
       </c>
       <c r="J39" s="5">
-        <v>96.38</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="K39" s="5">
         <v>0</v>
@@ -11539,7 +12053,7 @@
         <v>115.2</v>
       </c>
       <c r="J40" s="5">
-        <v>92.63</v>
+        <v>91.34999999999999</v>
       </c>
       <c r="K40" s="5">
         <v>115</v>
@@ -11583,7 +12097,7 @@
         <v>79.8</v>
       </c>
       <c r="J41" s="5">
-        <v>95.39</v>
+        <v>94.11</v>
       </c>
       <c r="K41" s="5">
         <v>0</v>
@@ -11600,7 +12114,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>98</v>
@@ -11627,7 +12141,7 @@
         <v>295</v>
       </c>
       <c r="J42" s="5">
-        <v>168.6</v>
+        <v>167.26</v>
       </c>
       <c r="K42" s="5">
         <v>0</v>
@@ -11671,7 +12185,7 @@
         <v>98.8</v>
       </c>
       <c r="J43" s="5">
-        <v>93.91</v>
+        <v>92.63</v>
       </c>
       <c r="K43" s="5">
         <v>0</v>
@@ -11693,7 +12207,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -11722,13 +12236,13 @@
         <v>101</v>
       </c>
       <c r="B2" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" s="5">
-        <v>48.49</v>
+        <v>32.7</v>
       </c>
       <c r="D2" s="5">
-        <v>51.52</v>
+        <v>51.44</v>
       </c>
       <c r="E2" s="5" t="b">
         <v>0</v>
@@ -11742,10 +12256,10 @@
         <v>2</v>
       </c>
       <c r="C3" s="5">
-        <v>195.03</v>
+        <v>194.91</v>
       </c>
       <c r="D3" s="5">
-        <v>195.03</v>
+        <v>194.91</v>
       </c>
       <c r="E3" s="5" t="b">
         <v>0</v>
@@ -11776,10 +12290,10 @@
         <v>1</v>
       </c>
       <c r="C5" s="5">
-        <v>121.43</v>
+        <v>121.88</v>
       </c>
       <c r="D5" s="5">
-        <v>121.43</v>
+        <v>121.88</v>
       </c>
       <c r="E5" s="5" t="b">
         <v>0</v>
@@ -11910,10 +12424,10 @@
         <v>516.79</v>
       </c>
       <c r="F14" s="5">
-        <v>592.8200000000001</v>
+        <v>593.0599999999999</v>
       </c>
       <c r="G14" s="5">
-        <v>76.03</v>
+        <v>76.27</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -11933,10 +12447,10 @@
         <v>466.42</v>
       </c>
       <c r="F15" s="5">
-        <v>592.8200000000001</v>
+        <v>593.0599999999999</v>
       </c>
       <c r="G15" s="5">
-        <v>126.4</v>
+        <v>126.63</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -11956,10 +12470,10 @@
         <v>500.85</v>
       </c>
       <c r="F16" s="5">
-        <v>592.8200000000001</v>
+        <v>593.0599999999999</v>
       </c>
       <c r="G16" s="5">
-        <v>91.98</v>
+        <v>92.20999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -11979,10 +12493,10 @@
         <v>513.9</v>
       </c>
       <c r="F17" s="5">
-        <v>592.8200000000001</v>
+        <v>593.0599999999999</v>
       </c>
       <c r="G17" s="5">
-        <v>78.92</v>
+        <v>79.16</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -12002,10 +12516,10 @@
         <v>515.4</v>
       </c>
       <c r="F18" s="5">
-        <v>592.8200000000001</v>
+        <v>593.0599999999999</v>
       </c>
       <c r="G18" s="5">
-        <v>77.42</v>
+        <v>77.66</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -12025,10 +12539,10 @@
         <v>516.1</v>
       </c>
       <c r="F19" s="5">
-        <v>592.8200000000001</v>
+        <v>593.0599999999999</v>
       </c>
       <c r="G19" s="5">
-        <v>76.73</v>
+        <v>76.95999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -12160,13 +12674,13 @@
         <v>403</v>
       </c>
       <c r="E25" s="5">
-        <v>535.75</v>
+        <v>535.99</v>
       </c>
       <c r="F25" s="5">
         <v>640.23</v>
       </c>
       <c r="G25" s="5">
-        <v>104.48</v>
+        <v>104.24</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -12183,13 +12697,13 @@
         <v>337</v>
       </c>
       <c r="E26" s="5">
-        <v>526.8</v>
+        <v>527.48</v>
       </c>
       <c r="F26" s="5">
         <v>640.23</v>
       </c>
       <c r="G26" s="5">
-        <v>113.43</v>
+        <v>112.75</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -12206,13 +12720,13 @@
         <v>404</v>
       </c>
       <c r="E27" s="5">
-        <v>518.8</v>
+        <v>518.35</v>
       </c>
       <c r="F27" s="5">
         <v>640.23</v>
       </c>
       <c r="G27" s="5">
-        <v>121.43</v>
+        <v>121.88</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -12229,13 +12743,13 @@
         <v>897</v>
       </c>
       <c r="E28" s="5">
-        <v>507.7</v>
+        <v>507.95</v>
       </c>
       <c r="F28" s="5">
         <v>527.95</v>
       </c>
       <c r="G28" s="5">
-        <v>20.25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -12252,13 +12766,36 @@
         <v>744</v>
       </c>
       <c r="E29" s="5">
-        <v>504.7</v>
+        <v>504.88</v>
       </c>
       <c r="F29" s="5">
-        <v>505.46</v>
+        <v>524.1</v>
       </c>
       <c r="G29" s="5">
-        <v>0.76</v>
+        <v>19.23</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C30" s="6">
+        <v>46282.5</v>
+      </c>
+      <c r="D30" s="5">
+        <v>645</v>
+      </c>
+      <c r="E30" s="5">
+        <v>491.4</v>
+      </c>
+      <c r="F30" s="5">
+        <v>524.1</v>
+      </c>
+      <c r="G30" s="5">
+        <v>32.7</v>
       </c>
     </row>
   </sheetData>
